--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ30"/>
+  <dimension ref="A1:AJ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,35 +608,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>EirZ0Wr4</t>
+          <t>W0WITkcl</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.03166292216256539</v>
+        <v>1.089213085724815</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.9295233270219083</v>
+        <v>-0.9048397881792709</v>
       </c>
       <c r="D2" t="n">
-        <v>1.376408122519553</v>
+        <v>1.260592784903993</v>
       </c>
       <c r="E2" t="n">
-        <v>1.796195393244528</v>
+        <v>0.3247493829518739</v>
       </c>
       <c r="F2" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.4719390238590598</v>
+        <v>0.5368536386174515</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1080439413343977</v>
+        <v>0.8383108509246437</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.5616338189825709</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.007732342947784333</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -672,22 +672,22 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.496400322755926</v>
+        <v>-0.594792318935968</v>
       </c>
       <c r="W2" t="n">
-        <v>2.090603257987097</v>
+        <v>-0.05253665648388181</v>
       </c>
       <c r="X2" t="n">
-        <v>2.465246835250709</v>
+        <v>-0.3801437221686224</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.6513708999193901</v>
+        <v>-0.7887035226919874</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.690680623344347</v>
+        <v>-0.06855930257644363</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2058211660090829</v>
+        <v>0.5582504710514602</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.389563151452224</v>
+        <v>-0.4105768518215517</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.293343516230779</v>
+        <v>-0.3255919275056208</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.419568621525167</v>
+        <v>-0.02755616308562162</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.980175996910999</v>
+        <v>-0.247152360448811</v>
       </c>
       <c r="AJ2" t="n">
         <v>-0.2315504637589359</v>
@@ -720,35 +720,35 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>t4ZkclrT</t>
+          <t>v3ivyY4E</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.597121179823038</v>
+        <v>-1.207215808483476</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.7320550162808089</v>
+        <v>0.4033877704805131</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.221164449715159</v>
+        <v>0.03625921582521156</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2580015122135339</v>
+        <v>1.927314344656745</v>
       </c>
       <c r="F3" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.8754560888496645</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.865645271452597</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1960996420384249</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007732342947784333</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -784,22 +784,22 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.622845834245432</v>
+        <v>-0.8983713024946106</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.115746573765477</v>
+        <v>0.02178038869446279</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9744371692785671</v>
+        <v>0.1411159918135424</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.031415896266951</v>
+        <v>-1.840022703745011</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1.369493899895923</v>
+        <v>-0.05366772438368607</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.262714646354401</v>
+        <v>-1.935415745825244</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -808,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1.107255153574944</v>
+        <v>0.5382101707084332</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.7514330917187826</v>
+        <v>-0.09920686251628327</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1.045231937113341</v>
+        <v>0.0407718873637366</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1.421437091877116</v>
+        <v>0.06937894505824396</v>
       </c>
       <c r="AJ3" t="n">
         <v>-0.2315504637589359</v>
@@ -832,20 +832,20 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>YH892O2B</t>
+          <t>YPSZP7dD</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.296398348438619</v>
+        <v>0.6517980582565688</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1396500840575105</v>
+        <v>-0.5592702443823468</v>
       </c>
       <c r="D4" t="n">
-        <v>1.624583845981469</v>
+        <v>0.8138764826725458</v>
       </c>
       <c r="E4" t="n">
-        <v>1.767057848486258</v>
+        <v>-1.190402944478186</v>
       </c>
       <c r="F4" t="n">
         <v>-0.2141296999117111</v>
@@ -854,13 +854,13 @@
         <v>-0.4719390238590598</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.595912181042843</v>
+        <v>-0.3788006650590997</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.711566564080417</v>
+        <v>-0.1960996420384249</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.973531838519109</v>
+        <v>-0.4875837024189391</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -893,25 +893,25 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-1.160999988376106</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.468622748059101</v>
+        <v>0.2604077185647436</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.463353857763193</v>
+        <v>-0.07310706081978585</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.141359856429053</v>
+        <v>-0.5298789862484943</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2548940329298516</v>
+        <v>0.7532770456170194</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1.795861860650786</v>
+        <v>-0.01922812976180889</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.009020469897717778</v>
+        <v>1.400950378925134</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-1.721515159473993</v>
+        <v>-0.09309664907338916</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -929,13 +929,13 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>-2.013691939574219</v>
+        <v>0.2821131411665878</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1.868281232275348</v>
+        <v>0.1348867207181722</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1.490401062556848</v>
+        <v>-0.2836703483059695</v>
       </c>
       <c r="AJ4" t="n">
         <v>-0.2315504637589359</v>
@@ -944,35 +944,35 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8jyraADG</t>
+          <t>tWk1tTtf</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1.553966552409826</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.09028300637223562</v>
+        <v>-1.225725793133557</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4931823275602075</v>
+        <v>0.6980611450569854</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0188051629900348</v>
+        <v>-0.9573025864120233</v>
       </c>
       <c r="F5" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5368536386174515</v>
+        <v>-0.2701804913637576</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4731773961295207</v>
+        <v>-0.01366721026397662</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5616338189825709</v>
+        <v>-0.1960996420384249</v>
       </c>
       <c r="J5" t="n">
-        <v>0.998364433681231</v>
+        <v>0.007732342947784333</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1008,22 +1008,22 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>2.049935758784715</v>
+        <v>0.07579685303272284</v>
       </c>
       <c r="W5" t="n">
-        <v>1.175718517188405</v>
+        <v>-0.04662868590506593</v>
       </c>
       <c r="X5" t="n">
-        <v>1.210825099401057</v>
+        <v>-0.5872372852737593</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2836103357705774</v>
+        <v>1.227845830337923</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.752191459768925</v>
+        <v>-0.03965241491589867</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1115422268398492</v>
+        <v>0.1549929534469005</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1032,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.891872947216038</v>
+        <v>-0.8057260339989766</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1041,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.768037889544479</v>
+        <v>-0.02929996702690747</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.394800005486243</v>
+        <v>-0.02755616308562162</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.597290275619194</v>
+        <v>-0.4082933546396582</v>
       </c>
       <c r="AJ5" t="n">
         <v>-0.2315504637589359</v>
@@ -1056,29 +1056,29 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tYhtcc5C</t>
+          <t>Y54hDUC7</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1.717997187710418</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.682687938595534</v>
+        <v>1.563514096084472</v>
       </c>
       <c r="D6" t="n">
         <v>-0.278096700559881</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3247493829518739</v>
+        <v>1.111463091425174</v>
       </c>
       <c r="F6" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0.8754560888496645</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0.2570895134607253</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1120,22 +1120,22 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.153909280839031</v>
+        <v>-1.40042858223836</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3476400881078478</v>
+        <v>-0.3409706085058983</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.715493670363737</v>
+        <v>-1.842436478839363</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6471816976291758</v>
+        <v>0.4291599280675897</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.3698361920532552</v>
+        <v>-0.3647567429424129</v>
       </c>
       <c r="AA6" t="n">
-        <v>-2.071438247180094</v>
+        <v>-2.388243413553347</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1144,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>-1.756660447341095</v>
+        <v>-2.067795346461504</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1153,13 +1153,13 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.3512357895383371</v>
+        <v>-0.3515811004480734</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.4446988945926462</v>
+        <v>-0.4286185625390873</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.325340052418141</v>
+        <v>-1.267178224827383</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0.2315504637589359</v>
@@ -1168,35 +1168,35 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>lvG7DIkg</t>
+          <t>Eql9v7B6</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>-1.043185173182884</v>
       </c>
       <c r="C7" t="n">
-        <v>1.020476241546449</v>
+        <v>-0.4111690113265222</v>
       </c>
       <c r="D7" t="n">
         <v>0.8800566755957232</v>
       </c>
       <c r="E7" t="n">
-        <v>1.082325546666904</v>
+        <v>-1.219540489236457</v>
       </c>
       <c r="F7" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4719390238590598</v>
+        <v>-0.2701804913637576</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.01366721026397662</v>
+        <v>-0.2570895134607253</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.5616338189825709</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.998364433681231</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1211,10 +1211,10 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.0259029127667809</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.04946140548819852</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1229,25 +1229,25 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-1.170571913096135</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2808779997132287</v>
+        <v>0.2980021905237897</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1335881705648471</v>
+        <v>0.03607337016945217</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2385442622696468</v>
+        <v>0.2591633999446381</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.7036710375825599</v>
+        <v>0.03305694656563592</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.00588397538023413</v>
+        <v>0.07404608762975451</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.3294883740769105</v>
+        <v>-0.1229461132239865</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.1148975252039309</v>
+        <v>0.1888281718235763</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1265,13 +1265,13 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.4289678686014315</v>
+        <v>0.04096567925237055</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.3233081526197025</v>
+        <v>0.3264213425116717</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.5738571070607847</v>
+        <v>0.5930015547394838</v>
       </c>
       <c r="AJ7" t="n">
         <v>-0.2315504637589359</v>
@@ -1280,35 +1280,35 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SORbFvLt</t>
+          <t>EL5MmBlK</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.553966552409826</v>
+        <v>-1.070523612399649</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9957927027038115</v>
+        <v>1.020476241546449</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6420877616373566</v>
+        <v>-0.5759075687141793</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7679085454832657</v>
+        <v>1.082325546666904</v>
       </c>
       <c r="F8" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2701804913637576</v>
+        <v>-0.06842195886845531</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1353783618623509</v>
+        <v>-0.01366721026397662</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.711566564080417</v>
+        <v>0.5616338189825709</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.973531838519109</v>
+        <v>0.998364433681231</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1323,10 +1323,10 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.0259029127667809</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.04946140548819852</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1341,25 +1341,25 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-1.078593450293186</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7812628910532985</v>
+        <v>0.7196219356322867</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.07375151262851086</v>
+        <v>0.2044093818969255</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.4047304621375349</v>
+        <v>1.318474300232675</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.565569696195364</v>
+        <v>-0.7500493612514639</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.103725394262938</v>
+        <v>0.1653533058616064</v>
       </c>
       <c r="AA8" t="n">
-        <v>-1.173437884240805</v>
+        <v>0.4893120469568223</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.07488210021979289</v>
+        <v>1.405367757501326</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1377,13 +1377,13 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.3309606938222447</v>
+        <v>-0.02929996702690747</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.192888347194226</v>
+        <v>-0.02755616308562162</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.317671657384758</v>
+        <v>0.7963135347923823</v>
       </c>
       <c r="AJ8" t="n">
         <v>-0.2315504637589359</v>
@@ -1392,35 +1392,35 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>4xHh663n</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.7151239025816996</v>
+        <v>-1.207215808483476</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.694713031143669</v>
+        <v>1.143893935759636</v>
       </c>
       <c r="D9" t="n">
-        <v>1.177867543750021</v>
+        <v>-1.022623870945627</v>
       </c>
       <c r="E9" t="n">
-        <v>1.504819945661825</v>
+        <v>0.06251148012744039</v>
       </c>
       <c r="F9" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4719390238590598</v>
+        <v>-0.6736975563543621</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9873564230509713</v>
+        <v>-2.08275678743634</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5616338189825709</v>
+        <v>-0.1960996420384249</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5030483883145077</v>
+        <v>-1.478215793152386</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1453,25 +1453,25 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.878937944282372</v>
       </c>
       <c r="V9" t="n">
-        <v>0.07470380949211698</v>
+        <v>-1.452478494549055</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4629751979494055</v>
+        <v>-1.998200702039554</v>
       </c>
       <c r="X9" t="n">
-        <v>0.5297241878300322</v>
+        <v>-1.779805625967784</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.083601701611451</v>
+        <v>-0.4928740742431326</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.4383954635426598</v>
+        <v>-1.684776614701277</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.692488846898387</v>
+        <v>-0.4968988719398274</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.8602064643335374</v>
+        <v>-1.714332846694679</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1489,13 +1489,13 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.2682622957520673</v>
+        <v>-1.908156469309918</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.413864716815992</v>
+        <v>-1.312542465240132</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.3473711009898883</v>
+        <v>-1.64584358332712</v>
       </c>
       <c r="AJ9" t="n">
         <v>-0.2315504637589359</v>
@@ -1504,35 +1504,35 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>6RvR2hEi</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.7698007810152303</v>
+        <v>-0.03166292216256539</v>
       </c>
       <c r="C10" t="n">
-        <v>1.143893935759636</v>
+        <v>-0.1396500840575105</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.370069883792308</v>
+        <v>1.376408122519553</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06251148012744039</v>
+        <v>1.767057848486258</v>
       </c>
       <c r="F10" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.480731686335571</v>
+        <v>-0.2701804913637576</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.961045635837966</v>
+        <v>0.1080439413343977</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.469300025101413</v>
+        <v>0.5616338189825709</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.973531838519109</v>
+        <v>0.5030483883145077</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1565,25 +1565,25 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.405329420810793</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.249920572238886</v>
+        <v>-0.03403580254361736</v>
       </c>
       <c r="W10" t="n">
-        <v>-2.500656814500413</v>
+        <v>0.001547932537519454</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.494643638890997</v>
+        <v>0.6026225747648385</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.3923545421353806</v>
+        <v>-0.2056906688618224</v>
       </c>
       <c r="Z10" t="n">
-        <v>-1.597645845610711</v>
+        <v>-0.0356767975974795</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.7701268309006439</v>
+        <v>-0.02567228954157029</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1.044626483830037</v>
+        <v>0.3543670029319601</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1601,50 +1601,50 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>-1.206961196953795</v>
+        <v>-0.2727509911397782</v>
       </c>
       <c r="AH10" t="n">
-        <v>-1.168629137631291</v>
+        <v>0.2500952348122824</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.767161984261072</v>
+        <v>0.1844391830926791</v>
       </c>
       <c r="AJ10" t="n">
-        <v>4.318713008673075</v>
+        <v>-0.2315504637589359</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>0lGMiS5j</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.553966552409826</v>
+        <v>0.296398348438619</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.151675176605645</v>
+        <v>1.736298867982935</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5262724240217962</v>
+        <v>-1.717515896638989</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.219540489236457</v>
+        <v>-0.3017078293509395</v>
       </c>
       <c r="F11" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G11" t="n">
-        <v>3.563231626046985</v>
+        <v>2.150921898579869</v>
       </c>
       <c r="H11" t="n">
-        <v>2.42055582170351</v>
+        <v>2.055422366908387</v>
       </c>
       <c r="I11" t="n">
-        <v>1.319367280003567</v>
+        <v>2.077100741024563</v>
       </c>
       <c r="J11" t="n">
-        <v>0.007732342947784333</v>
+        <v>1.988996524414678</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1680,22 +1680,22 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9389374439651142</v>
+        <v>1.420033735562321</v>
       </c>
       <c r="W11" t="n">
-        <v>1.489797116984839</v>
+        <v>1.310317853677538</v>
       </c>
       <c r="X11" t="n">
-        <v>1.040567755394083</v>
+        <v>1.058540864078273</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.3321797946580615</v>
+        <v>0.1304010902422169</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.003949726892125</v>
+        <v>1.720286827528908</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.07213921765189071</v>
+        <v>0.3523226618467456</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1704,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.630163470958121</v>
+        <v>1.445371092137504</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.7563100725615722</v>
+        <v>1.980261487561878</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.041418067742785</v>
+        <v>2.025681529713882</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.829766936142608</v>
+        <v>1.301385624521183</v>
       </c>
       <c r="AJ11" t="n">
         <v>-0.2315504637589359</v>
@@ -1728,35 +1728,35 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hKOA02XN</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-1.207215808483476</v>
+        <v>1.499289673976295</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.719396569986306</v>
+        <v>-1.349143487346745</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.469340173177074</v>
+        <v>-1.700970848408195</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3017078293509395</v>
+        <v>-0.2580015122135339</v>
       </c>
       <c r="F12" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5368536386174515</v>
+        <v>1.545646301093963</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4731773961295207</v>
+        <v>1.325155457318141</v>
       </c>
       <c r="I12" t="n">
-        <v>1.319367280003567</v>
+        <v>0.5616338189825709</v>
       </c>
       <c r="J12" t="n">
-        <v>0.007732342947784333</v>
+        <v>0.998364433681231</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1789,25 +1789,25 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-1.261505197936386</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3766137411664761</v>
+        <v>0.9708815040721605</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.2540430802744261</v>
+        <v>1.899415541446103</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4124566938475909</v>
+        <v>0.6547879698360566</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.3188748974479603</v>
+        <v>0.746763272877403</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.1597379438978459</v>
+        <v>1.089095380425255</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.03561617597554163</v>
+        <v>-1.454198610158018</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1816,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0.5575411794313563</v>
+        <v>0.2411785679412735</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1825,13 +1825,13 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.4151255053813223</v>
+        <v>0.7045635864654289</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.6477524993473881</v>
+        <v>0.8275391414095021</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.2740965442398248</v>
+        <v>1.226008806174201</v>
       </c>
       <c r="AJ12" t="n">
         <v>-0.2315504637589359</v>
@@ -1840,35 +1840,35 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>M5TEBdK5</t>
+          <t>KvdW7ZzS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.1410166790296269</v>
+        <v>-0.03166292216256539</v>
       </c>
       <c r="C13" t="n">
-        <v>1.39072932418601</v>
+        <v>1.662248251455022</v>
       </c>
       <c r="D13" t="n">
-        <v>1.227502688442405</v>
+        <v>1.012417061442078</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5348081874171026</v>
+        <v>1.927314344656745</v>
       </c>
       <c r="F13" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2701804913637576</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3514662445311464</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9538331030594207</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4875837024189391</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1904,22 +1904,22 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5351505832434981</v>
+        <v>0.7470432986101152</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.03979490748691092</v>
+        <v>0.02178038869446279</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1622642761838027</v>
+        <v>0.1411159918135424</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.206778108901433</v>
+        <v>2.278475063105918</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.001099586282540404</v>
+        <v>0.01739180440702725</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.9153806707537437</v>
+        <v>-0.1761111935605618</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -1928,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.1509613032172185</v>
+        <v>-0.758339144491079</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -1937,13 +1937,13 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.2515837238643533</v>
+        <v>-0.02929996702690747</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.2310301686783653</v>
+        <v>0.0407718873637366</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.2643662977205019</v>
+        <v>0.06937894505824396</v>
       </c>
       <c r="AJ13" t="n">
         <v>-0.2315504637589359</v>
@@ -1952,35 +1952,35 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>WvwvCQVo</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-1.070523612399649</v>
+        <v>0.597121179823038</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.01623238984432331</v>
+        <v>-0.4605360890117971</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.5759075687141793</v>
+        <v>-1.221164449715159</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4995746515014962</v>
+        <v>-0.8261836349998065</v>
       </c>
       <c r="F14" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6736975563543621</v>
+        <v>-0.2701804913637576</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.500511816657474</v>
+        <v>-0.3788006650590997</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9538331030594207</v>
+        <v>-0.1960996420384249</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.478215793152386</v>
+        <v>-0.9828997477856625</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2013,25 +2013,25 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>-1.035545007824282</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2170064161504245</v>
+        <v>-0.7156801716703117</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.05059261825294945</v>
+        <v>-0.4628997468732071</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1822910838396109</v>
+        <v>-0.609266773695147</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.3481965764134238</v>
+        <v>-0.2332007677117474</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.02870923935271722</v>
+        <v>-1.001715831986365</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.6165872783961117</v>
+        <v>-0.6961441913215439</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.2907812340986174</v>
+        <v>-0.8260750267184558</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2049,13 +2049,13 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.05861614857844481</v>
+        <v>-0.4164280648772658</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.277654845303494</v>
+        <v>-0.5332983712014703</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.078574522356291</v>
+        <v>-0.5062073676043577</v>
       </c>
       <c r="AJ14" t="n">
         <v>-0.2315504637589359</v>
@@ -2064,35 +2064,35 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>joLV7EJU</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.425923322217599</v>
+        <v>1.553966552409826</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.4111690113265222</v>
+        <v>-0.3371183947986099</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.006078822714832</v>
+        <v>-0.4931823275602075</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.219540489236457</v>
+        <v>-0.8261836349998065</v>
       </c>
       <c r="F15" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.06842195886845531</v>
+        <v>0.3350951061221493</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2570895134607253</v>
+        <v>0.1080439413343977</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.5616338189825709</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.007732342947784333</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2128,22 +2128,22 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.21286255209779</v>
+        <v>1.646740899264498</v>
       </c>
       <c r="W15" t="n">
-        <v>0.124652250918342</v>
+        <v>0.7387830244850578</v>
       </c>
       <c r="X15" t="n">
-        <v>1.435405434311113</v>
+        <v>1.128790339637771</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.05661715650242195</v>
+        <v>-0.2309545406728202</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.2397906736425315</v>
+        <v>1.201690378388217</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.163086748523127</v>
+        <v>0.05658045822621292</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2152,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.716894708445537</v>
+        <v>1.78077151427174</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2161,13 +2161,13 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.4868103131072283</v>
+        <v>1.339050158112247</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.6066185010396957</v>
+        <v>1.167223018514744</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.9511797117326438</v>
+        <v>1.335170873499355</v>
       </c>
       <c r="AJ15" t="n">
         <v>-0.2315504637589359</v>
@@ -2176,35 +2176,35 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Sf88FVcc</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.597121179823038</v>
+        <v>-0.7698007810152303</v>
       </c>
       <c r="C16" t="n">
-        <v>-1.29977640966147</v>
+        <v>-0.6086373220676217</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.327731845252264</v>
+        <v>-0.8075382439453</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9573025864120233</v>
+        <v>0.06251148012744039</v>
       </c>
       <c r="F16" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.06842195886845531</v>
+        <v>2.352680431075172</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.500511816657474</v>
+        <v>2.542266973301885</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1.319367280003567</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4875837024189391</v>
+        <v>1.988996524414678</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2240,22 +2240,22 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.495662880257049</v>
+        <v>2.526594904738802</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7907752709024144</v>
+        <v>2.581113077206389</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.048756624189495</v>
+        <v>1.567823620423898</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.04550048763565399</v>
+        <v>1.910331993766164</v>
       </c>
       <c r="Z16" t="n">
-        <v>-1.161638154939187</v>
+        <v>2.625470065916655</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.9904575147766768</v>
+        <v>-0.3696334551176731</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>-1.544686088029613</v>
+        <v>1.76435552879785</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2273,13 +2273,13 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>-1.169125075237379</v>
+        <v>2.086133582948928</v>
       </c>
       <c r="AH16" t="n">
-        <v>-1.092767806413914</v>
+        <v>2.583133040903918</v>
       </c>
       <c r="AI16" t="n">
-        <v>-1.522542875663299</v>
+        <v>2.271044393369793</v>
       </c>
       <c r="AJ16" t="n">
         <v>-0.2315504637589359</v>
@@ -2288,35 +2288,35 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>O2Fteteo</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.854689383794245</v>
+        <v>1.499289673976295</v>
       </c>
       <c r="C17" t="n">
-        <v>0.230602998582051</v>
+        <v>-1.497244720402569</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6751778580989453</v>
+        <v>0.3175250357487154</v>
       </c>
       <c r="E17" t="n">
-        <v>1.504819945661825</v>
+        <v>1.796195393244528</v>
       </c>
       <c r="F17" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4719390238590598</v>
+        <v>-0.2701804913637576</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.326179090633089</v>
+        <v>-0.2570895134607253</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1960996420384249</v>
+        <v>0.5616338189825709</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9828997477856625</v>
+        <v>0.998364433681231</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2349,25 +2349,25 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-1.123104581492723</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.130902766595961</v>
+        <v>0.3249097269802574</v>
       </c>
       <c r="W17" t="n">
-        <v>-2.615539626886055</v>
+        <v>0.06483960359767518</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.734342735704039</v>
+        <v>-0.05341390711155759</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.520534121852428</v>
+        <v>-0.3516884112795934</v>
       </c>
       <c r="Z17" t="n">
-        <v>-2.502272193922198</v>
+        <v>0.07382975853227154</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.921182783981265</v>
+        <v>-0.9126370237160275</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2376,7 +2376,7 @@
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>-2.011809429780987</v>
+        <v>0.7518369408646433</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2385,13 +2385,13 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>-1.467577703160486</v>
+        <v>-0.06269489081302528</v>
       </c>
       <c r="AH17" t="n">
-        <v>-2.32294473857401</v>
+        <v>0.2297291497713185</v>
       </c>
       <c r="AI17" t="n">
-        <v>-2.185538881189841</v>
+        <v>0.01002428378412317</v>
       </c>
       <c r="AJ17" t="n">
         <v>-0.2315504637589359</v>
@@ -2400,20 +2400,20 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>8KfYbJz0</t>
+          <t>CxyB0iT1</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0.6517980582565688</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6008560812216125</v>
+        <v>1.39072932418601</v>
       </c>
       <c r="D18" t="n">
         <v>0.8138764826725458</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6161248305345778</v>
+        <v>-0.5348081874171026</v>
       </c>
       <c r="F18" t="n">
         <v>-0.2141296999117111</v>
@@ -2422,7 +2422,7 @@
         <v>-0.2701804913637576</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6222229682558483</v>
+        <v>-0.01366721026397662</v>
       </c>
       <c r="I18" t="n">
         <v>0.5616338189825709</v>
@@ -2461,25 +2461,25 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.9586950056663653</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.108088087524279</v>
+        <v>-0.4872978369268575</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.1137088213420313</v>
+        <v>-0.104405048785081</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.7940685513874336</v>
+        <v>-0.6574521722189914</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.9867530901272389</v>
+        <v>0.3490994343771882</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.1329852696603492</v>
+        <v>-0.1106763164885312</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.07591772950822268</v>
+        <v>0.0867032540654535</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2488,7 +2488,7 @@
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.619459455853097</v>
+        <v>-0.748638370424368</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2497,13 +2497,13 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.02929996702690747</v>
+        <v>0.2669919934518059</v>
       </c>
       <c r="AH18" t="n">
         <v>-0.02755616308562162</v>
       </c>
       <c r="AI18" t="n">
-        <v>-0.7238330420091825</v>
+        <v>-0.6706268056623685</v>
       </c>
       <c r="AJ18" t="n">
         <v>-0.2315504637589359</v>
@@ -2512,35 +2512,35 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>0IkylEqd</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.1410166790296269</v>
+        <v>-1.425923322217599</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.4111690113265222</v>
+        <v>0.6008560812216125</v>
       </c>
       <c r="D19" t="n">
-        <v>1.227502688442405</v>
+        <v>-1.006078822714832</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.219540489236457</v>
+        <v>0.6161248305345778</v>
       </c>
       <c r="F19" t="n">
-        <v>4.670066788550652</v>
+        <v>-0.2141296999117111</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.06842195886845531</v>
+        <v>0.3350951061221493</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.500511816657474</v>
+        <v>0.3514662445311464</v>
       </c>
       <c r="I19" t="n">
         <v>0.5616338189825709</v>
       </c>
       <c r="J19" t="n">
-        <v>0.007732342947784333</v>
+        <v>-0.4875837024189391</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2573,25 +2573,25 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.5559680418311467</v>
       </c>
       <c r="V19" t="n">
-        <v>1.273516543404408</v>
+        <v>-0.1756111687180477</v>
       </c>
       <c r="W19" t="n">
-        <v>0.08761946074333166</v>
+        <v>-0.01460342319844615</v>
       </c>
       <c r="X19" t="n">
-        <v>0.9586705639829571</v>
+        <v>0.1212470653569702</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.3849065002042554</v>
+        <v>-0.6691498110728986</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.2263405153625745</v>
+        <v>-0.01065104159513782</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.244621106696946</v>
+        <v>-0.533662614916145</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2600,7 +2600,7 @@
         <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.272927282751588</v>
+        <v>0.4269154012763712</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2609,13 +2609,13 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.4868103131072283</v>
+        <v>-0.02929996702690747</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.403144495446952</v>
+        <v>-0.02755616308562162</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.540952834523467</v>
+        <v>0.09904899425808969</v>
       </c>
       <c r="AJ19" t="n">
         <v>-0.2315504637589359</v>
@@ -2624,35 +2624,35 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
+          <t>4QCyHCDr</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.089213085724815</v>
+        <v>-0.7151239025816996</v>
       </c>
       <c r="C20" t="n">
-        <v>1.020476241546449</v>
+        <v>1.316678707658098</v>
       </c>
       <c r="D20" t="n">
-        <v>1.260592784903993</v>
+        <v>1.028962109672872</v>
       </c>
       <c r="E20" t="n">
-        <v>1.082325546666904</v>
+        <v>-0.2142951950761283</v>
       </c>
       <c r="F20" t="n">
-        <v>4.670066788550652</v>
+        <v>-0.2141296999117111</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4719390238590598</v>
+        <v>-0.06842195886845531</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3514662445311464</v>
+        <v>0.1080439413343977</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1960996420384249</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.998364433681231</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2688,22 +2688,22 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0.133846700437054</v>
+        <v>-0.6944164915334855</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1926701163797982</v>
+        <v>-0.2329877339680262</v>
       </c>
       <c r="X20" t="n">
-        <v>1.036127442038615</v>
+        <v>-0.9564534481786326</v>
       </c>
       <c r="Y20" t="n">
-        <v>-1.605986959506016</v>
+        <v>0.4211764476809285</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.1250636447321454</v>
+        <v>-0.1945053637740942</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.9983217836589526</v>
+        <v>-0.1333123092186957</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2712,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.095420142668602</v>
+        <v>-1.015624769804571</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2721,13 +2721,13 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.3101836579181683</v>
+        <v>-0.02929996702690747</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.02755616308562162</v>
+        <v>0.1774593122464606</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.7209841232493839</v>
+        <v>-0.6133909909762525</v>
       </c>
       <c r="AJ20" t="n">
         <v>-0.2315504637589359</v>
@@ -2736,29 +2736,29 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>CEhO9e6F</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.03166292216256539</v>
+        <v>2.128073775961899</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.4605360890117971</v>
+        <v>-0.5592702443823468</v>
       </c>
       <c r="D21" t="n">
-        <v>1.012417061442078</v>
+        <v>0.5160656145182476</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8261836349998065</v>
+        <v>-1.190402944478186</v>
       </c>
       <c r="F21" t="n">
-        <v>4.670066788550652</v>
+        <v>-0.2141296999117111</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5368536386174515</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9600220025230181</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2797,25 +2797,25 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>-1.160999988376106</v>
       </c>
       <c r="V21" t="n">
-        <v>1.161923680103555</v>
+        <v>1.912948782075621</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9390163981553155</v>
+        <v>0.02178038869446279</v>
       </c>
       <c r="X21" t="n">
-        <v>1.927839211935948</v>
+        <v>0.1411159918135424</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.4517952611286653</v>
+        <v>2.761123722627791</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.4899034463059836</v>
+        <v>0.1389598140927969</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.9719848878506487</v>
+        <v>2.114008639437619</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -2824,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.7200011883147402</v>
+        <v>0.5737750336153633</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -2833,13 +2833,13 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.5076242581131015</v>
+        <v>0.2821131411665878</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.4293144476125482</v>
+        <v>0.0407718873637366</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.716491451974524</v>
+        <v>0.06937894505824396</v>
       </c>
       <c r="AJ21" t="n">
         <v>-0.2315504637589359</v>
@@ -2848,35 +2848,35 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>CSXdOfL8</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.03166292216256539</v>
+        <v>-0.4144010711972805</v>
       </c>
       <c r="C22" t="n">
         <v>0.8230079308053494</v>
       </c>
       <c r="D22" t="n">
-        <v>1.376408122519553</v>
+        <v>-1.254254546176747</v>
       </c>
       <c r="E22" t="n">
         <v>1.577663807557501</v>
       </c>
       <c r="F22" t="n">
-        <v>4.670066788550652</v>
+        <v>-0.2141296999117111</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.06842195886845531</v>
+        <v>0.3350951061221493</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.01366721026397662</v>
+        <v>0.7165996993262693</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1960996420384249</v>
+        <v>0.5616338189825709</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4875837024189391</v>
+        <v>0.998364433681231</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2909,25 +2909,25 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>-0.3472294703751533</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3510339609531953</v>
+        <v>0.943165398258195</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.1154880341121613</v>
+        <v>0.06379830569613401</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3925760087173585</v>
+        <v>1.468467825965679</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.7932606162391754</v>
+        <v>-0.7522196821152132</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.05522879746655593</v>
+        <v>0.1474987387857741</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.1360316521140587</v>
+        <v>0.5462783751488575</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
         <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.6086422939471545</v>
+        <v>1.856861683487586</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -2945,13 +2945,13 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.2370079252137642</v>
+        <v>0.3691385168257603</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.1818735210454771</v>
+        <v>0.2599980101074296</v>
       </c>
       <c r="AI22" t="n">
-        <v>-0.6696549661805394</v>
+        <v>0.5315939413020802</v>
       </c>
       <c r="AJ22" t="n">
         <v>-0.2315504637589359</v>
@@ -2960,35 +2960,35 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>CjGqFjre</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6517980582565688</v>
+        <v>-0.8791545378822918</v>
       </c>
       <c r="C23" t="n">
-        <v>-1.29977640966147</v>
+        <v>-0.01623238984432331</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8138764826725458</v>
+        <v>-0.4766372793294131</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9573025864120233</v>
+        <v>0.4995746515014962</v>
       </c>
       <c r="F23" t="n">
-        <v>4.670066788550652</v>
+        <v>-0.2141296999117111</v>
       </c>
       <c r="G23" t="n">
-        <v>0.940370703608056</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4731773961295207</v>
+        <v>-0.01366721026397662</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5616338189825709</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.007732342947784333</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -3021,25 +3021,25 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>-1.261505197936386</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.05391931179384817</v>
+        <v>-1.138337109907628</v>
       </c>
       <c r="W23" t="n">
-        <v>0.0049276563658999</v>
+        <v>-0.1947289342353713</v>
       </c>
       <c r="X23" t="n">
-        <v>0.1937563303813637</v>
+        <v>-1.630948720531108</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.2131683356077613</v>
+        <v>0.2324295649547101</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.01710127404834046</v>
+        <v>-0.2960408727739027</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.006139718077698</v>
+        <v>0.5285208514507926</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.004911393850210763</v>
+        <v>-1.9683079369891</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3057,13 +3057,13 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.2315849918636837</v>
+        <v>-0.4280972016694775</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.1061313033988671</v>
+        <v>-0.3777500611409011</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.2163906120807883</v>
+        <v>-0.8258208796635773</v>
       </c>
       <c r="AJ23" t="n">
         <v>-0.2315504637589359</v>
@@ -3072,35 +3072,35 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>8x0Cb1B6</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.553966552409826</v>
+        <v>-0.8791545378822918</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6008560812216125</v>
+        <v>-1.29977640966147</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4931823275602075</v>
+        <v>-1.204619401484364</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6161248305345778</v>
+        <v>-0.9573025864120233</v>
       </c>
       <c r="F24" t="n">
-        <v>4.670066788550652</v>
+        <v>-0.2141296999117111</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.06842195886845531</v>
+        <v>-1.077214621344967</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1080439413343977</v>
+        <v>-2.08275678743634</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1960996420384249</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4875837024189391</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3133,25 +3133,25 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>0.1813447660086083</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.8525906016566527</v>
+        <v>-1.882021357839101</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.1352947073790119</v>
+        <v>-2.297277799801587</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.8483475204178247</v>
+        <v>-2.011354300148683</v>
       </c>
       <c r="Y24" t="n">
-        <v>-1.025201807089608</v>
+        <v>0.3436263285092968</v>
       </c>
       <c r="Z24" t="n">
-        <v>-0.08389444689285835</v>
+        <v>-2.539931677154327</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.1086943940875728</v>
+        <v>-0.278927099856135</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3160,7 +3160,7 @@
         <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.3461294010357787</v>
+        <v>-2.359657498051674</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3169,13 +3169,13 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>-0.1175369471669792</v>
+        <v>-1.03675152551541</v>
       </c>
       <c r="AH24" t="n">
-        <v>-0.02755616308562162</v>
+        <v>-1.370316439662529</v>
       </c>
       <c r="AI24" t="n">
-        <v>-0.6240977458293089</v>
+        <v>-2.270969892550095</v>
       </c>
       <c r="AJ24" t="n">
         <v>-0.2315504637589359</v>
@@ -3184,35 +3184,35 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>GrNwFMem</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-1.070523612399649</v>
+        <v>1.717997187710418</v>
       </c>
       <c r="C25" t="n">
-        <v>-1.349143487346745</v>
+        <v>1.242628091130186</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5759075687141793</v>
+        <v>-0.02992097709796582</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2580015122135339</v>
+        <v>1.082325546666904</v>
       </c>
       <c r="F25" t="n">
-        <v>4.670066788550652</v>
+        <v>-0.2141296999117111</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2701804913637576</v>
+        <v>-2.489524348812083</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.01366721026397662</v>
+        <v>-2.813023697026587</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>-1.711566564080417</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.9828997477856625</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3248,22 +3248,22 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>2.665938848453598</v>
+        <v>-1.396982019742907</v>
       </c>
       <c r="W25" t="n">
-        <v>2.710338507098338</v>
+        <v>-1.061674350385209</v>
       </c>
       <c r="X25" t="n">
-        <v>2.842431350165445</v>
+        <v>-0.6334390267698649</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.1859227884261737</v>
+        <v>-0.4859054818021803</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.844640824284886</v>
+        <v>-1.611443012281618</v>
       </c>
       <c r="AA25" t="n">
-        <v>-1.005267394581133</v>
+        <v>0.3651564457104819</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3272,7 +3272,7 @@
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.488706026382861</v>
+        <v>-1.344420187035706</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3281,13 +3281,13 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.260555558236114</v>
+        <v>-1.708455691662727</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.356298295405935</v>
+        <v>-1.357809514731983</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.912031790143133</v>
+        <v>-1.007171657767268</v>
       </c>
       <c r="AJ25" t="n">
         <v>-0.2315504637589359</v>
@@ -3296,35 +3296,35 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>4CX22Dbk</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1323677131380268</v>
+        <v>-0.1410166790296269</v>
       </c>
       <c r="C26" t="n">
-        <v>-1.719396569986306</v>
+        <v>-0.509903166697072</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.757903099252917</v>
+        <v>1.47567841190432</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.3017078293509395</v>
+        <v>0.09164902488571078</v>
       </c>
       <c r="F26" t="n">
-        <v>4.670066788550652</v>
+        <v>-0.2141296999117111</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2701804913637576</v>
+        <v>0.133336573626847</v>
       </c>
       <c r="H26" t="n">
-        <v>0.229755092932772</v>
+        <v>-0.01366721026397662</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>-0.1960996420384249</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.4875837024189391</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3360,22 +3360,22 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0.882953639704771</v>
+        <v>-0.2071314549786354</v>
       </c>
       <c r="W26" t="n">
-        <v>0.2274869386033002</v>
+        <v>-0.02303588490830924</v>
       </c>
       <c r="X26" t="n">
-        <v>1.327486363677788</v>
+        <v>0.147991270140276</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.3400164933624907</v>
+        <v>-0.2264610288395323</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.2062360025596782</v>
+        <v>-0.05439035812966277</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.9779423162017148</v>
+        <v>1.892815678430225</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.093226843950578</v>
+        <v>-0.07035333128689646</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3393,13 +3393,13 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.2980917728764793</v>
+        <v>-0.02929996702690747</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.03865696889962052</v>
+        <v>-0.02755616308562162</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.034494799408063</v>
+        <v>-0.1453120106290587</v>
       </c>
       <c r="AJ26" t="n">
         <v>-0.2315504637589359</v>
@@ -3408,35 +3408,35 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bs5ow5pA</t>
+          <t>EirZ0Wr4</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1410166790296269</v>
+        <v>-0.03166292216256539</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.5592702443823468</v>
+        <v>-0.9295233270219083</v>
       </c>
       <c r="D27" t="n">
-        <v>1.47567841190432</v>
+        <v>1.376408122519553</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.190402944478186</v>
+        <v>1.796195393244528</v>
       </c>
       <c r="F27" t="n">
-        <v>4.670066788550652</v>
+        <v>-0.2141296999117111</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.077214621344967</v>
+        <v>-0.4719390238590598</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.9873564230509713</v>
+        <v>0.1080439413343977</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.9538331030594207</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.007732342947784333</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3472,22 +3472,22 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.125078760231576</v>
+        <v>1.480014227958506</v>
       </c>
       <c r="W27" t="n">
-        <v>0.02712555065140831</v>
+        <v>2.049241576318867</v>
       </c>
       <c r="X27" t="n">
-        <v>0.6374206422988038</v>
+        <v>2.483729165200385</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.9832267941496156</v>
+        <v>-0.6569179793766032</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.08260285821259347</v>
+        <v>1.714220339141191</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.566708966901738</v>
+        <v>0.277950916541772</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3496,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.9109008297567326</v>
+        <v>2.370025212782653</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3505,13 +3505,13 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.2723607597684297</v>
+        <v>1.303736280892403</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.1377760210229828</v>
+        <v>1.38373723528624</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.3215316792935797</v>
+        <v>1.944412391769952</v>
       </c>
       <c r="AJ27" t="n">
         <v>-0.2315504637589359</v>
@@ -3520,35 +3520,35 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>t4ZkclrT</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.207215808483476</v>
+        <v>0.597121179823038</v>
       </c>
       <c r="C28" t="n">
-        <v>-1.497244720402569</v>
+        <v>-0.7320550162808089</v>
       </c>
       <c r="D28" t="n">
-        <v>0.03625921582521156</v>
+        <v>-1.221164449715159</v>
       </c>
       <c r="E28" t="n">
-        <v>1.796195393244528</v>
+        <v>-0.2580015122135339</v>
       </c>
       <c r="F28" t="n">
-        <v>4.670066788550652</v>
+        <v>-0.2141296999117111</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.8754560888496645</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>-0.865645271452597</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>-0.1960996420384249</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.007732342947784333</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -3584,22 +3584,22 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.398459757923407</v>
+        <v>-1.660407798980844</v>
       </c>
       <c r="W28" t="n">
-        <v>0.4716190514642747</v>
+        <v>-1.104602795757691</v>
       </c>
       <c r="X28" t="n">
-        <v>1.766781653216937</v>
+        <v>-0.9850028903877913</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.1448260002789079</v>
+        <v>-1.067540651679185</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.3645607813971276</v>
+        <v>-1.408864141659888</v>
       </c>
       <c r="AA28" t="n">
-        <v>-1.074192660610044</v>
+        <v>-1.20842897188778</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
         <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.141628864298663</v>
+        <v>-1.142714915799211</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3617,13 +3617,13 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.5960011956255418</v>
+        <v>-0.7753770402141107</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.3536422967722714</v>
+        <v>-0.9721968460750741</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.180036058003137</v>
+        <v>-1.399920436458068</v>
       </c>
       <c r="AJ28" t="n">
         <v>-0.2315504637589359</v>
@@ -3632,35 +3632,35 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>YH892O2B</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4144010711972805</v>
+        <v>0.296398348438619</v>
       </c>
       <c r="C29" t="n">
-        <v>0.230602998582051</v>
+        <v>-0.1396500840575105</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.254254546176747</v>
+        <v>1.624583845981469</v>
       </c>
       <c r="E29" t="n">
-        <v>1.504819945661825</v>
+        <v>1.767057848486258</v>
       </c>
       <c r="F29" t="n">
-        <v>4.670066788550652</v>
+        <v>-0.2141296999117111</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.06842195886845531</v>
+        <v>-0.4719390238590598</v>
       </c>
       <c r="H29" t="n">
-        <v>0.594888547727895</v>
+        <v>-1.595912181042843</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5616338189825709</v>
+        <v>-1.711566564080417</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5030483883145077</v>
+        <v>-1.973531838519109</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3696,22 +3696,22 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.292114858726301</v>
+        <v>-1.48190451266272</v>
       </c>
       <c r="W29" t="n">
-        <v>0.3632914487180789</v>
+        <v>-1.427055129134087</v>
       </c>
       <c r="X29" t="n">
-        <v>1.994884917099731</v>
+        <v>-1.161010512904795</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.1024741093776278</v>
+        <v>0.2703477816712605</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.2619299972042452</v>
+        <v>-1.819969935263194</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.9489676892854951</v>
+        <v>0.06486224463853184</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.539929781154423</v>
+        <v>-1.709549235870077</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3729,13 +3729,13 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.781445221139121</v>
+        <v>-1.956509980354264</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.3586871068282901</v>
+        <v>-1.778105252524019</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.545933622912971</v>
+        <v>-1.462810302633607</v>
       </c>
       <c r="AJ29" t="n">
         <v>-0.2315504637589359</v>
@@ -3744,23 +3744,23 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>8jyraADG</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.425923322217599</v>
+        <v>1.553966552409826</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3124348559559725</v>
+        <v>-0.09028300637223562</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.006078822714832</v>
+        <v>-0.4931823275602075</v>
       </c>
       <c r="E30" t="n">
         <v>0.0188051629900348</v>
       </c>
       <c r="F30" t="n">
-        <v>4.670066788550652</v>
+        <v>-0.2141296999117111</v>
       </c>
       <c r="G30" t="n">
         <v>0.5368536386174515</v>
@@ -3769,10 +3769,10 @@
         <v>0.4731773961295207</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>0.5616338189825709</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.998364433681231</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3808,22 +3808,22 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.411520178269538</v>
+        <v>2.035265682544726</v>
       </c>
       <c r="W30" t="n">
-        <v>0.2962552225722602</v>
+        <v>1.18566836958129</v>
       </c>
       <c r="X30" t="n">
-        <v>1.587366187480087</v>
+        <v>1.19652349350994</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.3534298961035779</v>
+        <v>0.2113039822996117</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.3395123023563117</v>
+        <v>1.742507919918558</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.6296965642966124</v>
+        <v>0.08395498462488175</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -3832,7 +3832,7 @@
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.072795838996226</v>
+        <v>1.898704137276361</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -3841,15 +3841,3263 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.2926358554845221</v>
+        <v>1.769432546966023</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.3895865684214029</v>
+        <v>1.378369339401016</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.39555133951693</v>
+        <v>1.609470591963001</v>
       </c>
       <c r="AJ30" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>tYhtcc5C</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1.717997187710418</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.682687938595534</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.278096700559881</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.3247493829518739</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>-1.138706687041078</v>
+      </c>
+      <c r="W31" t="n">
+        <v>-0.3398936798803136</v>
+      </c>
+      <c r="X31" t="n">
+        <v>-1.718682740598389</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.7608349388679183</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-0.3764350441432474</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-2.001951945238825</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>-1.844043855576376</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>-0.3515811004480734</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>-0.4286185625390873</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>-1.306557476676585</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>IXMN9zkI</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2.128073775961899</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-1.225725793133557</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.574948701289086</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.9573025864120233</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>-1.411440131761689</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.02178038869446279</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.1411159918135424</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>-1.337269275758721</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-0.1263623523186772</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.3116548200461625</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>-0.6154110541653083</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>-0.02929996702690747</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.0407718873637366</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.06937894505824396</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>lvG7DIkg</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-1.043185173182884</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.020476241546449</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.8800566755957232</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.082325546666904</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-0.4719390238590598</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.01366721026397662</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>-1.173592561470896</v>
+      </c>
+      <c r="V33" t="n">
+        <v>-0.293440251859717</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.1249831791318199</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.2012274710612565</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>-0.7240660044614737</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-0.005673451698010646</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.3271800473278521</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>-0.1166278236623983</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>-0.4277384508795752</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>-0.3151103362786727</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.5351020447974798</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>SORbFvLt</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1.553966552409826</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.9957927027038115</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-0.6420877616373566</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.7679085454832657</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-0.2701804913637576</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.1353783618623509</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-1.711566564080417</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-1.973531838519109</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>-0.7779153569613199</v>
+      </c>
+      <c r="W34" t="n">
+        <v>-0.06988428184731134</v>
+      </c>
+      <c r="X34" t="n">
+        <v>-0.3203965028518937</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>-1.575390902013991</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-0.1013403979025525</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-1.270209941763065</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>-0.07117900723874863</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>-0.3407130752204027</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>-0.1899990468894154</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>-0.3080500873721655</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>4xHh663n</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>-0.7151239025816996</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-1.694713031143669</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.177867543750021</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.504819945661825</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-0.4719390238590598</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.9873564230509713</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.5616338189825709</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.5030483883145077</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.1171493171995293</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.4228005557273165</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.4935358501618273</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>-1.069434646804812</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.4627263354724778</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.6446907035388298</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8872439403035828</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.2867362320972082</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.4012526916759462</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0.2961717526787244</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>6RvR2hEi</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>-0.7698007810152303</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1.143893935759636</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-1.370069883792308</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.06251148012744039</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-1.480731686335571</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-1.961045635837966</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-2.469300025101413</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-1.973531838519109</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>-1.218175571911212</v>
+      </c>
+      <c r="W36" t="n">
+        <v>-2.436094929098569</v>
+      </c>
+      <c r="X36" t="n">
+        <v>-1.45456408211869</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>-0.3262620592130539</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-1.588366367192901</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.6807868660792538</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>-1.025545322652089</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>-1.182402542301783</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>-1.160116020661759</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>-1.742984514225241</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>4.318713008673075</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>hKOA02XN</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-1.207215808483476</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-1.719396569986306</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-1.469340173177074</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.3017078293509395</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.5368536386174515</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.4731773961295207</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.319367280003567</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.007732342947784333</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>-1.20289677362606</v>
+      </c>
+      <c r="V37" t="n">
+        <v>-0.4069742398415516</v>
+      </c>
+      <c r="W37" t="n">
+        <v>-0.2577336912255136</v>
+      </c>
+      <c r="X37" t="n">
+        <v>-0.4316404040308374</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>-0.3859730688365928</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-0.1578122578836808</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-0.05492948205070335</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>-0.5530631363798717</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>-0.4951685814116546</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>-0.6253661547238057</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>-0.2357325881094467</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>0lGMiS5j</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1.553966552409826</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-1.151675176605645</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-0.5262724240217962</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-1.219540489236457</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.563231626046985</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.42055582170351</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.319367280003567</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.007732342947784333</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.946396512439005</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.406952609504363</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.9973536054545717</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>-0.3318953234215662</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.051758440586128</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.1817644988205799</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.635854460899387</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0.7268603238061314</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0.9999034849901334</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0.8073751223904762</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.1410166790296269</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1.39072932418601</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.227502688442405</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.5348081874171026</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-0.2701804913637576</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3514662445311464</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-0.9538331030594207</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-0.4875837024189391</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.455006777055964</v>
+      </c>
+      <c r="W39" t="n">
+        <v>-0.04018400490677607</v>
+      </c>
+      <c r="X39" t="n">
+        <v>-0.1821700236897043</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.110276634241201</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-0.003032703881721578</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-0.9234196925934773</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>-0.1588384283195771</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.2669919934518059</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>-0.2325716384177039</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>-0.2528306420824957</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>-1.425923322217599</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.4111690113265222</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-1.006078822714832</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-1.219540489236457</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-0.06842195886845531</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-0.2570895134607253</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>-0.9586950056663653</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.263192359968233</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.1235648608910351</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.396667627533591</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>-0.0855352413924725</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0.2460594583282917</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.04624521606416113</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.762715003807036</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0.4394041631050383</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0.6139755157047229</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0.967889293284096</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>-1.070523612399649</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.01623238984432331</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-0.5759075687141793</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.4995746515014962</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-0.6736975563543621</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-0.500511816657474</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-0.9538331030594207</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-1.478215793152386</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.2133402970653561</v>
+      </c>
+      <c r="W41" t="n">
+        <v>-0.05092092992449319</v>
+      </c>
+      <c r="X41" t="n">
+        <v>-0.2095296175683644</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0.2644803130277159</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-0.02602866477659794</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.5682342763919547</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>-0.2255389235956398</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.04060692846246834</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0.2637816176494433</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0.07923821761217582</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>O2Fteteo</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1.854689383794245</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.230602998582051</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-0.6751778580989453</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.504819945661825</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-0.4719390238590598</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-2.326179090633089</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-0.1960996420384249</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-0.9828997477856625</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>-1.603269985480944</v>
+      </c>
+      <c r="V42" t="n">
+        <v>-2.132966149893547</v>
+      </c>
+      <c r="W42" t="n">
+        <v>-2.574698731588679</v>
+      </c>
+      <c r="X42" t="n">
+        <v>-1.689282418478465</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>-0.4552406030609477</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-2.572944768437778</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.9006648628719022</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>-2.012657366604393</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>-1.504157523932408</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>-2.222048537453641</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>-2.160543643785158</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Sf88FVcc</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.597121179823038</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-1.29977640966147</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-0.327731845252264</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-0.9573025864120233</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-0.06842195886845531</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-0.500511816657474</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-0.4875837024189391</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>-0.5141889441802113</v>
+      </c>
+      <c r="V43" t="n">
+        <v>-1.521990263942778</v>
+      </c>
+      <c r="W43" t="n">
+        <v>-0.7801827656546233</v>
+      </c>
+      <c r="X43" t="n">
+        <v>-0.9925466671576241</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>-0.07054121725435759</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-1.172053986987562</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.8905028914112498</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>-1.582283233423837</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>-1.194913083696065</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>-1.098737498313536</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>-1.462747093561621</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.6517980582565688</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.6008560812216125</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.8138764826725458</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.6161248305345778</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-0.2701804913637576</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-0.6222229682558483</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.5616338189825709</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.007732342947784333</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>-0.5977471394820821</v>
+      </c>
+      <c r="V44" t="n">
+        <v>-1.176475266666491</v>
+      </c>
+      <c r="W44" t="n">
+        <v>-0.1149282657147683</v>
+      </c>
+      <c r="X44" t="n">
+        <v>-0.8263310813372684</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>-1.058799582792977</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-0.1400079350442462</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.1123461872731252</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>-0.6684093001572291</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>-0.02929996702690747</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>-0.02755616308562162</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>-0.7170380667703563</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>8KIdPmPc</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2.128073775961899</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.1396500840575105</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.5160656145182476</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.767057848486258</v>
+      </c>
+      <c r="F45" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.942863280505861</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0.02178038869446279</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0.1411159918135424</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>2.132079193145781</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0.2092439518541639</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.286053360428063</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.848692770091745</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0.3753691673777553</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0.0407718873637366</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0.06937894505824396</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>fNwTkrUF</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>-0.1410166790296269</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.4111690113265222</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.227502688442405</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-1.219540489236457</v>
+      </c>
+      <c r="F46" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-0.06842195886845531</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-0.500511816657474</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.5616338189825709</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.007732342947784333</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.20463287600261</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.08746106225301788</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0.9243716293686391</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0.2859921867514609</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0.2243461774859929</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>-0.3178689284054995</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.257190244478226</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0.4394041631050383</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0.4089600403726406</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0.5695983958355227</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>42SH31wI</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2.128073775961899</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.7320550162808089</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1.574948701289086</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-0.2580015122135339</v>
+      </c>
+      <c r="F47" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-0.06842195886845531</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-0.01366721026397662</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>-0.5544241687168362</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.02178038869446279</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.1411159918135424</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>-2.675101897752685</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0.06091877559231133</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0.6329682010156911</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.130634721605117</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0.1517052712168554</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0.0407718873637366</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0.06937894505824396</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1.089213085724815</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1.020476241546449</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.260592784903993</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.082325546666904</v>
+      </c>
+      <c r="F48" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-0.4719390238590598</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.3514662445311464</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-0.1960996420384249</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.998364433681231</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.1175706276059488</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0.1882464447458413</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.003596850328274</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>-1.606384556814209</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0.1227199792320162</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.055149386203638</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.078627416905669</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>-0.3255919275056208</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>-0.02755616308562162</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0.7136834754346477</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>ALOjHNNj</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>-0.03166292216256539</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.4605360890117971</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.012417061442078</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-0.8261836349998065</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.5368536386174515</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.9600220025230181</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.177959786161002</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.9302535563236365</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.88825254291683</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0.4626902076180301</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0.510398252480795</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0.9696693265575431</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.7208807266009531</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0.5106542465537003</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0.4113423117879823</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>1.696663556204947</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>ILr8tvi2</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>-0.03166292216256539</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.8230079308053494</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1.376408122519553</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.577663807557501</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-0.06842195886845531</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-0.01366721026397662</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-0.1960996420384249</v>
+      </c>
+      <c r="J50" t="n">
+        <v>-0.4875837024189391</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>-0.4006449769997932</v>
+      </c>
+      <c r="W50" t="n">
+        <v>-0.1084034489494817</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0.4342106119390501</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>-0.8631423029723791</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-0.06901569115554196</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0.2160052034840917</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.619162785672667</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>-0.2789816416917733</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0.1592886538039505</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>-0.6489724310834457</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.6517980582565688</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-1.29977640966147</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.8138764826725458</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-0.9573025864120233</v>
+      </c>
+      <c r="F51" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.940370703608056</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.4731773961295207</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.5616338189825709</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.007732342947784333</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>-0.1127205818069059</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0.01017074886459737</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0.204011854509081</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>-0.2477840105017706</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0.001413939479967772</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1.005357316828769</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>-0.03941692523883295</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0.2593629788982363</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0.09604168328683022</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>-0.1552674394673403</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>6sP22LDL</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1.553966552409826</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.6008560812216125</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-0.4931823275602075</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.6161248305345778</v>
+      </c>
+      <c r="F52" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-0.06842195886845531</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.1080439413343977</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-0.1960996420384249</v>
+      </c>
+      <c r="J52" t="n">
+        <v>-0.4875837024189391</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>-0.8983910205806742</v>
+      </c>
+      <c r="W52" t="n">
+        <v>-0.1381903243726107</v>
+      </c>
+      <c r="X52" t="n">
+        <v>-0.8490903895195151</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>-1.087534171921025</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-0.0868461203156254</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0.05459975861799665</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>-0.3985588336643339</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>-0.1152259044820542</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>-0.02755616308562162</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>-0.6385007948239155</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>dC3sew6e</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>-1.070523612399649</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-1.349143487346745</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-0.5759075687141793</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-0.2580015122135339</v>
+      </c>
+      <c r="F53" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-0.2701804913637576</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-0.01366721026397662</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>2.618805440855269</v>
+      </c>
+      <c r="W53" t="n">
+        <v>2.646657023716149</v>
+      </c>
+      <c r="X53" t="n">
+        <v>2.796514964736973</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>-0.01134820652165304</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.83291317754004</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>-0.9541355638686089</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>2.552125223824961</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.226102512401802</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.332020147011346</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>2.900891191205055</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.1323677131380268</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-1.719396569986306</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-0.757903099252917</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-0.3017078293509395</v>
+      </c>
+      <c r="F54" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-0.2701804913637576</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.229755092932772</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0.8914627309582801</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0.2253851834221207</v>
+      </c>
+      <c r="X54" t="n">
+        <v>1.322348225029655</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>-0.377370950827492</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0.2114579763072699</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1.008738733161378</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1.163382599171247</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0.2930177261163261</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0.04811598775465516</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>1.04842291842086</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>-0.1410166790296269</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.5592702443823468</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.47567841190432</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-1.190402944478186</v>
+      </c>
+      <c r="F55" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-1.077214621344967</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-0.9873564230509713</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-0.9538331030594207</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.007732342947784333</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.142625408539304</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0.02442504020807</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0.5904419060151738</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.034051777963044</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0.07969115522664978</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>2.64122546404309</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.9119287306597392</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0.2821131411665878</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0.1348867207181722</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>0.3242745060850748</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>AZ3PVMxp</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>-1.207215808483476</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-1.497244720402569</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.03625921582521156</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.796195393244528</v>
+      </c>
+      <c r="F56" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.43211093703882</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0.4732273239770604</v>
+      </c>
+      <c r="X56" t="n">
+        <v>1.804254093189493</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0.2273263697291655</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0.3631928674725773</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>-1.012672886904112</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>2.140253700100303</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0.6889794450116975</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0.3545881986577743</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>1.158311890073888</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>hvcjgHz8</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>-0.4144010711972805</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.230602998582051</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-1.254254546176747</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.504819945661825</v>
+      </c>
+      <c r="F57" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-0.06842195886845531</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.594888547727895</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.5616338189825709</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.5030483883145077</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.2912577468473</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0.3701473247622408</v>
+      </c>
+      <c r="X57" t="n">
+        <v>2.044368253373634</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0.1422359270086119</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0.2647457881977981</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0.8528723272599358</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>1.529689198370042</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0.792281264287191</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>0.3886406665358992</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>1.548754327750485</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>dnnqk0iD</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2.128073775961899</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1.242628091130186</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-1.138439208561187</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.082325546666904</v>
+      </c>
+      <c r="F58" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0.7562452131781391</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0.02178038869446279</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0.1411159918135424</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>-1.053668086583754</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0.2159939167764675</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0.09259956739564955</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>1.462972437530633</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0.1762027597853505</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>0.0407718873637366</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>0.06937894505824396</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>QT6wuRFc</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>-1.425923322217599</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.3124348559559725</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-1.006078822714832</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.0188051629900348</v>
+      </c>
+      <c r="F59" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.5368536386174515</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.4731773961295207</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1.437848932297861</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0.2871464872417239</v>
+      </c>
+      <c r="X59" t="n">
+        <v>1.579675985576559</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>-0.3702392052882559</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0.3453156257871962</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0.5009044491737638</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>2.094204147349657</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0.2929811663942584</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>0.3735062363678441</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>1.373628326382051</v>
+      </c>
+      <c r="AJ59" t="n">
         <v>-0.2315504637589359</v>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ59"/>
+  <dimension ref="A1:AJ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,35 +608,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>W0WITkcl</t>
+          <t>4CX22Dbk</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.089213085724815</v>
+        <v>-0.1410166790296269</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.9048397881792709</v>
+        <v>-0.509903166697072</v>
       </c>
       <c r="D2" t="n">
-        <v>1.260592784903993</v>
+        <v>1.47567841190432</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3247493829518739</v>
+        <v>0.09164902488571078</v>
       </c>
       <c r="F2" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5368536386174515</v>
+        <v>0.133336573626847</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8383108509246437</v>
+        <v>-0.01366721026397662</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5616338189825709</v>
+        <v>-0.1960996420384249</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007732342947784333</v>
+        <v>-0.4875837024189391</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -672,22 +672,22 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.594792318935968</v>
+        <v>-0.2071314549786354</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.05253665648388181</v>
+        <v>-0.02303588490830924</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3801437221686224</v>
+        <v>0.147991270140276</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.7887035226919874</v>
+        <v>-0.2264610288395323</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.06855930257644363</v>
+        <v>-0.05439035812966277</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.5582504710514602</v>
+        <v>1.892815678430225</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.4105768518215517</v>
+        <v>-0.07035333128689646</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.3255919275056208</v>
+        <v>-0.02929996702690747</v>
       </c>
       <c r="AH2" t="n">
         <v>-0.02755616308562162</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.247152360448811</v>
+        <v>-0.1453120106290587</v>
       </c>
       <c r="AJ2" t="n">
         <v>-0.2315504637589359</v>
@@ -720,29 +720,29 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>v3ivyY4E</t>
+          <t>EirZ0Wr4</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.207215808483476</v>
+        <v>-0.03166292216256539</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4033877704805131</v>
+        <v>-0.9295233270219083</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03625921582521156</v>
+        <v>1.376408122519553</v>
       </c>
       <c r="E3" t="n">
-        <v>1.927314344656745</v>
+        <v>1.796195393244528</v>
       </c>
       <c r="F3" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0.4719390238590598</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.1080439413343977</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -784,22 +784,22 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.8983713024946106</v>
+        <v>1.480014227958506</v>
       </c>
       <c r="W3" t="n">
-        <v>0.02178038869446279</v>
+        <v>2.049241576318867</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1411159918135424</v>
+        <v>2.483729165200385</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.840022703745011</v>
+        <v>-0.6569179793766032</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.05366772438368607</v>
+        <v>1.714220339141191</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.935415745825244</v>
+        <v>0.277950916541772</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -808,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5382101707084332</v>
+        <v>2.370025212782653</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.09920686251628327</v>
+        <v>1.303736280892403</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0407718873637366</v>
+        <v>1.38373723528624</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.06937894505824396</v>
+        <v>1.944412391769952</v>
       </c>
       <c r="AJ3" t="n">
         <v>-0.2315504637589359</v>
@@ -832,35 +832,35 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>YPSZP7dD</t>
+          <t>t4ZkclrT</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6517980582565688</v>
+        <v>0.597121179823038</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.5592702443823468</v>
+        <v>-0.7320550162808089</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8138764826725458</v>
+        <v>-1.221164449715159</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.190402944478186</v>
+        <v>-0.2580015122135339</v>
       </c>
       <c r="F4" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4719390238590598</v>
+        <v>-0.8754560888496645</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3788006650590997</v>
+        <v>-0.865645271452597</v>
       </c>
       <c r="I4" t="n">
         <v>-0.1960996420384249</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4875837024189391</v>
+        <v>0.007732342947784333</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -893,25 +893,25 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.160999988376106</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2604077185647436</v>
+        <v>-1.660407798980844</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.07310706081978585</v>
+        <v>-1.104602795757691</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5298789862484943</v>
+        <v>-0.9850028903877913</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.7532770456170194</v>
+        <v>-1.067540651679185</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.01922812976180889</v>
+        <v>-1.408864141659888</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.400950378925134</v>
+        <v>-1.20842897188778</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.09309664907338916</v>
+        <v>-1.142714915799211</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -929,13 +929,13 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.2821131411665878</v>
+        <v>-0.7753770402141107</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.1348867207181722</v>
+        <v>-0.9721968460750741</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.2836703483059695</v>
+        <v>-1.399920436458068</v>
       </c>
       <c r="AJ4" t="n">
         <v>-0.2315504637589359</v>
@@ -944,35 +944,35 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tWk1tTtf</t>
+          <t>8jyraADG</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1.553966552409826</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.225725793133557</v>
+        <v>-0.09028300637223562</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6980611450569854</v>
+        <v>-0.4931823275602075</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9573025864120233</v>
+        <v>0.0188051629900348</v>
       </c>
       <c r="F5" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2701804913637576</v>
+        <v>0.5368536386174515</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.01366721026397662</v>
+        <v>0.4731773961295207</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1960996420384249</v>
+        <v>0.5616338189825709</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007732342947784333</v>
+        <v>0.998364433681231</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1008,22 +1008,22 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.07579685303272284</v>
+        <v>2.035265682544726</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.04662868590506593</v>
+        <v>1.18566836958129</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5872372852737593</v>
+        <v>1.19652349350994</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.227845830337923</v>
+        <v>0.2113039822996117</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.03965241491589867</v>
+        <v>1.742507919918558</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1549929534469005</v>
+        <v>0.08395498462488175</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1032,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.8057260339989766</v>
+        <v>1.898704137276361</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1041,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.02929996702690747</v>
+        <v>1.769432546966023</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.02755616308562162</v>
+        <v>1.378369339401016</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.4082933546396582</v>
+        <v>1.609470591963001</v>
       </c>
       <c r="AJ5" t="n">
         <v>-0.2315504637589359</v>
@@ -1056,35 +1056,35 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Y54hDUC7</t>
+          <t>YH892O2B</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.717997187710418</v>
+        <v>0.296398348438619</v>
       </c>
       <c r="C6" t="n">
-        <v>1.563514096084472</v>
+        <v>-0.1396500840575105</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.278096700559881</v>
+        <v>1.624583845981469</v>
       </c>
       <c r="E6" t="n">
-        <v>1.111463091425174</v>
+        <v>1.767057848486258</v>
       </c>
       <c r="F6" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8754560888496645</v>
+        <v>-0.4719390238590598</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2570895134607253</v>
+        <v>-1.595912181042843</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-1.711566564080417</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-1.973531838519109</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1120,22 +1120,22 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.40042858223836</v>
+        <v>-1.48190451266272</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3409706085058983</v>
+        <v>-1.427055129134087</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.842436478839363</v>
+        <v>-1.161010512904795</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4291599280675897</v>
+        <v>0.2703477816712605</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.3647567429424129</v>
+        <v>-1.819969935263194</v>
       </c>
       <c r="AA6" t="n">
-        <v>-2.388243413553347</v>
+        <v>0.06486224463853184</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1144,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>-2.067795346461504</v>
+        <v>-1.709549235870077</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1153,13 +1153,13 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.3515811004480734</v>
+        <v>-1.956509980354264</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.4286185625390873</v>
+        <v>-1.778105252524019</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.267178224827383</v>
+        <v>-1.462810302633607</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0.2315504637589359</v>
@@ -1168,35 +1168,35 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Eql9v7B6</t>
+          <t>tYhtcc5C</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.043185173182884</v>
+        <v>1.717997187710418</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.4111690113265222</v>
+        <v>-0.682687938595534</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8800566755957232</v>
+        <v>-0.278096700559881</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.219540489236457</v>
+        <v>0.3247493829518739</v>
       </c>
       <c r="F7" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2701804913637576</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2570895134607253</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5616338189825709</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.998364433681231</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1211,10 +1211,10 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0259029127667809</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.04946140548819852</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1229,25 +1229,25 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.170571913096135</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2980021905237897</v>
+        <v>-1.138706687041078</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03607337016945217</v>
+        <v>-0.3398936798803136</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2591633999446381</v>
+        <v>-1.718682740598389</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.03305694656563592</v>
+        <v>0.7608349388679183</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.07404608762975451</v>
+        <v>-0.3764350441432474</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.1229461132239865</v>
+        <v>-2.001951945238825</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.1888281718235763</v>
+        <v>-1.844043855576376</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1265,13 +1265,13 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.04096567925237055</v>
+        <v>-0.3515811004480734</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.3264213425116717</v>
+        <v>-0.4286185625390873</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.5930015547394838</v>
+        <v>-1.306557476676585</v>
       </c>
       <c r="AJ7" t="n">
         <v>-0.2315504637589359</v>
@@ -1280,35 +1280,35 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EL5MmBlK</t>
+          <t>IXMN9zkI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.070523612399649</v>
+        <v>2.155412215178664</v>
       </c>
       <c r="C8" t="n">
-        <v>1.020476241546449</v>
+        <v>-1.225725793133557</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5759075687141793</v>
+        <v>1.574948701289086</v>
       </c>
       <c r="E8" t="n">
-        <v>1.082325546666904</v>
+        <v>-0.9573025864120233</v>
       </c>
       <c r="F8" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.06842195886845531</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.01366721026397662</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5616338189825709</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.998364433681231</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1323,10 +1323,10 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0259029127667809</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.04946140548819852</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1341,25 +1341,25 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.078593450293186</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7196219356322867</v>
+        <v>-1.411440131761689</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2044093818969255</v>
+        <v>0.03635074945686407</v>
       </c>
       <c r="X8" t="n">
-        <v>1.318474300232675</v>
+        <v>0.3562942689800624</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.7500493612514639</v>
+        <v>-1.337269275758721</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1653533058616064</v>
+        <v>-0.1263623523186772</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.4893120469568223</v>
+        <v>0.3116548200461625</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.405367757501326</v>
+        <v>-0.6154110541653083</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1380,10 +1380,10 @@
         <v>-0.02929996702690747</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.02755616308562162</v>
+        <v>-0.01282280050715345</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.7963135347923823</v>
+        <v>0.1645540158069977</v>
       </c>
       <c r="AJ8" t="n">
         <v>-0.2315504637589359</v>
@@ -1392,35 +1392,35 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>SORbFvLt</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.207215808483476</v>
+        <v>1.553966552409826</v>
       </c>
       <c r="C9" t="n">
-        <v>1.143893935759636</v>
+        <v>0.9957927027038115</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.022623870945627</v>
+        <v>-0.6420877616373566</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06251148012744039</v>
+        <v>-0.7679085454832657</v>
       </c>
       <c r="F9" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6736975563543621</v>
+        <v>-0.2701804913637576</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.08275678743634</v>
+        <v>-0.1353783618623509</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1960996420384249</v>
+        <v>-1.711566564080417</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.478215793152386</v>
+        <v>-1.973531838519109</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1453,25 +1453,25 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.878937944282372</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.452478494549055</v>
+        <v>-0.7779153569613199</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.998200702039554</v>
+        <v>-0.06988428184731134</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.779805625967784</v>
+        <v>-0.3203965028518937</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.4928740742431326</v>
+        <v>-1.575390902013991</v>
       </c>
       <c r="Z9" t="n">
-        <v>-1.684776614701277</v>
+        <v>-0.1013403979025525</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.4968988719398274</v>
+        <v>-1.270209941763065</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>-1.714332846694679</v>
+        <v>-0.07117900723874863</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1489,13 +1489,13 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>-1.908156469309918</v>
+        <v>-0.3407130752204027</v>
       </c>
       <c r="AH9" t="n">
-        <v>-1.312542465240132</v>
+        <v>-0.1899990468894154</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.64584358332712</v>
+        <v>-0.3080500873721655</v>
       </c>
       <c r="AJ9" t="n">
         <v>-0.2315504637589359</v>
@@ -1504,35 +1504,35 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>lvG7DIkg</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.03166292216256539</v>
+        <v>-1.043185173182884</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1396500840575105</v>
+        <v>1.020476241546449</v>
       </c>
       <c r="D10" t="n">
-        <v>1.376408122519553</v>
+        <v>0.8800566755957232</v>
       </c>
       <c r="E10" t="n">
-        <v>1.767057848486258</v>
+        <v>1.082325546666904</v>
       </c>
       <c r="F10" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2701804913637576</v>
+        <v>-0.4719390238590598</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1080439413343977</v>
+        <v>-0.01366721026397662</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5616338189825709</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5030483883145077</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1565,25 +1565,25 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.405329420810793</v>
+        <v>-1.173592561470896</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.03403580254361736</v>
+        <v>-0.293440251859717</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001547932537519454</v>
+        <v>0.1249831791318199</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6026225747648385</v>
+        <v>0.2012274710612565</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.2056906688618224</v>
+        <v>-0.7240660044614737</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.0356767975974795</v>
+        <v>-0.005673451698010646</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.02567228954157029</v>
+        <v>0.3271800473278521</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.3543670029319601</v>
+        <v>-0.1166278236623983</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1601,13 +1601,13 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.2727509911397782</v>
+        <v>-0.4277384508795752</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.2500952348122824</v>
+        <v>-0.3151103362786727</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.1844391830926791</v>
+        <v>0.5351020447974798</v>
       </c>
       <c r="AJ10" t="n">
         <v>-0.2315504637589359</v>
@@ -1616,35 +1616,35 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>UilLdutJ</t>
+          <t>6RvR2hEi</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.296398348438619</v>
+        <v>-0.7698007810152303</v>
       </c>
       <c r="C11" t="n">
-        <v>1.736298867982935</v>
+        <v>1.143893935759636</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.717515896638989</v>
+        <v>-1.370069883792308</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3017078293509395</v>
+        <v>0.06251148012744039</v>
       </c>
       <c r="F11" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G11" t="n">
-        <v>2.150921898579869</v>
+        <v>-1.480731686335571</v>
       </c>
       <c r="H11" t="n">
-        <v>2.055422366908387</v>
+        <v>-1.961045635837966</v>
       </c>
       <c r="I11" t="n">
-        <v>2.077100741024563</v>
+        <v>-2.469300025101413</v>
       </c>
       <c r="J11" t="n">
-        <v>1.988996524414678</v>
+        <v>-1.973531838519109</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1680,22 +1680,22 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.420033735562321</v>
+        <v>-1.218175571911212</v>
       </c>
       <c r="W11" t="n">
-        <v>1.310317853677538</v>
+        <v>-2.436094929098569</v>
       </c>
       <c r="X11" t="n">
-        <v>1.058540864078273</v>
+        <v>-1.45456408211869</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1304010902422169</v>
+        <v>-0.3262620592130539</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.720286827528908</v>
+        <v>-1.588366367192901</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.3523226618467456</v>
+        <v>0.6807868660792538</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1704,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.445371092137504</v>
+        <v>-1.025545322652089</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1713,50 +1713,50 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.980261487561878</v>
+        <v>-1.182402542301783</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.025681529713882</v>
+        <v>-1.160116020661759</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.301385624521183</v>
+        <v>-1.742984514225241</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0.2315504637589359</v>
+        <v>4.318713008673075</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2uc40Ntf</t>
+          <t>4xHh663n</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.499289673976295</v>
+        <v>-0.7151239025816996</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.349143487346745</v>
+        <v>-1.694713031143669</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.700970848408195</v>
+        <v>1.177867543750021</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2580015122135339</v>
+        <v>1.504819945661825</v>
       </c>
       <c r="F12" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G12" t="n">
-        <v>1.545646301093963</v>
+        <v>-0.4719390238590598</v>
       </c>
       <c r="H12" t="n">
-        <v>1.325155457318141</v>
+        <v>-0.9873564230509713</v>
       </c>
       <c r="I12" t="n">
         <v>0.5616338189825709</v>
       </c>
       <c r="J12" t="n">
-        <v>0.998364433681231</v>
+        <v>0.5030483883145077</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1789,25 +1789,25 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.261505197936386</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9708815040721605</v>
+        <v>0.1171493171995293</v>
       </c>
       <c r="W12" t="n">
-        <v>1.899415541446103</v>
+        <v>0.4228005557273165</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6547879698360566</v>
+        <v>0.4935358501618273</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.746763272877403</v>
+        <v>-1.069434646804812</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.089095380425255</v>
+        <v>0.4627263354724778</v>
       </c>
       <c r="AA12" t="n">
-        <v>-1.454198610158018</v>
+        <v>0.6446907035388298</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1816,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.2411785679412735</v>
+        <v>0.8872439403035828</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1825,13 +1825,13 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.7045635864654289</v>
+        <v>0.2867362320972082</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.8275391414095021</v>
+        <v>0.4012526916759462</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.226008806174201</v>
+        <v>0.2961717526787244</v>
       </c>
       <c r="AJ12" t="n">
         <v>-0.2315504637589359</v>
@@ -1840,35 +1840,35 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>KvdW7ZzS</t>
+          <t>hKOA02XN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.03166292216256539</v>
+        <v>-1.207215808483476</v>
       </c>
       <c r="C13" t="n">
-        <v>1.662248251455022</v>
+        <v>-1.719396569986306</v>
       </c>
       <c r="D13" t="n">
-        <v>1.012417061442078</v>
+        <v>-1.469340173177074</v>
       </c>
       <c r="E13" t="n">
-        <v>1.927314344656745</v>
+        <v>-0.3017078293509395</v>
       </c>
       <c r="F13" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.5368536386174515</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.4731773961295207</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1.319367280003567</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.007732342947784333</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1901,25 +1901,25 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-1.20289677362606</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7470432986101152</v>
+        <v>-0.4069742398415516</v>
       </c>
       <c r="W13" t="n">
-        <v>0.02178038869446279</v>
+        <v>-0.2577336912255136</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1411159918135424</v>
+        <v>-0.4316404040308374</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.278475063105918</v>
+        <v>-0.3859730688365928</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.01739180440702725</v>
+        <v>-0.1578122578836808</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.1761111935605618</v>
+        <v>-0.05492948205070335</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -1928,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.758339144491079</v>
+        <v>-0.5530631363798717</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -1937,13 +1937,13 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.02929996702690747</v>
+        <v>-0.4951685814116546</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.0407718873637366</v>
+        <v>-0.6253661547238057</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.06937894505824396</v>
+        <v>-0.2357325881094467</v>
       </c>
       <c r="AJ13" t="n">
         <v>-0.2315504637589359</v>
@@ -1952,35 +1952,35 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>0lGMiS5j</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.597121179823038</v>
+        <v>1.553966552409826</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.4605360890117971</v>
+        <v>-1.151675176605645</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.221164449715159</v>
+        <v>-0.5262724240217962</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8261836349998065</v>
+        <v>-1.219540489236457</v>
       </c>
       <c r="F14" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2701804913637576</v>
+        <v>3.563231626046985</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3788006650590997</v>
+        <v>2.42055582170351</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1960996420384249</v>
+        <v>1.319367280003567</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9828997477856625</v>
+        <v>0.007732342947784333</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2013,25 +2013,25 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.035545007824282</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.7156801716703117</v>
+        <v>0.946396512439005</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.4628997468732071</v>
+        <v>1.406952609504363</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.609266773695147</v>
+        <v>0.9973536054545717</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.2332007677117474</v>
+        <v>-0.3318953234215662</v>
       </c>
       <c r="Z14" t="n">
-        <v>-1.001715831986365</v>
+        <v>2.051758440586128</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.6961441913215439</v>
+        <v>0.1817644988205799</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.8260750267184558</v>
+        <v>1.635854460899387</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2049,13 +2049,13 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.4164280648772658</v>
+        <v>0.7268603238061314</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.5332983712014703</v>
+        <v>0.9999034849901334</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.5062073676043577</v>
+        <v>0.8073751223904762</v>
       </c>
       <c r="AJ14" t="n">
         <v>-0.2315504637589359</v>
@@ -2064,35 +2064,35 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>WvwvCQVo</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.553966552409826</v>
+        <v>-1.070523612399649</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.3371183947986099</v>
+        <v>-0.01623238984432331</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4931823275602075</v>
+        <v>-0.5759075687141793</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.8261836349998065</v>
+        <v>0.4995746515014962</v>
       </c>
       <c r="F15" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3350951061221493</v>
+        <v>-0.6736975563543621</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1080439413343977</v>
+        <v>-0.500511816657474</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5616338189825709</v>
+        <v>-0.9538331030594207</v>
       </c>
       <c r="J15" t="n">
-        <v>0.007732342947784333</v>
+        <v>-1.478215793152386</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2128,22 +2128,22 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.646740899264498</v>
+        <v>0.2133402970653561</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7387830244850578</v>
+        <v>-0.05092092992449319</v>
       </c>
       <c r="X15" t="n">
-        <v>1.128790339637771</v>
+        <v>-0.2095296175683644</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.2309545406728202</v>
+        <v>0.2644803130277159</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.201690378388217</v>
+        <v>-0.02602866477659794</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.05658045822621292</v>
+        <v>0.5682342763919547</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2152,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.78077151427174</v>
+        <v>-0.2255389235956398</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2161,13 +2161,13 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.339050158112247</v>
+        <v>0.04060692846246834</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.167223018514744</v>
+        <v>0.2637816176494433</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.335170873499355</v>
+        <v>0.07923821761217582</v>
       </c>
       <c r="AJ15" t="n">
         <v>-0.2315504637589359</v>
@@ -2176,35 +2176,35 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>joLV7EJU</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.7698007810152303</v>
+        <v>-1.425923322217599</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.6086373220676217</v>
+        <v>-0.4111690113265222</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8075382439453</v>
+        <v>-1.006078822714832</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06251148012744039</v>
+        <v>-1.219540489236457</v>
       </c>
       <c r="F16" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G16" t="n">
-        <v>2.352680431075172</v>
+        <v>-0.06842195886845531</v>
       </c>
       <c r="H16" t="n">
-        <v>2.542266973301885</v>
+        <v>-0.2570895134607253</v>
       </c>
       <c r="I16" t="n">
-        <v>1.319367280003567</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.988996524414678</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2237,25 +2237,25 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.9586950056663653</v>
       </c>
       <c r="V16" t="n">
-        <v>2.526594904738802</v>
+        <v>1.263192359968233</v>
       </c>
       <c r="W16" t="n">
-        <v>2.581113077206389</v>
+        <v>0.1235648608910351</v>
       </c>
       <c r="X16" t="n">
-        <v>1.567823620423898</v>
+        <v>1.396667627533591</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.910331993766164</v>
+        <v>-0.0855352413924725</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.625470065916655</v>
+        <v>0.2460594583282917</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.3696334551176731</v>
+        <v>0.04624521606416113</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.76435552879785</v>
+        <v>1.762715003807036</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2273,13 +2273,13 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.086133582948928</v>
+        <v>0.4394041631050383</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.583133040903918</v>
+        <v>0.6139755157047229</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.271044393369793</v>
+        <v>0.967889293284096</v>
       </c>
       <c r="AJ16" t="n">
         <v>-0.2315504637589359</v>
@@ -2288,20 +2288,20 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>M5TEBdK5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.499289673976295</v>
+        <v>-0.1410166790296269</v>
       </c>
       <c r="C17" t="n">
-        <v>-1.497244720402569</v>
+        <v>1.39072932418601</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3175250357487154</v>
+        <v>1.227502688442405</v>
       </c>
       <c r="E17" t="n">
-        <v>1.796195393244528</v>
+        <v>-0.5348081874171026</v>
       </c>
       <c r="F17" t="n">
         <v>-0.2141296999117111</v>
@@ -2310,13 +2310,13 @@
         <v>-0.2701804913637576</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2570895134607253</v>
+        <v>0.3514662445311464</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5616338189825709</v>
+        <v>-0.9538331030594207</v>
       </c>
       <c r="J17" t="n">
-        <v>0.998364433681231</v>
+        <v>-0.4875837024189391</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2349,25 +2349,25 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.123104581492723</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3249097269802574</v>
+        <v>0.455006777055964</v>
       </c>
       <c r="W17" t="n">
-        <v>0.06483960359767518</v>
+        <v>-0.04018400490677607</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.05341390711155759</v>
+        <v>-0.1821700236897043</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.3516884112795934</v>
+        <v>1.110276634241201</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.07382975853227154</v>
+        <v>-0.003032703881721578</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.9126370237160275</v>
+        <v>-0.9234196925934773</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2376,7 +2376,7 @@
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.7518369408646433</v>
+        <v>-0.1588384283195771</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2385,13 +2385,13 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.06269489081302528</v>
+        <v>0.2669919934518059</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.2297291497713185</v>
+        <v>-0.2325716384177039</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.01002428378412317</v>
+        <v>-0.2528306420824957</v>
       </c>
       <c r="AJ17" t="n">
         <v>-0.2315504637589359</v>
@@ -2400,35 +2400,35 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>CxyB0iT1</t>
+          <t>Sf88FVcc</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6517980582565688</v>
+        <v>0.597121179823038</v>
       </c>
       <c r="C18" t="n">
-        <v>1.39072932418601</v>
+        <v>-1.29977640966147</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8138764826725458</v>
+        <v>-0.327731845252264</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5348081874171026</v>
+        <v>-0.9573025864120233</v>
       </c>
       <c r="F18" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2701804913637576</v>
+        <v>-0.06842195886845531</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.01366721026397662</v>
+        <v>-0.500511816657474</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5616338189825709</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.007732342947784333</v>
+        <v>-0.4875837024189391</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2461,25 +2461,25 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9586950056663653</v>
+        <v>-0.5141889441802113</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.4872978369268575</v>
+        <v>-1.521990263942778</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.104405048785081</v>
+        <v>-0.7801827656546233</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6574521722189914</v>
+        <v>-0.9925466671576241</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.3490994343771882</v>
+        <v>-0.07054121725435759</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.1106763164885312</v>
+        <v>-1.172053986987562</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.0867032540654535</v>
+        <v>0.8905028914112498</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2488,7 +2488,7 @@
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.748638370424368</v>
+        <v>-1.582283233423837</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2497,13 +2497,13 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.2669919934518059</v>
+        <v>-1.194913083696065</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.02755616308562162</v>
+        <v>-1.098737498313536</v>
       </c>
       <c r="AI18" t="n">
-        <v>-0.6706268056623685</v>
+        <v>-1.462747093561621</v>
       </c>
       <c r="AJ18" t="n">
         <v>-0.2315504637589359</v>
@@ -2512,35 +2512,35 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>0IkylEqd</t>
+          <t>O2Fteteo</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1.425923322217599</v>
+        <v>1.854689383794245</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6008560812216125</v>
+        <v>0.230602998582051</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.006078822714832</v>
+        <v>-0.6751778580989453</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6161248305345778</v>
+        <v>1.504819945661825</v>
       </c>
       <c r="F19" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3350951061221493</v>
+        <v>-0.4719390238590598</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3514662445311464</v>
+        <v>-2.326179090633089</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5616338189825709</v>
+        <v>-0.1960996420384249</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4875837024189391</v>
+        <v>-0.9828997477856625</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2573,25 +2573,25 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5559680418311467</v>
+        <v>-1.603269985480944</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1756111687180477</v>
+        <v>-2.132966149893547</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.01460342319844615</v>
+        <v>-2.574698731588679</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1212470653569702</v>
+        <v>-1.689282418478465</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.6691498110728986</v>
+        <v>-0.4552406030609477</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.01065104159513782</v>
+        <v>-2.572944768437778</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.533662614916145</v>
+        <v>0.9006648628719022</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2600,7 +2600,7 @@
         <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.4269154012763712</v>
+        <v>-2.012657366604393</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2609,13 +2609,13 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.02929996702690747</v>
+        <v>-1.504157523932408</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.02755616308562162</v>
+        <v>-2.222048537453641</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.09904899425808969</v>
+        <v>-2.160543643785158</v>
       </c>
       <c r="AJ19" t="n">
         <v>-0.2315504637589359</v>
@@ -2624,35 +2624,35 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>4QCyHCDr</t>
+          <t>8KfYbJz0</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.7151239025816996</v>
+        <v>0.6517980582565688</v>
       </c>
       <c r="C20" t="n">
-        <v>1.316678707658098</v>
+        <v>0.6008560812216125</v>
       </c>
       <c r="D20" t="n">
-        <v>1.028962109672872</v>
+        <v>0.8138764826725458</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2142951950761283</v>
+        <v>0.6161248305345778</v>
       </c>
       <c r="F20" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.06842195886845531</v>
+        <v>-0.2701804913637576</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1080439413343977</v>
+        <v>-0.6222229682558483</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.5616338189825709</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.007732342947784333</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2685,25 +2685,25 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>-0.5977471394820821</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6944164915334855</v>
+        <v>-1.176475266666491</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.2329877339680262</v>
+        <v>-0.1149282657147683</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.9564534481786326</v>
+        <v>-0.8263310813372684</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.4211764476809285</v>
+        <v>-1.058799582792977</v>
       </c>
       <c r="Z20" t="n">
-        <v>-0.1945053637740942</v>
+        <v>-0.1400079350442462</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.1333123092186957</v>
+        <v>0.1123461872731252</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2712,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>-1.015624769804571</v>
+        <v>-0.6684093001572291</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2724,10 +2724,10 @@
         <v>-0.02929996702690747</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.1774593122464606</v>
+        <v>-0.02755616308562162</v>
       </c>
       <c r="AI20" t="n">
-        <v>-0.6133909909762525</v>
+        <v>-0.7170380667703563</v>
       </c>
       <c r="AJ20" t="n">
         <v>-0.2315504637589359</v>
@@ -2736,23 +2736,23 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>CEhO9e6F</t>
+          <t>8KIdPmPc</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.128073775961899</v>
+        <v>2.155412215178664</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.5592702443823468</v>
+        <v>-0.1396500840575105</v>
       </c>
       <c r="D21" t="n">
         <v>0.5160656145182476</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.190402944478186</v>
+        <v>1.767057848486258</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2141296999117111</v>
+        <v>4.670066788550652</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2797,25 +2797,25 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.160999988376106</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.912948782075621</v>
+        <v>1.942863280505861</v>
       </c>
       <c r="W21" t="n">
-        <v>0.02178038869446279</v>
+        <v>0.03635074945686407</v>
       </c>
       <c r="X21" t="n">
-        <v>0.1411159918135424</v>
+        <v>0.3562942689800624</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.761123722627791</v>
+        <v>2.132079193145781</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.1389598140927969</v>
+        <v>0.2092439518541639</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.114008639437619</v>
+        <v>1.286053360428063</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -2824,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.5737750336153633</v>
+        <v>0.848692770091745</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -2833,13 +2833,13 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.2821131411665878</v>
+        <v>0.3753691673777553</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.0407718873637366</v>
+        <v>-0.01282280050715345</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.06937894505824396</v>
+        <v>0.1645540158069977</v>
       </c>
       <c r="AJ21" t="n">
         <v>-0.2315504637589359</v>
@@ -2848,35 +2848,35 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>CSXdOfL8</t>
+          <t>fNwTkrUF</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.4144010711972805</v>
+        <v>-0.1410166790296269</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8230079308053494</v>
+        <v>-0.4111690113265222</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.254254546176747</v>
+        <v>1.227502688442405</v>
       </c>
       <c r="E22" t="n">
-        <v>1.577663807557501</v>
+        <v>-1.219540489236457</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2141296999117111</v>
+        <v>4.670066788550652</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3350951061221493</v>
+        <v>-0.06842195886845531</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7165996993262693</v>
+        <v>-0.500511816657474</v>
       </c>
       <c r="I22" t="n">
         <v>0.5616338189825709</v>
       </c>
       <c r="J22" t="n">
-        <v>0.998364433681231</v>
+        <v>0.007732342947784333</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2909,25 +2909,25 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3472294703751533</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0.943165398258195</v>
+        <v>1.20463287600261</v>
       </c>
       <c r="W22" t="n">
-        <v>0.06379830569613401</v>
+        <v>0.08746106225301788</v>
       </c>
       <c r="X22" t="n">
-        <v>1.468467825965679</v>
+        <v>0.9243716293686391</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.7522196821152132</v>
+        <v>0.2859921867514609</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.1474987387857741</v>
+        <v>0.2243461774859929</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.5462783751488575</v>
+        <v>-0.3178689284054995</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
         <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.856861683487586</v>
+        <v>1.257190244478226</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -2945,13 +2945,13 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.3691385168257603</v>
+        <v>0.4394041631050383</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.2599980101074296</v>
+        <v>0.4089600403726406</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.5315939413020802</v>
+        <v>0.5695983958355227</v>
       </c>
       <c r="AJ22" t="n">
         <v>-0.2315504637589359</v>
@@ -2960,26 +2960,26 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>CjGqFjre</t>
+          <t>42SH31wI</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.8791545378822918</v>
+        <v>2.155412215178664</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.01623238984432331</v>
+        <v>-0.7320550162808089</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4766372793294131</v>
+        <v>1.574948701289086</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4995746515014962</v>
+        <v>-0.2580015122135339</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2141296999117111</v>
+        <v>4.670066788550652</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.06842195886845531</v>
       </c>
       <c r="H23" t="n">
         <v>-0.01366721026397662</v>
@@ -3021,25 +3021,25 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.261505197936386</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.138337109907628</v>
+        <v>-0.5544241687168362</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.1947289342353713</v>
+        <v>0.03635074945686407</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.630948720531108</v>
+        <v>0.3562942689800624</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.2324295649547101</v>
+        <v>-2.675101897752685</v>
       </c>
       <c r="Z23" t="n">
-        <v>-0.2960408727739027</v>
+        <v>0.06091877559231133</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.5285208514507926</v>
+        <v>0.6329682010156911</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>-1.9683079369891</v>
+        <v>1.130634721605117</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3057,13 +3057,13 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>-0.4280972016694775</v>
+        <v>0.1517052712168554</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.3777500611409011</v>
+        <v>-0.01282280050715345</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.8258208796635773</v>
+        <v>0.1645540158069977</v>
       </c>
       <c r="AJ23" t="n">
         <v>-0.2315504637589359</v>
@@ -3072,35 +3072,35 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>Aeu0r0Mk</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.8791545378822918</v>
+        <v>1.089213085724815</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.29977640966147</v>
+        <v>1.020476241546449</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.204619401484364</v>
+        <v>1.260592784903993</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9573025864120233</v>
+        <v>1.082325546666904</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2141296999117111</v>
+        <v>4.670066788550652</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.077214621344967</v>
+        <v>-0.4719390238590598</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.08275678743634</v>
+        <v>0.3514662445311464</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>-0.1960996420384249</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.998364433681231</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3133,25 +3133,25 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1813447660086083</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.882021357839101</v>
+        <v>0.1175706276059488</v>
       </c>
       <c r="W24" t="n">
-        <v>-2.297277799801587</v>
+        <v>0.1882464447458413</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.011354300148683</v>
+        <v>1.003596850328274</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.3436263285092968</v>
+        <v>-1.606384556814209</v>
       </c>
       <c r="Z24" t="n">
-        <v>-2.539931677154327</v>
+        <v>0.1227199792320162</v>
       </c>
       <c r="AA24" t="n">
-        <v>-0.278927099856135</v>
+        <v>1.055149386203638</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3160,7 +3160,7 @@
         <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>-2.359657498051674</v>
+        <v>1.078627416905669</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3169,13 +3169,13 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>-1.03675152551541</v>
+        <v>-0.3255919275056208</v>
       </c>
       <c r="AH24" t="n">
-        <v>-1.370316439662529</v>
+        <v>-0.02755616308562162</v>
       </c>
       <c r="AI24" t="n">
-        <v>-2.270969892550095</v>
+        <v>0.7136834754346477</v>
       </c>
       <c r="AJ24" t="n">
         <v>-0.2315504637589359</v>
@@ -3184,35 +3184,35 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>ALOjHNNj</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.717997187710418</v>
+        <v>-0.03166292216256539</v>
       </c>
       <c r="C25" t="n">
-        <v>1.242628091130186</v>
+        <v>-0.4605360890117971</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.02992097709796582</v>
+        <v>1.012417061442078</v>
       </c>
       <c r="E25" t="n">
-        <v>1.082325546666904</v>
+        <v>-0.8261836349998065</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2141296999117111</v>
+        <v>4.670066788550652</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.489524348812083</v>
+        <v>0.5368536386174515</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.813023697026587</v>
+        <v>0.9600220025230181</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.711566564080417</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.9828997477856625</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3248,22 +3248,22 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.396982019742907</v>
+        <v>1.177959786161002</v>
       </c>
       <c r="W25" t="n">
-        <v>-1.061674350385209</v>
+        <v>0.9302535563236365</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.6334390267698649</v>
+        <v>1.88825254291683</v>
       </c>
       <c r="Y25" t="n">
-        <v>-0.4859054818021803</v>
+        <v>0.4626902076180301</v>
       </c>
       <c r="Z25" t="n">
-        <v>-1.611443012281618</v>
+        <v>0.510398252480795</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.3651564457104819</v>
+        <v>0.9696693265575431</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3272,7 +3272,7 @@
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>-1.344420187035706</v>
+        <v>0.7208807266009531</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3281,13 +3281,13 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>-1.708455691662727</v>
+        <v>0.5106542465537003</v>
       </c>
       <c r="AH25" t="n">
-        <v>-1.357809514731983</v>
+        <v>0.4113423117879823</v>
       </c>
       <c r="AI25" t="n">
-        <v>-1.007171657767268</v>
+        <v>1.696663556204947</v>
       </c>
       <c r="AJ25" t="n">
         <v>-0.2315504637589359</v>
@@ -3296,26 +3296,26 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>4CX22Dbk</t>
+          <t>ILr8tvi2</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1410166790296269</v>
+        <v>-0.03166292216256539</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.509903166697072</v>
+        <v>0.8230079308053494</v>
       </c>
       <c r="D26" t="n">
-        <v>1.47567841190432</v>
+        <v>1.376408122519553</v>
       </c>
       <c r="E26" t="n">
-        <v>0.09164902488571078</v>
+        <v>1.577663807557501</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2141296999117111</v>
+        <v>4.670066788550652</v>
       </c>
       <c r="G26" t="n">
-        <v>0.133336573626847</v>
+        <v>-0.06842195886845531</v>
       </c>
       <c r="H26" t="n">
         <v>-0.01366721026397662</v>
@@ -3360,22 +3360,22 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.2071314549786354</v>
+        <v>-0.4006449769997932</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.02303588490830924</v>
+        <v>-0.1084034489494817</v>
       </c>
       <c r="X26" t="n">
-        <v>0.147991270140276</v>
+        <v>0.4342106119390501</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.2264610288395323</v>
+        <v>-0.8631423029723791</v>
       </c>
       <c r="Z26" t="n">
-        <v>-0.05439035812966277</v>
+        <v>-0.06901569115554196</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.892815678430225</v>
+        <v>0.2160052034840917</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.07035333128689646</v>
+        <v>0.619162785672667</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3393,13 +3393,13 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.02929996702690747</v>
+        <v>-0.2789816416917733</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.02755616308562162</v>
+        <v>0.1592886538039505</v>
       </c>
       <c r="AI26" t="n">
-        <v>-0.1453120106290587</v>
+        <v>-0.6489724310834457</v>
       </c>
       <c r="AJ26" t="n">
         <v>-0.2315504637589359</v>
@@ -3408,35 +3408,35 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>EirZ0Wr4</t>
+          <t>bepKi4a3</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.03166292216256539</v>
+        <v>0.6517980582565688</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.9295233270219083</v>
+        <v>-1.29977640966147</v>
       </c>
       <c r="D27" t="n">
-        <v>1.376408122519553</v>
+        <v>0.8138764826725458</v>
       </c>
       <c r="E27" t="n">
-        <v>1.796195393244528</v>
+        <v>-0.9573025864120233</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.2141296999117111</v>
+        <v>4.670066788550652</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.4719390238590598</v>
+        <v>0.940370703608056</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1080439413343977</v>
+        <v>0.4731773961295207</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>0.5616338189825709</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.007732342947784333</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3472,22 +3472,22 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.480014227958506</v>
+        <v>-0.1127205818069059</v>
       </c>
       <c r="W27" t="n">
-        <v>2.049241576318867</v>
+        <v>0.01017074886459737</v>
       </c>
       <c r="X27" t="n">
-        <v>2.483729165200385</v>
+        <v>0.204011854509081</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.6569179793766032</v>
+        <v>-0.2477840105017706</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.714220339141191</v>
+        <v>0.001413939479967772</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.277950916541772</v>
+        <v>1.005357316828769</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3496,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.370025212782653</v>
+        <v>-0.03941692523883295</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3505,13 +3505,13 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.303736280892403</v>
+        <v>0.2593629788982363</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.38373723528624</v>
+        <v>0.09604168328683022</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.944412391769952</v>
+        <v>-0.1552674394673403</v>
       </c>
       <c r="AJ27" t="n">
         <v>-0.2315504637589359</v>
@@ -3520,35 +3520,35 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>t4ZkclrT</t>
+          <t>6sP22LDL</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.597121179823038</v>
+        <v>1.553966552409826</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.7320550162808089</v>
+        <v>0.6008560812216125</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.221164449715159</v>
+        <v>-0.4931823275602075</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2580015122135339</v>
+        <v>0.6161248305345778</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2141296999117111</v>
+        <v>4.670066788550652</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.8754560888496645</v>
+        <v>-0.06842195886845531</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.865645271452597</v>
+        <v>0.1080439413343977</v>
       </c>
       <c r="I28" t="n">
         <v>-0.1960996420384249</v>
       </c>
       <c r="J28" t="n">
-        <v>0.007732342947784333</v>
+        <v>-0.4875837024189391</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -3584,22 +3584,22 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>-1.660407798980844</v>
+        <v>-0.8983910205806742</v>
       </c>
       <c r="W28" t="n">
-        <v>-1.104602795757691</v>
+        <v>-0.1381903243726107</v>
       </c>
       <c r="X28" t="n">
-        <v>-0.9850028903877913</v>
+        <v>-0.8490903895195151</v>
       </c>
       <c r="Y28" t="n">
-        <v>-1.067540651679185</v>
+        <v>-1.087534171921025</v>
       </c>
       <c r="Z28" t="n">
-        <v>-1.408864141659888</v>
+        <v>-0.0868461203156254</v>
       </c>
       <c r="AA28" t="n">
-        <v>-1.20842897188778</v>
+        <v>0.05459975861799665</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
         <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>-1.142714915799211</v>
+        <v>-0.3985588336643339</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3617,13 +3617,13 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.7753770402141107</v>
+        <v>-0.1152259044820542</v>
       </c>
       <c r="AH28" t="n">
-        <v>-0.9721968460750741</v>
+        <v>-0.02755616308562162</v>
       </c>
       <c r="AI28" t="n">
-        <v>-1.399920436458068</v>
+        <v>-0.6385007948239155</v>
       </c>
       <c r="AJ28" t="n">
         <v>-0.2315504637589359</v>
@@ -3632,35 +3632,35 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>YH892O2B</t>
+          <t>dC3sew6e</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.296398348438619</v>
+        <v>-1.425923322217599</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1396500840575105</v>
+        <v>-1.349143487346745</v>
       </c>
       <c r="D29" t="n">
-        <v>1.624583845981469</v>
+        <v>-0.5759075687141793</v>
       </c>
       <c r="E29" t="n">
-        <v>1.767057848486258</v>
+        <v>-0.2580015122135339</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2141296999117111</v>
+        <v>4.670066788550652</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.4719390238590598</v>
+        <v>-0.2701804913637576</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.595912181042843</v>
+        <v>-0.01366721026397662</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.711566564080417</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.973531838519109</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3696,22 +3696,22 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>-1.48190451266272</v>
+        <v>2.618805440855269</v>
       </c>
       <c r="W29" t="n">
-        <v>-1.427055129134087</v>
+        <v>2.646657023716149</v>
       </c>
       <c r="X29" t="n">
-        <v>-1.161010512904795</v>
+        <v>2.796514964736973</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.2703477816712605</v>
+        <v>-0.01134820652165304</v>
       </c>
       <c r="Z29" t="n">
-        <v>-1.819969935263194</v>
+        <v>1.83291317754004</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.06486224463853184</v>
+        <v>-0.9541355638686089</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>-1.709549235870077</v>
+        <v>2.552125223824961</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3729,13 +3729,13 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>-1.956509980354264</v>
+        <v>1.226102512401802</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1.778105252524019</v>
+        <v>1.332020147011346</v>
       </c>
       <c r="AI29" t="n">
-        <v>-1.462810302633607</v>
+        <v>2.900891191205055</v>
       </c>
       <c r="AJ29" t="n">
         <v>-0.2315504637589359</v>
@@ -3744,35 +3744,35 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>8jyraADG</t>
+          <t>Ob5Zdayq</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.553966552409826</v>
+        <v>2.155412215178664</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.09028300637223562</v>
+        <v>-1.719396569986306</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4931823275602075</v>
+        <v>-0.757903099252917</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0188051629900348</v>
+        <v>-0.3017078293509395</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2141296999117111</v>
+        <v>4.670066788550652</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5368536386174515</v>
+        <v>-0.2701804913637576</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4731773961295207</v>
+        <v>0.229755092932772</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5616338189825709</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.998364433681231</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3808,22 +3808,22 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>2.035265682544726</v>
+        <v>0.8914627309582801</v>
       </c>
       <c r="W30" t="n">
-        <v>1.18566836958129</v>
+        <v>0.2253851834221207</v>
       </c>
       <c r="X30" t="n">
-        <v>1.19652349350994</v>
+        <v>1.322348225029655</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.2113039822996117</v>
+        <v>-0.377370950827492</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.742507919918558</v>
+        <v>0.2114579763072699</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.08395498462488175</v>
+        <v>1.008738733161378</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -3832,7 +3832,7 @@
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.898704137276361</v>
+        <v>1.163382599171247</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -3841,13 +3841,13 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.769432546966023</v>
+        <v>0.2930177261163261</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.378369339401016</v>
+        <v>0.04811598775465516</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.609470591963001</v>
+        <v>1.04842291842086</v>
       </c>
       <c r="AJ30" t="n">
         <v>-0.2315504637589359</v>
@@ -3856,35 +3856,35 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>tYhtcc5C</t>
+          <t>bs5ow5pA</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.717997187710418</v>
+        <v>2.155412215178664</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.682687938595534</v>
+        <v>-0.5592702443823468</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.278096700559881</v>
+        <v>1.47567841190432</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3247493829518739</v>
+        <v>-1.190402944478186</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2141296999117111</v>
+        <v>4.670066788550652</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-1.077214621344967</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>-0.9873564230509713</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>-0.9538331030594207</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.007732342947784333</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -3920,22 +3920,22 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>-1.138706687041078</v>
+        <v>1.142625408539304</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3398936798803136</v>
+        <v>0.02442504020807</v>
       </c>
       <c r="X31" t="n">
-        <v>-1.718682740598389</v>
+        <v>0.5904419060151738</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.7608349388679183</v>
+        <v>1.034051777963044</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.3764350441432474</v>
+        <v>0.07969115522664978</v>
       </c>
       <c r="AA31" t="n">
-        <v>-2.001951945238825</v>
+        <v>2.64122546404309</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>-1.844043855576376</v>
+        <v>0.9119287306597392</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -3953,13 +3953,13 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.3515811004480734</v>
+        <v>0.2821131411665878</v>
       </c>
       <c r="AH31" t="n">
-        <v>-0.4286185625390873</v>
+        <v>0.1348867207181722</v>
       </c>
       <c r="AI31" t="n">
-        <v>-1.306557476676585</v>
+        <v>0.3242745060850748</v>
       </c>
       <c r="AJ31" t="n">
         <v>-0.2315504637589359</v>
@@ -3968,23 +3968,23 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>IXMN9zkI</t>
+          <t>AZ3PVMxp</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.128073775961899</v>
+        <v>-1.015846733966119</v>
       </c>
       <c r="C32" t="n">
-        <v>-1.225725793133557</v>
+        <v>-1.497244720402569</v>
       </c>
       <c r="D32" t="n">
-        <v>1.574948701289086</v>
+        <v>0.03625921582521156</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.9573025864120233</v>
+        <v>1.796195393244528</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.2141296999117111</v>
+        <v>4.670066788550652</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -4032,22 +4032,22 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>-1.411440131761689</v>
+        <v>1.43211093703882</v>
       </c>
       <c r="W32" t="n">
-        <v>0.02178038869446279</v>
+        <v>0.4732273239770604</v>
       </c>
       <c r="X32" t="n">
-        <v>0.1411159918135424</v>
+        <v>1.804254093189493</v>
       </c>
       <c r="Y32" t="n">
-        <v>-1.337269275758721</v>
+        <v>0.2273263697291655</v>
       </c>
       <c r="Z32" t="n">
-        <v>-0.1263623523186772</v>
+        <v>0.3631928674725773</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.3116548200461625</v>
+        <v>-1.012672886904112</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
@@ -4056,7 +4056,7 @@
         <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.6154110541653083</v>
+        <v>2.140253700100303</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4065,13 +4065,13 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.02929996702690747</v>
+        <v>0.6889794450116975</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.0407718873637366</v>
+        <v>0.3545881986577743</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.06937894505824396</v>
+        <v>1.158311890073888</v>
       </c>
       <c r="AJ32" t="n">
         <v>-0.2315504637589359</v>
@@ -4080,35 +4080,35 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>lvG7DIkg</t>
+          <t>hvcjgHz8</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.043185173182884</v>
+        <v>-0.8791545378822918</v>
       </c>
       <c r="C33" t="n">
-        <v>1.020476241546449</v>
+        <v>0.230602998582051</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8800566755957232</v>
+        <v>-1.254254546176747</v>
       </c>
       <c r="E33" t="n">
-        <v>1.082325546666904</v>
+        <v>1.504819945661825</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.2141296999117111</v>
+        <v>4.670066788550652</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.4719390238590598</v>
+        <v>-0.06842195886845531</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.01366721026397662</v>
+        <v>0.594888547727895</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>0.5616338189825709</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.5030483883145077</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -4141,25 +4141,25 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>-1.173592561470896</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>-0.293440251859717</v>
+        <v>1.2912577468473</v>
       </c>
       <c r="W33" t="n">
-        <v>0.1249831791318199</v>
+        <v>0.3701473247622408</v>
       </c>
       <c r="X33" t="n">
-        <v>0.2012274710612565</v>
+        <v>2.044368253373634</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.7240660044614737</v>
+        <v>0.1422359270086119</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.005673451698010646</v>
+        <v>0.2647457881977981</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.3271800473278521</v>
+        <v>0.8528723272599358</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.1166278236623983</v>
+        <v>1.529689198370042</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4177,13 +4177,13 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.4277384508795752</v>
+        <v>0.792281264287191</v>
       </c>
       <c r="AH33" t="n">
-        <v>-0.3151103362786727</v>
+        <v>0.3886406665358992</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.5351020447974798</v>
+        <v>1.548754327750485</v>
       </c>
       <c r="AJ33" t="n">
         <v>-0.2315504637589359</v>
@@ -4192,35 +4192,35 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>SORbFvLt</t>
+          <t>dnnqk0iD</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.553966552409826</v>
+        <v>2.155412215178664</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9957927027038115</v>
+        <v>1.242628091130186</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6420877616373566</v>
+        <v>-1.138439208561187</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7679085454832657</v>
+        <v>1.082325546666904</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.2141296999117111</v>
+        <v>4.670066788550652</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.2701804913637576</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.1353783618623509</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.711566564080417</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.973531838519109</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -4256,22 +4256,22 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>-0.7779153569613199</v>
+        <v>0.7562452131781391</v>
       </c>
       <c r="W34" t="n">
-        <v>-0.06988428184731134</v>
+        <v>0.03635074945686407</v>
       </c>
       <c r="X34" t="n">
-        <v>-0.3203965028518937</v>
+        <v>0.3562942689800624</v>
       </c>
       <c r="Y34" t="n">
-        <v>-1.575390902013991</v>
+        <v>-1.053668086583754</v>
       </c>
       <c r="Z34" t="n">
-        <v>-0.1013403979025525</v>
+        <v>0.2159939167764675</v>
       </c>
       <c r="AA34" t="n">
-        <v>-1.270209941763065</v>
+        <v>0.09259956739564955</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -4280,7 +4280,7 @@
         <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.07117900723874863</v>
+        <v>1.462972437530633</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4289,13 +4289,13 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.3407130752204027</v>
+        <v>0.1762027597853505</v>
       </c>
       <c r="AH34" t="n">
-        <v>-0.1899990468894154</v>
+        <v>-0.01282280050715345</v>
       </c>
       <c r="AI34" t="n">
-        <v>-0.3080500873721655</v>
+        <v>0.1645540158069977</v>
       </c>
       <c r="AJ34" t="n">
         <v>-0.2315504637589359</v>
@@ -4304,35 +4304,35 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>4xHh663n</t>
+          <t>QT6wuRFc</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7151239025816996</v>
+        <v>1.061874646508049</v>
       </c>
       <c r="C35" t="n">
-        <v>-1.694713031143669</v>
+        <v>-0.3124348559559725</v>
       </c>
       <c r="D35" t="n">
-        <v>1.177867543750021</v>
+        <v>-1.006078822714832</v>
       </c>
       <c r="E35" t="n">
-        <v>1.504819945661825</v>
+        <v>0.0188051629900348</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2141296999117111</v>
+        <v>4.670066788550652</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.4719390238590598</v>
+        <v>0.5368536386174515</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9873564230509713</v>
+        <v>0.4731773961295207</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5616338189825709</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0.5030483883145077</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -4368,22 +4368,22 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0.1171493171995293</v>
+        <v>1.437848932297861</v>
       </c>
       <c r="W35" t="n">
-        <v>0.4228005557273165</v>
+        <v>0.2871464872417239</v>
       </c>
       <c r="X35" t="n">
-        <v>0.4935358501618273</v>
+        <v>1.579675985576559</v>
       </c>
       <c r="Y35" t="n">
-        <v>-1.069434646804812</v>
+        <v>-0.3702392052882559</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.4627263354724778</v>
+        <v>0.3453156257871962</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.6446907035388298</v>
+        <v>0.5009044491737638</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -4392,7 +4392,7 @@
         <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.8872439403035828</v>
+        <v>2.094204147349657</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -4401,2703 +4401,15 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.2867362320972082</v>
+        <v>0.2929811663942584</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.4012526916759462</v>
+        <v>0.3735062363678441</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.2961717526787244</v>
+        <v>1.373628326382051</v>
       </c>
       <c r="AJ35" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>6RvR2hEi</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>-0.7698007810152303</v>
-      </c>
-      <c r="C36" t="n">
-        <v>1.143893935759636</v>
-      </c>
-      <c r="D36" t="n">
-        <v>-1.370069883792308</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.06251148012744039</v>
-      </c>
-      <c r="F36" t="n">
-        <v>-0.2141296999117111</v>
-      </c>
-      <c r="G36" t="n">
-        <v>-1.480731686335571</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-1.961045635837966</v>
-      </c>
-      <c r="I36" t="n">
-        <v>-2.469300025101413</v>
-      </c>
-      <c r="J36" t="n">
-        <v>-1.973531838519109</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>-1.218175571911212</v>
-      </c>
-      <c r="W36" t="n">
-        <v>-2.436094929098569</v>
-      </c>
-      <c r="X36" t="n">
-        <v>-1.45456408211869</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>-0.3262620592130539</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>-1.588366367192901</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0.6807868660792538</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>-1.025545322652089</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>-1.182402542301783</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>-1.160116020661759</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>-1.742984514225241</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>4.318713008673075</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>hKOA02XN</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>-1.207215808483476</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-1.719396569986306</v>
-      </c>
-      <c r="D37" t="n">
-        <v>-1.469340173177074</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-0.3017078293509395</v>
-      </c>
-      <c r="F37" t="n">
-        <v>-0.2141296999117111</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.5368536386174515</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.4731773961295207</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1.319367280003567</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.007732342947784333</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>-1.20289677362606</v>
-      </c>
-      <c r="V37" t="n">
-        <v>-0.4069742398415516</v>
-      </c>
-      <c r="W37" t="n">
-        <v>-0.2577336912255136</v>
-      </c>
-      <c r="X37" t="n">
-        <v>-0.4316404040308374</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>-0.3859730688365928</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>-0.1578122578836808</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>-0.05492948205070335</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>-0.5530631363798717</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>-0.4951685814116546</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>-0.6253661547238057</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>-0.2357325881094467</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>0lGMiS5j</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>1.553966552409826</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-1.151675176605645</v>
-      </c>
-      <c r="D38" t="n">
-        <v>-0.5262724240217962</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-1.219540489236457</v>
-      </c>
-      <c r="F38" t="n">
-        <v>-0.2141296999117111</v>
-      </c>
-      <c r="G38" t="n">
-        <v>3.563231626046985</v>
-      </c>
-      <c r="H38" t="n">
-        <v>2.42055582170351</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1.319367280003567</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.007732342947784333</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0.946396512439005</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.406952609504363</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0.9973536054545717</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>-0.3318953234215662</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.051758440586128</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0.1817644988205799</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.635854460899387</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.7268603238061314</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0.9999034849901334</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0.8073751223904762</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>M5TEBdK5</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>-0.1410166790296269</v>
-      </c>
-      <c r="C39" t="n">
-        <v>1.39072932418601</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1.227502688442405</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-0.5348081874171026</v>
-      </c>
-      <c r="F39" t="n">
-        <v>-0.2141296999117111</v>
-      </c>
-      <c r="G39" t="n">
-        <v>-0.2701804913637576</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.3514662445311464</v>
-      </c>
-      <c r="I39" t="n">
-        <v>-0.9538331030594207</v>
-      </c>
-      <c r="J39" t="n">
-        <v>-0.4875837024189391</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0.455006777055964</v>
-      </c>
-      <c r="W39" t="n">
-        <v>-0.04018400490677607</v>
-      </c>
-      <c r="X39" t="n">
-        <v>-0.1821700236897043</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.110276634241201</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>-0.003032703881721578</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>-0.9234196925934773</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>-0.1588384283195771</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0.2669919934518059</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>-0.2325716384177039</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>-0.2528306420824957</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>joLV7EJU</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>-1.425923322217599</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-0.4111690113265222</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-1.006078822714832</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-1.219540489236457</v>
-      </c>
-      <c r="F40" t="n">
-        <v>-0.2141296999117111</v>
-      </c>
-      <c r="G40" t="n">
-        <v>-0.06842195886845531</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-0.2570895134607253</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>-0.9586950056663653</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.263192359968233</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0.1235648608910351</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.396667627533591</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>-0.0855352413924725</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0.2460594583282917</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0.04624521606416113</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.762715003807036</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0.4394041631050383</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0.6139755157047229</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0.967889293284096</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>WvwvCQVo</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>-1.070523612399649</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.01623238984432331</v>
-      </c>
-      <c r="D41" t="n">
-        <v>-0.5759075687141793</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.4995746515014962</v>
-      </c>
-      <c r="F41" t="n">
-        <v>-0.2141296999117111</v>
-      </c>
-      <c r="G41" t="n">
-        <v>-0.6736975563543621</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-0.500511816657474</v>
-      </c>
-      <c r="I41" t="n">
-        <v>-0.9538331030594207</v>
-      </c>
-      <c r="J41" t="n">
-        <v>-1.478215793152386</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0.2133402970653561</v>
-      </c>
-      <c r="W41" t="n">
-        <v>-0.05092092992449319</v>
-      </c>
-      <c r="X41" t="n">
-        <v>-0.2095296175683644</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>0.2644803130277159</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>-0.02602866477659794</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0.5682342763919547</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>-0.2255389235956398</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0.04060692846246834</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0.2637816176494433</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0.07923821761217582</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>O2Fteteo</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>1.854689383794245</v>
-      </c>
-      <c r="C42" t="n">
-        <v>0.230602998582051</v>
-      </c>
-      <c r="D42" t="n">
-        <v>-0.6751778580989453</v>
-      </c>
-      <c r="E42" t="n">
-        <v>1.504819945661825</v>
-      </c>
-      <c r="F42" t="n">
-        <v>-0.2141296999117111</v>
-      </c>
-      <c r="G42" t="n">
-        <v>-0.4719390238590598</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-2.326179090633089</v>
-      </c>
-      <c r="I42" t="n">
-        <v>-0.1960996420384249</v>
-      </c>
-      <c r="J42" t="n">
-        <v>-0.9828997477856625</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>-1.603269985480944</v>
-      </c>
-      <c r="V42" t="n">
-        <v>-2.132966149893547</v>
-      </c>
-      <c r="W42" t="n">
-        <v>-2.574698731588679</v>
-      </c>
-      <c r="X42" t="n">
-        <v>-1.689282418478465</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>-0.4552406030609477</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>-2.572944768437778</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0.9006648628719022</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>-2.012657366604393</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>-1.504157523932408</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>-2.222048537453641</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>-2.160543643785158</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>Sf88FVcc</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>0.597121179823038</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-1.29977640966147</v>
-      </c>
-      <c r="D43" t="n">
-        <v>-0.327731845252264</v>
-      </c>
-      <c r="E43" t="n">
-        <v>-0.9573025864120233</v>
-      </c>
-      <c r="F43" t="n">
-        <v>-0.2141296999117111</v>
-      </c>
-      <c r="G43" t="n">
-        <v>-0.06842195886845531</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-0.500511816657474</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>-0.4875837024189391</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>-0.5141889441802113</v>
-      </c>
-      <c r="V43" t="n">
-        <v>-1.521990263942778</v>
-      </c>
-      <c r="W43" t="n">
-        <v>-0.7801827656546233</v>
-      </c>
-      <c r="X43" t="n">
-        <v>-0.9925466671576241</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>-0.07054121725435759</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>-1.172053986987562</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0.8905028914112498</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>-1.582283233423837</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>-1.194913083696065</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>-1.098737498313536</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>-1.462747093561621</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>8KfYbJz0</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>0.6517980582565688</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0.6008560812216125</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0.8138764826725458</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0.6161248305345778</v>
-      </c>
-      <c r="F44" t="n">
-        <v>-0.2141296999117111</v>
-      </c>
-      <c r="G44" t="n">
-        <v>-0.2701804913637576</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-0.6222229682558483</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.5616338189825709</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.007732342947784333</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>-0.5977471394820821</v>
-      </c>
-      <c r="V44" t="n">
-        <v>-1.176475266666491</v>
-      </c>
-      <c r="W44" t="n">
-        <v>-0.1149282657147683</v>
-      </c>
-      <c r="X44" t="n">
-        <v>-0.8263310813372684</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>-1.058799582792977</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>-0.1400079350442462</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0.1123461872731252</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>-0.6684093001572291</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>-0.02929996702690747</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>-0.02755616308562162</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>-0.7170380667703563</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>8KIdPmPc</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>2.128073775961899</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.1396500840575105</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0.5160656145182476</v>
-      </c>
-      <c r="E45" t="n">
-        <v>1.767057848486258</v>
-      </c>
-      <c r="F45" t="n">
-        <v>4.670066788550652</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.942863280505861</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0.02178038869446279</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0.1411159918135424</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>2.132079193145781</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0.2092439518541639</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>1.286053360428063</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0.848692770091745</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0.3753691673777553</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0.0407718873637366</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0.06937894505824396</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>fNwTkrUF</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>-0.1410166790296269</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-0.4111690113265222</v>
-      </c>
-      <c r="D46" t="n">
-        <v>1.227502688442405</v>
-      </c>
-      <c r="E46" t="n">
-        <v>-1.219540489236457</v>
-      </c>
-      <c r="F46" t="n">
-        <v>4.670066788550652</v>
-      </c>
-      <c r="G46" t="n">
-        <v>-0.06842195886845531</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-0.500511816657474</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.5616338189825709</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.007732342947784333</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.20463287600261</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0.08746106225301788</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0.9243716293686391</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0.2859921867514609</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0.2243461774859929</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>-0.3178689284054995</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.257190244478226</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0.4394041631050383</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0.4089600403726406</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0.5695983958355227</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>42SH31wI</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>2.128073775961899</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-0.7320550162808089</v>
-      </c>
-      <c r="D47" t="n">
-        <v>1.574948701289086</v>
-      </c>
-      <c r="E47" t="n">
-        <v>-0.2580015122135339</v>
-      </c>
-      <c r="F47" t="n">
-        <v>4.670066788550652</v>
-      </c>
-      <c r="G47" t="n">
-        <v>-0.06842195886845531</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-0.01366721026397662</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>-0.5544241687168362</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0.02178038869446279</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0.1411159918135424</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>-2.675101897752685</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>0.06091877559231133</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0.6329682010156911</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.130634721605117</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0.1517052712168554</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>0.0407718873637366</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0.06937894505824396</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>Aeu0r0Mk</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>1.089213085724815</v>
-      </c>
-      <c r="C48" t="n">
-        <v>1.020476241546449</v>
-      </c>
-      <c r="D48" t="n">
-        <v>1.260592784903993</v>
-      </c>
-      <c r="E48" t="n">
-        <v>1.082325546666904</v>
-      </c>
-      <c r="F48" t="n">
-        <v>4.670066788550652</v>
-      </c>
-      <c r="G48" t="n">
-        <v>-0.4719390238590598</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.3514662445311464</v>
-      </c>
-      <c r="I48" t="n">
-        <v>-0.1960996420384249</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.998364433681231</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0.1175706276059488</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0.1882464447458413</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.003596850328274</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>-1.606384556814209</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0.1227199792320162</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.055149386203638</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.078627416905669</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>-0.3255919275056208</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>-0.02755616308562162</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0.7136834754346477</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>ALOjHNNj</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>-0.03166292216256539</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.4605360890117971</v>
-      </c>
-      <c r="D49" t="n">
-        <v>1.012417061442078</v>
-      </c>
-      <c r="E49" t="n">
-        <v>-0.8261836349998065</v>
-      </c>
-      <c r="F49" t="n">
-        <v>4.670066788550652</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0.5368536386174515</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.9600220025230181</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.177959786161002</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0.9302535563236365</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.88825254291683</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0.4626902076180301</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0.510398252480795</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0.9696693265575431</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0.7208807266009531</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0.5106542465537003</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0.4113423117879823</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>1.696663556204947</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>ILr8tvi2</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>-0.03166292216256539</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0.8230079308053494</v>
-      </c>
-      <c r="D50" t="n">
-        <v>1.376408122519553</v>
-      </c>
-      <c r="E50" t="n">
-        <v>1.577663807557501</v>
-      </c>
-      <c r="F50" t="n">
-        <v>4.670066788550652</v>
-      </c>
-      <c r="G50" t="n">
-        <v>-0.06842195886845531</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-0.01366721026397662</v>
-      </c>
-      <c r="I50" t="n">
-        <v>-0.1960996420384249</v>
-      </c>
-      <c r="J50" t="n">
-        <v>-0.4875837024189391</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>-0.4006449769997932</v>
-      </c>
-      <c r="W50" t="n">
-        <v>-0.1084034489494817</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0.4342106119390501</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>-0.8631423029723791</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>-0.06901569115554196</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0.2160052034840917</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0.619162785672667</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>-0.2789816416917733</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0.1592886538039505</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>-0.6489724310834457</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>bepKi4a3</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>0.6517980582565688</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-1.29977640966147</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.8138764826725458</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-0.9573025864120233</v>
-      </c>
-      <c r="F51" t="n">
-        <v>4.670066788550652</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.940370703608056</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.4731773961295207</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.5616338189825709</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0.007732342947784333</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>-0.1127205818069059</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0.01017074886459737</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0.204011854509081</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>-0.2477840105017706</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0.001413939479967772</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>1.005357316828769</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>-0.03941692523883295</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0.2593629788982363</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0.09604168328683022</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>-0.1552674394673403</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>6sP22LDL</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>1.553966552409826</v>
-      </c>
-      <c r="C52" t="n">
-        <v>0.6008560812216125</v>
-      </c>
-      <c r="D52" t="n">
-        <v>-0.4931823275602075</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.6161248305345778</v>
-      </c>
-      <c r="F52" t="n">
-        <v>4.670066788550652</v>
-      </c>
-      <c r="G52" t="n">
-        <v>-0.06842195886845531</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.1080439413343977</v>
-      </c>
-      <c r="I52" t="n">
-        <v>-0.1960996420384249</v>
-      </c>
-      <c r="J52" t="n">
-        <v>-0.4875837024189391</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" t="n">
-        <v>-0.8983910205806742</v>
-      </c>
-      <c r="W52" t="n">
-        <v>-0.1381903243726107</v>
-      </c>
-      <c r="X52" t="n">
-        <v>-0.8490903895195151</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>-1.087534171921025</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>-0.0868461203156254</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0.05459975861799665</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>-0.3985588336643339</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>-0.1152259044820542</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>-0.02755616308562162</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>-0.6385007948239155</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>dC3sew6e</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>-1.070523612399649</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-1.349143487346745</v>
-      </c>
-      <c r="D53" t="n">
-        <v>-0.5759075687141793</v>
-      </c>
-      <c r="E53" t="n">
-        <v>-0.2580015122135339</v>
-      </c>
-      <c r="F53" t="n">
-        <v>4.670066788550652</v>
-      </c>
-      <c r="G53" t="n">
-        <v>-0.2701804913637576</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-0.01366721026397662</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>2.618805440855269</v>
-      </c>
-      <c r="W53" t="n">
-        <v>2.646657023716149</v>
-      </c>
-      <c r="X53" t="n">
-        <v>2.796514964736973</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>-0.01134820652165304</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>1.83291317754004</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>-0.9541355638686089</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>2.552125223824961</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.226102512401802</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.332020147011346</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>2.900891191205055</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>Ob5Zdayq</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>0.1323677131380268</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-1.719396569986306</v>
-      </c>
-      <c r="D54" t="n">
-        <v>-0.757903099252917</v>
-      </c>
-      <c r="E54" t="n">
-        <v>-0.3017078293509395</v>
-      </c>
-      <c r="F54" t="n">
-        <v>4.670066788550652</v>
-      </c>
-      <c r="G54" t="n">
-        <v>-0.2701804913637576</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.229755092932772</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0.8914627309582801</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0.2253851834221207</v>
-      </c>
-      <c r="X54" t="n">
-        <v>1.322348225029655</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>-0.377370950827492</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0.2114579763072699</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>1.008738733161378</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>1.163382599171247</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>0.2930177261163261</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>0.04811598775465516</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>1.04842291842086</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>bs5ow5pA</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>-0.1410166790296269</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-0.5592702443823468</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1.47567841190432</v>
-      </c>
-      <c r="E55" t="n">
-        <v>-1.190402944478186</v>
-      </c>
-      <c r="F55" t="n">
-        <v>4.670066788550652</v>
-      </c>
-      <c r="G55" t="n">
-        <v>-1.077214621344967</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-0.9873564230509713</v>
-      </c>
-      <c r="I55" t="n">
-        <v>-0.9538331030594207</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0.007732342947784333</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.142625408539304</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0.02442504020807</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0.5904419060151738</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.034051777963044</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>0.07969115522664978</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>2.64122546404309</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0.9119287306597392</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>0.2821131411665878</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>0.1348867207181722</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>0.3242745060850748</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>AZ3PVMxp</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>-1.207215808483476</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-1.497244720402569</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0.03625921582521156</v>
-      </c>
-      <c r="E56" t="n">
-        <v>1.796195393244528</v>
-      </c>
-      <c r="F56" t="n">
-        <v>4.670066788550652</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.43211093703882</v>
-      </c>
-      <c r="W56" t="n">
-        <v>0.4732273239770604</v>
-      </c>
-      <c r="X56" t="n">
-        <v>1.804254093189493</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>0.2273263697291655</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>0.3631928674725773</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>-1.012672886904112</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>2.140253700100303</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>0.6889794450116975</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>0.3545881986577743</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>1.158311890073888</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>hvcjgHz8</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>-0.4144010711972805</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0.230602998582051</v>
-      </c>
-      <c r="D57" t="n">
-        <v>-1.254254546176747</v>
-      </c>
-      <c r="E57" t="n">
-        <v>1.504819945661825</v>
-      </c>
-      <c r="F57" t="n">
-        <v>4.670066788550652</v>
-      </c>
-      <c r="G57" t="n">
-        <v>-0.06842195886845531</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.594888547727895</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0.5616338189825709</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0.5030483883145077</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1.2912577468473</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0.3701473247622408</v>
-      </c>
-      <c r="X57" t="n">
-        <v>2.044368253373634</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>0.1422359270086119</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>0.2647457881977981</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>0.8528723272599358</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>1.529689198370042</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>0.792281264287191</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>0.3886406665358992</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>1.548754327750485</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>dnnqk0iD</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>2.128073775961899</v>
-      </c>
-      <c r="C58" t="n">
-        <v>1.242628091130186</v>
-      </c>
-      <c r="D58" t="n">
-        <v>-1.138439208561187</v>
-      </c>
-      <c r="E58" t="n">
-        <v>1.082325546666904</v>
-      </c>
-      <c r="F58" t="n">
-        <v>4.670066788550652</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" t="n">
-        <v>0.7562452131781391</v>
-      </c>
-      <c r="W58" t="n">
-        <v>0.02178038869446279</v>
-      </c>
-      <c r="X58" t="n">
-        <v>0.1411159918135424</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>-1.053668086583754</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>0.2159939167764675</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>0.09259956739564955</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>1.462972437530633</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>0.1762027597853505</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>0.0407718873637366</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>0.06937894505824396</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>-0.2315504637589359</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>QT6wuRFc</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>-1.425923322217599</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-0.3124348559559725</v>
-      </c>
-      <c r="D59" t="n">
-        <v>-1.006078822714832</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0.0188051629900348</v>
-      </c>
-      <c r="F59" t="n">
-        <v>4.670066788550652</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0.5368536386174515</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.4731773961295207</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1.437848932297861</v>
-      </c>
-      <c r="W59" t="n">
-        <v>0.2871464872417239</v>
-      </c>
-      <c r="X59" t="n">
-        <v>1.579675985576559</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>-0.3702392052882559</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>0.3453156257871962</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>0.5009044491737638</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>2.094204147349657</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>0.2929811663942584</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>0.3735062363678441</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>1.373628326382051</v>
-      </c>
-      <c r="AJ59" t="n">
         <v>-0.2315504637589359</v>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ17"/>
+  <dimension ref="A1:AJ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,20 +608,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.597121179823038</v>
+        <v>-1.070523612399649</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.4605360890117971</v>
+        <v>1.242628091130186</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.221164449715159</v>
+        <v>1.376408122519553</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.8261836349998065</v>
+        <v>1.563095035178365</v>
       </c>
       <c r="F2" t="n">
         <v>-0.2141296999117111</v>
@@ -630,25 +630,25 @@
         <v>-0.2701804913637576</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3788006650590997</v>
+        <v>0.3514662445311464</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1960996420384249</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9828997477856625</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2.771076657903333</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-1.773863638298431</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.5972925438875869</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.456456394378136</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -657,37 +657,37 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>0.3626596330439072</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-0.5943856971021022</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>0.7083086930971625</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-1.163845344751582</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.06496690757846</v>
+        <v>1.167488387369385</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.7236213949856372</v>
+        <v>0.1874004399678055</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.4701978993431818</v>
+        <v>0.1067830340164654</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.585287285628355</v>
+        <v>0.8186424896808172</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.2769045331585789</v>
+        <v>-0.5263021603886666</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.9798862899177007</v>
+        <v>0.04303785672715998</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.5798414482843652</v>
+        <v>-0.219993938097167</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.7827649613810741</v>
+        <v>0.585985810212066</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.4935117548859267</v>
+        <v>-0.4685680448738501</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.5940689292608923</v>
+        <v>-0.02282983851293768</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.5389990185932176</v>
+        <v>0.4498768220636419</v>
       </c>
       <c r="AJ2" t="n">
         <v>-0.2315504637589359</v>
@@ -720,35 +720,35 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.553966552409826</v>
+        <v>-0.1410166790296269</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.3371183947986099</v>
+        <v>-0.9295233270219083</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4931823275602075</v>
+        <v>1.624583845981469</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.8261836349998065</v>
+        <v>1.796195393244528</v>
       </c>
       <c r="F3" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3350951061221493</v>
+        <v>2.756197496065776</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1080439413343977</v>
+        <v>1.812000063711638</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5616338189825709</v>
+        <v>1.319367280003567</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007732342947784333</v>
+        <v>0.998364433681231</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -781,25 +781,25 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0.3457191461877709</v>
       </c>
       <c r="V3" t="n">
-        <v>1.620882792853803</v>
+        <v>-0.06727821879089516</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7502846345246161</v>
+        <v>0.6717325408070056</v>
       </c>
       <c r="X3" t="n">
-        <v>1.141361970589499</v>
+        <v>0.7151066218841876</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.3852880119613843</v>
+        <v>-0.2700040968571655</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.212198726801861</v>
+        <v>-0.2645748851509903</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.04287781805486426</v>
+        <v>0.4216192822200535</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -808,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.823641129492807</v>
+        <v>0.2108210798924933</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.245208188468138</v>
+        <v>-0.51621888876959</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.205479494772884</v>
+        <v>-0.6105505285245687</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.358089632111246</v>
+        <v>0.338767951235472</v>
       </c>
       <c r="AJ3" t="n">
         <v>-0.2315504637589359</v>
@@ -832,35 +832,35 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.7698007810152303</v>
+        <v>0.05035239548773072</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.6086373220676217</v>
+        <v>0.230602998582051</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8075382439453</v>
+        <v>1.111687350826844</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06251148012744039</v>
+        <v>1.504819945661825</v>
       </c>
       <c r="F4" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G4" t="n">
-        <v>2.352680431075172</v>
+        <v>1.142129236103358</v>
       </c>
       <c r="H4" t="n">
-        <v>2.542266973301885</v>
+        <v>0.229755092932772</v>
       </c>
       <c r="I4" t="n">
-        <v>1.319367280003567</v>
+        <v>0.5616338189825709</v>
       </c>
       <c r="J4" t="n">
-        <v>1.988996524414678</v>
+        <v>0.5030483883145077</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -893,25 +893,25 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.1979681393697227</v>
       </c>
       <c r="V4" t="n">
-        <v>2.460974138531289</v>
+        <v>-0.09474155729465943</v>
       </c>
       <c r="W4" t="n">
-        <v>2.717006828558775</v>
+        <v>0.06724614626961115</v>
       </c>
       <c r="X4" t="n">
-        <v>1.604774637036507</v>
+        <v>0.1394922973434939</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.71595743726319</v>
+        <v>1.04952344159435</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.640843293809122</v>
+        <v>-0.01133409179215867</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.06057492859173137</v>
+        <v>0.7665653925516784</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.741768921880226</v>
+        <v>-0.3808636073416838</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -929,13 +929,13 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.938788073292398</v>
+        <v>0.8325223785677111</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.718081709902412</v>
+        <v>0.1029082303075219</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.299232479023324</v>
+        <v>-0.04717561665654878</v>
       </c>
       <c r="AJ4" t="n">
         <v>-0.2315504637589359</v>
@@ -944,35 +944,35 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.8791545378822918</v>
+        <v>-0.6604470241481688</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.497244720402569</v>
+        <v>-0.3371183947986099</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3175250357487154</v>
+        <v>-1.469340173177074</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9573025864120233</v>
+        <v>0.9657753676338224</v>
       </c>
       <c r="F5" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2701804913637576</v>
+        <v>-0.06842195886845531</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2570895134607253</v>
+        <v>0.229755092932772</v>
       </c>
       <c r="I5" t="n">
         <v>0.5616338189825709</v>
       </c>
       <c r="J5" t="n">
-        <v>0.998364433681231</v>
+        <v>0.5030483883145077</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -987,10 +987,10 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.0259029127667809</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.864405791522107</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1005,25 +1005,25 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.053198147676791</v>
+        <v>-0.6019334555042497</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2513748865275142</v>
+        <v>0.6515910443906093</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06449777637569343</v>
+        <v>0.4256548211297552</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.004596794714574026</v>
+        <v>0.4772700100802098</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.4787688472996981</v>
+        <v>-0.361371538334707</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.05775423404998493</v>
+        <v>0.8689325025727429</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.98816180252153</v>
+        <v>-0.1504619174396009</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1032,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.6750792393198582</v>
+        <v>0.6665552087078406</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1041,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.3630599931986345</v>
+        <v>0.6264604202787447</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.3271857076716748</v>
+        <v>0.4400412836800868</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.02137605848543457</v>
+        <v>0.6413695344448664</v>
       </c>
       <c r="AJ5" t="n">
         <v>-0.2315504637589359</v>
@@ -1056,20 +1056,20 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.8791545378822918</v>
+        <v>0.1050292739212614</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.29977640966147</v>
+        <v>-0.09028300637223562</v>
       </c>
       <c r="D6" t="n">
         <v>-1.204619401484364</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9573025864120233</v>
+        <v>0.06251148012744039</v>
       </c>
       <c r="F6" t="n">
         <v>-0.2141296999117111</v>
@@ -1078,13 +1078,13 @@
         <v>-1.077214621344967</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.08275678743634</v>
+        <v>-2.813023697026587</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.9538331030594207</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-2.468847883885833</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1117,25 +1117,25 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2136794338384538</v>
+        <v>-0.6104574001758863</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.87630835621688</v>
+        <v>-0.04208950321840557</v>
       </c>
       <c r="W6" t="n">
-        <v>-2.574052803182022</v>
+        <v>-1.308526885231355</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.114411076332587</v>
+        <v>-1.053351145116864</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2553066181888258</v>
+        <v>0.9718869809317627</v>
       </c>
       <c r="Z6" t="n">
-        <v>-2.363725030114238</v>
+        <v>-0.8464758951766252</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.05744328852240227</v>
+        <v>-0.8139513210409572</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1144,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>-2.312108936639211</v>
+        <v>-0.763370335763339</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1153,13 +1153,13 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>-1.079578722917836</v>
+        <v>0.5557811250471067</v>
       </c>
       <c r="AH6" t="n">
-        <v>-1.472277656239168</v>
+        <v>-0.1436008077353126</v>
       </c>
       <c r="AI6" t="n">
-        <v>-2.39979630217105</v>
+        <v>-0.7013853935767946</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0.2315504637589359</v>
@@ -1168,35 +1168,35 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.717997187710418</v>
+        <v>-1.617292396734957</v>
       </c>
       <c r="C7" t="n">
-        <v>1.242628091130186</v>
+        <v>-1.349143487346745</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.02992097709796582</v>
+        <v>-1.320434739099925</v>
       </c>
       <c r="E7" t="n">
-        <v>1.956451889415015</v>
+        <v>-0.1414513331804523</v>
       </c>
       <c r="F7" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.489524348812083</v>
+        <v>0.7386121711127538</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.813023697026587</v>
+        <v>0.3514662445311464</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.711566564080417</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9828997477856625</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1229,25 +1229,25 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.2460965936201191</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.356063958799919</v>
+        <v>1.747712537222637</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.06369590307519</v>
+        <v>2.500746567519433</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6940416854056052</v>
+        <v>1.615960594887789</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.5420335966303749</v>
+        <v>0.05916916278619382</v>
       </c>
       <c r="Z7" t="n">
-        <v>-1.63158002859831</v>
+        <v>1.571775300776941</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4083005445951021</v>
+        <v>-1.066589555195307</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>-1.270588475661334</v>
+        <v>1.42119670439947</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1265,13 +1265,13 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>-1.799449605153632</v>
+        <v>0.9629579204524428</v>
       </c>
       <c r="AH7" t="n">
-        <v>-1.364883077316842</v>
+        <v>1.276802407852746</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.9614828715635501</v>
+        <v>2.362110565326358</v>
       </c>
       <c r="AJ7" t="n">
         <v>-0.2315504637589359</v>
@@ -1280,35 +1280,35 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EirZ0Wr4</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.03166292216256539</v>
+        <v>-0.6604470241481688</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.9295233270219083</v>
+        <v>-1.694713031143669</v>
       </c>
       <c r="D8" t="n">
-        <v>1.376408122519553</v>
+        <v>-1.717515896638989</v>
       </c>
       <c r="E8" t="n">
-        <v>1.796195393244528</v>
+        <v>1.563095035178365</v>
       </c>
       <c r="F8" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4719390238590598</v>
+        <v>-0.06842195886845531</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1080439413343977</v>
+        <v>-0.1353783618623509</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-0.1960996420384249</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0.4875837024189391</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1341,25 +1341,25 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.2178279217037928</v>
       </c>
       <c r="V8" t="n">
-        <v>1.482252682004508</v>
+        <v>0.3568259336705719</v>
       </c>
       <c r="W8" t="n">
-        <v>2.106872920866423</v>
+        <v>0.5069887868232915</v>
       </c>
       <c r="X8" t="n">
-        <v>2.45941056089927</v>
+        <v>0.7870045200498109</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.5958057947202108</v>
+        <v>-0.8496846663855581</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.598286485600311</v>
+        <v>0.479025517889911</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.2317661738410359</v>
+        <v>0.9694752051124241</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.34410352226065</v>
+        <v>0.8469227488290401</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1377,13 +1377,13 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.301275098524897</v>
+        <v>0.1877514075408666</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.411907684601899</v>
+        <v>0.4555990545521446</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.013274083589997</v>
+        <v>0.6056692273940188</v>
       </c>
       <c r="AJ8" t="n">
         <v>-0.2315504637589359</v>
@@ -1392,29 +1392,29 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>t4ZkclrT</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.597121179823038</v>
+        <v>-0.1410166790296269</v>
       </c>
       <c r="C9" t="n">
         <v>-0.7320550162808089</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.221164449715159</v>
+        <v>-0.1126462182519375</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2580015122135339</v>
+        <v>-0.3599829188674802</v>
       </c>
       <c r="F9" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8754560888496645</v>
+        <v>0.133336573626847</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.865645271452597</v>
+        <v>-0.1353783618623509</v>
       </c>
       <c r="I9" t="n">
         <v>-0.1960996420384249</v>
@@ -1453,25 +1453,25 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.348552267271983</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.606499123961251</v>
+        <v>-0.4800719841521637</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.104986071307595</v>
+        <v>0.09779212214547947</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9657551247515979</v>
+        <v>0.4363455417471842</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.014206275826434</v>
+        <v>-1.227531774391915</v>
       </c>
       <c r="Z9" t="n">
-        <v>-1.369438393185354</v>
+        <v>-0.03563042454933149</v>
       </c>
       <c r="AA9" t="n">
-        <v>-1.45803396568641</v>
+        <v>-0.2241096919069236</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>-1.099835004725588</v>
+        <v>0.1185228386565988</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1489,13 +1489,13 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.7661086406435766</v>
+        <v>-0.2976041479596282</v>
       </c>
       <c r="AH9" t="n">
-        <v>-1.076100530113454</v>
+        <v>-0.3646411986468536</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.398351635913661</v>
+        <v>-0.08345008198673963</v>
       </c>
       <c r="AJ9" t="n">
         <v>-0.2315504637589359</v>
@@ -1504,35 +1504,35 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>YH892O2B</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.296398348438619</v>
+        <v>0.597121179823038</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1396500840575105</v>
+        <v>-0.6086373220676217</v>
       </c>
       <c r="D10" t="n">
-        <v>1.624583845981469</v>
+        <v>-1.221164449715159</v>
       </c>
       <c r="E10" t="n">
-        <v>1.767057848486258</v>
+        <v>1.504819945661825</v>
       </c>
       <c r="F10" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4719390238590598</v>
+        <v>2.957956028561079</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.595912181042843</v>
+        <v>2.298844670105136</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.711566564080417</v>
+        <v>2.077100741024563</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.973531838519109</v>
+        <v>2.484312569781401</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1565,25 +1565,25 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0.113433247628522</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.416050294698149</v>
+        <v>0.9004298542182174</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.433520132418</v>
+        <v>1.625196139539359</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.209946484358056</v>
+        <v>0.6862074688298988</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.2177316687732345</v>
+        <v>0.7419134142361675</v>
       </c>
       <c r="Z10" t="n">
-        <v>-1.725481945388793</v>
+        <v>1.291878058595774</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.103404913042841</v>
+        <v>-1.568416229700008</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1.645331164135031</v>
+        <v>0.6726677583418895</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1601,13 +1601,13 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>-2.053208087771309</v>
+        <v>1.204399995479845</v>
       </c>
       <c r="AH10" t="n">
-        <v>-1.853272922358693</v>
+        <v>1.634223672482451</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.471087530610581</v>
+        <v>0.9377892952774359</v>
       </c>
       <c r="AJ10" t="n">
         <v>-0.2315504637589359</v>
@@ -1616,35 +1616,35 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>8jyraADG</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.553966552409826</v>
+        <v>0.1050292739212614</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.09028300637223562</v>
+        <v>-0.4358525501691597</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4931823275602075</v>
+        <v>-0.5262724240217962</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0188051629900348</v>
+        <v>0.06251148012744039</v>
       </c>
       <c r="F11" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5368536386174515</v>
+        <v>-0.2701804913637576</v>
       </c>
       <c r="H11" t="n">
         <v>0.4731773961295207</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5616338189825709</v>
+        <v>-0.1960996420384249</v>
       </c>
       <c r="J11" t="n">
-        <v>0.998364433681231</v>
+        <v>0.5030483883145077</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1680,22 +1680,22 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>2.051732448140291</v>
+        <v>-1.073764743500308</v>
       </c>
       <c r="W11" t="n">
-        <v>1.194648472014848</v>
+        <v>-0.859734687215493</v>
       </c>
       <c r="X11" t="n">
-        <v>1.199995436527098</v>
+        <v>-1.184367260787876</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.2219051359329632</v>
+        <v>0.3083128616390803</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.786942227241142</v>
+        <v>-0.5414441995050682</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.1756634511933046</v>
+        <v>-1.153402667801588</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1704,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.928844725877407</v>
+        <v>-1.025314844252778</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.813760319852618</v>
+        <v>-0.3562250467679259</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.406080761305951</v>
+        <v>-0.5071061250520406</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.594125475475163</v>
+        <v>-1.398401694846551</v>
       </c>
       <c r="AJ11" t="n">
         <v>-0.2315504637589359</v>
@@ -1728,35 +1728,35 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>6RvR2hEi</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.7698007810152303</v>
+        <v>-1.207215808483476</v>
       </c>
       <c r="C12" t="n">
         <v>1.143893935759636</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.370069883792308</v>
+        <v>-1.022623870945627</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06251148012744039</v>
+        <v>-0.1414513331804523</v>
       </c>
       <c r="F12" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.480731686335571</v>
+        <v>-0.6736975563543621</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.961045635837966</v>
+        <v>-2.08275678743634</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.469300025101413</v>
+        <v>-0.1960996420384249</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.973531838519109</v>
+        <v>-1.478215793152386</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1789,25 +1789,25 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.90617421719767</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.263865315428883</v>
+        <v>-1.347808018683855</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.446342679924957</v>
+        <v>-2.035320119582094</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.485818353962881</v>
+        <v>-1.778968533462978</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.4142133382952967</v>
+        <v>-0.2831042788719289</v>
       </c>
       <c r="Z12" t="n">
-        <v>-1.569063330903899</v>
+        <v>-1.544986579728016</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.70991410961634</v>
+        <v>-0.4308261065813402</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1816,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>-1.043060200824413</v>
+        <v>-1.686098076902454</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1825,44 +1825,44 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>-1.283142776566572</v>
+        <v>-1.810446660755123</v>
       </c>
       <c r="AH12" t="n">
-        <v>-1.141702463957293</v>
+        <v>-1.284769646411466</v>
       </c>
       <c r="AI12" t="n">
-        <v>-1.762582486995461</v>
+        <v>-1.654945949074209</v>
       </c>
       <c r="AJ12" t="n">
-        <v>4.318713008673075</v>
+        <v>-0.2315504637589359</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>4xHh663n</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.155412215178664</v>
+        <v>-1.070523612399649</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.694713031143669</v>
+        <v>-0.1396500840575105</v>
       </c>
       <c r="D13" t="n">
-        <v>1.177867543750021</v>
+        <v>1.376408122519553</v>
       </c>
       <c r="E13" t="n">
-        <v>1.504819945661825</v>
+        <v>-0.3017078293509395</v>
       </c>
       <c r="F13" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4719390238590598</v>
+        <v>-0.2701804913637576</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9873564230509713</v>
+        <v>0.1080439413343977</v>
       </c>
       <c r="I13" t="n">
         <v>0.5616338189825709</v>
@@ -1871,16 +1871,16 @@
         <v>0.5030483883145077</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.220827543639729</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-1.262590220679441</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>0.5972925438875869</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.200490205437644</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1889,37 +1889,37 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.19148813529298</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>-0.1289943150260587</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>0.8240070720724897</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>0.09698002487353621</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.27701631285428</v>
       </c>
       <c r="V13" t="n">
-        <v>0.03554624041232873</v>
+        <v>-0.03803983815921605</v>
       </c>
       <c r="W13" t="n">
-        <v>0.4520037373605031</v>
+        <v>0.006141706476825215</v>
       </c>
       <c r="X13" t="n">
-        <v>0.5700867423553693</v>
+        <v>0.5096089433764011</v>
       </c>
       <c r="Y13" t="n">
-        <v>-1.127613312781931</v>
+        <v>-0.355377456989995</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.4422368711237737</v>
+        <v>-0.02512244961773773</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.5364884528847116</v>
+        <v>-0.1194468285306135</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -1928,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.8421200320003005</v>
+        <v>0.4424307806951598</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -1937,13 +1937,13 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.2893282533885405</v>
+        <v>-0.2061717089272695</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.3881820474398985</v>
+        <v>0.2339968552480013</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.3269172199221432</v>
+        <v>0.2000860621213111</v>
       </c>
       <c r="AJ13" t="n">
         <v>-0.2315504637589359</v>
@@ -1952,17 +1952,17 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hKOA02XN</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-1.015846733966119</v>
+        <v>-0.6604470241481688</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.719396569986306</v>
+        <v>1.736298867982935</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.469340173177074</v>
+        <v>-1.717515896638989</v>
       </c>
       <c r="E14" t="n">
         <v>-0.3017078293509395</v>
@@ -1971,16 +1971,16 @@
         <v>-0.2141296999117111</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5368536386174515</v>
+        <v>2.150921898579869</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4731773961295207</v>
+        <v>2.055422366908387</v>
       </c>
       <c r="I14" t="n">
-        <v>1.319367280003567</v>
+        <v>2.077100741024563</v>
       </c>
       <c r="J14" t="n">
-        <v>0.007732342947784333</v>
+        <v>1.988996524414678</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2013,25 +2013,25 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.167237431123993</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.4216800118610324</v>
+        <v>1.520879229113972</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.2454709613428968</v>
+        <v>1.316255610113583</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.424169263350948</v>
+        <v>1.056339141559731</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.2313503891723604</v>
+        <v>0.2044945498027004</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.1933345502696132</v>
+        <v>1.797981791023942</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.05657870526184997</v>
+        <v>0.2478232437389039</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.5811794152273339</v>
+        <v>1.518346675174791</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2049,13 +2049,13 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.3609561130198136</v>
+        <v>2.052372964804871</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.6423350612758683</v>
+        <v>2.020877494683265</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.2562899022040805</v>
+        <v>1.356905887530726</v>
       </c>
       <c r="AJ14" t="n">
         <v>-0.2315504637589359</v>
@@ -2064,35 +2064,35 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0lGMiS5j</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.553966552409826</v>
+        <v>-1.207215808483476</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.151675176605645</v>
+        <v>-1.349143487346745</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5262724240217962</v>
+        <v>-1.700970848408195</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.219540489236457</v>
+        <v>-0.1414513331804523</v>
       </c>
       <c r="F15" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G15" t="n">
-        <v>3.563231626046985</v>
+        <v>1.545646301093963</v>
       </c>
       <c r="H15" t="n">
-        <v>2.42055582170351</v>
+        <v>1.325155457318141</v>
       </c>
       <c r="I15" t="n">
-        <v>1.319367280003567</v>
+        <v>0.5616338189825709</v>
       </c>
       <c r="J15" t="n">
-        <v>0.007732342947784333</v>
+        <v>0.998364433681231</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2125,25 +2125,25 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-1.099802436887413</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9452672547276846</v>
+        <v>1.008654397868557</v>
       </c>
       <c r="W15" t="n">
-        <v>1.691987363762948</v>
+        <v>1.861927319595536</v>
       </c>
       <c r="X15" t="n">
-        <v>1.118282318625962</v>
+        <v>0.6479394242128244</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.271564000374857</v>
+        <v>0.8257322415274252</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.887599138609404</v>
+        <v>1.002346753689622</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.09112156327398194</v>
+        <v>-1.316014691908324</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2152,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.579780282775014</v>
+        <v>0.2370834270390244</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2161,13 +2161,13 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.8021537676952302</v>
+        <v>0.731236613098185</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.060693446165155</v>
+        <v>0.8424442620295582</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.942749991869502</v>
+        <v>1.185799216970234</v>
       </c>
       <c r="AJ15" t="n">
         <v>-0.2315504637589359</v>
@@ -2176,35 +2176,35 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Sf88FVcc</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0.597121179823038</v>
       </c>
       <c r="C16" t="n">
-        <v>-1.29977640966147</v>
+        <v>-0.4605360890117971</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.327731845252264</v>
+        <v>-1.221164449715159</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9573025864120233</v>
+        <v>-0.4182580083840211</v>
       </c>
       <c r="F16" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.06842195886845531</v>
+        <v>-0.2701804913637576</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.500511816657474</v>
+        <v>-0.3788006650590997</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-0.1960996420384249</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4875837024189391</v>
+        <v>-0.9828997477856625</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2237,25 +2237,25 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4812364164555286</v>
+        <v>-1.426032461361761</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.511605379925433</v>
+        <v>-0.7696995144923559</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7849508771530297</v>
+        <v>-0.4952060818492727</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.001384058100731</v>
+        <v>-0.6412699011319637</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.08177691085663405</v>
+        <v>-0.3334765441507994</v>
       </c>
       <c r="Z16" t="n">
-        <v>-1.173228471378871</v>
+        <v>-0.9779575367267035</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.051398014638758</v>
+        <v>-0.6074743200320217</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>-1.533227020469956</v>
+        <v>-0.7655943374979588</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2273,13 +2273,13 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>-1.152206718342537</v>
+        <v>-0.5419374131880329</v>
       </c>
       <c r="AH16" t="n">
-        <v>-1.135032103994335</v>
+        <v>-0.5672626430995943</v>
       </c>
       <c r="AI16" t="n">
-        <v>-1.480832789284498</v>
+        <v>-0.5365735141126164</v>
       </c>
       <c r="AJ16" t="n">
         <v>-0.2315504637589359</v>
@@ -2288,112 +2288,784 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>O2Fteteo</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.854689383794245</v>
+        <v>1.717997187710418</v>
       </c>
       <c r="C17" t="n">
-        <v>0.230602998582051</v>
+        <v>-0.3371183947986099</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6751778580989453</v>
+        <v>-0.4931823275602075</v>
       </c>
       <c r="E17" t="n">
-        <v>1.504819945661825</v>
+        <v>0.9657753676338224</v>
       </c>
       <c r="F17" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G17" t="n">
+        <v>0.3350951061221493</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1080439413343977</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.5616338189825709</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.007732342947784333</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.631682797429432</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.7661348294735219</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.21389429469007</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0.2992787341338696</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.207620467972968</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.05888767106370112</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.810644181009191</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.22120685422839</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.141104269015315</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.363543237908921</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>6D3e2qCs</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.6331085849314034</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-1.497244720402569</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.3175250357487154</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.3308453741092098</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.2701804913637576</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.2570895134607253</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5616338189825709</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.998364433681231</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-1.053198147676791</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.2583312051369537</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.04960056701360126</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.03470775563653992</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.4435870561097839</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.07873981039963396</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.9859769597196688</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.6752930945893728</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-0.2898486399121847</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.2998978714595746</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-0.005956118870570808</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>AsIP75lK</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.182750654395429</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.6086373220676217</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.8075382439453</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.504819945661825</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.352680431075172</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.542266973301885</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.319367280003567</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.988996524414678</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.510682654683559</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.703945565952939</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.590338214160267</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.812988657283377</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.637547315938177</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-0.1043372845390246</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.738538470629805</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.974612891193312</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>2.682768039510283</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>2.311925650792134</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>GrNwFMem</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.717997187710418</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.242628091130186</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.02992097709796582</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.563095035178365</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-2.489524348812083</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-2.813023697026587</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-1.711566564080417</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.9828997477856625</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-1.319983924784525</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-1.069488170420975</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.7060596566507752</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-0.441500516573364</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-1.593976154594746</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.2658296501691698</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-1.29099094064646</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-1.718079484164353</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>-1.348563881150783</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>-0.9724036753194831</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>8x0Cb1B6</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.1050292739212614</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.29977640966147</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-1.204619401484364</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9657753676338224</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-1.077214621344967</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-2.08275678743634</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.2051176610099886</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-1.972320239935639</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-2.517920801076223</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-2.095259360617531</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.2413396108989852</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-2.525516368104564</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-0.1760628333191043</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-2.335032658375503</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-1.043060355172216</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>-1.431863122345954</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>-2.403933335932738</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>EirZ0Wr4</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>-0.004324482945800021</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.9295233270219083</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.376408122519553</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.796195393244528</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G22" t="n">
         <v>-0.4719390238590598</v>
       </c>
-      <c r="H17" t="n">
-        <v>-2.326179090633089</v>
-      </c>
-      <c r="I17" t="n">
+      <c r="H22" t="n">
+        <v>0.1080439413343977</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.412986844041683</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.086695900613767</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.435256344899999</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-0.7977369732582185</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.581783473464327</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.1014573570150662</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.875469448718888</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.371672711845052</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.230793934919852</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.426557785456943</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.986048514755486</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>t4ZkclrT</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.7698007810152303</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.7320550162808089</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-1.221164449715159</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.3599829188674802</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.8754560888496645</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.865645271452597</v>
+      </c>
+      <c r="I23" t="n">
         <v>-0.1960996420384249</v>
       </c>
-      <c r="J17" t="n">
-        <v>-0.9828997477856625</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-2.130922335672412</v>
-      </c>
-      <c r="V17" t="n">
-        <v>-2.066027526891424</v>
-      </c>
-      <c r="W17" t="n">
-        <v>-2.7186271774175</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-1.767890704336502</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>-0.2875253220398427</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>-2.566437148379294</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0.9000813520607556</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>-2.003367309848083</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>-1.198735826608245</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>-2.424872832660383</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>-2.196023757834523</v>
-      </c>
-      <c r="AJ17" t="n">
+      <c r="J23" t="n">
+        <v>0.007732342947784333</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-1.650865829422533</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-1.1070578577899</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.9491396191770558</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-1.09605240134457</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-1.370608620150335</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-1.464606483697161</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-1.089681135308982</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>-0.7339572919776098</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>-1.097815972694075</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>-0.5913308310104343</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-0.8390839766921512</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>-0.7995128627403739</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>-1.076100530113454</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>-1.424982408056064</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>-0.2315504637589359</v>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ17"/>
+  <dimension ref="A1:AJ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,47 +608,47 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.597121179823038</v>
+        <v>-0.1410166790296269</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.4605360890117971</v>
+        <v>-0.9295233270219083</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.221164449715159</v>
+        <v>1.624583845981469</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.8261836349998065</v>
+        <v>0.4121620172266851</v>
       </c>
       <c r="F2" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2701804913637576</v>
+        <v>2.756197496065776</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3788006650590997</v>
+        <v>1.812000063711638</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1960996420384249</v>
+        <v>1.319367280003567</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9828997477856625</v>
+        <v>0.998364433681231</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2.771076657903333</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.2712300321775298</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.366007922700148</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-2.38303643972925</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -657,37 +657,37 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.4144142511245363</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-0.1289943150260587</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-0.6800718546067644</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-2.080809249933487</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.06496690757846</v>
+        <v>-0.03372932119444755</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.7236213949856372</v>
+        <v>-0.05244988721407477</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.4701978993431818</v>
+        <v>0.6617032516181389</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.585287285628355</v>
+        <v>0.7012487268397084</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.2769045331585789</v>
+        <v>-0.2590704155609191</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.9798862899177007</v>
+        <v>-0.239911641898062</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.5798414482843652</v>
+        <v>0.3930179281551214</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.7827649613810741</v>
+        <v>0.2158737757403636</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.4935117548859267</v>
+        <v>-0.5661054720734803</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.5940689292608923</v>
+        <v>-0.6721891065193775</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.5389990185932176</v>
+        <v>0.3120446446583533</v>
       </c>
       <c r="AJ2" t="n">
         <v>-0.2315504637589359</v>
@@ -720,47 +720,47 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.553966552409826</v>
+        <v>-0.004324482945800021</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.3371183947986099</v>
+        <v>1.242628091130186</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4931823275602075</v>
+        <v>1.376408122519553</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.8261836349998065</v>
+        <v>1.563095035178365</v>
       </c>
       <c r="F3" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3350951061221493</v>
+        <v>-0.2701804913637576</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1080439413343977</v>
+        <v>0.3514662445311464</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5616338189825709</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007732342947784333</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>3.281126480756054</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-2.285137055917422</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.494127152502242</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.4325916386161665</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -769,37 +769,37 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.028722962331144</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-1.990559843330233</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.865292482850435</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-1.27846583289932</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.167488387369385</v>
       </c>
       <c r="V3" t="n">
-        <v>1.620882792853803</v>
+        <v>0.1590764994318507</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7502846345246161</v>
+        <v>0.092146830019914</v>
       </c>
       <c r="X3" t="n">
-        <v>1.141361970589499</v>
+        <v>0.792786059330153</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.3852880119613843</v>
+        <v>-0.5575394014354503</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.212198726801861</v>
+        <v>0.02961067767941523</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.04287781805486426</v>
+        <v>-0.2720217231684587</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -808,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.823641129492807</v>
+        <v>0.5869118805734892</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.245208188468138</v>
+        <v>-0.4807320176981667</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.205479494772884</v>
+        <v>-0.09536455346961009</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.358089632111246</v>
+        <v>0.4172943012608215</v>
       </c>
       <c r="AJ3" t="n">
         <v>-0.2315504637589359</v>
@@ -832,35 +832,35 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.7698007810152303</v>
+        <v>-0.6604470241481688</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.6086373220676217</v>
+        <v>-0.3371183947986099</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8075382439453</v>
+        <v>-1.469340173177074</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06251148012744039</v>
+        <v>0.9657753676338224</v>
       </c>
       <c r="F4" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G4" t="n">
-        <v>2.352680431075172</v>
+        <v>-0.06842195886845531</v>
       </c>
       <c r="H4" t="n">
-        <v>2.542266973301885</v>
+        <v>0.229755092932772</v>
       </c>
       <c r="I4" t="n">
-        <v>1.319367280003567</v>
+        <v>0.5616338189825709</v>
       </c>
       <c r="J4" t="n">
-        <v>1.988996524414678</v>
+        <v>0.5030483883145077</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -875,10 +875,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.0259029127667809</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.864405791522107</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -893,25 +893,25 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.6019334555042497</v>
       </c>
       <c r="V4" t="n">
-        <v>2.460974138531289</v>
+        <v>0.6515910443906093</v>
       </c>
       <c r="W4" t="n">
-        <v>2.717006828558775</v>
+        <v>0.4256548211297552</v>
       </c>
       <c r="X4" t="n">
-        <v>1.604774637036507</v>
+        <v>0.4772700100802098</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.71595743726319</v>
+        <v>-0.361371538334707</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.640843293809122</v>
+        <v>0.8689325025727429</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.06057492859173137</v>
+        <v>-0.1504619174396009</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.741768921880226</v>
+        <v>0.6665552087078406</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -929,13 +929,13 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.938788073292398</v>
+        <v>0.6264604202787447</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.718081709902412</v>
+        <v>0.4400412836800868</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.299232479023324</v>
+        <v>0.6413695344448664</v>
       </c>
       <c r="AJ4" t="n">
         <v>-0.2315504637589359</v>
@@ -944,35 +944,35 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.8791545378822918</v>
+        <v>0.05035239548773072</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.497244720402569</v>
+        <v>0.230602998582051</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3175250357487154</v>
+        <v>1.111687350826844</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9573025864120233</v>
+        <v>1.504819945661825</v>
       </c>
       <c r="F5" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2701804913637576</v>
+        <v>1.142129236103358</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2570895134607253</v>
+        <v>0.229755092932772</v>
       </c>
       <c r="I5" t="n">
         <v>0.5616338189825709</v>
       </c>
       <c r="J5" t="n">
-        <v>0.998364433681231</v>
+        <v>0.5030483883145077</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1005,25 +1005,25 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.053198147676791</v>
+        <v>0.1979681393697227</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2513748865275142</v>
+        <v>-0.09474155729465943</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06449777637569343</v>
+        <v>0.06724614626961115</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.004596794714574026</v>
+        <v>0.1394922973434939</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.4787688472996981</v>
+        <v>1.04952344159435</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.05775423404998493</v>
+        <v>-0.01133409179215867</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.98816180252153</v>
+        <v>0.7665653925516784</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1032,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.6750792393198582</v>
+        <v>-0.3808636073416838</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1041,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.3630599931986345</v>
+        <v>0.8325223785677111</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.3271857076716748</v>
+        <v>0.1029082303075219</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.02137605848543457</v>
+        <v>-0.04717561665654878</v>
       </c>
       <c r="AJ5" t="n">
         <v>-0.2315504637589359</v>
@@ -1056,20 +1056,20 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.8791545378822918</v>
+        <v>0.1050292739212614</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.29977640966147</v>
+        <v>-0.09028300637223562</v>
       </c>
       <c r="D6" t="n">
         <v>-1.204619401484364</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9573025864120233</v>
+        <v>0.06251148012744039</v>
       </c>
       <c r="F6" t="n">
         <v>-0.2141296999117111</v>
@@ -1078,13 +1078,13 @@
         <v>-1.077214621344967</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.08275678743634</v>
+        <v>-2.813023697026587</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.9538331030594207</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-2.468847883885833</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1117,25 +1117,25 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2136794338384538</v>
+        <v>-0.6104574001758863</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.87630835621688</v>
+        <v>-0.04208950321840557</v>
       </c>
       <c r="W6" t="n">
-        <v>-2.574052803182022</v>
+        <v>-1.308526885231355</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.114411076332587</v>
+        <v>-1.053351145116864</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2553066181888258</v>
+        <v>0.9718869809317627</v>
       </c>
       <c r="Z6" t="n">
-        <v>-2.363725030114238</v>
+        <v>-0.8464758951766252</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.05744328852240227</v>
+        <v>-0.8139513210409467</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1144,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>-2.312108936639211</v>
+        <v>-0.763370335763339</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1153,13 +1153,13 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>-1.079578722917836</v>
+        <v>0.5557811250471067</v>
       </c>
       <c r="AH6" t="n">
-        <v>-1.472277656239168</v>
+        <v>-0.1436008077353126</v>
       </c>
       <c r="AI6" t="n">
-        <v>-2.39979630217105</v>
+        <v>-0.7013853935767946</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0.2315504637589359</v>
@@ -1168,35 +1168,35 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.717997187710418</v>
+        <v>-1.617292396734957</v>
       </c>
       <c r="C7" t="n">
-        <v>1.242628091130186</v>
+        <v>-1.349143487346745</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.02992097709796582</v>
+        <v>-1.320434739099925</v>
       </c>
       <c r="E7" t="n">
-        <v>1.956451889415015</v>
+        <v>-0.1414513331804523</v>
       </c>
       <c r="F7" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.489524348812083</v>
+        <v>0.7386121711127538</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.813023697026587</v>
+        <v>0.3514662445311464</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.711566564080417</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9828997477856625</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1229,25 +1229,25 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.2460965936201191</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.356063958799919</v>
+        <v>1.747712537222637</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.06369590307519</v>
+        <v>2.500746567519433</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6940416854056052</v>
+        <v>1.615960594887789</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.5420335966303749</v>
+        <v>0.05916916278619382</v>
       </c>
       <c r="Z7" t="n">
-        <v>-1.63158002859831</v>
+        <v>1.571775300776941</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4083005445951021</v>
+        <v>-1.066589555195307</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>-1.270588475661334</v>
+        <v>1.42119670439947</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1265,13 +1265,13 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>-1.799449605153632</v>
+        <v>0.9629579204524428</v>
       </c>
       <c r="AH7" t="n">
-        <v>-1.364883077316842</v>
+        <v>1.276802407852746</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.9614828715635501</v>
+        <v>2.362110565326358</v>
       </c>
       <c r="AJ7" t="n">
         <v>-0.2315504637589359</v>
@@ -1280,35 +1280,35 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EirZ0Wr4</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.03166292216256539</v>
+        <v>-0.6604470241481688</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.9295233270219083</v>
+        <v>-1.694713031143669</v>
       </c>
       <c r="D8" t="n">
-        <v>1.376408122519553</v>
+        <v>-1.717515896638989</v>
       </c>
       <c r="E8" t="n">
-        <v>1.796195393244528</v>
+        <v>1.563095035178365</v>
       </c>
       <c r="F8" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4719390238590598</v>
+        <v>-0.06842195886845531</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1080439413343977</v>
+        <v>-0.1353783618623509</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-0.1960996420384249</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0.4875837024189391</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1341,25 +1341,25 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.2178279217037928</v>
       </c>
       <c r="V8" t="n">
-        <v>1.482252682004508</v>
+        <v>0.3568259336705719</v>
       </c>
       <c r="W8" t="n">
-        <v>2.106872920866423</v>
+        <v>0.5069887868232915</v>
       </c>
       <c r="X8" t="n">
-        <v>2.45941056089927</v>
+        <v>0.7870045200498109</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.5958057947202108</v>
+        <v>-0.8496846663855581</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.598286485600311</v>
+        <v>0.479025517889911</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.2317661738410359</v>
+        <v>0.9694752051124241</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.34410352226065</v>
+        <v>0.8469227488290401</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1377,13 +1377,13 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.301275098524897</v>
+        <v>0.1877514075408666</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.411907684601899</v>
+        <v>0.4555990545521446</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.013274083589997</v>
+        <v>0.6056692273940188</v>
       </c>
       <c r="AJ8" t="n">
         <v>-0.2315504637589359</v>
@@ -1392,29 +1392,29 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>t4ZkclrT</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.597121179823038</v>
+        <v>-0.1410166790296269</v>
       </c>
       <c r="C9" t="n">
         <v>-0.7320550162808089</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.221164449715159</v>
+        <v>-0.1126462182519375</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2580015122135339</v>
+        <v>-0.3599829188674802</v>
       </c>
       <c r="F9" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8754560888496645</v>
+        <v>0.133336573626847</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.865645271452597</v>
+        <v>-0.1353783618623509</v>
       </c>
       <c r="I9" t="n">
         <v>-0.1960996420384249</v>
@@ -1453,25 +1453,25 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.020692722195863</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.606499123961251</v>
+        <v>-0.4891369219512727</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.104986071307595</v>
+        <v>0.0981442439586775</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9657551247515979</v>
+        <v>0.4368655501183706</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.014206275826434</v>
+        <v>-1.248830382306413</v>
       </c>
       <c r="Z9" t="n">
-        <v>-1.369438393185354</v>
+        <v>-0.03185057220549152</v>
       </c>
       <c r="AA9" t="n">
-        <v>-1.45803396568641</v>
+        <v>-0.2577539388102943</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>-1.099835004725588</v>
+        <v>0.130310392683026</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1489,13 +1489,13 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.7661086406435766</v>
+        <v>-0.3128838966008364</v>
       </c>
       <c r="AH9" t="n">
-        <v>-1.076100530113454</v>
+        <v>-0.3646411986468536</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.398351635913661</v>
+        <v>-0.08659509246065092</v>
       </c>
       <c r="AJ9" t="n">
         <v>-0.2315504637589359</v>
@@ -1504,35 +1504,35 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>YH892O2B</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0.296398348438619</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1396500840575105</v>
+        <v>-0.6086373220676217</v>
       </c>
       <c r="D10" t="n">
-        <v>1.624583845981469</v>
+        <v>-1.221164449715159</v>
       </c>
       <c r="E10" t="n">
-        <v>1.767057848486258</v>
+        <v>1.504819945661825</v>
       </c>
       <c r="F10" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4719390238590598</v>
+        <v>2.957956028561079</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.595912181042843</v>
+        <v>2.298844670105136</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.711566564080417</v>
+        <v>2.077100741024563</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.973531838519109</v>
+        <v>2.484312569781401</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1565,25 +1565,25 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0.1167793200460198</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.416050294698149</v>
+        <v>0.9293784527593748</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.433520132418</v>
+        <v>1.655685947101691</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.209946484358056</v>
+        <v>0.7105724869125425</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.2177316687732345</v>
+        <v>0.7913868461426311</v>
       </c>
       <c r="Z10" t="n">
-        <v>-1.725481945388793</v>
+        <v>1.322515069771795</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.103404913042841</v>
+        <v>-1.545895745456675</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1.645331164135031</v>
+        <v>0.6737979928777064</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1601,13 +1601,13 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>-2.053208087771309</v>
+        <v>1.244501565767964</v>
       </c>
       <c r="AH10" t="n">
-        <v>-1.853272922358693</v>
+        <v>1.653626788082522</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.471087530610581</v>
+        <v>0.9598006390385579</v>
       </c>
       <c r="AJ10" t="n">
         <v>-0.2315504637589359</v>
@@ -1616,35 +1616,35 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>8jyraADG</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.553966552409826</v>
+        <v>0.1050292739212614</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.09028300637223562</v>
+        <v>-0.4358525501691597</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4931823275602075</v>
+        <v>-0.5262724240217962</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0188051629900348</v>
+        <v>0.06251148012744039</v>
       </c>
       <c r="F11" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5368536386174515</v>
+        <v>-0.2701804913637576</v>
       </c>
       <c r="H11" t="n">
         <v>0.4731773961295207</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5616338189825709</v>
+        <v>-0.1960996420384249</v>
       </c>
       <c r="J11" t="n">
-        <v>0.998364433681231</v>
+        <v>0.5030483883145077</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1680,22 +1680,22 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>2.051732448140291</v>
+        <v>-1.073764743500308</v>
       </c>
       <c r="W11" t="n">
-        <v>1.194648472014848</v>
+        <v>-0.859734687215493</v>
       </c>
       <c r="X11" t="n">
-        <v>1.199995436527098</v>
+        <v>-1.184367260787876</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.2219051359329632</v>
+        <v>0.3083128616390803</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.786942227241142</v>
+        <v>-0.5414441995050682</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.1756634511933046</v>
+        <v>-1.153402667801588</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1704,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.928844725877407</v>
+        <v>-1.025314844252778</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.813760319852618</v>
+        <v>-0.3562250467679259</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.406080761305951</v>
+        <v>-0.5071061250520406</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.594125475475163</v>
+        <v>-1.398401694846551</v>
       </c>
       <c r="AJ11" t="n">
         <v>-0.2315504637589359</v>
@@ -1728,35 +1728,35 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>6RvR2hEi</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.7698007810152303</v>
+        <v>-0.004324482945800021</v>
       </c>
       <c r="C12" t="n">
         <v>1.143893935759636</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.370069883792308</v>
+        <v>-1.022623870945627</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06251148012744039</v>
+        <v>-0.1414513331804523</v>
       </c>
       <c r="F12" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.480731686335571</v>
+        <v>-0.6736975563543621</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.961045635837966</v>
+        <v>-2.08275678743634</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.469300025101413</v>
+        <v>-0.1960996420384249</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.973531838519109</v>
+        <v>-1.478215793152386</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1789,25 +1789,25 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.90617421719767</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.263865315428883</v>
+        <v>-1.362636350260676</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.446342679924957</v>
+        <v>-2.025290830393228</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.485818353962881</v>
+        <v>-1.765110638418499</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.4142133382952967</v>
+        <v>-0.2940379601681752</v>
       </c>
       <c r="Z12" t="n">
-        <v>-1.569063330903899</v>
+        <v>-1.569649822980944</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.70991410961634</v>
+        <v>-0.4022247525164082</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1816,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>-1.043060200824413</v>
+        <v>-1.691150772750324</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1825,44 +1825,44 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>-1.283142776566572</v>
+        <v>-1.760560077451233</v>
       </c>
       <c r="AH12" t="n">
-        <v>-1.141702463957293</v>
+        <v>-1.223131068416657</v>
       </c>
       <c r="AI12" t="n">
-        <v>-1.762582486995461</v>
+        <v>-1.62822264249709</v>
       </c>
       <c r="AJ12" t="n">
-        <v>4.318713008673075</v>
+        <v>-0.2315504637589359</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>4xHh663n</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.155412215178664</v>
+        <v>-0.004324482945800021</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.694713031143669</v>
+        <v>-0.1396500840575105</v>
       </c>
       <c r="D13" t="n">
-        <v>1.177867543750021</v>
+        <v>1.376408122519553</v>
       </c>
       <c r="E13" t="n">
-        <v>1.504819945661825</v>
+        <v>-0.3017078293509395</v>
       </c>
       <c r="F13" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4719390238590598</v>
+        <v>-0.2701804913637576</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9873564230509713</v>
+        <v>0.1080439413343977</v>
       </c>
       <c r="I13" t="n">
         <v>0.5616338189825709</v>
@@ -1871,16 +1871,16 @@
         <v>0.5030483883145077</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.7308773664924498</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-1.773863638298431</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.494127152502242</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.1766254496756741</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1889,37 +1889,37 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.5254248060057426</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>-1.525168461254189</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.980990861825762</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>-0.01764046327420183</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.27701631285428</v>
       </c>
       <c r="V13" t="n">
-        <v>0.03554624041232873</v>
+        <v>-0.06636377869517085</v>
       </c>
       <c r="W13" t="n">
-        <v>0.4520037373605031</v>
+        <v>-0.008494497519726144</v>
       </c>
       <c r="X13" t="n">
-        <v>0.5700867423553693</v>
+        <v>0.4837525130257369</v>
       </c>
       <c r="Y13" t="n">
-        <v>-1.127613312781931</v>
+        <v>-0.3866146980367787</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.4422368711237737</v>
+        <v>-0.03854962866548254</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.5364884528847116</v>
+        <v>-0.1714746136019052</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -1928,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.8421200320003005</v>
+        <v>0.4433568510565832</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -1937,13 +1937,13 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.2893282533885405</v>
+        <v>-0.2183356817515861</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.3881820474398985</v>
+        <v>0.1614621402913289</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.3269172199221432</v>
+        <v>0.1675035413184905</v>
       </c>
       <c r="AJ13" t="n">
         <v>-0.2315504637589359</v>
@@ -1952,35 +1952,35 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hKOA02XN</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-1.015846733966119</v>
+        <v>-1.207215808483476</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.719396569986306</v>
+        <v>-1.349143487346745</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.469340173177074</v>
+        <v>-1.700970848408195</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.3017078293509395</v>
+        <v>-0.1414513331804523</v>
       </c>
       <c r="F14" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5368536386174515</v>
+        <v>1.545646301093963</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4731773961295207</v>
+        <v>1.325155457318141</v>
       </c>
       <c r="I14" t="n">
-        <v>1.319367280003567</v>
+        <v>0.5616338189825709</v>
       </c>
       <c r="J14" t="n">
-        <v>0.007732342947784333</v>
+        <v>0.998364433681231</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2013,25 +2013,25 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.167237431123993</v>
+        <v>-1.099802436887413</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.4216800118610324</v>
+        <v>1.008654397868557</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.2454709613428968</v>
+        <v>1.861927319595536</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.424169263350948</v>
+        <v>0.6479394242128244</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.2313503891723604</v>
+        <v>0.8257322415274252</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.1933345502696132</v>
+        <v>1.002346753689622</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.05657870526184997</v>
+        <v>-1.316014691908324</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.5811794152273339</v>
+        <v>0.2370834270390244</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2049,13 +2049,13 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.3609561130198136</v>
+        <v>0.731236613098185</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.6423350612758683</v>
+        <v>0.8424442620295582</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.2562899022040805</v>
+        <v>1.185799216970234</v>
       </c>
       <c r="AJ14" t="n">
         <v>-0.2315504637589359</v>
@@ -2064,35 +2064,35 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0lGMiS5j</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.553966552409826</v>
+        <v>-0.6604470241481688</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.151675176605645</v>
+        <v>1.736298867982935</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5262724240217962</v>
+        <v>-1.717515896638989</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.219540489236457</v>
+        <v>-0.3017078293509395</v>
       </c>
       <c r="F15" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G15" t="n">
-        <v>3.563231626046985</v>
+        <v>2.150921898579869</v>
       </c>
       <c r="H15" t="n">
-        <v>2.42055582170351</v>
+        <v>2.055422366908387</v>
       </c>
       <c r="I15" t="n">
-        <v>1.319367280003567</v>
+        <v>2.077100741024563</v>
       </c>
       <c r="J15" t="n">
-        <v>0.007732342947784333</v>
+        <v>1.988996524414678</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2128,22 +2128,22 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9452672547276846</v>
+        <v>1.520879229113972</v>
       </c>
       <c r="W15" t="n">
-        <v>1.691987363762948</v>
+        <v>1.316255610113583</v>
       </c>
       <c r="X15" t="n">
-        <v>1.118282318625962</v>
+        <v>1.056339141559731</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.271564000374857</v>
+        <v>0.2044945498027004</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.887599138609404</v>
+        <v>1.797981791023942</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.09112156327398194</v>
+        <v>0.2478232437389039</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2152,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.579780282775014</v>
+        <v>1.518346675174791</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2161,13 +2161,13 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.8021537676952302</v>
+        <v>2.052372964804871</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.060693446165155</v>
+        <v>2.020877494683265</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.942749991869502</v>
+        <v>1.356905887530726</v>
       </c>
       <c r="AJ15" t="n">
         <v>-0.2315504637589359</v>
@@ -2176,35 +2176,35 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Sf88FVcc</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.597121179823038</v>
+        <v>1.717997187710418</v>
       </c>
       <c r="C16" t="n">
-        <v>-1.29977640966147</v>
+        <v>-0.3371183947986099</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.327731845252264</v>
+        <v>-0.4931823275602075</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9573025864120233</v>
+        <v>0.9657753676338224</v>
       </c>
       <c r="F16" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.06842195886845531</v>
+        <v>0.3350951061221493</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.500511816657474</v>
+        <v>0.1080439413343977</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.5616338189825709</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4875837024189391</v>
+        <v>0.007732342947784333</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2237,25 +2237,25 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4812364164555286</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.511605379925433</v>
+        <v>1.631682797429432</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7849508771530297</v>
+        <v>0.7661348294735219</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.001384058100731</v>
+        <v>1.21389429469007</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.08177691085663405</v>
+        <v>-0.2992787341338696</v>
       </c>
       <c r="Z16" t="n">
-        <v>-1.173228471378871</v>
+        <v>1.207620467972968</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.051398014638758</v>
+        <v>-0.05888767106370112</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>-1.533227020469956</v>
+        <v>1.810644181009191</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2273,13 +2273,13 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>-1.152206718342537</v>
+        <v>1.22120685422839</v>
       </c>
       <c r="AH16" t="n">
-        <v>-1.135032103994335</v>
+        <v>1.141104269015315</v>
       </c>
       <c r="AI16" t="n">
-        <v>-1.480832789284498</v>
+        <v>1.363543237908921</v>
       </c>
       <c r="AJ16" t="n">
         <v>-0.2315504637589359</v>
@@ -2288,29 +2288,29 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>O2Fteteo</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.854689383794245</v>
+        <v>0.296398348438619</v>
       </c>
       <c r="C17" t="n">
-        <v>0.230602998582051</v>
+        <v>-0.4605360890117971</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6751778580989453</v>
+        <v>-1.221164449715159</v>
       </c>
       <c r="E17" t="n">
-        <v>1.504819945661825</v>
+        <v>-0.4182580083840211</v>
       </c>
       <c r="F17" t="n">
         <v>-0.2141296999117111</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4719390238590598</v>
+        <v>-0.2701804913637576</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.326179090633089</v>
+        <v>-0.3788006650590997</v>
       </c>
       <c r="I17" t="n">
         <v>-0.1960996420384249</v>
@@ -2319,16 +2319,16 @@
         <v>-0.9828997477856625</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-2.329421570623875</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.2712300321775298</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-4.527476648196155</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.4325916386161665</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2337,37 +2337,37 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>0.5846807428063197</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>-0.1289943150260587</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.911468612557419</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.476122415865154</v>
       </c>
       <c r="U17" t="n">
-        <v>-2.130922335672412</v>
+        <v>-1.426032461361761</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.066027526891424</v>
+        <v>-0.7407509159511985</v>
       </c>
       <c r="W17" t="n">
-        <v>-2.7186271774175</v>
+        <v>-0.4647162742869412</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.767890704336502</v>
+        <v>-0.6169048830493199</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.2875253220398427</v>
+        <v>-0.2840031122443358</v>
       </c>
       <c r="Z17" t="n">
-        <v>-2.566437148379294</v>
+        <v>-0.9473205255506831</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.9000813520607556</v>
+        <v>-0.5849538357886888</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2376,7 +2376,7 @@
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>-2.003367309848083</v>
+        <v>-0.7644641029621418</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2385,15 +2385,463 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>-1.198735826608245</v>
+        <v>-0.5018358428999141</v>
       </c>
       <c r="AH17" t="n">
-        <v>-2.424872832660383</v>
+        <v>-0.5478595274995232</v>
       </c>
       <c r="AI17" t="n">
-        <v>-2.196023757834523</v>
+        <v>-0.5145621703514944</v>
       </c>
       <c r="AJ17" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AsIP75lK</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.296398348438619</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.6086373220676217</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.8075382439453</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.504819945661825</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.352680431075172</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.542266973301885</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.319367280003567</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.988996524414678</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.519747592482668</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.703593444139741</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.589818205789081</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.834287265197876</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.633767463594336</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.07069303763565396</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.726750916603378</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.98989263983452</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>2.682768039510283</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>2.315070661266045</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>6D3e2qCs</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.6331085849314034</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-1.497244720402569</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.3175250357487154</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.3308453741092098</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.2701804913637576</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.2570895134607253</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.5616338189825709</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.998364433681231</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-1.053198147676791</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.2583312051369537</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.04960056701360126</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.03470775563653992</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-0.4435870561097839</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.07873981039963396</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-0.9859769597196688</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.6752930945893728</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-0.2898486399121847</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.2998978714595746</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-0.005956118870570808</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>8x0Cb1B6</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.1050292739212614</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-1.29977640966147</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-1.204619401484364</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9657753676338224</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1.077214621344967</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-2.08275678743634</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.2051176610099886</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-1.972320239935639</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-2.517920801076223</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-2.095259360617531</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.2413396108989852</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-2.525516368104564</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-0.1760628333190938</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-2.335032658375503</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-1.043060355172216</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>-1.431863122345954</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>-2.403933335932738</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>GrNwFMem</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.717997187710418</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.242628091130186</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.02992097709796582</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.563095035178365</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-2.489524348812083</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-2.813023697026587</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-1.711566564080417</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.9828997477856625</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-1.319983924784525</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-1.069488170420975</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.7060596566507752</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.441500516573364</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-1.593976154594746</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.2658296501691698</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-1.29099094064646</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-1.718079484164353</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>-1.348563881150783</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>-0.9724036753194831</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>-0.2315504637589359</v>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ21"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,172 +436,122 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>id_team_home</t>
+          <t>id_team_away</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>id_team_away</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_home</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>is_cup</t>
+          <t>h2h_35_segun_loc</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>h2h_35_segun_loc</t>
+          <t>h2h_35</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>h2h_35</t>
+          <t>h2h_3_segun_loc</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>h2h_3_segun_loc</t>
+          <t>h2h_3</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>h2h_3</t>
+          <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goals</t>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goals_against</t>
+          <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_fouls</t>
+          <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_fouls_against</t>
+          <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
+          <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
+          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_ball_possession</t>
+          <t>dif_mean_val_player_start</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
+          <t>dif_mean_pot_player_start</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts</t>
+          <t>dif_mean_val_player_sub</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
+          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_home_against</t>
+          <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_sub</t>
+          <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_val_player_start</t>
+          <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_pot_player_start</t>
+          <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_age_player_sub</t>
+          <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
           <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>is_rival_match</t>
         </is>
       </c>
     </row>
@@ -612,109 +562,79 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1410166790296269</v>
+        <v>-0.1409155046653783</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.9295233270219083</v>
+        <v>1.623933695757177</v>
       </c>
       <c r="D2" t="n">
-        <v>1.624583845981469</v>
+        <v>0.4103454469992215</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4121620172266851</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2141296999117111</v>
+        <v>2.764882144511015</v>
       </c>
       <c r="G2" t="n">
-        <v>2.756197496065776</v>
+        <v>1.817061217334993</v>
       </c>
       <c r="H2" t="n">
-        <v>1.812000063711638</v>
+        <v>1.319603292416398</v>
       </c>
       <c r="I2" t="n">
-        <v>1.319367280003567</v>
+        <v>0.9957959296544173</v>
       </c>
       <c r="J2" t="n">
-        <v>0.998364433681231</v>
+        <v>-0.2253334316095116</v>
       </c>
       <c r="K2" t="n">
-        <v>2.771076657903333</v>
+        <v>-0.5237630731994108</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2712300321775298</v>
+        <v>-0.189692752620763</v>
       </c>
       <c r="M2" t="n">
-        <v>1.366007922700148</v>
+        <v>-2.662282758106758</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.38303643972925</v>
+        <v>-0.1050562870029181</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0.05183822688398863</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4144142511245363</v>
+        <v>0.6638432478402458</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.1289943150260587</v>
+        <v>0.7027618626312362</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6800718546067644</v>
+        <v>-0.2404015385001411</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.080809249933487</v>
+        <v>0.3929819418100262</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.03372932119444755</v>
+        <v>0.216787032767272</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.05244988721407477</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6617032516181389</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7012487268397084</v>
+        <v>-0.5662987575901934</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.2590704155609191</v>
+        <v>-0.6738914923311381</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.239911641898062</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.3930179281551214</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.2158737757403636</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-0.5661054720734803</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-0.6721891065193775</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.3120446446583533</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-0.2315504637589359</v>
+        <v>0.3124917103224339</v>
       </c>
     </row>
     <row r="3">
@@ -724,781 +644,571 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.004324482945800021</v>
+        <v>-0.004471716800532986</v>
       </c>
       <c r="C3" t="n">
-        <v>1.242628091130186</v>
+        <v>1.375574110547928</v>
       </c>
       <c r="D3" t="n">
-        <v>1.376408122519553</v>
+        <v>1.562797379084372</v>
       </c>
       <c r="E3" t="n">
-        <v>1.563095035178365</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2141296999117111</v>
+        <v>-0.2688016221451399</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2701804913637576</v>
+        <v>0.3524101698710252</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3514662445311464</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0.8021447451083321</v>
       </c>
       <c r="K3" t="n">
-        <v>3.281126480756054</v>
+        <v>-1.022176105877531</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.285137055917422</v>
+        <v>1.011499265512334</v>
       </c>
       <c r="M3" t="n">
-        <v>1.494127152502242</v>
+        <v>0.3188974567012969</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4325916386161665</v>
+        <v>0.2622775143508074</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.1599687498815947</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.028722962331144</v>
+        <v>0.09261046601659235</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.990559843330233</v>
+        <v>0.7944272709752679</v>
       </c>
       <c r="S3" t="n">
-        <v>1.865292482850435</v>
+        <v>0.02983736649974578</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.27846583289932</v>
+        <v>-0.2733519141052485</v>
       </c>
       <c r="U3" t="n">
-        <v>1.167488387369385</v>
+        <v>0.5882333810706701</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1590764994318507</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.092146830019914</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.792786059330153</v>
+        <v>-0.4807401837618539</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.5575394014354503</v>
+        <v>-0.09545522824694366</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.02961067767941523</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-0.2720217231684587</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.5869118805734892</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-0.4807320176981667</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-0.09536455346961009</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.4172943012608215</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>-0.2315504637589359</v>
+        <v>0.4179643077886048</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.6604470241481688</v>
+        <v>0.05010579834540515</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.3371183947986099</v>
+        <v>1.110657219658063</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.469340173177074</v>
+        <v>1.504445382523099</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9657753676338224</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2141296999117111</v>
+        <v>1.146917468961066</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.06842195886845531</v>
+        <v>0.2303559159156945</v>
       </c>
       <c r="H4" t="n">
-        <v>0.229755092932772</v>
+        <v>0.5613919607762649</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5616338189825709</v>
+        <v>0.5004923415979325</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5030483883145077</v>
+        <v>0.005391093790016673</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1.220682541174008</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.251737669138954</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-0.5158330034449584</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.846693112980627</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0259029127667809</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.864405791522107</v>
+        <v>-0.09418599693846595</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>0.06763649274791685</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.1402194430667265</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0.01121626380744741</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.7672563505965543</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6019334555042497</v>
+        <v>-0.3806069247661253</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6515910443906093</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4256548211297552</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4772700100802098</v>
+        <v>0.8353618064932755</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.361371538334707</v>
+        <v>0.103371551423308</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.8689325025727429</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-0.1504619174396009</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.6665552087078406</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.6264604202787447</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.4400412836800868</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.6413695344448664</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-0.2315504637589359</v>
+        <v>-0.04748945490324837</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05035239548773072</v>
+        <v>-0.6594018985517905</v>
       </c>
       <c r="C5" t="n">
-        <v>0.230602998582051</v>
+        <v>-1.472282466518124</v>
       </c>
       <c r="D5" t="n">
-        <v>1.111687350826844</v>
+        <v>0.9646894143313194</v>
       </c>
       <c r="E5" t="n">
-        <v>1.504819945661825</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2141296999117111</v>
+        <v>-0.06655603770139627</v>
       </c>
       <c r="G5" t="n">
-        <v>1.142129236103358</v>
+        <v>0.2303559159156945</v>
       </c>
       <c r="H5" t="n">
-        <v>0.229755092932772</v>
+        <v>0.5613919607762649</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5616338189825709</v>
+        <v>0.5004923415979325</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5030483883145077</v>
+        <v>0.2361156191895449</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2.217508606530248</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.732214476392193</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.630616751216841</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.4798904623515435</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.6531366162405556</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>0.4271000623018968</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.4784697626372272</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.8713907163568377</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.1515555461527297</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1979681393697227</v>
+        <v>0.6679643386647403</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.09474155729465943</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06724614626961115</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1394922973434939</v>
+        <v>0.6288530339423462</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.04952344159435</v>
+        <v>0.4414465915045138</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.01133409179215867</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.7665653925516784</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-0.3808636073416838</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0.8325223785677111</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.1029082303075219</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-0.04717561665654878</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-0.2315504637589359</v>
+        <v>0.6425141793480427</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1050292739212614</v>
+        <v>-1.614508413605708</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.09028300637223562</v>
+        <v>-1.323266715392575</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.204619401484364</v>
+        <v>-0.1439985203328764</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06251148012744039</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2141296999117111</v>
+        <v>0.7424263000735782</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.077214621344967</v>
+        <v>0.3524101698710252</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.813023697026587</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9538331030594207</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.468847883885833</v>
+        <v>3.004809923983883</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-1.022176105877531</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.612095274578883</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-1.827552297960503</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.7378562211338769</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.750712116138605</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.508299370885329</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.618753563727747</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.576102179479876</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-1.069466019853633</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6104574001758863</v>
+        <v>1.423436146550723</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.04208950321840557</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.308526885231355</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.053351145116864</v>
+        <v>0.966080178167964</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9718869809317627</v>
+        <v>1.28054571798633</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.8464758951766252</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-0.8139513210409467</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-0.763370335763339</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.5557811250471067</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>-0.1436008077353126</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>-0.7013853935767946</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>-0.2315504637589359</v>
+        <v>2.366900100902028</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.617292396734957</v>
+        <v>0.1046833134913433</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.349143487346745</v>
+        <v>-1.207365575628259</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.320434739099925</v>
+        <v>0.06023346763158076</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1414513331804523</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2141296999117111</v>
+        <v>-1.077783959920114</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7386121711127538</v>
+        <v>-2.821000432967572</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3514662445311464</v>
+        <v>-0.9550307025040008</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-2.471329186740976</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.274375983487422</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.0253500405212911</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.63112317438048</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.153627916847552</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.007708742513178406</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.04146409982093601</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.312185814824336</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-1.054292984472531</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.8485784786327489</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.8163361374764504</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2460965936201191</v>
+        <v>-0.7635345152830193</v>
       </c>
       <c r="V7" t="n">
-        <v>1.747712537222637</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.500746567519433</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.615960594887789</v>
+        <v>0.5580204813244484</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.05916916278619382</v>
+        <v>-0.1438262598948648</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.571775300776941</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-1.066589555195307</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.42119670439947</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0.9629579204524428</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.276802407852746</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>2.362110565326358</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>-0.2315504637589359</v>
+        <v>-0.7030849854441478</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.6604470241481688</v>
+        <v>-0.1409155046653783</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.694713031143669</v>
+        <v>-0.1145834007075643</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.717515896638989</v>
+        <v>-0.3628185074376518</v>
       </c>
       <c r="E8" t="n">
-        <v>1.563095035178365</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2141296999117111</v>
+        <v>0.1356895467423473</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.06842195886845531</v>
+        <v>-0.1358068459502975</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1353783618623509</v>
+        <v>-0.196819370863868</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1960996420384249</v>
+        <v>0.00518875354144776</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4875837024189391</v>
+        <v>-0.6291013510586859</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.9714760248349484</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.651141660072405</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-0.7543274206296028</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.4602429451756123</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.489104527732015</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>0.09862553198384877</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.4380087701595549</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.03178729187682</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.2590563638356938</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2178279217037928</v>
+        <v>0.1311295065694522</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3568259336705719</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5069887868232915</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7870045200498109</v>
+        <v>-0.3125281093420729</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.8496846663855581</v>
+        <v>-0.3654842618897111</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.479025517889911</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.9694752051124241</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0.8469227488290401</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.1877514075408666</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.4555990545521446</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.6056692273940188</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>-0.2315504637589359</v>
+        <v>-0.08699242943092042</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.1410166790296269</v>
+        <v>-0.6594018985517905</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.7320550162808089</v>
+        <v>-1.720642051727373</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1126462182519375</v>
+        <v>1.562797379084372</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3599829188674802</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2141296999117111</v>
+        <v>-0.06655603770139627</v>
       </c>
       <c r="G9" t="n">
-        <v>0.133336573626847</v>
+        <v>-0.1358068459502975</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1353783618623509</v>
+        <v>-0.196819370863868</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1960996420384249</v>
+        <v>-0.4901148345150371</v>
       </c>
       <c r="J9" t="n">
-        <v>0.007732342947784333</v>
+        <v>3.004809923983883</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.0253500405212911</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.612095274578883</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-0.3965857948526362</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.002850032898938158</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.3579804990886523</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>0.5086734160874546</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.7886376423661434</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.4804470766698585</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.9705610370728527</v>
       </c>
       <c r="U9" t="n">
-        <v>1.020692722195863</v>
+        <v>0.8485303324475568</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.4891369219512727</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0981442439586775</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4368655501183706</v>
+        <v>0.1891927469111894</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.248830382306413</v>
+        <v>0.4570478324938768</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.03185057220549152</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>-0.2577539388102943</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.130310392683026</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>-0.3128838966008364</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-0.3646411986468536</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-0.08659509246065092</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>-0.2315504637589359</v>
+        <v>0.6067382515536669</v>
       </c>
     </row>
     <row r="10">
@@ -1508,109 +1218,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.296398348438619</v>
+        <v>0.2957046165021268</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.6086373220676217</v>
+        <v>-1.223922881308875</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.221164449715159</v>
+        <v>1.504445382523099</v>
       </c>
       <c r="E10" t="n">
-        <v>1.504819945661825</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2141296999117111</v>
+        <v>2.967127728954758</v>
       </c>
       <c r="G10" t="n">
-        <v>2.957956028561079</v>
+        <v>2.305278233156316</v>
       </c>
       <c r="H10" t="n">
-        <v>2.298844670105136</v>
+        <v>2.07781462405653</v>
       </c>
       <c r="I10" t="n">
-        <v>2.077100741024563</v>
+        <v>2.481706693823872</v>
       </c>
       <c r="J10" t="n">
-        <v>2.484312569781401</v>
+        <v>1.735825034286478</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.4730629921568287</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.011499265512334</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-2.185293923737469</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>0.3159605457332691</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.9312925100894996</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.660751506081562</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.7120986681850504</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.326179234350701</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>-1.549704966937891</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1167793200460198</v>
+        <v>0.6752150918795786</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9293784527593748</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.655685947101691</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.7105724869125425</v>
+        <v>1.248234308393638</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.7913868461426311</v>
+        <v>1.658422986843066</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.322515069771795</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-1.545895745456675</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.6737979928777064</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.244501565767964</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.653626788082522</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0.9598006390385579</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>-0.2315504637589359</v>
+        <v>0.9616197878572775</v>
       </c>
     </row>
     <row r="11">
@@ -1620,109 +1300,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1050292739212614</v>
+        <v>0.1046833134913433</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.4358525501691597</v>
+        <v>-0.5285160427229788</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5262724240217962</v>
+        <v>0.06023346763158076</v>
       </c>
       <c r="E11" t="n">
-        <v>0.06251148012744039</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2141296999117111</v>
+        <v>-0.2688016221451399</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2701804913637576</v>
+        <v>0.4744644238263558</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4731773961295207</v>
+        <v>-0.196819370863868</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1960996420384249</v>
+        <v>0.5004923415979325</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5030483883145077</v>
+        <v>-0.5137390883589218</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.2238564758177688</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.852333678205502</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>-1.589057880775858</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.6402067375583977</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1.074507859102803</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.8620726987014932</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>-1.185492413338189</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0.5427357879132352</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-1.156448075663122</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-1.025767234427298</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.073764743500308</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.859734687215493</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.184367260787876</v>
+        <v>-0.3559632382531545</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.3083128616390803</v>
+        <v>-0.5083472509166989</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.5414441995050682</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>-1.153402667801588</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>-1.025314844252778</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>-0.3562250467679259</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>-0.5071061250520406</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>-1.398401694846551</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>-0.2315504637589359</v>
+        <v>-1.401577713537859</v>
       </c>
     </row>
     <row r="12">
@@ -1732,109 +1382,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.004324482945800021</v>
+        <v>-0.004471716800532986</v>
       </c>
       <c r="C12" t="n">
-        <v>1.143893935759636</v>
+        <v>-1.025235213141476</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.022623870945627</v>
+        <v>-0.1439985203328764</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1414513331804523</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2141296999117111</v>
+        <v>-0.6732927910326272</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6736975563543621</v>
+        <v>-2.088674909235588</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.08275678743634</v>
+        <v>-0.196819370863868</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1960996420384249</v>
+        <v>-1.480722010628007</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.478215793152386</v>
+        <v>-1.378956058607153</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1.719095573852128</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0.5500503580606922</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.061583254324707</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>-0.06397790005110647</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-1.363762654551787</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.031059392189668</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-1.76704834691491</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-1.573675126215317</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>-0.4038083258764854</v>
       </c>
       <c r="U12" t="n">
-        <v>1.90617421719767</v>
+        <v>-1.692335764688764</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.362636350260676</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.025290830393228</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.765110638418499</v>
+        <v>-1.763343357537452</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.2940379601681752</v>
+        <v>-1.226372846465839</v>
       </c>
       <c r="Z12" t="n">
-        <v>-1.569649822980944</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>-0.4022247525164082</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>-1.691150772750324</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>-1.760560077451233</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>-1.223131068416657</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>-1.62822264249709</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>-0.2315504637589359</v>
+        <v>-1.631885470193009</v>
       </c>
     </row>
     <row r="13">
@@ -1844,109 +1464,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.004324482945800021</v>
+        <v>-0.004471716800532986</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1396500840575105</v>
+        <v>1.375574110547928</v>
       </c>
       <c r="D13" t="n">
-        <v>1.376408122519553</v>
+        <v>-0.3044665108763784</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3017078293509395</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2141296999117111</v>
+        <v>-0.2688016221451399</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2701804913637576</v>
+        <v>0.1083016619603638</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1080439413343977</v>
+        <v>0.5613919607762649</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5616338189825709</v>
+        <v>0.5004923415979325</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5030483883145077</v>
+        <v>-0.3406956943092757</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7308773664924498</v>
+        <v>-2.01900217123377</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.773863638298431</v>
+        <v>2.573048889085361</v>
       </c>
       <c r="M13" t="n">
-        <v>1.494127152502242</v>
+        <v>-0.5158330034449584</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1766254496756741</v>
+        <v>0.4482401156064248</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0.0657705751663259</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.5254248060057426</v>
+        <v>-0.008327076458257148</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.525168461254189</v>
+        <v>0.4849613356755301</v>
       </c>
       <c r="S13" t="n">
-        <v>1.980990861825762</v>
+        <v>-0.03850415927807428</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.01764046327420183</v>
+        <v>-0.1726091342044169</v>
       </c>
       <c r="U13" t="n">
-        <v>1.27701631285428</v>
+        <v>0.4445204017295771</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.06636377869517085</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.008494497519726144</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.4837525130257369</v>
+        <v>-0.217774880956173</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.3866146980367787</v>
+        <v>0.1620890674504618</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.03854962866548254</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>-0.1714746136019052</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.4433568510565832</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>-0.2183356817515861</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0.1614621402913289</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0.1675035413184905</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>-0.2315504637589359</v>
+        <v>0.1676444385877339</v>
       </c>
     </row>
     <row r="14">
@@ -1956,109 +1546,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-1.207215808483476</v>
+        <v>-1.205177050011172</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.349143487346745</v>
+        <v>-1.704084746046756</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.700970848408195</v>
+        <v>-0.1439985203328764</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1414513331804523</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2141296999117111</v>
+        <v>1.551408637848553</v>
       </c>
       <c r="G14" t="n">
-        <v>1.545646301093963</v>
+        <v>1.328844201513671</v>
       </c>
       <c r="H14" t="n">
-        <v>1.325155457318141</v>
+        <v>0.5613919607762649</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5616338189825709</v>
+        <v>0.9957959296544173</v>
       </c>
       <c r="J14" t="n">
-        <v>0.998364433681231</v>
+        <v>-0.5714202197088039</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>0.7222695084958886</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0.06957355080745331</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>0.4381446652936191</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>0.1912356217363007</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.010673614877703</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.867599903306541</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>0.6493779714812621</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.005159679126696</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>-1.319376551921011</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.099802436887413</v>
+        <v>0.2380200204875473</v>
       </c>
       <c r="V14" t="n">
-        <v>1.008654397868557</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.861927319595536</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6479394242128244</v>
+        <v>0.7338564181252707</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.8257322415274252</v>
+        <v>0.844973927888093</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.002346753689622</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>-1.316014691908324</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0.2370834270390244</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0.731236613098185</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0.8424442620295582</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.185799216970234</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>-0.2315504637589359</v>
+        <v>1.188097078212216</v>
       </c>
     </row>
     <row r="15">
@@ -2068,781 +1628,571 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.6604470241481688</v>
+        <v>-0.6594018985517905</v>
       </c>
       <c r="C15" t="n">
-        <v>1.736298867982935</v>
+        <v>-1.720642051727373</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.717515896638989</v>
+        <v>-0.3044665108763784</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3017078293509395</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2141296999117111</v>
+        <v>2.158145391179784</v>
       </c>
       <c r="G15" t="n">
-        <v>2.150921898579869</v>
+        <v>2.061169725245655</v>
       </c>
       <c r="H15" t="n">
-        <v>2.055422366908387</v>
+        <v>2.07781462405653</v>
       </c>
       <c r="I15" t="n">
-        <v>2.077100741024563</v>
+        <v>1.986403105767387</v>
       </c>
       <c r="J15" t="n">
-        <v>1.988996524414678</v>
+        <v>1.043651458087894</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>-0.0253500405212911</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.5500503580606922</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.511369542624519</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-0.7030564382345432</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.523577913252349</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.320322132835318</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.058349107515832</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.802910090320242</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>0.2475047003659878</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.520693008884322</v>
       </c>
       <c r="V15" t="n">
-        <v>1.520879229113972</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.316255610113583</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.056339141559731</v>
+        <v>2.057857454652201</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.2044945498027004</v>
+        <v>2.026699832177155</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.797981791023942</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.2478232437389039</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.518346675174791</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.052372964804871</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>2.020877494683265</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.356905887530726</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>-0.2315504637589359</v>
+        <v>1.359566188614808</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.717997187710418</v>
+        <v>0.2957046165021268</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.3371183947986099</v>
+        <v>-1.223922881308875</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4931823275602075</v>
+        <v>-0.4211705039989253</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9657753676338224</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2141296999117111</v>
+        <v>-0.2688016221451399</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3350951061221493</v>
+        <v>-0.3799153538609588</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1080439413343977</v>
+        <v>-0.196819370863868</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5616338189825709</v>
+        <v>-0.9854184225715219</v>
       </c>
       <c r="J16" t="n">
-        <v>0.007732342947784333</v>
+        <v>-0.1099711689097475</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>-0.0253500405212911</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.670169559874002</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-0.3965857948526362</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.1821820575105373</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.7410522881324523</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.4658916386134428</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>-0.6172360619669081</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0.9496912270319396</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.5868930102292979</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.7646294859251103</v>
       </c>
       <c r="V16" t="n">
-        <v>1.631682797429432</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.7661348294735219</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.21389429469007</v>
+        <v>-0.5018897694240008</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.2992787341338696</v>
+        <v>-0.5492145228381278</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.207620467972968</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>-0.05888767106370112</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.810644181009191</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.22120685422839</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.141104269015315</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.363543237908921</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>-0.2315504637589359</v>
+        <v>-0.5158660314194312</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.296398348438619</v>
+        <v>1.714720010296518</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.4605360890117971</v>
+        <v>-0.4954014313617456</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.221164449715159</v>
+        <v>0.9646894143313194</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4182580083840211</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2141296999117111</v>
+        <v>0.337935131186091</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2701804913637576</v>
+        <v>0.1083016619603638</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3788006650590997</v>
+        <v>0.5613919607762649</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1960996420384249</v>
+        <v>0.00518875354144776</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9828997477856625</v>
+        <v>1.562781640236832</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.329421570623875</v>
+        <v>-0.274556556860351</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2712300321775298</v>
+        <v>-0.06957355080745331</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.527476648196155</v>
+        <v>0.4381446652936191</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4325916386161665</v>
+        <v>0.01285480229752424</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.634528462693829</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.5846807428063197</v>
+        <v>0.7685821963735053</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.1289943150260587</v>
+        <v>1.216124706339477</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.911468612557419</v>
+        <v>1.210979159532454</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.476122415865154</v>
+        <v>-0.05980309113933777</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.426032461361761</v>
+        <v>1.813312121978407</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.7407509159511985</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.4647162742869412</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6169048830493199</v>
+        <v>1.224889085787244</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.2840031122443358</v>
+        <v>1.144468423673357</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.9473205255506831</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>-0.5849538357886888</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>-0.7644641029621418</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>-0.5018358428999141</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>-0.5478595274995232</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>-0.5145621703514944</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>-0.2315504637589359</v>
+        <v>1.366217598294228</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.296398348438619</v>
+        <v>-0.6321131409788215</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.6086373220676217</v>
+        <v>0.3159065469884668</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8075382439453</v>
+        <v>-0.3336425091570151</v>
       </c>
       <c r="E18" t="n">
-        <v>1.504819945661825</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2141296999117111</v>
+        <v>-0.2688016221451399</v>
       </c>
       <c r="G18" t="n">
-        <v>2.352680431075172</v>
+        <v>-0.2578610999056282</v>
       </c>
       <c r="H18" t="n">
-        <v>2.542266973301885</v>
+        <v>0.5613919607762649</v>
       </c>
       <c r="I18" t="n">
-        <v>1.319367280003567</v>
+        <v>0.9957959296544173</v>
       </c>
       <c r="J18" t="n">
-        <v>1.988996524414678</v>
+        <v>1.851187296986242</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-3.26503475292907</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-1.751242376193789</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-1.469810672183536</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.1710871858057174</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.2593551171263855</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>0.04993897772909629</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>-0.03422434457187035</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.07909712001744847</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.9886965477301066</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.6767118386123446</v>
       </c>
       <c r="V18" t="n">
-        <v>2.519747592482668</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.703593444139741</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.589818205789081</v>
+        <v>-0.2894429041752938</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.834287265197876</v>
+        <v>0.3009116032273241</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.633767463594336</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>-0.07069303763565396</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.726750916603378</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.98989263983452</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>2.682768039510283</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>2.315070661266045</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>-0.2315504637589359</v>
+        <v>-0.006182645569333367</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.6331085849314034</v>
+        <v>0.2957046165021268</v>
       </c>
       <c r="C19" t="n">
-        <v>-1.497244720402569</v>
+        <v>-0.8099902392934607</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3175250357487154</v>
+        <v>1.504445382523099</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3308453741092098</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2141296999117111</v>
+        <v>2.360390975623528</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2701804913637576</v>
+        <v>2.549386741066977</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2570895134607253</v>
+        <v>1.319603292416398</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5616338189825709</v>
+        <v>1.986403105767387</v>
       </c>
       <c r="J19" t="n">
-        <v>0.998364433681231</v>
+        <v>2.947128792634002</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.9714760248349484</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.150646367127241</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>0.7958862910705856</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.005769724956744</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.523771277241745</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.711743281307598</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.592574597106977</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.640917886201839</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.0716314316190774</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.053198147676791</v>
+        <v>1.729326552019747</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2583312051369537</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.04960056701360126</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.03470775563653992</v>
+        <v>1.995241650525383</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.4435870561097839</v>
+        <v>2.69043977174481</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.07873981039963396</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>-0.9859769597196688</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0.6752930945893728</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>-0.2898486399121847</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0.2998978714595746</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>-0.005956118870570808</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>-0.2315504637589359</v>
+        <v>2.319760556451635</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>GrNwFMem</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1050292739212614</v>
+        <v>1.714720010296518</v>
       </c>
       <c r="C20" t="n">
-        <v>-1.29977640966147</v>
+        <v>-0.03179687230448136</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.204619401484364</v>
+        <v>1.562797379084372</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9657753676338224</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2141296999117111</v>
+        <v>-2.49350305102632</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.077214621344967</v>
+        <v>-2.821000432967572</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.08275678743634</v>
+        <v>-1.713242034144134</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-0.9854184225715219</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-2.647940948304558</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.4730629921568287</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.670169559874002</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>0.4381446652936191</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-0.6490884794752877</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-1.321053650559085</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.072443543739898</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>-0.7065155778283757</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-1.598066134827456</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.2655461482766159</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2051176610099886</v>
+        <v>-1.291735647243869</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.972320239935639</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-2.517920801076223</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.095259360617531</v>
+        <v>-1.720770651494317</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.2413396108989852</v>
+        <v>-1.352156132229058</v>
       </c>
       <c r="Z20" t="n">
-        <v>-2.525516368104564</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>-0.1760628333190938</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>-2.335032658375503</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>-1.043060355172216</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>-1.431863122345954</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>-2.403933335932738</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>-0.2315504637589359</v>
+        <v>-0.9746773407920279</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>8x0Cb1B6</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.717997187710418</v>
+        <v>0.1046833134913433</v>
       </c>
       <c r="C21" t="n">
-        <v>1.242628091130186</v>
+        <v>-1.207365575628259</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.02992097709796582</v>
+        <v>0.9646894143313194</v>
       </c>
       <c r="E21" t="n">
-        <v>1.563095035178365</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2141296999117111</v>
+        <v>-1.077783959920114</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.489524348812083</v>
+        <v>-2.088674909235588</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.813023697026587</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.711566564080417</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9828997477856625</v>
+        <v>-1.494318321306917</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1.220682541174008</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-1.150646367127241</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.749863959809163</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>0.698438915562221</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-1.974255290966436</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.525139307526768</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>-2.097659001729367</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-2.532083056531371</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-0.1772062828554125</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>-2.336926096621772</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.319983924784525</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-1.069488170420975</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7060596566507752</v>
+        <v>-1.044287845380814</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.441500516573364</v>
+        <v>-1.435688120635636</v>
       </c>
       <c r="Z21" t="n">
-        <v>-1.593976154594746</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0.2658296501691698</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>-1.29099094064646</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>-1.718079484164353</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>-1.348563881150783</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>-0.9724036753194831</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>-0.2315504637589359</v>
+        <v>-2.409239281692511</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:AJ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,451 +436,1965 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_team_away</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>h2h_35_segun_loc</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>h2h_35</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>h2h_3_segun_loc</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>h2h_3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_match_mean_rat_player_start_home_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>is_rival_match</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.8777119591355431</v>
+        <v>-0.1410166790296269</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.8099902392934607</v>
+        <v>-0.9295233270219083</v>
       </c>
       <c r="D2" t="n">
-        <v>1.504445382523099</v>
+        <v>1.624583845981469</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2130278742385446</v>
+        <v>0.4121620172266851</v>
       </c>
       <c r="F2" t="n">
-        <v>2.360390975623528</v>
+        <v>-0.2141296999117111</v>
       </c>
       <c r="G2" t="n">
-        <v>2.549386741066977</v>
+        <v>2.756197496065776</v>
       </c>
       <c r="H2" t="n">
-        <v>1.319603292416398</v>
+        <v>1.812000063711638</v>
       </c>
       <c r="I2" t="n">
-        <v>1.986403105767387</v>
+        <v>1.319367280003567</v>
       </c>
       <c r="J2" t="n">
-        <v>2.947128792634002</v>
+        <v>0.998364433681231</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9714760248349484</v>
+        <v>2.771076657903333</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.150646367127241</v>
+        <v>0.2712300321775298</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7958862910705856</v>
+        <v>1.366007922700148</v>
       </c>
       <c r="N2" t="n">
-        <v>1.005769724956744</v>
+        <v>-2.38303643972925</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8832386718168479</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.523771277241745</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.711743281307598</v>
+        <v>-0.4144142511245363</v>
       </c>
       <c r="R2" t="n">
-        <v>1.592574597106977</v>
+        <v>-0.1289943150260587</v>
       </c>
       <c r="S2" t="n">
-        <v>2.640917886201839</v>
+        <v>-0.6800718546067644</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0716314316190774</v>
+        <v>-2.080809249933487</v>
       </c>
       <c r="U2" t="n">
-        <v>1.729326552019747</v>
+        <v>-0.03372932119444755</v>
       </c>
       <c r="V2" t="n">
-        <v>1.54795682812886</v>
+        <v>-0.05244988721407477</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.5341779296084523</v>
+        <v>0.6617032516181389</v>
       </c>
       <c r="X2" t="n">
-        <v>1.995241650525383</v>
+        <v>0.7012487268397084</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.69043977174481</v>
+        <v>-0.2590704155609191</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.319760556451635</v>
+        <v>-0.239911641898062</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.3930179281551214</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.2158737757403636</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-0.5661054720734803</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.6721891065193775</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.3120446446583533</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-0.2315504637589359</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1319720710643124</v>
+        <v>-0.004324482945800021</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3159065469884668</v>
+        <v>1.242628091130186</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3336425091570151</v>
+        <v>1.376408122519553</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2130278742385446</v>
+        <v>1.956451889415015</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2688016221451399</v>
+        <v>-0.2141296999117111</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2578610999056282</v>
+        <v>-0.2701804913637576</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5613919607762649</v>
+        <v>0.3514662445311464</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9957959296544173</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.851187296986242</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.26503475292907</v>
+        <v>2.261026835050612</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.751242376193789</v>
+        <v>-1.773863638298431</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.469810672183536</v>
+        <v>1.494127152502242</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1710871858057174</v>
+        <v>0.4325916386161665</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7530649221800305</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2593551171263855</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.04993897772909629</v>
+        <v>-0.4699195285651395</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.03422434457187035</v>
+        <v>-1.059777079178146</v>
       </c>
       <c r="S3" t="n">
-        <v>0.07909712001744847</v>
+        <v>0.939705451047817</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9886965477301066</v>
+        <v>0.3262210011690123</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6767118386123446</v>
+        <v>1.510037758907387</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.007888742154263037</v>
+        <v>0.1768067745757343</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.056874010323365</v>
+        <v>0.08768825816194689</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2894429041752938</v>
+        <v>0.7741648071810402</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3009116032273241</v>
+        <v>-0.5343585892310004</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.006182645569333367</v>
+        <v>0.03302688316610842</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-0.2413610967439022</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.5922453718865184</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-0.4863552564196948</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.1020527486196343</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.4168870337174381</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-0.2315504637589359</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.469121192139797</v>
+        <v>-0.6604470241481688</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.207365575628259</v>
+        <v>-0.3371183947986099</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9646894143313194</v>
+        <v>-1.469340173177074</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2130278742385446</v>
+        <v>0.9657753676338224</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.077783959920114</v>
+        <v>-0.2141296999117111</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.088674909235588</v>
+        <v>-0.06842195886845531</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.229755092932772</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.5616338189825709</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.494318321306917</v>
+        <v>0.5030483883145077</v>
       </c>
       <c r="K4" t="n">
-        <v>1.220682541174008</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.150646367127241</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.749863959809163</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.698438915562221</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4019729088765895</v>
+        <v>0.0259029127667809</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.974255290966436</v>
+        <v>1.864405791522107</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.525139307526768</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-2.097659001729367</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.532083056531371</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1772062828554125</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.336926096621772</v>
+        <v>-0.6019334555042497</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.174772919866605</v>
+        <v>0.6515910443906093</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.4470619161559669</v>
+        <v>0.4256548211297552</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.044287845380814</v>
+        <v>0.4772700100802098</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.435688120635636</v>
+        <v>-0.361371538334707</v>
       </c>
       <c r="Z4" t="n">
-        <v>-2.409239281692511</v>
+        <v>0.8689325025727429</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0.1504619174396009</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.6665552087078406</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.6264604202787447</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.4400412836800868</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.6413695344448664</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.2315504637589359</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.7139794136977287</v>
+        <v>0.05035239548773072</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.03179687230448136</v>
+        <v>0.230602998582051</v>
       </c>
       <c r="D5" t="n">
-        <v>1.562797379084372</v>
+        <v>1.111687350826844</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2130278742385446</v>
+        <v>1.504819945661825</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.49350305102632</v>
+        <v>-0.2141296999117111</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.821000432967572</v>
+        <v>1.142129236103358</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.713242034144134</v>
+        <v>0.229755092932772</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9854184225715219</v>
+        <v>0.5616338189825709</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.647940948304558</v>
+        <v>0.5030483883145077</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4730629921568287</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.670169559874002</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4381446652936191</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6490884794752877</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4374345966721875</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.321053650559085</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.072443543739898</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.7065155778283757</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.598066134827456</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2655461482766159</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.291735647243869</v>
+        <v>0.1979681393697227</v>
       </c>
       <c r="V5" t="n">
+        <v>-0.09474155729465943</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.06724614626961115</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.1394922973434939</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.04952344159435</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.01133409179215867</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.7665653925516784</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.3808636073416838</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.8325223785677111</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1029082303075219</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.04717561665654878</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0xK7DDE5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.47195123475953</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.09028300637223562</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.204619401484364</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.956451889415015</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1.077214621344967</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-2.813023697026587</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.9538331030594207</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-2.468847883885833</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.750977012197891</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.7513168030604506</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.109769463095961</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.688557827556659</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.08138258648091765</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-1.059777079178146</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-1.142865370508073</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.357805394498655</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.6104574001758863</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.1119699999232877</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-1.376179191351831</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-1.066815799262983</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.9532936543196771</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0.8940781599622004</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.6493986757413511</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0.7881125850188675</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.5163678211813261</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.1677818915541333</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.7005077893915066</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SjzlgqTj</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.47195123475953</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1.349143487346745</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.320434739099925</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.1414513331804523</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7386121711127538</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3514662445311464</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.2460965936201191</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.733303070731202</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.496619699868751</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.576955014588211</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.1111688737207897</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.56282696202111</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-0.9648573750626364</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.386800644276254</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.9535467089881503</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.287075475603183</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>2.366110837641378</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>d4DGBiqI</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.1410166790296269</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.7320550162808089</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.1126462182519375</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.3599829188674802</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.133336573626847</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.1353783618623509</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.1960996420384249</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.007732342947784333</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.020692722195863</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-0.4891369219512727</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.0981442439586775</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.4368655501183706</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-1.248830382306413</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0.03185057220549152</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0.2577539388102943</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.130310392683026</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0.3128838966008364</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0.3646411986468536</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-0.08659509246065092</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ELeQ0zVa</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.6604470241481688</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-1.694713031143669</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.717515896638989</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.563095035178365</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.06842195886845531</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.1353783618623509</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.1960996420384249</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.4875837024189391</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.2178279217037928</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.3568259336705719</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.5069887868232915</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.7870045200498109</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.8496846663855581</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.479025517889911</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.9694752051124241</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.8469227488290401</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.1877514075408666</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.4555990545521446</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.6056692273940188</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>WdSjHeFt</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.296398348438619</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.6086373220676217</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.221164449715159</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.504819945661825</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.957956028561079</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.298844670105136</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.077100741024563</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.484312569781401</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.9293784527593748</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.655685947101691</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.7105724869125425</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.7913868461426311</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.322515069771795</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-1.545895745456675</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.6737979928777064</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.244501565767964</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.653626788082522</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.9598006390385579</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EaryFQkA</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.1050292739212614</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.4358525501691597</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.5262724240217962</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.06251148012744039</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.2701804913637576</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.4731773961295207</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.1960996420384249</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5030483883145077</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-1.073764743500308</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.859734687215493</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-1.184367260787876</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.3083128616390803</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.5414441995050682</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-1.153402667801588</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-1.025314844252778</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-0.3562250467679259</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0.5071061250520406</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-1.398401694846551</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fZZxp2dD</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.3050473143302191</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.143893935759636</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-1.022623870945627</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.1414513331804523</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.6736975563543621</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-2.08275678743634</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.1960996420384249</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-1.478215793152386</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.90617421719767</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-1.362636350260676</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-2.025290830393228</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-1.765110638418499</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0.2940379601681752</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-1.569649822980944</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.4022247525164082</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-1.957618660823569</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.7828368977662553</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-1.691150772750324</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-1.874903426494011</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.2324429887734203</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-1.760560077451233</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-1.223131068416657</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-1.62822264249709</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>0hYMmpcl</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.9338314163158226</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.1396500840575105</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.376408122519553</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.3017078293509395</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.2701804913637576</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1080439413343977</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5616338189825709</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.5030483883145077</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.7308773664924498</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-1.773863638298431</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.494127152502242</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1766254496756741</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.5254248060057426</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-1.525168461254189</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.980990861825762</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.01764046327420183</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.27701631285428</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.06636377869517085</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.008494497519726144</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.4837525130257369</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0.3866146980367787</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.03854962866548254</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.1714746136019052</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0.007482881738491608</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.0007632051479246862</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.4433568510565832</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.158995435558079</v>
       </c>
-      <c r="W5" t="n">
-        <v>-0.7084099565134231</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-1.720770651494317</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-1.352156132229058</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-0.9746773407920279</v>
+      <c r="AF13" t="n">
+        <v>-0.5341779296084523</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-0.2183356817515861</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.1614621402913289</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.1675035413184905</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>UilLdutJ</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.854689383794245</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.736298867982935</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.717515896638989</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.3017078293509395</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.150921898579869</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.055422366908387</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.077100741024563</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.988996524414678</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.520879229113972</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.316255610113583</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.056339141559731</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.2044945498027004</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.797981791023942</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.2478232437389039</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.1695402544417907</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.518346675174791</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.052372964804871</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.020877494683265</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.356905887530726</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2uc40Ntf</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.6517980582565688</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-1.349143487346745</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-1.700970848408195</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.1414513331804523</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.545646301093963</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.325155457318141</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.5616338189825709</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.998364433681231</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-1.099802436887413</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.008654397868557</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.861927319595536</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.6479394242128244</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.8257322415274252</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.002346753689622</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-1.316014691908324</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.5286085508236101</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.2370834270390244</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.731236613098185</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.8424442620295582</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.185799216970234</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>M7MVoOR0</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.553966552409826</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.3371183947986099</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.4931823275602075</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9657753676338224</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.3350951061221493</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1080439413343977</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.5616338189825709</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.007732342947784333</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.631682797429432</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.7661348294735219</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.21389429469007</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0.2992787341338696</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.207620467972968</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.05888767106370112</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.4024269433345589</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.2044282292672814</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.810644181009191</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0.007888742154263037</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.585645064402025</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.22120685422839</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.141104269015315</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.363543237908921</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>dbt7KrYP</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.089213085724815</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.4605360890117971</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.221164449715159</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.4182580083840211</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.2701804913637576</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.3788006650590997</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.1960996420384249</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.9828997477856625</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-2.329421570623875</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.2712300321775298</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-4.527476648196155</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.4325916386161665</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.5846807428063197</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0.1289943150260587</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.911468612557419</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.476122415865154</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-1.426032461361761</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-0.7407509159511985</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.4647162742869412</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.6169048830493199</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0.2840031122443358</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0.9473205255506831</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.5849538357886888</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-0.4378201067321261</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.9783553209208383</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.7644641029621418</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-0.5913308310104343</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0.3163878959772388</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-0.5018358428999141</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-0.5478595274995232</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0.5145621703514944</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-0.2315504637589359</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ17"/>
+  <dimension ref="A1:Z17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,172 +436,122 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>id_team_home</t>
+          <t>id_team_away</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>id_team_away</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_home</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>is_cup</t>
+          <t>h2h_35_segun_loc</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>h2h_35_segun_loc</t>
+          <t>h2h_35</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>h2h_35</t>
+          <t>h2h_3_segun_loc</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>h2h_3_segun_loc</t>
+          <t>h2h_3</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>h2h_3</t>
+          <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goals</t>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goals_against</t>
+          <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_fouls</t>
+          <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_fouls_against</t>
+          <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
+          <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
+          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_ball_possession</t>
+          <t>dif_mean_val_player_start</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
+          <t>dif_mean_pot_player_start</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts</t>
+          <t>dif_mean_val_player_sub</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
+          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_home_against</t>
+          <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_sub</t>
+          <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_val_player_start</t>
+          <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_pot_player_start</t>
+          <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_age_player_sub</t>
+          <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
           <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>is_rival_match</t>
         </is>
       </c>
     </row>
@@ -612,109 +562,79 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1410166790296269</v>
+        <v>-0.1409155046653783</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.9295233270219083</v>
+        <v>1.623933695757177</v>
       </c>
       <c r="D2" t="n">
-        <v>1.624583845981469</v>
+        <v>0.4103454469992215</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4121620172266851</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2141296999117111</v>
+        <v>2.764882144511015</v>
       </c>
       <c r="G2" t="n">
-        <v>2.756197496065776</v>
+        <v>1.817061217334993</v>
       </c>
       <c r="H2" t="n">
-        <v>1.812000063711638</v>
+        <v>1.319603292416398</v>
       </c>
       <c r="I2" t="n">
-        <v>1.319367280003567</v>
+        <v>0.9957959296544173</v>
       </c>
       <c r="J2" t="n">
-        <v>0.998364433681231</v>
+        <v>-0.2253334316095116</v>
       </c>
       <c r="K2" t="n">
-        <v>2.771076657903333</v>
+        <v>-0.5237630731994108</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2712300321775298</v>
+        <v>-0.189692752620763</v>
       </c>
       <c r="M2" t="n">
-        <v>1.366007922700148</v>
+        <v>-2.662282758106758</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.38303643972925</v>
+        <v>-0.1050562870029181</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0.05183822688398863</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4144142511245363</v>
+        <v>0.6638432478402458</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.1289943150260587</v>
+        <v>0.7027618626312362</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6800718546067644</v>
+        <v>-0.2404015385001411</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.080809249933487</v>
+        <v>0.3929819418100262</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.03372932119444755</v>
+        <v>0.216787032767272</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.05244988721407477</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6617032516181389</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7012487268397084</v>
+        <v>-0.5662987575901934</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.2590704155609191</v>
+        <v>-0.6738914923311381</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.239911641898062</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.3930179281551214</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.2158737757403636</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-0.5661054720734803</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-0.6721891065193775</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.3120446446583533</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-0.2315504637589359</v>
+        <v>0.3124917103224339</v>
       </c>
     </row>
     <row r="3">
@@ -724,109 +644,79 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.004324482945800021</v>
+        <v>-0.004471716800532986</v>
       </c>
       <c r="C3" t="n">
-        <v>1.242628091130186</v>
+        <v>1.375574110547928</v>
       </c>
       <c r="D3" t="n">
-        <v>1.376408122519553</v>
+        <v>1.956673355872968</v>
       </c>
       <c r="E3" t="n">
-        <v>1.956451889415015</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2141296999117111</v>
+        <v>-0.2688016221451399</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2701804913637576</v>
+        <v>0.3524101698710252</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3514662445311464</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-1.148231533207624</v>
       </c>
       <c r="K3" t="n">
-        <v>2.261026835050612</v>
+        <v>-0.8560384283181575</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.773863638298431</v>
+        <v>0.8513403297612547</v>
       </c>
       <c r="M3" t="n">
-        <v>1.494127152502242</v>
+        <v>0.7163881520090374</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4325916386161665</v>
+        <v>0.2622775143508074</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.1777225442662836</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.4699195285651395</v>
+        <v>0.0881387713629873</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.059777079178146</v>
+        <v>0.7757799646174626</v>
       </c>
       <c r="S3" t="n">
-        <v>0.939705451047817</v>
+        <v>0.03326265473348402</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3262210011690123</v>
+        <v>-0.2426316203760073</v>
       </c>
       <c r="U3" t="n">
-        <v>1.510037758907387</v>
+        <v>0.5935727406839464</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1768067745757343</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.08768825816194689</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7741648071810402</v>
+        <v>-0.4863756156280073</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.5343585892310004</v>
+        <v>-0.1021621109473967</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.03302688316610842</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-0.2413610967439022</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.5922453718865184</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-0.4863552564196948</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-0.1020527486196343</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.4168870337174381</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>-0.2315504637589359</v>
+        <v>0.4175561775670826</v>
       </c>
     </row>
     <row r="4">
@@ -836,109 +726,79 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.6604470241481688</v>
+        <v>-0.6594018985517905</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.3371183947986099</v>
+        <v>-1.472282466518124</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.469340173177074</v>
+        <v>0.9646894143313194</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9657753676338224</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2141296999117111</v>
+        <v>-0.06655603770139627</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.06842195886845531</v>
+        <v>0.2303559159156945</v>
       </c>
       <c r="H4" t="n">
-        <v>0.229755092932772</v>
+        <v>0.5613919607762649</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5616338189825709</v>
+        <v>0.5004923415979325</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5030483883145077</v>
+        <v>0.2361156191895449</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2.217508606530248</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.732214476392193</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.630616751216841</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.7651434704354582</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0259029127667809</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.864405791522107</v>
+        <v>0.6531366162405556</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>0.4271000623018968</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.4784697626372272</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.8713907163568377</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.1515555461527297</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6019334555042497</v>
+        <v>0.6679643386647403</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6515910443906093</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4256548211297552</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4772700100802098</v>
+        <v>0.6288530339423462</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.361371538334707</v>
+        <v>0.4414465915045138</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.8689325025727429</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-0.1504619174396009</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.6665552087078406</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.6264604202787447</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.4400412836800868</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.6413695344448664</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-0.2315504637589359</v>
+        <v>0.6425141793480427</v>
       </c>
     </row>
     <row r="5">
@@ -948,109 +808,79 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05035239548773072</v>
+        <v>0.05010579834540515</v>
       </c>
       <c r="C5" t="n">
-        <v>0.230602998582051</v>
+        <v>1.110657219658063</v>
       </c>
       <c r="D5" t="n">
-        <v>1.111687350826844</v>
+        <v>1.504445382523099</v>
       </c>
       <c r="E5" t="n">
-        <v>1.504819945661825</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2141296999117111</v>
+        <v>1.146917468961066</v>
       </c>
       <c r="G5" t="n">
-        <v>1.142129236103358</v>
+        <v>0.2303559159156945</v>
       </c>
       <c r="H5" t="n">
-        <v>0.229755092932772</v>
+        <v>0.5613919607762649</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5616338189825709</v>
+        <v>0.5004923415979325</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5030483883145077</v>
+        <v>0.005391093790016673</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1.220682541174008</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.251737669138954</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.5158330034449584</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.846693112980627</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.09418599693846595</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>0.06763649274791685</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.1402194430667265</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0.01121626380744741</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.7672563505965543</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1979681393697227</v>
+        <v>-0.3806069247661253</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.09474155729465943</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06724614626961115</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1394922973434939</v>
+        <v>0.8353618064932755</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.04952344159435</v>
+        <v>0.103371551423308</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.01133409179215867</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.7665653925516784</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-0.3808636073416838</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0.8325223785677111</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.1029082303075219</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-0.04717561665654878</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-0.2315504637589359</v>
+        <v>-0.04748945490324837</v>
       </c>
     </row>
     <row r="6">
@@ -1060,109 +890,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.47195123475953</v>
+        <v>1.469121192139797</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.09028300637223562</v>
+        <v>-1.207365575628259</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.204619401484364</v>
+        <v>1.956673355872968</v>
       </c>
       <c r="E6" t="n">
-        <v>1.956451889415015</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2141296999117111</v>
+        <v>-1.077783959920114</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.077214621344967</v>
+        <v>-2.821000432967572</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.813023697026587</v>
+        <v>-0.9550307025040008</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9538331030594207</v>
+        <v>-2.471329186740976</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.468847883885833</v>
+        <v>0.5822024072888373</v>
       </c>
       <c r="K6" t="n">
-        <v>1.750977012197891</v>
+        <v>-0.7729695895384707</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7513168030604506</v>
+        <v>-0.5500503580606922</v>
       </c>
       <c r="M6" t="n">
-        <v>1.109769463095961</v>
+        <v>0.6766390824782634</v>
       </c>
       <c r="N6" t="n">
-        <v>0.688557827556659</v>
+        <v>-0.01603954730366944</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.1114372931261955</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.08138258648091765</v>
+        <v>-1.380037240173107</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.059777079178146</v>
+        <v>-1.067776477894671</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.142865370508073</v>
+        <v>-0.8963073046955959</v>
       </c>
       <c r="T6" t="n">
-        <v>1.357805394498655</v>
+        <v>-0.6514632634676368</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6104574001758863</v>
+        <v>-0.7883039877848043</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1119699999232877</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.376179191351831</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.066815799262983</v>
+        <v>0.518521715656671</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9532936543196771</v>
+        <v>-0.1680749083126769</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.8940781599622004</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-0.6493986757413511</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-0.7881125850188675</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.5163678211813261</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>-0.1677818915541333</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>-0.7005077893915066</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>-0.2315504637589359</v>
+        <v>-0.7022055223089936</v>
       </c>
     </row>
     <row r="7">
@@ -1172,109 +972,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.47195123475953</v>
+        <v>1.469121192139797</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.349143487346745</v>
+        <v>-1.323266715392575</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.320434739099925</v>
+        <v>-0.1439985203328764</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1414513331804523</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2141296999117111</v>
+        <v>0.7424263000735782</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7386121711127538</v>
+        <v>0.3524101698710252</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3514662445311464</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3.350896712083176</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.9391072670978439</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.252731017583201</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-2.026297645614373</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.8324036273495784</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.736283535464816</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.504160356735155</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.579693408176132</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.567130049562269</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.9675358631726646</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2460965936201191</v>
+        <v>1.389002241347</v>
       </c>
       <c r="V7" t="n">
-        <v>1.733303070731202</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.496619699868751</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.576955014588211</v>
+        <v>0.9566485599117556</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1111688737207897</v>
+        <v>1.290847489814226</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.56282696202111</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-0.9648573750626364</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.386800644276254</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0.9535467089881503</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.287075475603183</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>2.366110837641378</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>-0.2315504637589359</v>
+        <v>2.370908846633435</v>
       </c>
     </row>
     <row r="8">
@@ -1284,109 +1054,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.1410166790296269</v>
+        <v>-0.1409155046653783</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.7320550162808089</v>
+        <v>-0.1145834007075643</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1126462182519375</v>
+        <v>-0.3628185074376518</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3599829188674802</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2141296999117111</v>
+        <v>0.1356895467423473</v>
       </c>
       <c r="G8" t="n">
-        <v>0.133336573626847</v>
+        <v>-0.1358068459502975</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1353783618623509</v>
+        <v>-0.196819370863868</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1960996420384249</v>
+        <v>0.00518875354144776</v>
       </c>
       <c r="J8" t="n">
-        <v>0.007732342947784333</v>
+        <v>-0.6291013510586859</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.9714760248349484</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.651141660072405</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-0.7543274206296028</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.4602429451756123</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.489104527732015</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>0.09862553198384877</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.4380087701595549</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.03178729187682</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.2590563638356938</v>
       </c>
       <c r="U8" t="n">
-        <v>1.020692722195863</v>
+        <v>0.1311295065694522</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4891369219512727</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0981442439586775</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4368655501183706</v>
+        <v>-0.3125281093420729</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.248830382306413</v>
+        <v>-0.3654842618897111</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.03185057220549152</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>-0.2577539388102943</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0.130310392683026</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>-0.3128838966008364</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-0.3646411986468536</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>-0.08659509246065092</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>-0.2315504637589359</v>
+        <v>-0.08699242943092042</v>
       </c>
     </row>
     <row r="9">
@@ -1396,109 +1136,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.6604470241481688</v>
+        <v>-0.6594018985517905</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.694713031143669</v>
+        <v>-1.720642051727373</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.717515896638989</v>
+        <v>1.562797379084372</v>
       </c>
       <c r="E9" t="n">
-        <v>1.563095035178365</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2141296999117111</v>
+        <v>-0.06655603770139627</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.06842195886845531</v>
+        <v>-0.1358068459502975</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1353783618623509</v>
+        <v>-0.196819370863868</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1960996420384249</v>
+        <v>-0.4901148345150371</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4875837024189391</v>
+        <v>3.004809923983883</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.0253500405212911</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.612095274578883</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-0.3965857948526362</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.002850032898938158</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.3579804990886523</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>0.5086734160874546</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.7886376423661434</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.4804470766698585</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.9705610370728527</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2178279217037928</v>
+        <v>0.8485303324475568</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3568259336705719</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5069887868232915</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7870045200498109</v>
+        <v>0.1891927469111894</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.8496846663855581</v>
+        <v>0.4570478324938768</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.479025517889911</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.9694752051124241</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.8469227488290401</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.1877514075408666</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.4555990545521446</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0.6056692273940188</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>-0.2315504637589359</v>
+        <v>0.6067382515536669</v>
       </c>
     </row>
     <row r="10">
@@ -1508,109 +1218,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.296398348438619</v>
+        <v>0.2957046165021268</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.6086373220676217</v>
+        <v>-1.223922881308875</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.221164449715159</v>
+        <v>1.504445382523099</v>
       </c>
       <c r="E10" t="n">
-        <v>1.504819945661825</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2141296999117111</v>
+        <v>2.967127728954758</v>
       </c>
       <c r="G10" t="n">
-        <v>2.957956028561079</v>
+        <v>2.305278233156316</v>
       </c>
       <c r="H10" t="n">
-        <v>2.298844670105136</v>
+        <v>2.07781462405653</v>
       </c>
       <c r="I10" t="n">
-        <v>2.077100741024563</v>
+        <v>2.481706693823872</v>
       </c>
       <c r="J10" t="n">
-        <v>2.484312569781401</v>
+        <v>1.735825034286478</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.4730629921568287</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.011499265512334</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-2.185293923737469</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>0.3159605457332691</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.9312925100894996</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.660751506081562</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.7120986681850504</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.326179234350701</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>-1.549704966937891</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.6752150918795786</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9293784527593748</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.655685947101691</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.7105724869125425</v>
+        <v>1.248234308393638</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.7913868461426311</v>
+        <v>1.658422986843066</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.322515069771795</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-1.545895745456675</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.6737979928777064</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.244501565767964</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.653626788082522</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0.9598006390385579</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>-0.2315504637589359</v>
+        <v>0.9616197878572775</v>
       </c>
     </row>
     <row r="11">
@@ -1620,109 +1300,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1050292739212614</v>
+        <v>0.1046833134913433</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.4358525501691597</v>
+        <v>-0.5285160427229788</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5262724240217962</v>
+        <v>0.06023346763158076</v>
       </c>
       <c r="E11" t="n">
-        <v>0.06251148012744039</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2141296999117111</v>
+        <v>-0.2688016221451399</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2701804913637576</v>
+        <v>0.4744644238263558</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4731773961295207</v>
+        <v>-0.196819370863868</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1960996420384249</v>
+        <v>0.5004923415979325</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5030483883145077</v>
+        <v>-0.5137390883589218</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.2238564758177688</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.852333678205502</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>-1.589057880775858</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.6402067375583977</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1.074507859102803</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.8620726987014932</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>-1.185492413338189</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0.5427357879132352</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-1.156448075663122</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-1.025767234427298</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.073764743500308</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.859734687215493</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.184367260787876</v>
+        <v>-0.3559632382531545</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.3083128616390803</v>
+        <v>-0.5083472509166989</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.5414441995050682</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>-1.153402667801588</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>-1.025314844252778</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>-0.3562250467679259</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>-0.5071061250520406</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>-1.398401694846551</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>-0.2315504637589359</v>
+        <v>-1.401577713537859</v>
       </c>
     </row>
     <row r="12">
@@ -1732,109 +1382,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.3050473143302191</v>
+        <v>-0.3046480501031927</v>
       </c>
       <c r="C12" t="n">
-        <v>1.143893935759636</v>
+        <v>-1.025235213141476</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.022623870945627</v>
+        <v>-0.1439985203328764</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1414513331804523</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2141296999117111</v>
+        <v>-0.6732927910326272</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6736975563543621</v>
+        <v>-2.088674909235588</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.08275678743634</v>
+        <v>-0.196819370863868</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1960996420384249</v>
+        <v>-1.480722010628007</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.478215793152386</v>
+        <v>-1.378956058607153</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1.719095573852128</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0.5500503580606922</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.061583254324707</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>-0.06397790005110647</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-1.710530492661176</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-1.363762654551787</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.031059392189668</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-1.76704834691491</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-1.573675126215317</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>-0.4038083258764854</v>
       </c>
       <c r="U12" t="n">
-        <v>1.90617421719767</v>
+        <v>-1.692335764688764</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.362636350260676</v>
+        <v>-1.874903426494011</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.025290830393228</v>
+        <v>0.2324429887734203</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.765110638418499</v>
+        <v>-1.763343357537452</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.2940379601681752</v>
+        <v>-1.226372846465839</v>
       </c>
       <c r="Z12" t="n">
-        <v>-1.569649822980944</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>-0.4022247525164082</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>-1.957618660823569</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>-0.7828368977662553</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>-1.691150772750324</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>-1.874903426494011</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0.2324429887734203</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>-1.760560077451233</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>-1.223131068416657</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>-1.62822264249709</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>-0.2315504637589359</v>
+        <v>-1.631885470193009</v>
       </c>
     </row>
     <row r="13">
@@ -1844,109 +1464,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.9338314163158226</v>
+        <v>-0.9322894742814812</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1396500840575105</v>
+        <v>1.375574110547928</v>
       </c>
       <c r="D13" t="n">
-        <v>1.376408122519553</v>
+        <v>-0.3044665108763784</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3017078293509395</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2141296999117111</v>
+        <v>-0.2688016221451399</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2701804913637576</v>
+        <v>0.1083016619603638</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1080439413343977</v>
+        <v>0.5613919607762649</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5616338189825709</v>
+        <v>0.5004923415979325</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5030483883145077</v>
+        <v>-0.3406956943092757</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7308773664924498</v>
+        <v>-2.01900217123377</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.773863638298431</v>
+        <v>2.573048889085361</v>
       </c>
       <c r="M13" t="n">
-        <v>1.494127152502242</v>
+        <v>-0.5158330034449584</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1766254496756741</v>
+        <v>0.4482401156064248</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>0.01189434312501176</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0.0657705751663259</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.5254248060057426</v>
+        <v>-0.008327076458257148</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.525168461254189</v>
+        <v>0.4849613356755301</v>
       </c>
       <c r="S13" t="n">
-        <v>1.980990861825762</v>
+        <v>-0.03850415927807428</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.01764046327420183</v>
+        <v>-0.1726091342044169</v>
       </c>
       <c r="U13" t="n">
-        <v>1.27701631285428</v>
+        <v>0.4445204017295771</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.06636377869517085</v>
+        <v>1.158995435558079</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.008494497519726144</v>
+        <v>-0.5341779296084523</v>
       </c>
       <c r="X13" t="n">
-        <v>0.4837525130257369</v>
+        <v>-0.217774880956173</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.3866146980367787</v>
+        <v>0.1620890674504618</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.03854962866548254</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>-0.1714746136019052</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>-0.007482881738491608</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>-0.0007632051479246862</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.4433568510565832</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.158995435558079</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>-0.5341779296084523</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>-0.2183356817515861</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0.1614621402913289</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0.1675035413184905</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>-0.2315504637589359</v>
+        <v>0.1676444385877339</v>
       </c>
     </row>
     <row r="14">
@@ -1956,109 +1546,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.854689383794245</v>
+        <v>1.851163798161364</v>
       </c>
       <c r="C14" t="n">
-        <v>1.736298867982935</v>
+        <v>-1.720642051727373</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.717515896638989</v>
+        <v>-0.3044665108763784</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.3017078293509395</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2141296999117111</v>
+        <v>2.158145391179784</v>
       </c>
       <c r="G14" t="n">
-        <v>2.150921898579869</v>
+        <v>2.061169725245655</v>
       </c>
       <c r="H14" t="n">
-        <v>2.055422366908387</v>
+        <v>2.07781462405653</v>
       </c>
       <c r="I14" t="n">
-        <v>2.077100741024563</v>
+        <v>1.986403105767387</v>
       </c>
       <c r="J14" t="n">
-        <v>1.988996524414678</v>
+        <v>1.043651458087894</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>-0.0253500405212911</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0.5500503580606922</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.511369542624519</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>-0.7030564382345432</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-1.436968901095135</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.523577913252349</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.320322132835318</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.058349107515832</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.802910090320242</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>0.2475047003659878</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.520693008884322</v>
       </c>
       <c r="V14" t="n">
-        <v>1.520879229113972</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.316255610113583</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.056339141559731</v>
+        <v>2.057857454652201</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.2044945498027004</v>
+        <v>2.026699832177155</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.797981791023942</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.2478232437389039</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>-0.1695402544417907</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.518346675174791</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.052372964804871</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>2.020877494683265</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.356905887530726</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>-0.2315504637589359</v>
+        <v>1.359566188614808</v>
       </c>
     </row>
     <row r="15">
@@ -2068,109 +1628,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6517980582565688</v>
+        <v>0.6504584649507246</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.349143487346745</v>
+        <v>-1.704084746046756</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.700970848408195</v>
+        <v>-0.1439985203328764</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1414513331804523</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2141296999117111</v>
+        <v>1.551408637848553</v>
       </c>
       <c r="G15" t="n">
-        <v>1.545646301093963</v>
+        <v>1.328844201513671</v>
       </c>
       <c r="H15" t="n">
-        <v>1.325155457318141</v>
+        <v>0.5613919607762649</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5616338189825709</v>
+        <v>0.9957959296544173</v>
       </c>
       <c r="J15" t="n">
-        <v>0.998364433681231</v>
+        <v>-0.5714202197088039</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.7222695084958886</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.06957355080745331</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>0.4381446652936191</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>0.1912356217363007</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-1.183671131126578</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.010673614877703</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.867599903306541</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>0.6493779714812621</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.005159679126696</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-1.319376551921011</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.099802436887413</v>
+        <v>0.2380200204875473</v>
       </c>
       <c r="V15" t="n">
-        <v>1.008654397868557</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.861927319595536</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6479394242128244</v>
+        <v>0.7338564181252707</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.8257322415274252</v>
+        <v>0.844973927888093</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.002346753689622</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>-1.316014691908324</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>-0.5286085508236101</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0.2370834270390244</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0.731236613098185</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0.8424442620295582</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.185799216970234</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>-0.2315504637589359</v>
+        <v>1.188097078212216</v>
       </c>
     </row>
     <row r="16">
@@ -2180,109 +1710,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.553966552409826</v>
+        <v>1.550987464858704</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.3371183947986099</v>
+        <v>-0.4954014313617456</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4931823275602075</v>
+        <v>0.9646894143313194</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9657753676338224</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2141296999117111</v>
+        <v>0.337935131186091</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3350951061221493</v>
+        <v>0.1083016619603638</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1080439413343977</v>
+        <v>0.5613919607762649</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5616338189825709</v>
+        <v>0.00518875354144776</v>
       </c>
       <c r="J16" t="n">
-        <v>0.007732342947784333</v>
+        <v>1.562781640236832</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>-0.274556556860351</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.06957355080745331</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>0.4381446652936191</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.01285480229752424</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.3072608470353701</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.634528462693829</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>0.7685821963735053</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.216124706339477</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.210979159532454</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.05980309113933777</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.813312121978407</v>
       </c>
       <c r="V16" t="n">
-        <v>1.631682797429432</v>
+        <v>-0.007888742154263037</v>
       </c>
       <c r="W16" t="n">
-        <v>0.7661348294735219</v>
+        <v>1.585645064402025</v>
       </c>
       <c r="X16" t="n">
-        <v>1.21389429469007</v>
+        <v>1.224889085787244</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.2992787341338696</v>
+        <v>1.144468423673357</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.207620467972968</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>-0.05888767106370112</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0.4024269433345589</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>-0.2044282292672814</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.810644181009191</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>-0.007888742154263037</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.585645064402025</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.22120685422839</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.141104269015315</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.363543237908921</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>-0.2315504637589359</v>
+        <v>1.366217598294228</v>
       </c>
     </row>
     <row r="17">
@@ -2292,109 +1792,79 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.089213085724815</v>
+        <v>1.08707858611823</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.4605360890117971</v>
+        <v>-1.223922881308875</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.221164449715159</v>
+        <v>-0.4211705039989253</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4182580083840211</v>
+        <v>-0.2130278742385446</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2141296999117111</v>
+        <v>-0.2688016221451399</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2701804913637576</v>
+        <v>-0.3799153538609588</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3788006650590997</v>
+        <v>-0.196819370863868</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1960996420384249</v>
+        <v>-0.9854184225715219</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9828997477856625</v>
+        <v>-0.1099711689097475</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.329421570623875</v>
+        <v>-0.0253500405212911</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2712300321775298</v>
+        <v>-0.670169559874002</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.527476648196155</v>
+        <v>-0.3965857948526362</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4325916386161665</v>
+        <v>-0.1821820575105373</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.03876521086869965</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.7410522881324523</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.5846807428063197</v>
+        <v>-0.4658916386134428</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.1289943150260587</v>
+        <v>-0.6172360619669081</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.911468612557419</v>
+        <v>-0.9496912270319396</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.476122415865154</v>
+        <v>-0.5868930102292979</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.426032461361761</v>
+        <v>-0.7646294859251103</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.7407509159511985</v>
+        <v>-0.5913308310104343</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.4647162742869412</v>
+        <v>-0.3163878959772388</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6169048830493199</v>
+        <v>-0.5018897694240008</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.2840031122443358</v>
+        <v>-0.5492145228381278</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.9473205255506831</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>-0.5849538357886888</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>-0.4378201067321261</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>-0.9783553209208383</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>-0.7644641029621418</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>-0.5913308310104343</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>-0.3163878959772388</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>-0.5018358428999141</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>-0.5478595274995232</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>-0.5145621703514944</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>-0.2315504637589359</v>
+        <v>-0.5158660314194312</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -598,7 +598,7 @@
         <v>-2.662282758106758</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1050562870029181</v>
+        <v>-0.08815602316780975</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.6594018985517905</v>
+        <v>0.1319720710643124</v>
       </c>
       <c r="C4" t="n">
         <v>-1.472282466518124</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9646894143313194</v>
+        <v>-1.442330443821211</v>
       </c>
       <c r="E4" t="n">
         <v>-0.2130278742385446</v>
@@ -750,40 +750,40 @@
         <v>0.5004923415979325</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2361156191895449</v>
+        <v>-0.4752850007923335</v>
       </c>
       <c r="K4" t="n">
-        <v>2.217508606530248</v>
+        <v>1.885233251411501</v>
       </c>
       <c r="L4" t="n">
-        <v>1.732214476392193</v>
+        <v>1.331817137014494</v>
       </c>
       <c r="M4" t="n">
-        <v>1.630616751216841</v>
+        <v>0.5176428043551671</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7651434704354582</v>
+        <v>-0.4427684955461023</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6531366162405556</v>
+        <v>0.6315547122350521</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4271000623018968</v>
+        <v>0.4488989718038946</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4784697626372272</v>
+        <v>0.5086564613568327</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8713907163568377</v>
+        <v>0.8759710566501249</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1515555461527297</v>
+        <v>-0.1209990101366796</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6679643386647403</v>
+        <v>0.6908853955205636</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -792,13 +792,13 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6288530339423462</v>
+        <v>0.5674860116380969</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4414465915045138</v>
+        <v>0.3738122244275836</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.6425141793480427</v>
+        <v>0.6486849687657753</v>
       </c>
     </row>
     <row r="5">
@@ -814,7 +814,7 @@
         <v>1.110657219658063</v>
       </c>
       <c r="D5" t="n">
-        <v>1.504445382523099</v>
+        <v>-0.9609264721907048</v>
       </c>
       <c r="E5" t="n">
         <v>-0.2130278742385446</v>
@@ -832,16 +832,16 @@
         <v>0.5004923415979325</v>
       </c>
       <c r="J5" t="n">
-        <v>0.005391093790016673</v>
+        <v>-0.4945120445756281</v>
       </c>
       <c r="K5" t="n">
-        <v>1.220682541174008</v>
+        <v>0.3899941533771419</v>
       </c>
       <c r="L5" t="n">
-        <v>1.251737669138954</v>
+        <v>0.9714595315745645</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5158330034449584</v>
+        <v>-0.7543274206296028</v>
       </c>
       <c r="N5" t="n">
         <v>1.846693112980627</v>
@@ -850,22 +850,22 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.09418599693846595</v>
+        <v>-0.08505654130909829</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06763649274791685</v>
+        <v>0.06274347214403024</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1402194430667265</v>
+        <v>0.1439720481582368</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.01121626380744741</v>
+        <v>-0.01027842851034661</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7672563505965543</v>
+        <v>0.7777865197717574</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3806069247661253</v>
+        <v>-0.380332753332864</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8353618064932755</v>
+        <v>0.8375193471562661</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.103371551423308</v>
+        <v>0.1021643125372265</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.04748945490324837</v>
+        <v>-0.03887337244886817</v>
       </c>
     </row>
     <row r="6">
@@ -1050,23 +1050,23 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.1409155046653783</v>
+        <v>-0.6594018985517905</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1145834007075643</v>
+        <v>-1.720642051727373</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3628185074376518</v>
+        <v>1.562797379084372</v>
       </c>
       <c r="E8" t="n">
         <v>-0.2130278742385446</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1356895467423473</v>
+        <v>-0.06655603770139627</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1358068459502975</v>
@@ -1075,43 +1075,43 @@
         <v>-0.196819370863868</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00518875354144776</v>
+        <v>-0.4901148345150371</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6291013510586859</v>
+        <v>3.004809923983883</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9714760248349484</v>
+        <v>-0.0253500405212911</v>
       </c>
       <c r="L8" t="n">
-        <v>0.651141660072405</v>
+        <v>1.612095274578883</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7543274206296028</v>
+        <v>-0.3965857948526362</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4602429451756123</v>
+        <v>-0.7030564382345432</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.489104527732015</v>
+        <v>0.3579804990886523</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.09862553198384877</v>
+        <v>0.5086734160874546</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4380087701595549</v>
+        <v>0.7886376423661434</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.03178729187682</v>
+        <v>0.4804470766698585</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2590563638356938</v>
+        <v>0.9705610370728527</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1311295065694522</v>
+        <v>0.8485303324475568</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1120,35 +1120,35 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3125281093420729</v>
+        <v>0.1891927469111894</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.3654842618897111</v>
+        <v>0.4570478324938768</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.08699242943092042</v>
+        <v>0.6067382515536669</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.6594018985517905</v>
+        <v>-0.1409155046653783</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.720642051727373</v>
+        <v>-0.1145834007075643</v>
       </c>
       <c r="D9" t="n">
-        <v>1.562797379084372</v>
+        <v>0.8625734203490908</v>
       </c>
       <c r="E9" t="n">
         <v>-0.2130278742385446</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.06655603770139627</v>
+        <v>0.1356895467423473</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1358068459502975</v>
@@ -1157,43 +1157,43 @@
         <v>-0.196819370863868</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4901148345150371</v>
+        <v>0.00518875354144776</v>
       </c>
       <c r="J9" t="n">
-        <v>3.004809923983883</v>
+        <v>-0.7636906575417438</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0253500405212911</v>
+        <v>0.8053383472755751</v>
       </c>
       <c r="L9" t="n">
-        <v>1.612095274578883</v>
+        <v>-0.06957355080745331</v>
       </c>
       <c r="M9" t="n">
         <v>-0.3965857948526362</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.002850032898938158</v>
+        <v>0.4602429451756123</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3579804990886523</v>
+        <v>-0.5101640194634793</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5086734160874546</v>
+        <v>0.09893823364935267</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7886376423661434</v>
+        <v>0.4431656173423279</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4804470766698585</v>
+        <v>-0.03105690431341256</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9705610370728527</v>
+        <v>-0.2171943677661439</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8485303324475568</v>
+        <v>0.1339420797688852</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1891927469111894</v>
+        <v>-0.3252888430674349</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4570478324938768</v>
+        <v>-0.3654842618897111</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.6067382515536669</v>
+        <v>-0.08936479131529046</v>
       </c>
     </row>
     <row r="10">
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2957046165021268</v>
+        <v>1.08707858611823</v>
       </c>
       <c r="C10" t="n">
         <v>-1.223922881308875</v>
       </c>
       <c r="D10" t="n">
-        <v>1.504445382523099</v>
+        <v>0.8625734203490908</v>
       </c>
       <c r="E10" t="n">
         <v>-0.2130278742385446</v>
@@ -1242,40 +1242,40 @@
         <v>2.481706693823872</v>
       </c>
       <c r="J10" t="n">
-        <v>1.735825034286478</v>
+        <v>1.101332589437776</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4730629921568287</v>
+        <v>-0.274556556860351</v>
       </c>
       <c r="L10" t="n">
-        <v>1.011499265512334</v>
+        <v>-1.030527165313931</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.185293923737469</v>
+        <v>-1.469810672183536</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3159605457332691</v>
+        <v>0.2397411156432659</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9312925100894996</v>
+        <v>0.9480126068875719</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.660751506081562</v>
+        <v>1.66394862422726</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7120986681850504</v>
+        <v>0.7248003744305928</v>
       </c>
       <c r="S10" t="n">
-        <v>1.326179234350701</v>
+        <v>1.342049917131261</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.549704966937891</v>
+        <v>-1.525018666915829</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6752150918795786</v>
+        <v>0.6791792983314079</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1284,13 +1284,13 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.248234308393638</v>
+        <v>1.290620498328629</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.658422986843066</v>
+        <v>1.711503172786653</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.9616197878572775</v>
+        <v>0.9933554756223164</v>
       </c>
     </row>
     <row r="11">
@@ -1300,13 +1300,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1046833134913433</v>
+        <v>1.08707858611823</v>
       </c>
       <c r="C11" t="n">
         <v>-0.5285160427229788</v>
       </c>
       <c r="D11" t="n">
-        <v>0.06023346763158076</v>
+        <v>-1.442330443821211</v>
       </c>
       <c r="E11" t="n">
         <v>-0.2130278742385446</v>
@@ -1324,40 +1324,40 @@
         <v>0.5004923415979325</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5137390883589218</v>
+        <v>-0.3022416067426874</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2238564758177688</v>
+        <v>0.140787637038082</v>
       </c>
       <c r="L11" t="n">
-        <v>1.852333678205502</v>
+        <v>0.7712608618857147</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.589057880775858</v>
+        <v>-2.026297645614373</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6402067375583977</v>
+        <v>0.553011982445468</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.074507859102803</v>
+        <v>-1.061166363146078</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.8620726987014932</v>
+        <v>-0.8478361549396471</v>
       </c>
       <c r="R11" t="n">
-        <v>-1.185492413338189</v>
+        <v>-1.152044397962451</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5427357879132352</v>
+        <v>-0.5388597876857049</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.156448075663122</v>
+        <v>-1.07008597894394</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.025767234427298</v>
+        <v>-1.006124893570912</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1366,13 +1366,13 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3559632382531545</v>
+        <v>-0.3270113796198824</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.5083472509166989</v>
+        <v>-0.5100816720747272</v>
       </c>
       <c r="Z11" t="n">
-        <v>-1.401577713537859</v>
+        <v>-1.388855951425268</v>
       </c>
     </row>
     <row r="12">
@@ -1421,7 +1421,7 @@
         <v>-0.06397790005110647</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.710530492661176</v>
+        <v>-1.264726417516516</v>
       </c>
       <c r="P12" t="n">
         <v>-1.363762654551787</v>
@@ -1442,10 +1442,10 @@
         <v>-1.692335764688764</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.874903426494011</v>
+        <v>-2.341657097578948</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2324429887734203</v>
+        <v>0.03207615783270289</v>
       </c>
       <c r="X12" t="n">
         <v>-1.763343357537452</v>
@@ -1537,334 +1537,6 @@
       </c>
       <c r="Z13" t="n">
         <v>0.1676444385877339</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>UilLdutJ</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.851163798161364</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-1.720642051727373</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.3044665108763784</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.2130278742385446</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2.158145391179784</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.061169725245655</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.07781462405653</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.986403105767387</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.043651458087894</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-0.0253500405212911</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-0.5500503580606922</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.511369542624519</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-0.7030564382345432</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-1.436968901095135</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.523577913252349</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.320322132835318</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.058349107515832</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.802910090320242</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.2475047003659878</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.520693008884322</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.057857454652201</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.026699832177155</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.359566188614808</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>2uc40Ntf</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.6504584649507246</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-1.704084746046756</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-0.1439985203328764</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-0.2130278742385446</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1.551408637848553</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.328844201513671</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.5613919607762649</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.9957959296544173</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-0.5714202197088039</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.7222695084958886</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-0.06957355080745331</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.4381446652936191</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.1912356217363007</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-1.183671131126578</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.010673614877703</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.867599903306541</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.6493779714812621</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.005159679126696</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-1.319376551921011</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.2380200204875473</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.7338564181252707</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.844973927888093</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.188097078212216</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>M7MVoOR0</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1.550987464858704</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.4954014313617456</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.9646894143313194</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-0.2130278742385446</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.337935131186091</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.1083016619603638</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.5613919607762649</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.00518875354144776</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.562781640236832</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-0.274556556860351</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-0.06957355080745331</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.4381446652936191</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.01285480229752424</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-0.3072608470353701</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.634528462693829</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.7685821963735053</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.216124706339477</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.210979159532454</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-0.05980309113933777</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.813312121978407</v>
-      </c>
-      <c r="V16" t="n">
-        <v>-0.007888742154263037</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.585645064402025</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.224889085787244</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.144468423673357</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.366217598294228</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>dbt7KrYP</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.08707858611823</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-1.223922881308875</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-0.4211705039989253</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-0.2130278742385446</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-0.2688016221451399</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-0.3799153538609588</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.196819370863868</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-0.9854184225715219</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-0.1099711689097475</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-0.0253500405212911</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-0.670169559874002</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-0.3965857948526362</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-0.1821820575105373</v>
-      </c>
-      <c r="O17" t="n">
-        <v>-0.03876521086869965</v>
-      </c>
-      <c r="P17" t="n">
-        <v>-0.7410522881324523</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>-0.4658916386134428</v>
-      </c>
-      <c r="R17" t="n">
-        <v>-0.6172360619669081</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-0.9496912270319396</v>
-      </c>
-      <c r="T17" t="n">
-        <v>-0.5868930102292979</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-0.7646294859251103</v>
-      </c>
-      <c r="V17" t="n">
-        <v>-0.5913308310104343</v>
-      </c>
-      <c r="W17" t="n">
-        <v>-0.3163878959772388</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-0.5018897694240008</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>-0.5492145228381278</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>-0.5158660314194312</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -1272,7 +1272,7 @@
         <v>1.342049917131261</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.525018666915829</v>
+        <v>-1.525018666915819</v>
       </c>
       <c r="U10" t="n">
         <v>0.6791792983314079</v>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,13 +562,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1409155046653783</v>
+        <v>1.851163798161364</v>
       </c>
       <c r="C2" t="n">
         <v>1.623933695757177</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4103454469992215</v>
+        <v>-0.1439985203328764</v>
       </c>
       <c r="E2" t="n">
         <v>-0.2130278742385446</v>
@@ -586,40 +586,40 @@
         <v>0.9957959296544173</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2253334316095116</v>
+        <v>-0.8598258764582142</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5237630731994108</v>
+        <v>-1.022176105877531</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.189692752620763</v>
+        <v>-2.231719183447028</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.662282758106758</v>
+        <v>-2.185293923737469</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.08815602316780975</v>
+        <v>-0.2171060131235528</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.05183822688398863</v>
+        <v>0.03275263576375812</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6638432478402458</v>
+        <v>0.6670960307465499</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7027618626312362</v>
+        <v>0.7021162093978237</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2404015385001411</v>
+        <v>-0.1641126984364259</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3929819418100262</v>
+        <v>0.5619887914346774</v>
       </c>
       <c r="U2" t="n">
-        <v>0.216787032767272</v>
+        <v>0.1997472844878767</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -628,13 +628,13 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5662987575901934</v>
+        <v>-0.4749646264936156</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.6738914923311381</v>
+        <v>-0.7571043019097156</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.3124917103224339</v>
+        <v>0.2882028847382935</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.004471716800532986</v>
+        <v>-0.9322894742814812</v>
       </c>
       <c r="C3" t="n">
         <v>1.375574110547928</v>
@@ -668,40 +668,40 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.148231533207624</v>
+        <v>-1.2251397083408</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.8560384283181575</v>
+        <v>-0.6899007507587844</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8513403297612547</v>
+        <v>0.2907840546324759</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7163881520090374</v>
+        <v>0.7561372215398112</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2622775143508074</v>
+        <v>0.3052608443360562</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1777225442662836</v>
+        <v>0.1637596680440685</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0881387713629873</v>
+        <v>0.07172462291501054</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7757799646174626</v>
+        <v>0.7220611380267955</v>
       </c>
       <c r="S3" t="n">
-        <v>0.03326265473348402</v>
+        <v>0.02066417255738295</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2426316203760073</v>
+        <v>-0.3481790641352454</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5935727406839464</v>
+        <v>0.5983160252249133</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -710,13 +710,13 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.4863756156280073</v>
+        <v>-0.4612787566822334</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.1021621109473967</v>
+        <v>-0.1360060346661361</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.4175561775670826</v>
+        <v>0.3749736953624429</v>
       </c>
     </row>
     <row r="4">
@@ -768,22 +768,22 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6315547122350521</v>
+        <v>0.6269268673136388</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4488989718038946</v>
+        <v>0.4615754349629818</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5086564613568327</v>
+        <v>0.5265598592163208</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8759710566501249</v>
+        <v>0.875512712776369</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1209990101366796</v>
+        <v>-0.08964200102777327</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6908853955205636</v>
+        <v>0.693813490717845</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -792,13 +792,13 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5674860116380969</v>
+        <v>0.5362978999644579</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3738122244275836</v>
+        <v>0.3768973904697924</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.6486849687657753</v>
+        <v>0.6775412870208719</v>
       </c>
     </row>
     <row r="5">
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05010579834540515</v>
+        <v>-0.3046480501031927</v>
       </c>
       <c r="C5" t="n">
         <v>1.110657219658063</v>
@@ -832,40 +832,40 @@
         <v>0.5004923415979325</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4945120445756281</v>
+        <v>-0.379149781875864</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3899941533771419</v>
+        <v>0.3069253145974551</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9714595315745645</v>
+        <v>1.171658201263414</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7543274206296028</v>
+        <v>-0.277338586260314</v>
       </c>
       <c r="N5" t="n">
-        <v>1.846693112980627</v>
+        <v>1.717949773649812</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.08505654130909829</v>
+        <v>-0.08914326992887753</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06274347214403024</v>
+        <v>0.05337177585227463</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1439720481582368</v>
+        <v>0.1295783371213627</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.01027842851034661</v>
+        <v>-0.007753763559808019</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7777865197717574</v>
+        <v>0.7680250587234536</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.380332753332864</v>
+        <v>-0.3472247547293261</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8375193471562661</v>
+        <v>0.7521634155664599</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1021643125372265</v>
+        <v>0.127419451950377</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.03887337244886817</v>
+        <v>-0.04933275909304332</v>
       </c>
     </row>
     <row r="6">
@@ -932,22 +932,22 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1114372931261955</v>
+        <v>-0.1418814225652608</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.380037240173107</v>
+        <v>-1.377849709044232</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.067776477894671</v>
+        <v>-1.057616510489455</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8963073046955959</v>
+        <v>-0.9346190975891642</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6514632634676368</v>
+        <v>-0.6820796760870795</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7883039877848043</v>
+        <v>-0.8060108042112075</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -956,13 +956,13 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.518521715656671</v>
+        <v>0.4614766711625282</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.1680749083126769</v>
+        <v>-0.1594488253317864</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.7022055223089936</v>
+        <v>-0.6863795268624296</v>
       </c>
     </row>
     <row r="7">
@@ -978,7 +978,7 @@
         <v>-1.323266715392575</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1439985203328764</v>
+        <v>-1.63197443264535</v>
       </c>
       <c r="E7" t="n">
         <v>-0.2130278742385446</v>
@@ -996,16 +996,16 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3.350896712083176</v>
+        <v>2.197274085085535</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9391072670978439</v>
+        <v>-1.188313783436904</v>
       </c>
       <c r="L7" t="n">
-        <v>2.252731017583201</v>
+        <v>1.812293944267733</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.026297645614373</v>
+        <v>-1.867301367491277</v>
       </c>
       <c r="N7" t="n">
         <v>0.8324036273495784</v>
@@ -1014,22 +1014,22 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.736283535464816</v>
+        <v>1.721612495762787</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.504160356735155</v>
+        <v>2.495848819470343</v>
       </c>
       <c r="R7" t="n">
-        <v>1.579693408176132</v>
+        <v>1.572750262191843</v>
       </c>
       <c r="S7" t="n">
-        <v>1.567130049562269</v>
+        <v>1.546573823570957</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9675358631726646</v>
+        <v>-0.9664069531439723</v>
       </c>
       <c r="U7" t="n">
-        <v>1.389002241347</v>
+        <v>1.359491939964218</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1038,13 +1038,13 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.9566485599117556</v>
+        <v>0.9715270728503083</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.290847489814226</v>
+        <v>1.245777238067179</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.370908846633435</v>
+        <v>2.354039464143812</v>
       </c>
     </row>
     <row r="8">
@@ -1054,13 +1054,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.6594018985517905</v>
+        <v>1.851163798161364</v>
       </c>
       <c r="C8" t="n">
         <v>-1.720642051727373</v>
       </c>
       <c r="D8" t="n">
-        <v>1.562797379084372</v>
+        <v>-1.63197443264535</v>
       </c>
       <c r="E8" t="n">
         <v>-0.2130278742385446</v>
@@ -1078,40 +1078,40 @@
         <v>-0.4901148345150371</v>
       </c>
       <c r="J8" t="n">
-        <v>3.004809923983883</v>
+        <v>3.062491055333766</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0253500405212911</v>
+        <v>-0.1084188793009777</v>
       </c>
       <c r="L8" t="n">
-        <v>1.612095274578883</v>
+        <v>0.05054565100585642</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3965857948526362</v>
+        <v>-0.5953311425065066</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7030564382345432</v>
+        <v>0.04954983030345027</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3579804990886523</v>
+        <v>0.400449389511546</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5086734160874546</v>
+        <v>0.4964760435151073</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7886376423661434</v>
+        <v>0.7517067182497096</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4804470766698585</v>
+        <v>0.4681701313336251</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9705610370728527</v>
+        <v>1.007930212091709</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8485303324475568</v>
+        <v>0.8427778751709515</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1120,13 +1120,13 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1891927469111894</v>
+        <v>0.211938427019418</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4570478324938768</v>
+        <v>0.4769002052872182</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.6067382515536669</v>
+        <v>0.6324202236413661</v>
       </c>
     </row>
     <row r="9">
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.1409155046653783</v>
+        <v>-0.9322894742814812</v>
       </c>
       <c r="C9" t="n">
         <v>-0.1145834007075643</v>
@@ -1160,40 +1160,40 @@
         <v>0.00518875354144776</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7636906575417438</v>
+        <v>-0.7252365699751555</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8053383472755751</v>
+        <v>0.4730629921568287</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.06957355080745331</v>
+        <v>0.3708635225080158</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3965857948526362</v>
+        <v>-0.6748292815680544</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4602429451756123</v>
+        <v>0.6895736037527651</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5101640194634793</v>
+        <v>-0.5083432920255414</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.09893823364935267</v>
+        <v>0.09128236607324969</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4431656173423279</v>
+        <v>0.4327508983658969</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.03105690431341256</v>
+        <v>-0.02758377608752189</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2171943677661439</v>
+        <v>-0.2590662979264013</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1339420797688852</v>
+        <v>0.1439444820028882</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3252888430674349</v>
+        <v>-0.3797691185332868</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.3654842618897111</v>
+        <v>-0.3520704964888046</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.08936479131529046</v>
+        <v>-0.09934130784141243</v>
       </c>
     </row>
     <row r="10">
@@ -1257,40 +1257,40 @@
         <v>0.2397411156432659</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0.3883161334253084</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9480126068875719</v>
+        <v>0.978680937374945</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.66394862422726</v>
+        <v>1.662546159864771</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7248003744305928</v>
+        <v>0.7217142168890046</v>
       </c>
       <c r="S10" t="n">
-        <v>1.342049917131261</v>
+        <v>1.36964784515993</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.525018666915819</v>
+        <v>-1.545544796541083</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6791792983314079</v>
+        <v>0.6962789077639718</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.6727936948446035</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-1.274664043954578</v>
       </c>
       <c r="X10" t="n">
-        <v>1.290620498328629</v>
+        <v>1.302051900665146</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.711503172786653</v>
+        <v>1.750288117317274</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.9933554756223164</v>
+        <v>1.002248827497033</v>
       </c>
     </row>
     <row r="11">
@@ -1339,204 +1339,40 @@
         <v>0.553011982445468</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0.0843588094630399</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.061166363146078</v>
+        <v>-1.052774460318576</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.8478361549396471</v>
+        <v>-0.8452491874450515</v>
       </c>
       <c r="R11" t="n">
-        <v>-1.152044397962451</v>
+        <v>-1.147966677305008</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5388597876857049</v>
+        <v>-0.5400694339260258</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.07008597894394</v>
+        <v>-1.013002951324686</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.006124893570912</v>
+        <v>-0.9954454365408021</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.3968501347250438</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-1.86995680254656</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3270113796198824</v>
+        <v>-0.3625593503050114</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.5100816720747272</v>
+        <v>-0.4866970077258136</v>
       </c>
       <c r="Z11" t="n">
-        <v>-1.388855951425268</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>fZZxp2dD</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>-0.3046480501031927</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-1.025235213141476</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-0.1439985203328764</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-0.2130278742385446</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-0.6732927910326272</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-2.088674909235588</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-0.196819370863868</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-1.480722010628007</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-1.378956058607153</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1.719095573852128</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-0.5500503580606922</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3.061583254324707</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-0.06397790005110647</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-1.264726417516516</v>
-      </c>
-      <c r="P12" t="n">
-        <v>-1.363762654551787</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-2.031059392189668</v>
-      </c>
-      <c r="R12" t="n">
-        <v>-1.76704834691491</v>
-      </c>
-      <c r="S12" t="n">
-        <v>-1.573675126215317</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-0.4038083258764854</v>
-      </c>
-      <c r="U12" t="n">
-        <v>-1.692335764688764</v>
-      </c>
-      <c r="V12" t="n">
-        <v>-2.341657097578948</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.03207615783270289</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-1.763343357537452</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>-1.226372846465839</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>-1.631885470193009</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>0hYMmpcl</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>-0.9322894742814812</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1.375574110547928</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.3044665108763784</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.2130278742385446</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-0.2688016221451399</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.1083016619603638</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.5613919607762649</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.5004923415979325</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-0.3406956943092757</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-2.01900217123377</v>
-      </c>
-      <c r="L13" t="n">
-        <v>2.573048889085361</v>
-      </c>
-      <c r="M13" t="n">
-        <v>-0.5158330034449584</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.4482401156064248</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.01189434312501176</v>
-      </c>
-      <c r="P13" t="n">
-        <v>-0.0657705751663259</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-0.008327076458257148</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.4849613356755301</v>
-      </c>
-      <c r="S13" t="n">
-        <v>-0.03850415927807428</v>
-      </c>
-      <c r="T13" t="n">
-        <v>-0.1726091342044169</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.4445204017295771</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.158995435558079</v>
-      </c>
-      <c r="W13" t="n">
-        <v>-0.5341779296084523</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-0.217774880956173</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.1620890674504618</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0.1676444385877339</v>
+        <v>-1.379588204255043</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.851163798161364</v>
+        <v>-0.2227817773842855</v>
       </c>
       <c r="C2" t="n">
         <v>1.623933695757177</v>
@@ -601,25 +601,25 @@
         <v>-0.2171060131235528</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.663395803320004</v>
       </c>
       <c r="P2" t="n">
-        <v>0.03275263576375812</v>
+        <v>0.01686417503890518</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6670960307465499</v>
+        <v>0.6205063849745768</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7021162093978237</v>
+        <v>0.7122051769890965</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1641126984364259</v>
+        <v>-0.1561908660804011</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5619887914346774</v>
+        <v>0.5490078416179056</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1997472844878767</v>
+        <v>0.1975396298784326</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -628,13 +628,13 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.4749646264936156</v>
+        <v>-0.4821851179678819</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.7571043019097156</v>
+        <v>-0.7847568366074681</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2882028847382935</v>
+        <v>0.2551261718347522</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.9322894742814812</v>
+        <v>1.05978982854526</v>
       </c>
       <c r="C3" t="n">
         <v>1.375574110547928</v>
@@ -683,25 +683,25 @@
         <v>0.3052608443360562</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.177064084980374</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1637596680440685</v>
+        <v>0.1370383199469582</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.07172462291501054</v>
+        <v>0.06339459934421389</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7220611380267955</v>
+        <v>0.7219914004317636</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02066417255738295</v>
+        <v>0.01674248922781893</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3481790641352454</v>
+        <v>-0.3887612547309172</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5983160252249133</v>
+        <v>0.6014243538713209</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -710,13 +710,13 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.4612787566822334</v>
+        <v>-0.478966562654272</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.1360060346661361</v>
+        <v>-0.1656539338450213</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.3749736953624429</v>
+        <v>0.3558025479993306</v>
       </c>
     </row>
     <row r="4">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1319720710643124</v>
+        <v>-1.041444504573358</v>
       </c>
       <c r="C4" t="n">
         <v>-1.472282466518124</v>
@@ -765,40 +765,40 @@
         <v>-0.4427684955461023</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.04735603092060974</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6269268673136388</v>
+        <v>0.6309570322859029</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4615754349629818</v>
+        <v>0.4635151025223658</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5265598592163208</v>
+        <v>0.5355002042312591</v>
       </c>
       <c r="S4" t="n">
-        <v>0.875512712776369</v>
+        <v>0.8635226564414414</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.08964200102777327</v>
+        <v>-0.105214210894958</v>
       </c>
       <c r="U4" t="n">
-        <v>0.693813490717845</v>
+        <v>0.6836227884484447</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.007888742154263037</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-1.056874010323365</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5362978999644579</v>
+        <v>0.5816191209962247</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3768973904697924</v>
+        <v>0.3302430369039732</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.6775412870208719</v>
+        <v>0.661374214086233</v>
       </c>
     </row>
     <row r="5">
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3046480501031927</v>
+        <v>-1.614508413605708</v>
       </c>
       <c r="C5" t="n">
         <v>1.110657219658063</v>
@@ -847,40 +847,40 @@
         <v>1.717949773649812</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.64819793712189</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.08914326992887753</v>
+        <v>-0.07412379204473521</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.05337177585227463</v>
+        <v>0.05411390998497218</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1295783371213627</v>
+        <v>0.1262009006984491</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.007753763559808019</v>
+        <v>-0.003428584893786866</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7680250587234536</v>
+        <v>0.7542456625158543</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3472247547293261</v>
+        <v>-0.3353308459322706</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.007888742154263037</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.1975965833924232</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7521634155664599</v>
+        <v>0.7433010076859812</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.127419451950377</v>
+        <v>0.135206887974792</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.04933275909304332</v>
+        <v>-0.04537322412497298</v>
       </c>
     </row>
     <row r="6">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.469121192139797</v>
+        <v>0.2957046165021268</v>
       </c>
       <c r="C6" t="n">
         <v>-1.207365575628259</v>
@@ -929,40 +929,40 @@
         <v>-0.01603954730366944</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.008369478472472802</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1418814225652608</v>
+        <v>-0.1771234672890094</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.377849709044232</v>
+        <v>-1.333210804083377</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.057616510489455</v>
+        <v>-1.027766493190334</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9346190975891642</v>
+        <v>-0.9919447737510796</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6820796760870795</v>
+        <v>-0.7156849812893225</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8060108042112075</v>
+        <v>-0.8080338905715168</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.174772919866605</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-1.231106037228336</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4614766711625282</v>
+        <v>0.4208480027062109</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.1594488253317864</v>
+        <v>-0.1713065939461891</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.6863795268624296</v>
+        <v>-0.6513629615846813</v>
       </c>
     </row>
     <row r="7">
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.469121192139797</v>
+        <v>1.714720010296518</v>
       </c>
       <c r="C7" t="n">
         <v>-1.323266715392575</v>
@@ -1011,25 +1011,25 @@
         <v>0.8324036273495784</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.7581308775794017</v>
       </c>
       <c r="P7" t="n">
-        <v>1.721612495762787</v>
+        <v>1.71109351050026</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.495848819470343</v>
+        <v>2.500883231113295</v>
       </c>
       <c r="R7" t="n">
-        <v>1.572750262191843</v>
+        <v>1.595080742181313</v>
       </c>
       <c r="S7" t="n">
-        <v>1.546573823570957</v>
+        <v>1.541209990776296</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9664069531439723</v>
+        <v>-0.9479779329196314</v>
       </c>
       <c r="U7" t="n">
-        <v>1.359491939964218</v>
+        <v>1.343335424388541</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1038,13 +1038,13 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.9715270728503083</v>
+        <v>0.9819029044276161</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.245777238067179</v>
+        <v>1.235475466239283</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.354039464143812</v>
+        <v>2.38372917423397</v>
       </c>
     </row>
     <row r="8">
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.851163798161364</v>
+        <v>0.1865495862102505</v>
       </c>
       <c r="C8" t="n">
         <v>-1.720642051727373</v>
@@ -1093,40 +1093,40 @@
         <v>0.04954983030345027</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.528621793860868</v>
       </c>
       <c r="P8" t="n">
-        <v>0.400449389511546</v>
+        <v>0.3814095682365882</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4964760435151073</v>
+        <v>0.4950924299006026</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7517067182497096</v>
+        <v>0.7616585608271912</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4681701313336251</v>
+        <v>0.4376863254640643</v>
       </c>
       <c r="T8" t="n">
-        <v>1.007930212091709</v>
+        <v>1.020396257148586</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8427778751709515</v>
+        <v>0.8222436706432373</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.007888742154263037</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-1.100432017049607</v>
       </c>
       <c r="X8" t="n">
-        <v>0.211938427019418</v>
+        <v>0.2111467156891737</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4769002052872182</v>
+        <v>0.4908505213041606</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.6324202236413661</v>
+        <v>0.6373933659703001</v>
       </c>
     </row>
     <row r="9">
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.9322894742814812</v>
+        <v>-0.6594018985517905</v>
       </c>
       <c r="C9" t="n">
         <v>-0.1145834007075643</v>
@@ -1175,25 +1175,25 @@
         <v>0.6895736037527651</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.4121048196753318</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5083432920255414</v>
+        <v>-0.5255760106117101</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.09128236607324969</v>
+        <v>0.08821512167236624</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4327508983658969</v>
+        <v>0.4086932648925549</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.02758377608752189</v>
+        <v>-0.02552570931113856</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2590662979264013</v>
+        <v>-0.1684550105948153</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1439444820028882</v>
+        <v>0.1883858981172759</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1202,177 +1202,13 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3797691185332868</v>
+        <v>-0.4254367645004546</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.3520704964888046</v>
+        <v>-0.3332912249275356</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.09934130784141243</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>WdSjHeFt</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.08707858611823</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-1.223922881308875</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.8625734203490908</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-0.2130278742385446</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2.967127728954758</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2.305278233156316</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.07781462405653</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.481706693823872</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.101332589437776</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-0.274556556860351</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-1.030527165313931</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-1.469810672183536</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.2397411156432659</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-0.3883161334253084</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.978680937374945</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.662546159864771</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.7217142168890046</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.36964784515993</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-1.545544796541083</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.6962789077639718</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.6727936948446035</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-1.274664043954578</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.302051900665146</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.750288117317274</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.002248827497033</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>EaryFQkA</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.08707858611823</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.5285160427229788</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-1.442330443821211</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-0.2130278742385446</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-0.2688016221451399</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.4744644238263558</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.196819370863868</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.5004923415979325</v>
-      </c>
-      <c r="J11" t="n">
-        <v>-0.3022416067426874</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.140787637038082</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.7712608618857147</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-2.026297645614373</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.553011982445468</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-0.0843588094630399</v>
-      </c>
-      <c r="P11" t="n">
-        <v>-1.052774460318576</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-0.8452491874450515</v>
-      </c>
-      <c r="R11" t="n">
-        <v>-1.147966677305008</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-0.5400694339260258</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-1.013002951324686</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-0.9954454365408021</v>
-      </c>
-      <c r="V11" t="n">
-        <v>-0.3968501347250438</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-1.86995680254656</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-0.3625593503050114</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>-0.4866970077258136</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>-1.379588204255043</v>
+        <v>-0.1000929056773387</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -768,22 +768,22 @@
         <v>0.04735603092060974</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6309570322859029</v>
+        <v>0.6339533171576649</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4635151025223658</v>
+        <v>0.4586409670961376</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5355002042312591</v>
+        <v>0.5171992074136931</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8635226564414414</v>
+        <v>0.8685210976725627</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.105214210894958</v>
+        <v>-0.06516480114141915</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6836227884484447</v>
+        <v>0.7035457233551683</v>
       </c>
       <c r="V4" t="n">
         <v>-0.007888742154263037</v>
@@ -792,13 +792,13 @@
         <v>-1.056874010323365</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5816191209962247</v>
+        <v>0.5443672142339635</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3302430369039732</v>
+        <v>0.3333580113137389</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.661374214086233</v>
+        <v>0.6596389823656643</v>
       </c>
     </row>
     <row r="5">
@@ -881,334 +881,6 @@
       </c>
       <c r="Z5" t="n">
         <v>-0.04537322412497298</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>0xK7DDE5</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.2957046165021268</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-1.207365575628259</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.956673355872968</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-0.2130278742385446</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-1.077783959920114</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-2.821000432967572</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-0.9550307025040008</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-2.471329186740976</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.5822024072888373</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-0.7729695895384707</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-0.5500503580606922</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.6766390824782634</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-0.01603954730366944</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-0.008369478472472802</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-0.1771234672890094</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-1.333210804083377</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-1.027766493190334</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-0.9919447737510796</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-0.7156849812893225</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-0.8080338905715168</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-1.174772919866605</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-1.231106037228336</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.4208480027062109</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-0.1713065939461891</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-0.6513629615846813</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>SjzlgqTj</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1.714720010296518</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-1.323266715392575</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-1.63197443264535</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-0.2130278742385446</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.7424263000735782</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.3524101698710252</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.197274085085535</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-1.188313783436904</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.812293944267733</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-1.867301367491277</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.8324036273495784</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-0.7581308775794017</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.71109351050026</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.500883231113295</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.595080742181313</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.541209990776296</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.9479779329196314</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.343335424388541</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.9819029044276161</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.235475466239283</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.38372917423397</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>ELeQ0zVa</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.1865495862102505</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-1.720642051727373</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-1.63197443264535</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-0.2130278742385446</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-0.06655603770139627</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-0.1358068459502975</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.196819370863868</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-0.4901148345150371</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.062491055333766</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-0.1084188793009777</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.05054565100585642</v>
-      </c>
-      <c r="M8" t="n">
-        <v>-0.5953311425065066</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.04954983030345027</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.528621793860868</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.3814095682365882</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.4950924299006026</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.7616585608271912</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.4376863254640643</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.020396257148586</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.8222436706432373</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-0.007888742154263037</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-1.100432017049607</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.2111467156891737</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.4908505213041606</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.6373933659703001</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>d4DGBiqI</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>-0.6594018985517905</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.1145834007075643</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.8625734203490908</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-0.2130278742385446</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.1356895467423473</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-0.1358068459502975</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.196819370863868</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.00518875354144776</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-0.7252365699751555</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.4730629921568287</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.3708635225080158</v>
-      </c>
-      <c r="M9" t="n">
-        <v>-0.6748292815680544</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.6895736037527651</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.4121048196753318</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-0.5255760106117101</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.08821512167236624</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.4086932648925549</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-0.02552570931113856</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.1684550105948153</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.1883858981172759</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-0.4254367645004546</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>-0.3332912249275356</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-0.1000929056773387</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,68 +558,68 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hCGaFZqg</t>
+          <t>rgFQPs4S</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.2227817773842855</v>
+        <v>-1.614508413605708</v>
       </c>
       <c r="C2" t="n">
-        <v>1.623933695757177</v>
+        <v>1.110657219658063</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1439985203328764</v>
+        <v>0.06023346763158076</v>
       </c>
       <c r="E2" t="n">
         <v>-0.2130278742385446</v>
       </c>
       <c r="F2" t="n">
-        <v>2.764882144511015</v>
+        <v>1.551408637848553</v>
       </c>
       <c r="G2" t="n">
-        <v>1.817061217334993</v>
+        <v>1.20678994755834</v>
       </c>
       <c r="H2" t="n">
         <v>1.319603292416398</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9957959296544173</v>
+        <v>0.5004923415979325</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.8598258764582142</v>
+        <v>2.504906785618239</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.022176105877531</v>
+        <v>-0.3576253956400375</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.231719183447028</v>
+        <v>0.9314197976367943</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.185293923737469</v>
+        <v>-0.5953311425065066</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2171060131235528</v>
+        <v>1.196866446182821</v>
       </c>
       <c r="O2" t="n">
-        <v>1.663395803320004</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01686417503890518</v>
+        <v>0.8787797772058084</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6205063849745768</v>
+        <v>1.189385169766042</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7122051769890965</v>
+        <v>0.9247660095164423</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1561908660804011</v>
+        <v>0.922038708955953</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5490078416179056</v>
+        <v>-0.3314599732483232</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1975396298784326</v>
+        <v>0.9946788017748472</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -628,38 +628,38 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.4821851179678819</v>
+        <v>0.9045778451464715</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.7847568366074681</v>
+        <v>0.8571133855759132</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2551261718347522</v>
+        <v>1.229456793315582</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6ZvTGnLc</t>
+          <t>WIJkQBF8</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1.05978982854526</v>
       </c>
       <c r="C3" t="n">
-        <v>1.375574110547928</v>
+        <v>1.176886442380529</v>
       </c>
       <c r="D3" t="n">
-        <v>1.956673355872968</v>
+        <v>-1.63197443264535</v>
       </c>
       <c r="E3" t="n">
         <v>-0.2130278742385446</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2688016221451399</v>
+        <v>1.95589980673604</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3524101698710252</v>
+        <v>0.7185729317370172</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -668,40 +668,40 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.2251397083408</v>
+        <v>0.543748319722249</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6899007507587844</v>
+        <v>0.4730629921568287</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2907840546324759</v>
+        <v>0.9314197976367945</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7561372215398112</v>
+        <v>-0.1978404471987653</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3052608443360562</v>
+        <v>1.061648053937562</v>
       </c>
       <c r="O3" t="n">
-        <v>1.177064084980374</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1370383199469582</v>
+        <v>-0.9241658707098616</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.06339459934421389</v>
+        <v>-0.1168667675265947</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7219914004317636</v>
+        <v>0.1202565207535708</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01674248922781893</v>
+        <v>-0.1249267186612038</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3887612547309172</v>
+        <v>-0.7017340338154651</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6014243538713209</v>
+        <v>-0.1629123701870234</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -710,26 +710,26 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.478966562654272</v>
+        <v>0.07052283369984637</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.1656539338450213</v>
+        <v>0.02123459461842354</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.3558025479993306</v>
+        <v>-0.8645170316066862</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>Esk5Iad2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.041444504573358</v>
+        <v>0.05010579834540515</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.472282466518124</v>
+        <v>-0.677531793848528</v>
       </c>
       <c r="D4" t="n">
         <v>-1.442330443821211</v>
@@ -738,149 +738,641 @@
         <v>-0.2130278742385446</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.06655603770139627</v>
+        <v>-0.6732927910326272</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2303559159156945</v>
+        <v>-0.1358068459502975</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5613919607762649</v>
+        <v>-0.9550307025040008</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5004923415979325</v>
+        <v>-0.4901148345150371</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4752850007923335</v>
+        <v>-0.7636906575417438</v>
       </c>
       <c r="K4" t="n">
-        <v>1.885233251411501</v>
+        <v>-0.689900750758784</v>
       </c>
       <c r="L4" t="n">
-        <v>1.331817137014494</v>
+        <v>-1.631123174380479</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5176428043551671</v>
+        <v>0.2791483871705225</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4427684955461023</v>
+        <v>0.3193100253404917</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04735603092060974</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6339533171576649</v>
+        <v>-1.605805314873279</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4586409670961376</v>
+        <v>-2.99867649519798</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5171992074136931</v>
+        <v>-2.029734094356396</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8685210976725627</v>
+        <v>-2.766740535580823</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.06516480114141915</v>
+        <v>-0.7440088354806712</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7035457233551683</v>
+        <v>-1.690234213550776</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.007888742154263037</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.056874010323365</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5443672142339635</v>
+        <v>-1.02642284936272</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3333580113137389</v>
+        <v>-2.214169409442646</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.6596389823656643</v>
+        <v>-2.576223998303059</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>6cNF7rrp</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.614508413605708</v>
+        <v>1.714720010296518</v>
       </c>
       <c r="C5" t="n">
-        <v>1.110657219658063</v>
+        <v>-1.372938632434424</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9609264721907048</v>
+        <v>-0.3628185074376518</v>
       </c>
       <c r="E5" t="n">
         <v>-0.2130278742385446</v>
       </c>
       <c r="F5" t="n">
-        <v>1.146917468961066</v>
+        <v>-1.684520713251345</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2303559159156945</v>
+        <v>-1.844566401324927</v>
       </c>
       <c r="H5" t="n">
+        <v>-0.196819370863868</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.9854184225715219</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.2253334316095116</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.3069253145974554</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-1.230725835002781</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.074129777786004</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.05780820157376176</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-1.614757789286013</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-2.189280325505941</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-1.525661695897021</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-1.397326175282559</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.5085959206949485</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-1.285801925931222</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.7888816399164904</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-1.169505360020046</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-1.840455904501587</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>zFWqD4KM</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-1.041444504573358</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.3298283745555798</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8625734203490908</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.7424263000735782</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1.356349385503604</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.196819370863868</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-1.480722010628007</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-1.109777445641036</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.6392006697162018</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.3708635225080158</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.630616751216841</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.4555838957824422</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1003606255338001</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.05362849236064238</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.06480916307070281</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.02058804823770775</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.961909506713743</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.4225429800094635</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.3783126990727378</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0.04188462368473105</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.1853866263110415</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4WHcOkpL</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.6594018985517905</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.8099902392934607</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.081393407453866</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.944671884517322</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7185729317370172</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.319603292416398</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.986403105767387</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9282891953881295</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.137613702394322</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-1.150646367127241</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.153627916847552</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.204925820555055</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.7762629396672724</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.420007847433459</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.04420649453261447</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.3732898524838401</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.6675635101480495</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.3743169261402676</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.09780248361323805</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.6095958795156852</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.7173289449746664</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>zTBIR3ZF</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.2227817773842855</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.623933695757177</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.504445382523099</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.2688016221451399</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-1.966620655280257</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.196819370863868</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.9854184225715219</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-2.301854160205266</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.137613702394322</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-1.070566899251701</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.1183423081372179</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.3658553998013681</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-1.191982694446052</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-1.261014283095832</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.8759926282337663</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-1.984060646822466</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.570056403668789</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-1.951326556276012</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.5675832378168857</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-1.181637365615979</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-1.077658840926566</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>SQjcKLRk</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.004471716800532986</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.4954014313617456</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.06023346763158076</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1356895467423473</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.5965186777816865</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.5613919607762649</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.5004923415979325</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-0.379149781875864</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.3069253145974551</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.171658201263414</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-0.277338586260314</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.717949773649812</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.64819793712189</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.07412379204473521</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.05411390998497218</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.1262009006984491</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.003428584893786866</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.7542456625158543</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-0.3353308459322706</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-0.007888742154263037</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.1975965833924232</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.7433010076859812</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.135206887974792</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-0.04537322412497298</v>
+      <c r="I9" t="n">
+        <v>0.9957959296544173</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.158819997518947</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-1.188313783436904</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.091578733387874</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-1.549308811245084</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.953891233627326</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.685196568256548</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.998794284705154</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.561288937354954</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.497934056923021</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.6148172554006155</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.713980226883332</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.148182614143022</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.243452185397689</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.411535438931474</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>v1I9TP43</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.2227817773842855</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.025235213141476</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.562797379084372</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1.684520713251345</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1.966620655280257</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.9550307025040008</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.9854184225715219</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-2.571032773171382</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.303751379953695</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.02953381686968354</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.266601863709226</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.270933879417282</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-2.104766071189512</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-2.15187539638774</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-1.848980860565405</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-2.035148823766344</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.759094904818174</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-1.588383179499802</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-1.364915683122761</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0.5955303385152577</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-1.903307958616155</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>n7VN5MCd</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.1865495862102505</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.704084746046756</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.956673355872968</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.2688016221451399</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.01375259199496684</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-1.878859196972798</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.303751379953695</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.670169559874002</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.6766390824782634</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.4348078249860372</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.1456499796356354</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.2981285465188994</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.9873116469652075</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.1694908160901271</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.1428221313198321</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-1.403738699304649</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.1188617321897991</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.2155854335345813</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.656077117575508</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,68 +558,68 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rgFQPs4S</t>
+          <t>OAeKROjD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.614508413605708</v>
+        <v>1.05978982854526</v>
       </c>
       <c r="C2" t="n">
-        <v>1.110657219658063</v>
+        <v>1.375574110547928</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06023346763158076</v>
+        <v>0.8625734203490908</v>
       </c>
       <c r="E2" t="n">
         <v>-0.2130278742385446</v>
       </c>
       <c r="F2" t="n">
-        <v>1.551408637848553</v>
+        <v>0.1356895467423473</v>
       </c>
       <c r="G2" t="n">
-        <v>1.20678994755834</v>
+        <v>0.4744644238263558</v>
       </c>
       <c r="H2" t="n">
-        <v>1.319603292416398</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5004923415979325</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.504906785618239</v>
+        <v>-0.6291013510586859</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3576253956400375</v>
+        <v>0.7222695084958886</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9314197976367943</v>
+        <v>0.2907840546324759</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5953311425065066</v>
+        <v>0.5573918738859412</v>
       </c>
       <c r="N2" t="n">
-        <v>1.196866446182821</v>
+        <v>0.1914744180139985</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8787797772058084</v>
+        <v>0.7493271898012938</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.189385169766042</v>
+        <v>0.6510981957562791</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9247660095164423</v>
+        <v>1.071620435125803</v>
       </c>
       <c r="S2" t="n">
-        <v>0.922038708955953</v>
+        <v>0.7944128538303132</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3314599732483232</v>
+        <v>1.000897328586375</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9946788017748472</v>
+        <v>1.333864533404485</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -628,80 +628,80 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.9045778451464715</v>
+        <v>0.09719543789083547</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.8571133855759132</v>
+        <v>-0.3304296216420097</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.229456793315582</v>
+        <v>0.6499597458774431</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WIJkQBF8</t>
+          <t>xIieTySH</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.05978982854526</v>
+        <v>0.2957046165021268</v>
       </c>
       <c r="C3" t="n">
-        <v>1.176886442380529</v>
+        <v>-1.207365575628259</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.63197443264535</v>
+        <v>0.8625734203490908</v>
       </c>
       <c r="E3" t="n">
         <v>-0.2130278742385446</v>
       </c>
       <c r="F3" t="n">
-        <v>1.95589980673604</v>
+        <v>0.5401807156298346</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7185729317370172</v>
+        <v>0.9626814396476785</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1.319603292416398</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1.491099517710902</v>
       </c>
       <c r="J3" t="n">
-        <v>0.543748319722249</v>
+        <v>0.1207533564897808</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4730629921568287</v>
+        <v>-1.271382622216591</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9314197976367945</v>
+        <v>-0.3098119544340728</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1978404471987653</v>
+        <v>0.6766390824782634</v>
       </c>
       <c r="N3" t="n">
-        <v>1.061648053937562</v>
+        <v>-0.03679492377340055</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9241658707098616</v>
+        <v>0.09457882456945529</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1168667675265947</v>
+        <v>0.4810556536596741</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1202565207535708</v>
+        <v>0.1343949150465756</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1249267186612038</v>
+        <v>-0.03565603601868504</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7017340338154651</v>
+        <v>0.44257334442193</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1629123701870234</v>
+        <v>-0.3071312466234463</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -710,80 +710,80 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.07052283369984637</v>
+        <v>0.4406589695097713</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02123459461842354</v>
+        <v>1.531997183354967</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.8645170316066862</v>
+        <v>0.5956801059630952</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Esk5Iad2</t>
+          <t>WvDUsysB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05010579834540515</v>
+        <v>1.05978982854526</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.677531793848528</v>
+        <v>1.176886442380529</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.442330443821211</v>
+        <v>0.4103454469992215</v>
       </c>
       <c r="E4" t="n">
         <v>-0.2130278742385446</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6732927910326272</v>
+        <v>2.360390975623528</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1358068459502975</v>
+        <v>2.549386741066977</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9550307025040008</v>
+        <v>2.07781462405653</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4901148345150371</v>
+        <v>1.491099517710902</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7636906575417438</v>
+        <v>2.543360873184827</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.689900750758784</v>
+        <v>-1.022176105877531</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.631123174380479</v>
+        <v>1.852333678205502</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2791483871705225</v>
+        <v>-1.946799506552825</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3193100253404917</v>
+        <v>0.3437717190369574</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.605805314873279</v>
+        <v>1.167952953036024</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.99867649519798</v>
+        <v>1.290275487597341</v>
       </c>
       <c r="R4" t="n">
-        <v>-2.029734094356396</v>
+        <v>1.093259906776837</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.766740535580823</v>
+        <v>1.98059607803264</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7440088354806712</v>
+        <v>-1.457037841511675</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.690234213550776</v>
+        <v>1.414334012649652</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -792,80 +792,80 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.02642284936272</v>
+        <v>1.547402543641466</v>
       </c>
       <c r="Y4" t="n">
-        <v>-2.214169409442646</v>
+        <v>1.465762990642046</v>
       </c>
       <c r="Z4" t="n">
-        <v>-2.576223998303059</v>
+        <v>0.996366569701115</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6cNF7rrp</t>
+          <t>pOEMqcCb</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.714720010296518</v>
+        <v>0.1865495862102505</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.372938632434424</v>
+        <v>-1.704084746046756</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3628185074376518</v>
+        <v>-1.442330443821211</v>
       </c>
       <c r="E5" t="n">
         <v>-0.2130278742385446</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.684520713251345</v>
+        <v>-0.6732927910326272</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.844566401324927</v>
+        <v>-0.01375259199496684</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.196819370863868</v>
+        <v>-0.9550307025040008</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9854184225715219</v>
+        <v>0.00518875354144776</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2253334316095116</v>
+        <v>-1.551999452656799</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3069253145974554</v>
+        <v>-0.274556556860351</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.230725835002781</v>
+        <v>-1.030527165313931</v>
       </c>
       <c r="M5" t="n">
-        <v>1.074129777786004</v>
+        <v>0.6766390824782634</v>
       </c>
       <c r="N5" t="n">
-        <v>0.05780820157376176</v>
+        <v>0.4636623752076179</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.614757789286013</v>
+        <v>-0.0284997531252147</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.189280325505941</v>
+        <v>-0.3339253738619532</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.525661695897021</v>
+        <v>-0.5255180481601657</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.397326175282559</v>
+        <v>-0.3232323872235581</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5085959206949485</v>
+        <v>-1.239294032475278</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.285801925931222</v>
+        <v>-0.686576609536212</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -874,80 +874,80 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7888816399164904</v>
+        <v>0.5498720452282947</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.169505360020046</v>
+        <v>0.06402450624731532</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1.840455904501587</v>
+        <v>-0.6633932296946635</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zFWqD4KM</t>
+          <t>A50vXJSh</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.041444504573358</v>
+        <v>0.2957046165021268</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.3298283745555798</v>
+        <v>-0.03179687230448136</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8625734203490908</v>
+        <v>-1.442330443821211</v>
       </c>
       <c r="E6" t="n">
         <v>-0.2130278742385446</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7424263000735782</v>
+        <v>-1.684520713251345</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.356349385503604</v>
+        <v>-2.698946179012241</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.196819370863868</v>
+        <v>-0.9550307025040008</v>
       </c>
       <c r="I6" t="n">
         <v>-1.480722010628007</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.109777445641036</v>
+        <v>0.9282891953881295</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6392006697162018</v>
+        <v>-0.0253500405212911</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3708635225080158</v>
+        <v>0.651141660072405</v>
       </c>
       <c r="M6" t="n">
-        <v>1.630616751216841</v>
+        <v>-0.7543274206296028</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4555838957824422</v>
+        <v>0.6309640423458002</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1003606255338001</v>
+        <v>-0.1639945572358345</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.05362849236064238</v>
+        <v>-0.5890955907447925</v>
       </c>
       <c r="R6" t="n">
-        <v>0.06480916307070281</v>
+        <v>-0.2692994300399392</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.02058804823770775</v>
+        <v>0.04522002001956966</v>
       </c>
       <c r="T6" t="n">
-        <v>1.961909506713743</v>
+        <v>-0.07049062378305172</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4225429800094635</v>
+        <v>0.5350874094442895</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -956,80 +956,80 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3783126990727378</v>
+        <v>-0.07423276507556928</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.04188462368473105</v>
+        <v>-0.3874828371471984</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1853866263110415</v>
+        <v>-0.7242499805040066</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4WHcOkpL</t>
+          <t>O8QDoJsn</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.6594018985517905</v>
+        <v>1.714720010296518</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.8099902392934607</v>
+        <v>-1.323266715392575</v>
       </c>
       <c r="D7" t="n">
-        <v>1.081393407453866</v>
+        <v>-0.3628185074376518</v>
       </c>
       <c r="E7" t="n">
         <v>-0.2130278742385446</v>
       </c>
       <c r="F7" t="n">
-        <v>0.944671884517322</v>
+        <v>-1.482275128807601</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7185729317370172</v>
+        <v>-1.356349385503604</v>
       </c>
       <c r="H7" t="n">
-        <v>1.319603292416398</v>
+        <v>-0.196819370863868</v>
       </c>
       <c r="I7" t="n">
-        <v>1.986403105767387</v>
+        <v>0.00518875354144776</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9282891953881295</v>
+        <v>-0.6291013510586859</v>
       </c>
       <c r="K7" t="n">
-        <v>1.137613702394322</v>
+        <v>-1.76979565489471</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.150646367127241</v>
+        <v>0.7712608618857147</v>
       </c>
       <c r="M7" t="n">
-        <v>1.153627916847552</v>
+        <v>-1.70830508936818</v>
       </c>
       <c r="N7" t="n">
-        <v>1.204925820555055</v>
+        <v>1.337059760880079</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7762629396672724</v>
+        <v>-0.06582020164781434</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.420007847433459</v>
+        <v>0.1127725751058526</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.04420649453261447</v>
+        <v>0.103981455940396</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3732898524838401</v>
+        <v>-0.01413674785531117</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6675635101480495</v>
+        <v>0.3879341682779229</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3743169261402676</v>
+        <v>0.04984303582076435</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1038,38 +1038,38 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.09780248361323805</v>
+        <v>-0.2235312019726915</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6095958795156852</v>
+        <v>-0.02745737378686692</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.7173289449746664</v>
+        <v>0.3690515243023547</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>Yqo4RFdU</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.2227817773842855</v>
+        <v>1.714720010296518</v>
       </c>
       <c r="C8" t="n">
-        <v>1.623933695757177</v>
+        <v>-1.372938632434424</v>
       </c>
       <c r="D8" t="n">
-        <v>1.504445382523099</v>
+        <v>0.4103454469992215</v>
       </c>
       <c r="E8" t="n">
         <v>-0.2130278742385446</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2688016221451399</v>
+        <v>3.573864482285989</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.966620655280257</v>
+        <v>1.695006963379663</v>
       </c>
       <c r="H8" t="n">
         <v>-0.196819370863868</v>
@@ -1078,40 +1078,40 @@
         <v>-0.9854184225715219</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.301854160205266</v>
+        <v>0.9859703267380115</v>
       </c>
       <c r="K8" t="n">
-        <v>1.137613702394322</v>
+        <v>-0.5237630731994108</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.070566899251701</v>
+        <v>-3.432911201580126</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1183423081372179</v>
+        <v>-0.873574629221925</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3658553998013681</v>
+        <v>-0.09263345337460566</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.191982694446052</v>
+        <v>0.6201497447458596</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.261014283095832</v>
+        <v>-0.2055281840621719</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.8759926282337663</v>
+        <v>0.3507694266347365</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.984060646822466</v>
+        <v>1.369474279206345</v>
       </c>
       <c r="T8" t="n">
-        <v>1.570056403668789</v>
+        <v>0.1007064968629245</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.951326556276012</v>
+        <v>0.7240706535136953</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1120,80 +1120,80 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5675832378168857</v>
+        <v>0.1066364064543261</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.181637365615979</v>
+        <v>-0.6891435168298057</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1.077658840926566</v>
+        <v>-0.404946026576299</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SQjcKLRk</t>
+          <t>S66wtFBN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.004471716800532986</v>
+        <v>-1.614508413605708</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.4954014313617456</v>
+        <v>0.3159065469884668</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06023346763158076</v>
+        <v>1.081393407453866</v>
       </c>
       <c r="E9" t="n">
         <v>-0.2130278742385446</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1356895467423473</v>
+        <v>-1.077783959920114</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5965186777816865</v>
+        <v>-0.8681323696822815</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5613919607762649</v>
+        <v>-0.9550307025040008</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9957959296544173</v>
+        <v>-0.9854184225715219</v>
       </c>
       <c r="J9" t="n">
-        <v>2.158819997518947</v>
+        <v>-0.05229003755986538</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.188313783436904</v>
+        <v>2.217508606530248</v>
       </c>
       <c r="L9" t="n">
-        <v>1.091578733387874</v>
+        <v>-0.06957355080745331</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.549308811245084</v>
+        <v>0.7958862910705856</v>
       </c>
       <c r="N9" t="n">
-        <v>0.953891233627326</v>
+        <v>0.3679448672312057</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.685196568256548</v>
+        <v>-1.072731979264405</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.998794284705154</v>
+        <v>-0.2793653515244697</v>
       </c>
       <c r="R9" t="n">
-        <v>2.561288937354954</v>
+        <v>-0.8526559431199082</v>
       </c>
       <c r="S9" t="n">
-        <v>3.497934056923021</v>
+        <v>-0.3961192993224306</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6148172554006155</v>
+        <v>-0.2214504396623839</v>
       </c>
       <c r="U9" t="n">
-        <v>2.713980226883332</v>
+        <v>-0.3125454249888999</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1202,80 +1202,80 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.148182614143022</v>
+        <v>-1.11009907695268</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.243452185397689</v>
+        <v>-0.278786624848519</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.411535438931474</v>
+        <v>-0.8082189945988657</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>v1I9TP43</t>
+          <t>44gmVcc5</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.2227817773842855</v>
+        <v>-0.004471716800532986</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.025235213141476</v>
+        <v>-0.5285160427229788</v>
       </c>
       <c r="D10" t="n">
-        <v>1.562797379084372</v>
+        <v>1.504445382523099</v>
       </c>
       <c r="E10" t="n">
         <v>-0.2130278742385446</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.684520713251345</v>
+        <v>-1.886766297695089</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.966620655280257</v>
+        <v>-1.356349385503604</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9550307025040008</v>
+        <v>-2.471453365784267</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9854184225715219</v>
+        <v>-1.976025598684491</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.571032773171382</v>
+        <v>-1.03286927050786</v>
       </c>
       <c r="K10" t="n">
-        <v>1.303751379953695</v>
+        <v>-1.76979565489471</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.02953381686968354</v>
+        <v>-0.9104079635006215</v>
       </c>
       <c r="M10" t="n">
-        <v>2.266601863709226</v>
+        <v>-2.304541132329791</v>
       </c>
       <c r="N10" t="n">
-        <v>0.270933879417282</v>
+        <v>0.05438545492678623</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.104766071189512</v>
+        <v>-0.3719259793922557</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.15187539638774</v>
+        <v>-0.5119062036332385</v>
       </c>
       <c r="R10" t="n">
-        <v>-1.848980860565405</v>
+        <v>-0.1518886272722849</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.035148823766344</v>
+        <v>-0.4283315426516623</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.759094904818174</v>
+        <v>-0.111900085313597</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.588383179499802</v>
+        <v>-0.2749148815008868</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1284,29 +1284,29 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.364915683122761</v>
+        <v>-0.1689098475438871</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.5955303385152577</v>
+        <v>-0.3818266994031492</v>
       </c>
       <c r="Z10" t="n">
-        <v>-1.903307958616155</v>
+        <v>-0.6561186863943668</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>n7VN5MCd</t>
+          <t>2ucWYubt</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0.1865495862102505</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.704084746046756</v>
+        <v>-1.720642051727373</v>
       </c>
       <c r="D11" t="n">
-        <v>1.956673355872968</v>
+        <v>-0.3628185074376518</v>
       </c>
       <c r="E11" t="n">
         <v>-0.2130278742385446</v>
@@ -1315,64 +1315,884 @@
         <v>-0.2688016221451399</v>
       </c>
       <c r="G11" t="n">
+        <v>-0.6240238617716202</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.9550307025040008</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.00518875354144776</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.062491055333766</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.5237630731994108</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.732214476392193</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-1.231316254998892</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.222079353169538</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.1577085895735337</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.08753882827458924</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.1961980216053526</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.05474338781047755</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.6482041601560844</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.2788062427951743</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.8507633061611336</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.1053389036821074</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.3284387882772671</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>rgFQPs4S</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-1.614508413605708</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.110657219658063</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.06023346763158076</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.551408637848553</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.20678994755834</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.319603292416398</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5004923415979325</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.312636347785299</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.1914877180806642</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.011499265512334</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.4363348643834106</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.209045056345307</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.9639870001912482</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.156525487113428</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.8216451379581221</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.9048647517879397</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.4888971752234327</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.7959748393478759</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.872613397037264</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.8330133204056178</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.248814006630851</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WIJkQBF8</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.05978982854526</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.176886442380529</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.63197443264535</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.95589980673604</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7185729317370172</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.7360187575551898</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.4730629921568287</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.011499265512334</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.03884416907566966</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.7468349611752405</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.8379681064522699</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.1287739480864025</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.04060871753379659</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.1231562563477827</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.7278058455550517</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.403148988330654</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.07997493520996027</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.02123459461842354</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.8645170316066862</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Esk5Iad2</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.05010579834540515</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.677531793848528</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.442330443821211</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.6732927910326272</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.1358068459502975</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.9550307025040008</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.4901148345150371</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.9944151829412722</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.689900750758784</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-1.631123174380479</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2791483871705225</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.2900972807023709</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-1.643199213833078</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-2.99867649519798</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-2.029734094356396</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-2.749458372952045</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.6786025320345184</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-1.658878025488254</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-1.051793139767453</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-2.214169409442646</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-2.576223998303059</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6cNF7rrp</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.714720010296518</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-1.372938632434424</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.3628185074376518</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.684520713251345</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-1.844566401324927</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.196819370863868</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.9854184225715219</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0.2253334316095116</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.3069253145974554</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-1.230725835002781</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.074129777786004</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.01751132971259185</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-1.546799099188193</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-2.187112098393382</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-1.51475103792171</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-1.330312087405997</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.5615583433672423</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-1.333480531619886</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.6963695626836706</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-1.169505360020046</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-1.830479387975465</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>4WHcOkpL</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-0.6594018985517905</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.8099902392934607</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.081393407453866</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.944671884517322</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7185729317370172</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.319603292416398</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.986403105767387</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.8898351078215413</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.303751379953695</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-1.150646367127241</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.2331260559091</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.204925820555055</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.8907758991113807</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.4410813084924982</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.07747764927536611</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.422229088499062</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.2713755333035737</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.308649928641535</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.1657209617979026</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.5568462470766212</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.8407883369854253</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>zFWqD4KM</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-1.041444504573358</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.3298283745555798</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.8625734203490908</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.7424263000735782</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-1.356349385503604</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.196819370863868</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-1.480722010628007</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-1.263593795907389</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.6392006697162018</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.2907840546324759</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.551118612155292</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.4555838957824422</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.2070873410030994</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.0958232627004949</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.0674762127979964</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.01786492636304546</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.721871023490893</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.5095010963301201</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.06605133436300113</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0.02745737378686692</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.2195284828671015</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>zTBIR3ZF</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.2227817773842855</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.623933695757177</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.504445382523099</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.2688016221451399</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-1.966620655280257</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.196819370863868</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.9854184225715219</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-2.301854160205266</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.137613702394322</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-1.070566899251701</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.1183423081372179</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.3873470647939958</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-1.185938540571168</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-1.27693853936549</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0.9384864525256899</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-1.885719997233963</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.553850037255643</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-1.959220947343566</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.6091890042609707</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-1.078023479985864</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-1.068772351206077</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>SQjcKLRk</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.004471716800532986</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.4954014313617456</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.06023346763158076</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1356895467423473</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.5965186777816865</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5613919607762649</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9957959296544173</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.120365909952359</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-1.188313783436904</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.251737669138954</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-1.469810672183536</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.9348472304810861</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.647357588892093</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.634690062387254</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.441635388225708</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.064060386712519</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.4005505938041666</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.591357230286238</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.455299671947521</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.26722435852485</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.317719233524727</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>v1I9TP43</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>-0.2227817773842855</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-1.025235213141476</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.562797379084372</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-1.684520713251345</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1.966620655280257</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.9550307025040008</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.9854184225715219</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-2.686395035871147</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.303751379953695</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.02953381686968354</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.266601863709226</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.3315682342622101</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-2.40462876753568</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-2.125521398881653</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-1.758402194448151</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-2.694758393765706</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.1900110866702691</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-1.841354286635013</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-1.710427816918038</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-0.640615494446082</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-1.856307480759761</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>n7VN5MCd</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.1865495862102505</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.704084746046756</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.956673355872968</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.2688016221451399</v>
+      </c>
+      <c r="G21" t="n">
         <v>-0.01375259199496684</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>-1.878859196972798</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-1.994221459672562</v>
+      </c>
+      <c r="K21" t="n">
         <v>1.303751379953695</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L21" t="n">
         <v>-0.670169559874002</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M21" t="n">
         <v>0.6766390824782634</v>
       </c>
-      <c r="N11" t="n">
-        <v>0.4348078249860372</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>-0.1456499796356354</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-0.2981285465188994</v>
-      </c>
-      <c r="R11" t="n">
-        <v>-0.9873116469652075</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-0.1694908160901271</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-0.1428221313198321</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-1.403738699304649</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.1188617321897991</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>-0.2155854335345813</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>-0.656077117575508</v>
+      <c r="N21" t="n">
+        <v>0.4491356016477868</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.1637051801778766</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.2596374962267206</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-0.7555510871396418</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.2707937604570462</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.4968863405292254</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-1.28636649433962</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.498083457035785</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.2873189876210719</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-0.3366068883723683</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,68 +558,68 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rgFQPs4S</t>
+          <t>vuXo7iAM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.851163798161364</v>
+        <v>-0.1409155046653783</v>
       </c>
       <c r="C2" t="n">
-        <v>1.110657219658063</v>
+        <v>-0.1145834007075643</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06023346763158076</v>
+        <v>0.9646894143313194</v>
       </c>
       <c r="E2" t="n">
         <v>-0.2130278742385446</v>
       </c>
       <c r="F2" t="n">
-        <v>1.551408637848553</v>
+        <v>1.95589980673604</v>
       </c>
       <c r="G2" t="n">
-        <v>1.20678994755834</v>
+        <v>0.4744644238263558</v>
       </c>
       <c r="H2" t="n">
-        <v>1.319603292416398</v>
+        <v>0.5613919607762649</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5004923415979325</v>
+        <v>0.00518875354144776</v>
       </c>
       <c r="J2" t="n">
-        <v>2.312636347785299</v>
+        <v>-0.5137390883589218</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1914877180806642</v>
+        <v>0.7222695084958886</v>
       </c>
       <c r="L2" t="n">
-        <v>1.011499265512334</v>
+        <v>-1.150646367127241</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4363348643834106</v>
+        <v>2.703841628547741</v>
       </c>
       <c r="N2" t="n">
-        <v>1.209045056345307</v>
+        <v>0.773444826386477</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3477884902303393</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9639870001912482</v>
+        <v>-0.4445058144886453</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.156525487113428</v>
+        <v>-0.1297920110204571</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8216451379581221</v>
+        <v>0.236118616236393</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9048647517879397</v>
+        <v>0.009661193275293462</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4888971752234327</v>
+        <v>-0.6637525208285112</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7959748393478759</v>
+        <v>0.2058719537400296</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -628,80 +628,80 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.872613397037264</v>
+        <v>-0.6600013359894412</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.8330133204056178</v>
+        <v>-0.1301531616962072</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.248814006630851</v>
+        <v>-0.6814950646803996</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WIJkQBF8</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.696374686324615</v>
+        <v>0.6504584649507246</v>
       </c>
       <c r="C3" t="n">
-        <v>1.176886442380529</v>
+        <v>-1.472282466518124</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.63197443264535</v>
+        <v>-0.3044665108763784</v>
       </c>
       <c r="E3" t="n">
         <v>-0.2130278742385446</v>
       </c>
       <c r="F3" t="n">
-        <v>1.95589980673604</v>
+        <v>-0.4710472065888835</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7185729317370172</v>
+        <v>0.1083016619603638</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.5613919607762649</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.5004923415979325</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7360187575551898</v>
+        <v>1.79350616563636</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4730629921568287</v>
+        <v>-0.5237630731994108</v>
       </c>
       <c r="L3" t="n">
-        <v>1.011499265512334</v>
+        <v>3.894360109031767</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.03884416907566966</v>
+        <v>-0.277338586260314</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7468349611752405</v>
+        <v>1.160151518487089</v>
       </c>
       <c r="O3" t="n">
-        <v>1.151734307983518</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.8379681064522699</v>
+        <v>0.8576170374252818</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1287739480864025</v>
+        <v>2.145462807050716</v>
       </c>
       <c r="R3" t="n">
-        <v>0.04060871753379659</v>
+        <v>1.188364475461635</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1231562563477827</v>
+        <v>1.125773633188278</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7278058455550517</v>
+        <v>0.1747009528627636</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.403148988330654</v>
+        <v>0.7711913367647489</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -710,244 +710,244 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.07997493520996027</v>
+        <v>0.5973000246047925</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02123459461842354</v>
+        <v>0.5037277360890295</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.8645170316066862</v>
+        <v>1.810450318232644</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Esk5Iad2</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6504584649507246</v>
+        <v>1.469121192139797</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.677531793848528</v>
+        <v>-0.3298283745555798</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.442330443821211</v>
+        <v>-0.3336425091570151</v>
       </c>
       <c r="E4" t="n">
         <v>-0.2130278742385446</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6732927910326272</v>
+        <v>-0.8755383754763707</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1358068459502975</v>
+        <v>-0.8681323696822815</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9550307025040008</v>
+        <v>0.5613919607762649</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4901148345150371</v>
+        <v>0.5004923415979325</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9944151829412722</v>
+        <v>-2.936346605053969</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.689900750758784</v>
+        <v>-1.022176105877531</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.631123174380479</v>
+        <v>-2.231719183447028</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2791483871705225</v>
+        <v>1.511369542624519</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2900972807023709</v>
+        <v>0.8761033461679141</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3969069534772184</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.643199213833078</v>
+        <v>-1.272844518391666</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.99867649519798</v>
+        <v>-0.8034384926216697</v>
       </c>
       <c r="R4" t="n">
-        <v>-2.029734094356396</v>
+        <v>-0.9778496819099544</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.749458372952045</v>
+        <v>-1.019370431977989</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6786025320345184</v>
+        <v>-0.0315551693333737</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.658878025488254</v>
+        <v>-1.585485675001891</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.007888742154263037</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3599459027034815</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.051793139767453</v>
+        <v>-0.8856927648389589</v>
       </c>
       <c r="Y4" t="n">
-        <v>-2.214169409442646</v>
+        <v>-0.9904763044692818</v>
       </c>
       <c r="Z4" t="n">
-        <v>-2.576223998303059</v>
+        <v>-1.221590414349536</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6cNF7rrp</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1409155046653783</v>
+        <v>-0.8777119591355431</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.372938632434424</v>
+        <v>-0.4954014313617456</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3628185074376518</v>
+        <v>1.504445382523099</v>
       </c>
       <c r="E5" t="n">
         <v>-0.2130278742385446</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.684520713251345</v>
+        <v>0.1356895467423473</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.844566401324927</v>
+        <v>0.2303559159156945</v>
       </c>
       <c r="H5" t="n">
         <v>-0.196819370863868</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9854184225715219</v>
+        <v>-0.4901148345150371</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2253334316095116</v>
+        <v>1.21669485213754</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3069253145974554</v>
+        <v>-1.271382622216591</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.230725835002781</v>
+        <v>0.5310224582590953</v>
       </c>
       <c r="M5" t="n">
-        <v>1.074129777786004</v>
+        <v>0.4381446652936191</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01751132971259185</v>
+        <v>0.9065896709537432</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03722412012186746</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.546799099188193</v>
+        <v>2.212393193417223</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.187112098393382</v>
+        <v>1.490215137831961</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.51475103792171</v>
+        <v>1.571146726095469</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.330312087405997</v>
+        <v>2.227145565910904</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5615583433672423</v>
+        <v>-0.9288290924980817</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.333480531619886</v>
+        <v>2.033864478390808</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.174772919866605</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.601998554681022</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6963695626836706</v>
+        <v>1.566139044022252</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.169505360020046</v>
+        <v>1.33867203472359</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1.830479387975465</v>
+        <v>1.633034599343112</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zFWqD4KM</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.469121192139797</v>
+        <v>1.851163798161364</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.3298283745555798</v>
+        <v>1.110657219658063</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8625734203490908</v>
+        <v>0.3082294530169929</v>
       </c>
       <c r="E6" t="n">
         <v>-0.2130278742385446</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7424263000735782</v>
+        <v>-0.8755383754763707</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.356349385503604</v>
+        <v>-0.5019696078162895</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.196819370863868</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.480722010628007</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.263593795907389</v>
+        <v>0.7552458013384835</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6392006697162018</v>
+        <v>-0.274556556860351</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2907840546324759</v>
+        <v>2.212691283645432</v>
       </c>
       <c r="M6" t="n">
-        <v>1.551118612155292</v>
+        <v>-0.1580913776679918</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4555838957824422</v>
+        <v>0.6884094718989956</v>
       </c>
       <c r="O6" t="n">
-        <v>1.278383192967797</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2070873410030994</v>
+        <v>0.3506074955538264</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0958232627004949</v>
+        <v>0.05376246738160985</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0674762127979964</v>
+        <v>-0.3915230452700365</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01786492636304546</v>
+        <v>0.1984952556592487</v>
       </c>
       <c r="T6" t="n">
-        <v>1.721871023490893</v>
+        <v>-0.02754685922820594</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5095010963301201</v>
+        <v>-0.4615861011869381</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -956,177 +956,1243 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.06605133436300113</v>
+        <v>0.8573979822968688</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.02745737378686692</v>
+        <v>0.8316853576309289</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2195284828671015</v>
+        <v>0.1867279135328897</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4WHcOkpL</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.041444504573358</v>
+        <v>1.851163798161364</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.8099902392934607</v>
+        <v>-0.03179687230448136</v>
       </c>
       <c r="D7" t="n">
-        <v>1.081393407453866</v>
+        <v>-1.194334458435799</v>
       </c>
       <c r="E7" t="n">
         <v>-0.2130278742385446</v>
       </c>
       <c r="F7" t="n">
-        <v>0.944671884517322</v>
+        <v>-1.886766297695089</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7185729317370172</v>
+        <v>-1.600457893414265</v>
       </c>
       <c r="H7" t="n">
-        <v>1.319603292416398</v>
+        <v>-0.9550307025040008</v>
       </c>
       <c r="I7" t="n">
-        <v>1.986403105767387</v>
+        <v>-0.4901148345150371</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8898351078215413</v>
+        <v>0.8129269326883655</v>
       </c>
       <c r="K7" t="n">
-        <v>1.303751379953695</v>
+        <v>0.9714760248349484</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.150646367127241</v>
+        <v>-0.4299311562473825</v>
       </c>
       <c r="M7" t="n">
-        <v>1.2331260559091</v>
+        <v>1.869111168401485</v>
       </c>
       <c r="N7" t="n">
-        <v>1.204925820555055</v>
+        <v>0.7610433396981412</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04735603092060974</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8907758991113807</v>
+        <v>-0.6883768064004694</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4410813084924982</v>
+        <v>-0.7426518439975158</v>
       </c>
       <c r="R7" t="n">
-        <v>0.07747764927536611</v>
+        <v>-0.8191965919956238</v>
       </c>
       <c r="S7" t="n">
-        <v>0.422229088499062</v>
+        <v>-0.5324750896054391</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2713755333035737</v>
+        <v>0.6667393743044835</v>
       </c>
       <c r="U7" t="n">
-        <v>0.308649928641535</v>
+        <v>-0.5534646100190286</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5755533467019082</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.772562272178829</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1657209617979026</v>
+        <v>-0.7886702609251285</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5568462470766212</v>
+        <v>-0.4798500256978401</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.8407883369854253</v>
+        <v>-0.7215895760970401</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>Whh3dzd4</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.3046480501031927</v>
+        <v>1.469121192139797</v>
       </c>
       <c r="C8" t="n">
-        <v>1.623933695757177</v>
+        <v>-1.223922881308875</v>
       </c>
       <c r="D8" t="n">
-        <v>1.504445382523099</v>
+        <v>0.3082294530169929</v>
       </c>
       <c r="E8" t="n">
         <v>-0.2130278742385446</v>
       </c>
       <c r="F8" t="n">
+        <v>-0.6732927910326272</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-1.234295131548274</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.9550307025040008</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5004923415979325</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.908868428336125</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.7729695895384707</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5310224582590953</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.9928218378142473</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.298653359550665</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.7225640194618784</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.4831656505900639</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.4836938592548032</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.6283398894815047</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.6220123546175393</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.03407761018359728</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.811230863708557</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-0.005324660875370118</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0.4427459391919398</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>KIQjmWIj</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.9322894742814812</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-1.025235213141476</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.504445382523099</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-1.077783959920114</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-2.45483767110158</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5613919607762649</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.00518875354144776</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.5137390883589218</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.220682541174008</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.8913800636990244</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.630616751216841</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.7331121350836561</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-1.659308116088656</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-2.083669596565007</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-1.625736675437237</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-2.26669615001255</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.4011848473015888</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-1.931503034162926</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.5653062610593198</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.3515786584241036</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-1.443418259307856</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>pIgDNCf3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.6504584649507246</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.677531793848528</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.9646894143313194</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1.482275128807601</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-2.45483767110158</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.9550307025040008</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.976025598684491</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-1.321274927257271</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.9714760248349484</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.06957355080745331</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.630616751216841</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.9368172997720747</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-1.912949039727991</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-2.833321472741077</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-2.076977243389495</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-2.874116067335966</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.1810534653356299</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-1.593905975203196</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-2.161428136554233</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-2.887003881952117</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-2.248994256246272</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>CCDxBZAc</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-1.041444504573358</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.8099902392934607</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.4211705039989253</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.753654222292296</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.939115471290324</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.319603292416398</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9957959296544173</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.197274085085535</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.9714760248349484</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-1.751242376193789</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-1.589057880775858</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.04510503423721424</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.362500541630343</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.40708119083307</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.648636643626786</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.816164251279534</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.2347794243775576</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.200884772884083</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.376385274214456</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.486321821746502</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.990271486106802</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.9233460406804153</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.375574110547928</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.8296344799278396</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1356895467423473</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.4744644238263558</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0.1484252564763358</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.6392006697162018</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.1306251188813959</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.279148387170523</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.3180364451927833</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.7299301655372658</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.7166870659112139</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.145631065058331</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.8015571915659802</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.160813765941626</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.270758679021048</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.1491228620700686</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0.3791215900473002</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.7139757269200583</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.8777119591355431</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-1.207365575628259</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.9609264721907048</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5401807156298346</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9626814396476785</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.319603292416398</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.491099517710902</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.005391093790016673</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.689900750758784</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.1306251188813964</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.3586465262320708</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0566341198750891</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.2315675036014701</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.2955209950026482</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.1017841706537011</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.07568928172679383</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.5748826811770238</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.3613691262043023</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.7909206616339625</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.230664395715491</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.4910560076530494</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-1.696374686324615</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.176886442380529</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.504445382523099</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.360390975623528</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.549386741066977</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.07781462405653</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.491099517710902</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.620462771586714</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.140787637038082</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.091578733387874</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.4363348643834101</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.3893569334645975</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.261097155246598</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.329170470570119</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.08613161023297</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.021309225743526</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-1.245471890692398</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.397529281103762</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.499822978648317</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.530685615182433</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.9679334976016691</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>pOEMqcCb</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.9233460406804153</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-1.704084746046756</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.9609264721907048</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.6732927910326272</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.01375259199496684</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.9550307025040008</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.00518875354144776</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-1.648134671573269</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.5237630731994108</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-1.39088477075386</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.5971409434167152</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.5780855916035298</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.0299275389730883</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.3827261433125844</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0.535519484637532</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.298125770414562</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-1.139581419096907</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.8015067839830212</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.5430139940760982</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.06284409489203575</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.7317656229536874</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>A50vXJSh</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.851163798161364</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.03179687230448136</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.8296344799278396</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1.684520713251345</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-2.698946179012241</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.9550307025040008</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-1.480722010628007</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.3899319694558974</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.8053383472755753</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.3708635225080158</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.03884416907566966</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.5565939266109053</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.1869157705651185</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.5720589469696236</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.2664505360130505</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.01056166893224265</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.1321039950230182</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.5177021553230782</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.2000525025697955</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0.1400882906031456</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.6130672463295618</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>O8QDoJsn</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-1.696374686324615</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-1.323266715392575</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.194334458435799</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-1.482275128807601</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-1.356349385503604</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.196819370863868</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.00518875354144776</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.4176038694424515</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-2.185139848793143</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.411896604890033</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-2.185293923737468</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.319150040052888</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.02419127223043445</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1060933314094351</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0.01093504918457017</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.01957307499578324</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.4598105769156048</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.03220925493980905</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.1844908157400436</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.02123459461842354</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.3409759440450945</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Yqo4RFdU</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.1409155046653783</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-1.372938632434424</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.3336425091570151</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.573864482285989</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.695006963379663</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.196819370863868</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.9854184225715219</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.312830071054009</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.3576253956400376</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-1.951441045882639</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-1.469810672183536</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.08009664879557309</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.4827216772291456</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.1277950336974354</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3561237310115089</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.104831659383071</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.2917504402851411</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.6820029135994681</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.07225567603555257</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.616974478136173</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0.3178122397389875</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>S66wtFBN</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.3046480501031927</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.3159065469884668</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.4211705039989253</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1.077783959920114</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.8681323696822815</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.9550307025040008</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.9854184225715219</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.4560579570090398</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.802164412631815</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-1.150646367127241</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.1996502481089747</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.3127829270834711</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-1.03884141056063</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.2410429411188232</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-0.7224554246145306</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.4016665034797649</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.4783560123471185</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.2592617795825159</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-1.087413759140861</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-0.2958042218871357</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-0.7122781606726589</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>44gmVcc5</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>-1.041444504573358</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.5285160427229788</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.06023346763158076</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-1.886766297695089</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1.356349385503604</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-2.471453365784267</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-1.976025598684491</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.9944151829412722</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-1.022176105877531</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.4299311562473825</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-2.026297645614372</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.04956972999325675</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-0.4171933670247839</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-0.5081817716629927</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-0.1496216350040789</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.4529801555083525</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.1881365872524876</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.2896440301103962</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.2586315546703365</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-0.4278135584525906</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-0.6755978349116235</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>2ucWYubt</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.9322894742814812</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.720642051727373</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.3044665108763784</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.2130278742385446</v>
+      </c>
+      <c r="F21" t="n">
         <v>-0.2688016221451399</v>
       </c>
-      <c r="G8" t="n">
-        <v>-1.966620655280257</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.196819370863868</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-0.9854184225715219</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-2.301854160205266</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.137613702394322</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-1.070566899251701</v>
-      </c>
-      <c r="M8" t="n">
-        <v>-0.1183423081372179</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.3873470647939958</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.028144592074725</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-1.185938540571168</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-1.27693853936549</v>
-      </c>
-      <c r="R8" t="n">
-        <v>-0.9384864525256899</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-1.885719997233963</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.553850037255643</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-1.959220947343566</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.6091890042609707</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-1.078023479985864</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-1.068772351206077</v>
+      <c r="G21" t="n">
+        <v>-0.6240238617716202</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.9550307025040008</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.00518875354144776</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.69717722345118</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.0253500405212911</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.052532347894352</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-1.151818115937344</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.390629725843171</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.09488831514590594</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.09403808904448728</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-0.1178594973426214</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.07196754661401546</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.5032010461255892</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.3240538387371175</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.7551720664160742</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.1141919888467059</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.3762263024373934</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:BZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,697 +436,5381 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_team_away</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>h2h_35_segun_loc</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>h2h_35</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>h2h_3_segun_loc</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>h2h_3</t>
+          <t>dif_mean_last_120_matches_expected_points_against</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_ball_possession</t>
+          <t>dif_mean_last_360_matches_expected_points_against</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
+          <t>dif_mean_last_120_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts</t>
+          <t>dif_mean_last_120_matches_shots_on_goal_against</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
+          <t>dif_mean_last_360_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
+          <t>dif_mean_last_360_matches_shots_on_goal_against</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>dif_sum_pot_player_miss</t>
+          <t>dif_mean_last_120_matches_goal_attempts</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_sub</t>
+          <t>dif_mean_last_120_matches_goal_attempts_against</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_val_player_start</t>
+          <t>dif_mean_last_360_matches_goal_attempts</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_pot_player_start</t>
+          <t>dif_mean_last_360_matches_goal_attempts_against</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_val_player_sub</t>
+          <t>dif_mean_last_120_matches_goals</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_120_matches_goals_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_goals</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_goals_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_points</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_points</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_goal_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_goal_ratio_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_goal_ratio</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_goal_ratio_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_PPS</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_PPS_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_PPS</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_PPS_against</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_attacks</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_attacks_against</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_attacks</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_attacks_against</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_dangerous_attacks_against</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_dangerous_attacks_against</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_dead_balls_against</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_dead_balls_against</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_ball_possession</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_ball_possession</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_total_passes</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_total_passes_against</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_total_passes</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_total_passes_against</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_yellow_cards_against</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_yellow_cards_against</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_red_cards</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_red_cards_against</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_defensive_actions</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_defensive_actions_against</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_defensive_actions</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_defensive_actions_against</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_PPDA</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_PPDA_against</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_PPDA</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_PPDA_against</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_KGP</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_KGP_against</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_KGP</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_KGP_against</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_120_matches_clean_sheet_against</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_clean_sheet_against</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_360_matches_mean_rat_player_start_home_against</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_360_matches_mean_rat_player_start_away_against</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>is_rival_match</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rgFQPs4S</t>
+          <t>SIOithtm</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.851163798161364</v>
+        <v>0.1325479996510943</v>
       </c>
       <c r="C2" t="n">
-        <v>1.110657219658063</v>
+        <v>-0.3419271370252056</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06023346763158076</v>
+        <v>-1.209860349677208</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2130278742385446</v>
+        <v>-1.441860900939873</v>
       </c>
       <c r="F2" t="n">
-        <v>1.551408637848553</v>
+        <v>-0.4199759602720987</v>
       </c>
       <c r="G2" t="n">
-        <v>1.20678994755834</v>
+        <v>-1.073779168040133</v>
       </c>
       <c r="H2" t="n">
-        <v>1.319603292416398</v>
+        <v>-0.2288267322982719</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5004923415979325</v>
+        <v>-0.9792874076637662</v>
       </c>
       <c r="J2" t="n">
-        <v>2.312636347785299</v>
+        <v>0.5616360837273462</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1914877180806642</v>
+        <v>-0.2192114824202945</v>
       </c>
       <c r="L2" t="n">
-        <v>1.011499265512334</v>
+        <v>0.2191687093406323</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4363348643834106</v>
+        <v>-0.7402425965428119</v>
       </c>
       <c r="N2" t="n">
-        <v>1.209045056345307</v>
+        <v>-0.2038685428453549</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3477884902303393</v>
+        <v>-0.5402342388201683</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9639870001912482</v>
+        <v>0.88702355401101</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.156525487113428</v>
+        <v>-0.1834803093808312</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8216451379581221</v>
+        <v>-0.4123033262402986</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9048647517879397</v>
+        <v>-0.758134895774825</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4888971752234327</v>
+        <v>-0.5146805775651</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7959748393478759</v>
+        <v>-1.041914770985443</v>
       </c>
       <c r="V2" t="n">
+        <v>-0.8931636970634422</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.03646109586683264</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-0.08107385294103736</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.02272527268132</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.1170089652392315</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.794650393100172</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.4173374605914387</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.305746875076653</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.8793372745969241</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.334067066741354</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.4608351233065626</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.6819756950881616</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.1353885100349233</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1.054897253442706</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-0.4088206335472036</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.4148594684768233</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-0.08296556812036375</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.157005595583068</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.2474832912195888</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1.628397802213661</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.16367907064111</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.237815413901267</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.3940784351137959</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>-0.02460559608713148</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-0.5863392149670551</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>-0.5125679082025213</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-0.6612430180080433</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-0.4121651103549693</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.3978684735075494</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0.3006346369184039</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.4145725895678771</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-0.8418312172523984</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>-1.154071338678082</v>
+      </c>
+      <c r="BC2" t="n">
         <v>0</v>
       </c>
-      <c r="W2" t="n">
+      <c r="BD2" t="n">
         <v>0</v>
       </c>
-      <c r="X2" t="n">
-        <v>0.872613397037264</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.8330133204056178</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.248814006630851</v>
+      <c r="BE2" t="n">
+        <v>0.6256088351665275</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.607423011472333</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0.6859144709221001</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0.4812226913465504</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>-2.494062752277008</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>-3.074028622423348</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>-0.6848135770974141</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>-0.8604533564883726</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.4070591625342008</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>-1.546012332901292</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>-1.023995970718769</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>-1.278966312850842</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0.8711686893266564</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1.486498413970875</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>0.07191915876007746</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1.261685064273134</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>0.7100436069057205</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0.7408887852064822</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>-0.8976852828095194</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>-0.09768545779796206</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>-0.08110174641427655</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>-0.2306826362346843</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WIJkQBF8</t>
+          <t>lnhZhVPh</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.696374686324615</v>
+        <v>-0.6333692052878306</v>
       </c>
       <c r="C3" t="n">
-        <v>1.176886442380529</v>
+        <v>-1.502841163061446</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.63197443264535</v>
+        <v>1.620089766376452</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2130278742385446</v>
+        <v>-0.9602957376508675</v>
       </c>
       <c r="F3" t="n">
-        <v>1.95589980673604</v>
+        <v>1.774713097592452</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7185729317370172</v>
+        <v>-1.073779168040133</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0.2288267322982719</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>3.221131778682758</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7360187575551898</v>
+        <v>1.790764412640715</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4730629921568287</v>
+        <v>-0.7164468278078512</v>
       </c>
       <c r="L3" t="n">
-        <v>1.011499265512334</v>
+        <v>-0.1046980425310336</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.03884416907566966</v>
+        <v>-1.152260294987207</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7468349611752405</v>
+        <v>0.1286189211394148</v>
       </c>
       <c r="O3" t="n">
-        <v>1.151734307983518</v>
+        <v>-1.755969790763997</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.8379681064522699</v>
+        <v>-0.03304011481699805</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1287739480864025</v>
+        <v>-0.6269066384565541</v>
       </c>
       <c r="R3" t="n">
-        <v>0.04060871753379659</v>
+        <v>-0.1084848975043324</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1231562563477827</v>
+        <v>0.1490855444878128</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7278058455550517</v>
+        <v>1.150950763456232</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.403148988330654</v>
+        <v>-0.6269374253705327</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.348352974652718</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-0.4039004630834648</v>
       </c>
       <c r="X3" t="n">
-        <v>0.07997493520996027</v>
+        <v>-0.7995351322494201</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02123459461842354</v>
+        <v>0.6585015976263101</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.8645170316066862</v>
+        <v>-0.02918087129051068</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-0.1848558014003255</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.8805828831355628</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5663821755426559</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-0.9736045924323579</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.592203881557649</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-0.04702776695655764</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-0.2890328900107353</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.4194841879305528</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-0.588600357080745</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.8329506578333519</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-1.395584462053934</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-0.1892807006918432</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-0.5256696863835244</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.4699273655103546</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>-0.7342333590266178</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.2144906988352751</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.1891495310814259</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.03520513933092721</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-0.2892604060091509</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-0.3227829214897657</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.3493549400678716</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.083577657475784</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-0.2167010649149771</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0.2582083522976676</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.9305804249420363</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.0492817884343735</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>-0.2698122124771174</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-0.5451764669246462</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-1.851341919998944</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>-0.1933239380550177</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.2342475991258921</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0.5451735010513835</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0.05964883542182177</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>0.1128433447542305</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0.7293820000347337</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.3785745373738804</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.4287596063200587</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>-0.06971772655823372</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.7672636870181362</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0.6581227269288653</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0.2194655141620395</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>-0.129154408447606</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>-1.691813146032753</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>-1.169895572659975</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>-0.4728397960589084</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>-0.7501904217511368</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>0.9699238655889366</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>0.8086616268498604</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>-0.9206632295340886</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>0.6343626120072902</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>0.4084576710172716</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>-0.2306826362346843</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Esk5Iad2</t>
+          <t>SW3Qfiet</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6504584649507246</v>
+        <v>1.554965665966241</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.677531793848528</v>
+        <v>-0.09492415276217575</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.442330443821211</v>
+        <v>-1.722892242061205</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2130278742385446</v>
+        <v>-1.441860900939873</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6732927910326272</v>
+        <v>-0.3233544294227159</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1358068459502975</v>
+        <v>-1.073779168040133</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9550307025040008</v>
+        <v>-0.2288267322982719</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4901148345150371</v>
+        <v>-0.9792874076637663</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9944151829412722</v>
+        <v>-4.232710753724766</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.689900750758784</v>
+        <v>1.046478487657123</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.631123174380479</v>
+        <v>-0.1509647213698431</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2791483871705225</v>
+        <v>1.12779059134041</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2900972807023709</v>
+        <v>-0.7863562990613502</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3969069534772184</v>
+        <v>0.09014715848403922</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.643199213833078</v>
+        <v>-2.434181884685214</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.99867649519798</v>
+        <v>-0.03825350016132755</v>
       </c>
       <c r="R4" t="n">
-        <v>-2.029734094356396</v>
+        <v>-1.437751005209541</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.749458372952045</v>
+        <v>0.451492357908692</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6786025320345184</v>
+        <v>1.150950763456232</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.658878025488254</v>
+        <v>0.1007764705628619</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.007888742154263037</v>
+        <v>-0.2478696131711772</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3599459027034815</v>
+        <v>-0.4039004630834648</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.051793139767453</v>
+        <v>0.7893322474678526</v>
       </c>
       <c r="Y4" t="n">
-        <v>-2.214169409442646</v>
+        <v>-1.071085677201167</v>
       </c>
       <c r="Z4" t="n">
-        <v>-2.576223998303059</v>
+        <v>0.8725825380869684</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0.688090885702875</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.4588841015911989</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-2.076059704600641</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.02313007591877258</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-1.010444338492005</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-0.4503956946957547</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.819442894775441</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-3.4464321503535</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.722412050422026</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-1.409808537645122</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.480581782193511</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-3.7508376418364</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.4174101232518795</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-2.337976635020971</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.6308424230233211</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-4.561802351416212</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.4350702259315611</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-1.658956634995401</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.558425348751774</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.621900893700975</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.171810453995524</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-1.957823434124781</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.82479474578215</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-0.3454466341709114</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-0.05933438480938589</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.510444992968387</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.5503044031743419</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.253551161383915</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.558187426337004</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.08583894953360664</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-0.5339800123612816</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-1.166228487960146</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>-0.4920845174232226</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-0.6622814061864157</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>-0.6127255882934662</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>3.672899921804642</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.053579772460315</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>2.852954953708359</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>2.165781550533203</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>-1.346949109294884</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.8470716308980939</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>-0.2224398179670826</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>-1.407037386548375</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0.3058788643571638</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1.030670647051916</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>-0.5536515707756495</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0.6207155818558034</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.6678778698776392</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>1.246300973256198</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0.4231027797589286</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>-0.1330073283441636</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>-0.2306826362346843</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6cNF7rrp</t>
+          <t>dzYLoEIP</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1409155046653783</v>
+        <v>-0.2230564169276922</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.372938632434424</v>
+        <v>-1.700443550471869</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3628185074376518</v>
+        <v>-1.325706260860691</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2130278742385446</v>
+        <v>-0.9602957376508675</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.684520713251345</v>
+        <v>0.9603316232905119</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.844566401324927</v>
+        <v>-1.073779168040133</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.196819370863868</v>
+        <v>-0.2288267322982719</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9854184225715219</v>
+        <v>-0.9792874076637663</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2253334316095116</v>
+        <v>-1.911469104247336</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3069253145974554</v>
+        <v>-0.9424628938931042</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.230725835002781</v>
+        <v>-1.26136501350127</v>
       </c>
       <c r="M5" t="n">
-        <v>1.074129777786004</v>
+        <v>-1.270275351215344</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01751132971259185</v>
+        <v>0.07938545366529917</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03722412012186746</v>
+        <v>-0.675315966813927</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.546799099188193</v>
+        <v>-4.184546913187279</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.187112098393382</v>
+        <v>-0.74265304205393</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.51475103792171</v>
+        <v>-0.9673442892611189</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.330312087405997</v>
+        <v>-0.9597394380554108</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5615583433672423</v>
+        <v>-0.9310884128204328</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.333480531619886</v>
+        <v>-0.1528207962018059</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.174772919866605</v>
+        <v>-0.5541407166991157</v>
       </c>
       <c r="W5" t="n">
-        <v>2.601998554681022</v>
+        <v>0.1472585877414832</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6963695626836706</v>
+        <v>0.1766041356087981</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.169505360020046</v>
+        <v>2.756645845414169</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1.830479387975465</v>
+        <v>2.836642350309054</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.44958965196392</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9365221051762005</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.6805326768412228</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.793461644267767</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.4102196460596956</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.8519177697679431</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.76270837744294</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-2.973425916022275</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.464811675196254</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0.6260007171443056</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2.340863649892523</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-6.422005347694818</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-0.513774986081817</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0.9547074868511484</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.3404614988199045</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-1.335263961086749</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.4313037471640493</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.04112482690132486</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.923253804938929</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.869639491939797</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.231364973361515</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-1.793076417555493</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.469872132010867</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-1.369515797869244</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-1.859179493448337</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.2319271890011252</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-0.379445857277747</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.7582180934764016</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-0.7602925291714409</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.3650018371222306</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-0.4470108487966956</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>-1.608832450635542</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-2.297757308552458</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>-2.880302700544744</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-2.228763317809423</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1.687164991265848</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.4549158328234431</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>3.564951112583091</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.562331830581842</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>-0.9554715520730244</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>-0.2843931961547553</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0.4306109541738569</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>-0.2679343486108591</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0.3058788643571638</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0.7186213098024995</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>-0.1152187493687931</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0.4823815628531888</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-0.05065825646182585</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>1.088159816797765</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>-0.513422805324955</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0.6744092518027874</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>4.334959996653813</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zFWqD4KM</t>
+          <t>x8OGzlAO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.469121192139797</v>
+        <v>1.554965665966241</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.3298283745555798</v>
+        <v>-0.934734299256477</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8625734203490908</v>
+        <v>-0.1175989013757955</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2130278742385446</v>
+        <v>0.4114353335359955</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7424263000735782</v>
+        <v>-0.3233544294227159</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.356349385503604</v>
+        <v>-1.073779168040133</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.196819370863868</v>
+        <v>-0.2288267322982719</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.480722010628007</v>
+        <v>-0.9792874076637663</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.263593795907389</v>
+        <v>-5.716542441048944</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6392006697162018</v>
+        <v>0.5040399290525155</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2907840546324759</v>
+        <v>-1.26136501350127</v>
       </c>
       <c r="M6" t="n">
-        <v>1.551118612155292</v>
+        <v>0.341810316861014</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4555838957824422</v>
+        <v>-1.147295161257948</v>
       </c>
       <c r="O6" t="n">
-        <v>1.278383192967797</v>
+        <v>-3.602086740012033</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2070873410030994</v>
+        <v>-2.613706502993119</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0958232627004949</v>
+        <v>0.3700872134822044</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0674762127979964</v>
+        <v>-1.470122061526905</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01786492636304546</v>
+        <v>0.8547014424698641</v>
       </c>
       <c r="T6" t="n">
-        <v>1.721871023490893</v>
+        <v>-0.9310884128204328</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5095010963301201</v>
+        <v>0.8489671644337764</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-2.365492068931375</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.8821373221747472</v>
       </c>
       <c r="X6" t="n">
-        <v>0.06605133436300113</v>
+        <v>1.668280159651876</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.02745737378686692</v>
+        <v>4.403480445060509</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2195284828671015</v>
+        <v>1.923537920977931</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.5819017987608207</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8471456688124765</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.310583831334216</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0.1969318037139588</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-0.4978701229186278</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-1.097317612231939</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-1.260041475109632</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.4103879141934135</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.4591293696279559</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-0.1396835921517532</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-3.783829647009402</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.671234119309045</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.290901489328716</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-0.281191091202194</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.9196084538415779</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2.907506993126007</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.7060523248811647</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.1734301017038965</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-1.167914374950255</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.5321077853861652</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.6123144530995168</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.927638670937918</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.8159477541379451</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.1774690779528025</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-1.139241449992756</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.77986339070138</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0.6072560282920417</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-0.7550999151525045</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.5353286224362194</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0.5422775475407982</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.2487424597199898</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.459888357247201</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0.4256797285971597</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-0.08427366937386871</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.170966028615464</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.5344748612607645</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-0.08974387279809726</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>2.014948584082296</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-1.570972870858531</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>2.09732287482574</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-1.188635564635276</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.855923120333585</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>3.149374765201688</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0.8961886391640193</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>2.43489266467429</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0.05108335530277307</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0.5124726640969972</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.3028127665580169</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.640571430776318</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>-0.7821077373354735</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>-0.03346240929189401</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>-0.2306826362346843</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4WHcOkpL</t>
+          <t>ttV7xAuC</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.041444504573358</v>
+        <v>0.1872563714324461</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.8099902392934607</v>
+        <v>-0.6136304197145382</v>
       </c>
       <c r="D7" t="n">
-        <v>1.081393407453866</v>
+        <v>-0.5313342984596638</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2130278742385446</v>
+        <v>0.8638147293529397</v>
       </c>
       <c r="F7" t="n">
-        <v>0.944671884517322</v>
+        <v>-1.220554358738413</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7185729317370172</v>
+        <v>-1.073779168040133</v>
       </c>
       <c r="H7" t="n">
-        <v>1.319603292416398</v>
+        <v>-0.2288267322982719</v>
       </c>
       <c r="I7" t="n">
-        <v>1.986403105767387</v>
+        <v>2.621071894918968</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8898351078215413</v>
+        <v>-4.756704121855746</v>
       </c>
       <c r="K7" t="n">
-        <v>1.303751379953695</v>
+        <v>-0.5808371881566993</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.150646367127241</v>
+        <v>0.5893021400511081</v>
       </c>
       <c r="M7" t="n">
-        <v>1.2331260559091</v>
+        <v>1.467673953277445</v>
       </c>
       <c r="N7" t="n">
-        <v>1.204925820555055</v>
+        <v>-1.028367564502293</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04735603092060974</v>
+        <v>-0.2700707828326508</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8907758991113807</v>
+        <v>0.1689250807793945</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4410813084924982</v>
+        <v>1.629597058341814</v>
       </c>
       <c r="R7" t="n">
-        <v>0.07747764927536611</v>
+        <v>-0.7506950733224707</v>
       </c>
       <c r="S7" t="n">
-        <v>0.422229088499062</v>
+        <v>0.04828327334751988</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2713755333035737</v>
+        <v>-0.5146805775650999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.308649928641535</v>
+        <v>1.445944581227622</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5755533467019082</v>
+        <v>-0.9564807722720108</v>
       </c>
       <c r="W7" t="n">
-        <v>0.772562272178829</v>
+        <v>-0.7713398303000969</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1657209617979026</v>
+        <v>1.123163425653131</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5568462470766212</v>
+        <v>-0.281195708422551</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.8407883369854253</v>
+        <v>-0.6325209918411396</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.07469773449149789</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.6246861540976115</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.68256326625994</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-0.02185444584874176</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.8361321354264555</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.1911576897080011</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-0.649693221618897</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.5468320202504977</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.217464256340878</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-0.08687087269554855</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0.4711024549743986</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-1.239142634835201</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.454448069724303</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-0.2706647361237697</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1.260877399354063</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.7226069807769225</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.4824251927814926</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0.919767549308143</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-0.06695036567465573</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.9091068854003702</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-0.3701315053103795</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.173189923057184</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.305628396208641</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0.06143429737274688</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-1.499210471720546</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-1.046590614966136</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-1.974996468640914</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>-0.7808117315349652</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-0.4875301814645649</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.5045832809165429</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.04581441140262334</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.1910903309110672</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0.2817013449999859</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>-0.1334012944334871</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>-0.1084672336406186</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.09298030213878558</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.6923442088186919</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>2.226347761623058</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>-0.1734093137717554</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>2.133857370821611</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>-0.8045515967871555</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.591175395567248</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.8711686893266564</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.3058788643571638</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.529476784624846</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>-1.490990706197205</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0.6183424583076992</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.4632392998507224</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.519309007081128</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1.091383545553229</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>-0.06463417354690695</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>-0.2306826362346843</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>EB8yv2aJ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.3046480501031927</v>
+        <v>0.05048544197906663</v>
       </c>
       <c r="C8" t="n">
-        <v>1.623933695757177</v>
+        <v>-1.181737283519507</v>
       </c>
       <c r="D8" t="n">
-        <v>1.504445382523099</v>
+        <v>0.3126859115914277</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2130278742385446</v>
+        <v>-0.8289597840265933</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2688016221451399</v>
+        <v>1.49865158087993</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.966620655280257</v>
+        <v>-1.073779168040133</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.196819370863868</v>
+        <v>-0.2288267322982719</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9854184225715219</v>
+        <v>-3.379526942718923</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.301854160205266</v>
+        <v>-3.985405472504068</v>
       </c>
       <c r="K8" t="n">
-        <v>1.137613702394322</v>
+        <v>3.125826295641451</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.070566899251701</v>
+        <v>1.514635716827298</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1183423081372179</v>
+        <v>2.489920370325572</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3873470647939958</v>
+        <v>-0.002297344644028284</v>
       </c>
       <c r="O8" t="n">
-        <v>2.028144592074725</v>
+        <v>0.270256129142384</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.185938540571168</v>
+        <v>1.201191636049842</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.27693853936549</v>
+        <v>2.173715389919575</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.9384864525256899</v>
+        <v>-0.7986673997088853</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.885719997233963</v>
+        <v>2.669142322995139</v>
       </c>
       <c r="T8" t="n">
-        <v>1.553850037255643</v>
+        <v>1.567358598711565</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.959220947343566</v>
+        <v>2.227134422544001</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.1821415849992826</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1472585877414832</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6091890042609707</v>
+        <v>1.224580492443595</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.078023479985864</v>
+        <v>-0.1987261599904533</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1.068772351206077</v>
+        <v>-0.3589409766817545</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0.7641765487961613</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.160986981703972</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-1.263425325990792</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.2936559670746842</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-0.5832845318848976</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.3104762444107497</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.652984280187058</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.2193661657134957</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.877237429872173</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-0.7976909560431341</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.6074598866183932</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0.6411200141206302</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.861631648581882</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-1.279798122816854</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-1.18050813392756</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-3.469352345241669</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.7896663621815629</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0.1811236776654006</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.097530797982229</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.565216248632446</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.8807522893193214</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-1.157623639359666</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.253982974126906</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0.9968671791356569</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-0.7792724282649663</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.77986339070138</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>-0.4641627646236875</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-0.9276397356137575</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.1943756878026247</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0.1933239380550177</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>-1.722558581077285</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-0.1039789775391968</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0.2634637536445221</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>-0.2532888732826788</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>-0.2834295990035717</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>-1.487242692177255</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>-1.110505496181169</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1.460546216793642</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.829491381545392</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0.8602193486880365</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0.8678820786324932</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0.1294251059652501</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>-1.976588905517132</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>-1.465050460063403</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0.4704002460813729</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>-1.538865554511747</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0.5739720473963774</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0.5578025304199542</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1.100310722644479</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>-0.4753576302984767</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0.682473892626942</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>-0.2306826362346843</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>WUqjkmPH</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.2230564169276922</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.238891962258185</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.8126743684766944</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-1.529418203356055</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9603316232905119</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-1.073779168040133</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.2288267322982719</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.3792275238999775</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.7853730761938882</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.7616500410249019</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.422102359149679</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.687280973448345</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.4442796094684717</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-1.530833577441066</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.143695882166339</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-1.350046074264922</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.2993904120944508</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.467537780714554</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.5146805775651</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.8946461752174742</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.3769891261981566</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.617016056608011</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.009749724618679546</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.020329105128249</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-1.443487558812017</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.571264603577895</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-0.9988832335920931</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0.3598387261401548</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-1.37869553573608</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-1.068983240778943</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-1.630779546181834</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.1548567488916176</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.5650245677247754</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0.4137601857484625</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.7248801856127848</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-1.100263820903527</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.8340024503086453</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0.4424067842715705</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.5220481527918731</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-0.5635988862703756</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.776948265805842</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.0636329290785981</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.475629044491024</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.2718077910255293</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>-0.625139537112325</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>-0.6531782033652758</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-0.4579837118511292</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-0.4456232764045852</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.4093684430012955</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.4806191477822987</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.2319271890011252</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.9546255798550431</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.9065262185640518</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.1943756878026247</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0.1933239380550177</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.5531345321960396</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.2205972617560935</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-0.071387835878876</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0.475205068110638</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-1.193925168055668</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-0.9950570633716951</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.4698015530304906</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-1.009636513588701</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>-0.3467258079803836</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>3.045831786207406</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>-0.1550746918996069</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1.65576020763599</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0.3016171703578987</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>-2.055360234870258</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>-0.5324128513519787</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>-1.734396513943769</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.8502528270510675</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.8360924587078318</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0.07249307267139332</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0.8225482511202401</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.194234300298231</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>-0.2306826362346843</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8SWavWAa</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.05048544197906663</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.140090768552973</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.4982354666929544</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.1430942484331619</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.49865158087993</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1.073779168040133</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.2288267322982719</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.8592754309110087</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.3813914260981033</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-1.078072533544256</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.9837649404684135</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.2232457723593083</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.4824285214874875</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-1.148102014792083</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.7972612448570583</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.7755817127916328</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.9018710378177173</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.8547014424698641</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.3064766599374334</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.3167139366171079</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.9512679728668972</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.01808912750600123</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.6757025887649272</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.1013830513319638</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.4105305941728067</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.6634479536176808</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-1.011803800915615</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.4472058956209614</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-3.059855297831009</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.3234872966607638</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.9149795055312105</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.07625129200265901</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.9789050227645981</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.1028728017221153</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.8302942118707299</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0.3041820925850381</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.1628881759511824</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-1.04863404739282</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-0.2536241150719269</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.09531269314219132</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.507646636376768</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.1441308609097013</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.014553301529923</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-0.9350181422188778</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-1.310220196521864</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-0.4669152149678604</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.554283419102323</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-0.9976773165258072</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.8478284443117909</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.920495234693459</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-0.3160090126991296</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.344792374586693</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-0.9635855315431856</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.8080909701430954</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-0.8214404351294223</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.4864581734631904</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.3297729058826909</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-1.908637101953996</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>-2.147184550223257</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.740037634520738</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.3195199285333152</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>2.526697131987333</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.9638816517501142</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.03930362336340623</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1.176709317979861</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.072770724176302</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.5482238393545483</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>-0.09706889292023183</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>-0.2253999329690063</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>-1.398930019251185</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>-0.5221778666683861</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0.7823863962209257</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0.8507085369851407</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0.4493557434303531</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>-0.1835123093169993</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-0.07227044694803753</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>4.334959996653813</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>z3jsi9f5</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.9258193904806951</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.354639372503628</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.371848528126131</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.4114353335359955</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.553863884222435</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1.073779168040133</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.2288267322982719</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-1.399329326298418</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.3113749971377666</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.9560720612230219</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-1.26136501350127</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.5471565146979733</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.6503657972287392</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.926863446352972</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.1901241558364138</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.079526054579047</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.404585647046786</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.459515069311623</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-1.451598206889599</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.5655070315579731</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.5650215195169178</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.910967550381317</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.4457854884842723</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.3406316511086059</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.8097054980986237</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.607738271607089</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0.1054827319043741</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.8326963445741478</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.3048686616172206</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.4768774880706499</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.7269245485671956</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.005645223454461</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.6241503470161791</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.9269221355540024</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.3946995786115434</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.276663510512</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.7009222761920874</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.5346131664502859</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-0.08197821409970864</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-0.2039539206149111</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.05951523284307277</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.1183377678936284</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0.7686187959730842</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.06008394308791434</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.7392840017371782</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.1777008135055474</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-0.3306791990475879</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.9350774302373605</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-0.2883060035652883</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-0.5992879174010712</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-0.04204091184900222</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.6720404633101058</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-0.02432188390723937</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-0.3170537141477675</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.3301064761736526</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.8256379113650747</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-0.09512689828568875</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-3.003497223317679</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-2.411183505089085</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-1.566561954806035</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1.632694914834552</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.805333794210281</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>3.304929890950706</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.7433448446997292</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.6675164750658353</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.5842916750528984</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-0.01958610680244507</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.440720208295414</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>-1.110864595179289</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-0.6014634381689469</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1.205233705699035</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0.5323063571497285</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>-0.3265976833967559</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1.368145338848608</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>-0.5198763797025584</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>-0.7526805147244133</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>-0.2306826362346843</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vuXo7iAM</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.554965665966241</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-1.305238775651022</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.1175989013757955</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.3619875044736187</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.3233544294227159</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-1.073779168040133</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.2288267322982719</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.021012011155179</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-4.311064902230333</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.82046242157187</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.237035643794441</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.9248046946280133</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.444160689950789</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-3.039246206704705</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.1240439262024181</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.7201610300767173</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.28202534088376</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.157108255890743</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.9427468458285655</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.148243441982142</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-1.008210207988526</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.6984176385664311</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.251343329513301</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>4.419830167791337</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-1.5289839878163</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.5787974565577886</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0.413394336669571</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.310858945287396</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.9571646250497816</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.497849964667502</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.2437446817420774</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-2.702682801542279</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.6423428944904567</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.247221441908217</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-0.6883490665023247</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-3.591229228867832</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.189520390595006</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.264482709023499</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-0.2481812592572328</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-1.77116592423763</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.027476749941912</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.4408998644668826</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0.306583487242381</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-3.031084236801269</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.8772089363525212</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-1.710494578680016</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.635836885021483</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.8825409463659966</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.4759978025485249</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-1.319225960856651</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.601767693251762</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-0.0200585617548295</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.255242728251182</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.3404983740741652</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-0.04377239113254056</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-2.113919817117921</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0.3828853814037385</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2.861506846965721</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3.743536573697264</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>5.001866000290745</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>-1.9161399283014</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>-2.184903271189349</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>-2.18160916187383</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-0.6833146396145138</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1.915779991618758</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0.7459833402039979</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0.4555926903074704</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>-0.2679343486108591</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>-2.350515122273686</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-0.1584264486788146</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>-0.8207428297936196</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>-0.447690535394427</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.4037528231662625</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>-0.5598772225604997</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>-0.8682218028909631</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>-0.2980010616477292</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>-0.2306826362346843</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.2966731149951496</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-1.354639372503628</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.474651003810884</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.4114353335359955</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.553863884222435</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-1.073779168040133</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.2288267322982719</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-4.579646710246501</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-2.431992577767025</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.769729899129933</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.1509647213698431</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.558400394364916</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.9364826439222599</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.953089366259353</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.4594110832982698</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.75088997476001</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0.7761832163740759</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.8547014424698641</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.5146805775651</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.07398807226217272</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.7729667378059184</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.800735740216327</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.130663815746669</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-2.894059665679505</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.8461219587916164</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.8107687482662999</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0.03393789155949319</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.526555003719233</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.30480879184117</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.4139588955573074</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.6425304720702592</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.003148598515049</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-1.54531093929146</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>2.27994717049149</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-1.055593069387601</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>4.549348444582526</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-2.195978827978515</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>2.35736395626303</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-0.9320381961262104</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-0.3142100414727907</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-3.520163973435834</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.601953197657598</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-1.044169974071516</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.7587726412820448</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.084493951483899</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.240495512008447</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-0.2825388370630555</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.035910383388345</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-0.6019718451053591</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-1.139241449992756</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.77986339070138</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0.04392837746772347</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.6253032268808828</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-0.3170537141477675</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.3301064761736526</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0.01682469021442791</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-1.107214626270094</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>-0.3683669632181777</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0.04381265828454053</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0.06112722144292487</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>4.959609183483733</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.2087077100596549</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1.612715554822613</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>2.003866285916177</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-2.210538881455657</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>1.141702880217488</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-2.273861863394982</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0.3016171703578985</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-1.465050460063403</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>-0.8511446257943155</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>-0.4802425717276271</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0.5902904726903793</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.3584451315260678</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>1.198558681844749</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>-0.3292856317422164</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0.2346971150929424</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>-0.2306826362346843</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.004222929802285143</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.725143848898172</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.332741307859407</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.3036159695294969</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.04932861813918896</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-1.073779168040133</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.2288267322982719</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.2208323598638119</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.4367067837788804</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-1.123275746761307</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-1.076298298146032</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.8595829555414256</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.8290768902029633</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.4501797534909956</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.4594110832982698</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.7415506953530033</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.744086969399625</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-1.161343980335997</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-1.763904083331099</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.726171138452359</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.2954935381165402</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.03646109586683264</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.2473755463902256</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.1831852317525831</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.5480269951674203</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.6209094061827253</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-1.042231941442224</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.004707458781193559</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-1.728210529283143</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.002697230615587</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-1.25431623604878</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-0.6034547175665689</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.7105649475189988</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-2.566824874562708</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.932906800191676</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-0.4967825107266075</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.07650713073685524</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-1.878222318059298</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.966799800244489</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.1567012973901054</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.9258534935535814</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.07210832664149085</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.653824478822637</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-1.37963822288787</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-2.540813547535205</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>-0.567351140084114</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.747914652862331</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-1.544930193331005</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.911720249335979</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-1.859179493448337</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.0492817884343735</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-0.6286132318246318</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-0.9125425013233981</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-1.339912518048552</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.3301064761736526</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.1037938537790136</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0.6041873627414364</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0.5243030606082422</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0.9237524151827468</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>1.799568377896298</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-2.351790227377637</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>1.289575388591893</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>-3.031784715894856</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>-1.046316522477562</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-0.8702667069313971</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>-2.307532707836582</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1.253550348676267</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>2.010271727264172</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>2.667117963584586</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0.8344578062056922</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>1.648591451693273</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0.7429652292210733</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.9600962740048539</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>-0.9412495870588732</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0.2400905737715639</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0.05305239877888174</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>4.334959996653813</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.1872563714324461</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.461194648094912</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.107057873992455</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.3092851473837823</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.220554358738413</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-1.073779168040133</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.2288267322982719</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.2208323598638119</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-1.11193991609586</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.4136335026184144</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.4042354246958704</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.7876295469181309</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.2165546330985296</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.9456647691111776</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.9319047085879864</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.3185177673976434</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0.08683298006508529</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2498878156281058</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.567358598711565</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.012688892739647</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.128133599033697</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.9550595139084127</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.631533044356474</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-1.247334883564621</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.7461712582021531</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.0644183815136412</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.1046795658879763</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0.5495256564944796</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-0.9396562937107908</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-1.210307313209783</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.1497018531288163</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-0.7884087337758823</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-0.7630313978975107</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0.6971041104663676</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-0.8357845749842298</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-0.1629417859478866</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.189520390595006</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.4444480764587024</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.2226091199784443</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1.654649259560776</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.256129076815653</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.5253956958314493</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-0.3558736876590249</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-0.1728122896434628</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.112201946239403</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-0.1217808541138261</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.04909476771927817</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.8734369750973471</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.6794572697517567</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-1.859179493448337</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-1.411881416099639</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-0.8833502300378582</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.6365521465482091</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-0.6239113553180029</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.062909056093791</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.234392980118627</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0.6927081552765155</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2.587443220715895</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>3.962601065929339</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>-1.858469004220661</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-0.9839067644908249</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>-2.400048373367173</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-1.880702379823587</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>-0.06941374395198789</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0.206371986451509</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>-0.5581378854507583</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0.7255340562230378</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>-1.976588905517132</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0.3058788643571638</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0.248461412636601</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>-1.116440422324613</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>-0.5539756616790604</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.6061241812353628</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>-0.2966283908293946</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0.9663563771420829</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0.4122767253714634</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>-0.2306826362346843</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OC8I1VXq</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.05048544197906663</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.732897930784245</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.4982354666929544</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-1.529418203356055</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.49865158087993</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.073779168040133</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.2288267322982719</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-5.17970659401029</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-3.427132164401902</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.498510619827629</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-1.677765123050555</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.4654126677394463</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.27867612796463</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.228941185051885</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.3933308536642742</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.1815859276236206</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.08100897653252087</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.459515069311623</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-1.555700165703432</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.4898356313757372</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.2281631614696474</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.9739971639789051</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.023859214420801</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.04620839885287695</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.2113466378962164</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.6766917188568662</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.01620940743867565</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.4470755058736876</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.890105072200017</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.323393982093254</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.04774737578838437</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.719845411326139</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-1.677206908479975</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-0.01794554577437214</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.7793345702901811</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>3.188305489715431</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-1.458417595763878</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-0.1948670758919116</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-0.1509961871739531</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.4339564929199645</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-0.8779593073392666</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-0.5273194511058942</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-0.5598051212509647</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.685459657514344</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.3577280518589947</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.381812842874963</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>-2.226339675416284</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.6157277462882614</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0.02843650435971155</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>-0.7792724282649663</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.601767693251762</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.489309451823887</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0.364971086008462</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0.7058050897530168</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0.8535368904023231</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0.6256088351665275</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0.02880221126342193</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-2.243818008905631</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>-2.481216561171548</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>-2.358496085486608</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>2.383209845507952</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>1.745187627798604</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>2.608506297624569</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>1.675062392520414</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>-0.6633969039811097</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0.0829367182101933</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1.066291071459456</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0.5863929298422776</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>-1.465050460063403</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>-0.4279236035760378</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>-1.203741616309954</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0.5240182930510731</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0.7889304264559062</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>1.606429216313358</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>-0.04210929214254857</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>-1.055829022411201</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>-0.2306826362346843</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>WxCQa92d</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.004222929802285143</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.4654286291567204</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.03485182195902178</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.1430942484331619</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.04932861813918896</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-1.073779168040133</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.2288267322982719</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-3.379526942718923</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-3.14554694321002</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-1.756120731800015</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.699702432182535</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.03733147179241893</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.03250879059405371</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-3.196841556030757</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.951556664551907</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.488010954139703</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0.3273448197280698</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.0482832733475196</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-1.763904083331099</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.8254048515341851</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-1.031201068306977</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.168175107432959</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.2653440690504545</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>3.020154566226818</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-3.856911605658145</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.2790558732069728</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-0.4398080473888331</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.2399433366848075</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.749578564794017</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.215626312646459</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.1115317591290174</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-0.4739869062200487</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.838502890924229</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0.02796154453236138</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-0.5864040461485107</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-1.318544294797307</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>4.780951747024815</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.08722039758341935</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.1636034402593248</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-2.335572257200585</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0.6463895384856759</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-0.4243078163278886</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-0.1785187661193791</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>-1.23143152933154</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-0.2338280776661889</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0.04622105698972478</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.018320722341196</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>-0.5584292881905041</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-0.4359444935780536</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-0.5992879174010712</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-0.1333636121323782</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>-1.705016289867172</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>-0.1828428439560162</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0.1943756878026247</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-0.1933239380550177</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>-0.8818566666196239</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0.6927081552765155</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-0.2036784466178587</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>-0.01452457206700309</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.69138446133212</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>-1.019352643383344</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>-0.06894245274326294</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>-0.4520099449721096</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>-4.068799760154662</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1.35628108914255</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>-0.340781420102762</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>-0.4705464939729984</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>2.010271727264172</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1.486498413970875</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>1.910082415663908</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1.789696267778238</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0.6414415158792157</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0.6107980251186915</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>-0.5561689871789127</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>-0.5100644765006354</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>0.5989685460025095</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>-0.2306826362346843</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Whh3dzd4</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.472903108294213</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-1.700443550471869</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-1.226409765560563</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.9602957376508675</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-1.427600496272804</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-1.073779168040133</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.2288267322982719</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-1.579347291427555</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-3.17125689818841</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.580837188156699</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-1.446431728856508</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.7030949909829151</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.6698584058953272</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.1802016438132114</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-2.434181884685214</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1274292089880591</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-1.187199029313146</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-1.161343980335997</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.9310884128204328</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.09824225400680137</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-1.128337453152433</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.4039004630834648</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.6705897651006842</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.408857796752455</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.811224457880985</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.1680109092300029</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9343526959550336</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.2223865054425224</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.793789255708316</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.5766994999222652</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.851887931199952</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.9871498218335292</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.01015186975930011</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.5434897522957809</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-0.7739741329540051</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.7230201375033352</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.6745297514514264</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-0.1069762357634107</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.2626024561016483</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>3.754765847329913</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.138273256544028</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.454001719752999</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-0.8891083462048543</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.389046270401682</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.741059308594809</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.5965865192388</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-2.475599771913974</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.381373284444641</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>-1.429795635958757</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>-2.579117536903917</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>2.423671995802144</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>-1.123957972423838</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>2.452127780854752</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0.8762815570698143</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>-0.8912311570265784</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-0.01216503097376751</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0.8697497403466738</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>-0.055713592900324</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0.7978704573910945</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>-1.262631327506255</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>-0.1885209769254627</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>-0.8177021590288995</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0.4319792761679934</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>-2.374645521239717</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>-1.215587794402387</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>-1.877059681898813</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0.1306369180731697</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>-1.407037386548375</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>-0.8747406852565471</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>1.539405627173692</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>-0.3180569224909308</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>0.4434324075664868</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0.8663570715869557</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>-0.5908617089056478</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>-0.9460565656769881</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>-0.4923786763789649</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>-0.2306826362346843</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>KIQjmWIj</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.7154317629598582</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.226179726779763</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-1.027816774960306</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.082707985393397</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1.634646633807196</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-1.073779168040133</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.2288267322982719</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.021012011155179</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.056194270401021</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.227291340525326</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.486235972442296</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.1465796952721809</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.5736383154508974</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.270256129142384</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.278339345897267</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.2243926145179236</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.4135576009600799</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.9597394380554108</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.879664475153065</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.7734252875389429</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.6241408746215064</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-1.230639039320887</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.6431838209474541</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.1414625875073278</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-0.4548970572054767</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.5949908663487788</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-0.167835662232762</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.044637869309121</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.01784583828387933</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.3447761116732349</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>-0.3203033984795438</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-1.454243192129412</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.02834441723357774</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-0.1830500348551136</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>-0.2175330850093099</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.2029990085210963</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.5150570525942074</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-0.1570681277858656</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-0.1710668780746354</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-0.235455669431448</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>-0.03956744213554828</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.5181717675365474</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0.2293013391786545</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>-2.110085498272642</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.1235316412441104</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>-3.682690926417355</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.47486952482692</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>-0.3490696382384547</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>-0.4927324042416673</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0.840588169510089</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.87573579410189</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>-1.067147811027148</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.730911331326715</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.217234491703409</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>-0.1933239380550177</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0.2342475991258921</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0.5599269664738968</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>-0.2604042783497625</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0.6259540953769115</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>-0.03885770361057515</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>-5.351563944385362</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0.2301229601629308</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>-1.487592820301939</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0.9589728886373222</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>-1.90603845264783</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0.2664393670968958</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>-0.6845447981271665</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>-2.830916183970269</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>-0.5795857978531195</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>-0.6714166470358097</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>0.3988059377978661</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0.6210482324334051</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>0.5360796830378799</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>-1.6224286431027</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>0.7830356384155437</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>0.2307520194351704</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>-0.2306826362346843</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>pIgDNCf3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.1325479996510943</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.238891962258185</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.6802790414098565</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-1.529418203356055</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.4199759602720987</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1.073779168040133</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.2288267322982719</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.421251546210336</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.567439550306752</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-1.032869320327206</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.03410199398539483</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-1.534629077166372</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.8134116960066535</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-1.530833577441066</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.278339345897267</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-1.32138506004081</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.602601767153977</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.6530969001892782</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-1.139292330448099</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-2.016209408516104</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.658729588951809</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.800735740216327</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-2.6630737345242</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.413824483230478</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-1.488756639783969</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.6603143553425976</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-1.019590853612022</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.229573060273491</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-1.378957583566686</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.920580758964567</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-1.630727332880039</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-0.9826104507956617</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.138089813164529</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>-0.8855985954886078</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.524251654224025</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>-2.063265911611377</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2.787543011309578</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>-1.633754925016303</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.36146714795738</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>-2.361823714547699</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.611810474174806</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.237580374297951</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.432043521381148</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>-2.395912692988423</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>-2.764997724646137</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>-2.521286410527589</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.55239359091496</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>-2.493980541048908</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.493120060379419</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.020572680373984</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>-0.3160090126991296</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>2.436145475102048</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0.6927967448848429</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.217234491703409</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>-2.2870455949697</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>-0.4470108487966959</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>-0.07447204669417051</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0.5236064275869727</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0.5713678453106688</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.179250380814868</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>-2.884546685009911</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0.5330191509897141</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>-4.518695803081296</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>-2.28499570438845</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>2.048043821315143</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>-0.2624322115917498</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0.05104893653169299</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>2.010271727264172</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>0.3058788643571638</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>-1.664300901920317</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>0.8372387592047223</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>0.7239584089290473</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>0.5635037778235799</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>-2.029054246885554</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>-0.6391416662927096</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>-0.07845398295606633</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>-0.2306826362346843</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>CCDxBZAc</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.2230564169276922</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.157036985093204</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.8126743684766944</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8638147293529397</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9603316232905119</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-1.073779168040133</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.2288267322982719</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-5.17970659401029</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-5.060081590600739</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.6848527819207182</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.6818354977287272</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.010011565224728</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-0.5167870797485324</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.2700707828326508</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.01059953752850989</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.04641086574819007</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-0.3492308119504434</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.273955949836898</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.318135092945566</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.174761073973037</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.1454781745386461</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.249576689391379</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.363747245206065</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.015274899945768</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.009034349982214</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.556877520924568</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-0.2535736575352326</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-0.3598168209982079</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.1840052636764448</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-1.069134174640318</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.2125281015839407</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.5987463877939704</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>-1.854584246354184</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.283937877887995</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>-1.526726537536495</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>2.186783315379267</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>-1.558088032549639</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.373319216784125</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>-0.812244001614998</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>-1.022999389844875</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>-0.5730895381742781</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>-0.2815713589591863</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>-1.279069662578073</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.796219496176359</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.948485830783421</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.560064364651071</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>-1.812332562349306</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.723588300061017</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>-1.122709816223898</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>-0.7792724282649663</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.971608197502399</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>-1.762793806953279</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0.2945849886614754</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0.2966615681927032</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0.5394786418651207</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0.1907630173435992</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>-0.2810205626093551</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>-0.5375049904099608</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>-0.0155152114200569</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>-1.682897745171476</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>3.035688011262785</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>-0.1604000558154127</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>2.42514012457621</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>1.669719245327261</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>1.539941916624729</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>1.197763351882438</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0.7966523544772494</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>-0.2679343486108591</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>-3.235979784483969</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>0.2503109029153073</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>-1.893139432039356</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>0.4590906335630113</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>0.7579160335760344</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>1.505995509171816</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>0.1983378925893961</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>-0.06765950451316136</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>-0.2306826362346843</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.719090781310296</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-1.181737283519507</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.371848528126131</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.8289597840265933</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.553863884222435</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-1.073779168040133</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.2288267322982719</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.6792574657818717</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-2.278019605224944</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.4136335026184144</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.1266353516630137</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.7588755255712512</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.7357251207065885</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.2700707828326508</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.3933308536642742</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.4945579038269196</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.8883699387194994</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.064328696153381</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.255052722270065</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.429563142877606</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.02925236388158249</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.9739971639789051</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.6344599350565815</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.3961149114862061</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.8097054980986237</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.500531238859018</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.2406803872370693</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.8323565380428851</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>-0.01893420672951901</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.3283219387002609</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>-0.3907307226267043</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.2103429537544117</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0.7787870005475409</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.5470489986407603</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.274852006330859</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>-1.087423793027422</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>-0.1028996554775161</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0.3839350381170728</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>-0.1066278195132987</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>-0.1173241113694341</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.294237797961276</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>-0.3509504637257165</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0.20711112756685</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>-0.2363294440247474</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0.08689071747868421</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>-0.3244788120757193</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>-0.05681402864669298</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0.6047874361365103</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0.5397746042916379</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>-1.319225960856651</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0.5058952898512525</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>-1.000869289397677</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>-0.6267015320925885</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>-1.169436050731754</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.202490499888103</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>-0.4180211276085005</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0.3828853814037385</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>-2.929444228438576</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>-3.169185266173093</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.680508080471471</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>-1.271602174504372</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>2.539045027523774</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>3.715639313620603</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>1.309112462383922</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>1.660266476406512</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>-0.4347166264377335</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>0.7795648258831388</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>-0.2679343486108591</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>-1.465050460063403</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>0.2682773799084554</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>-0.4138066191200144</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>0.6766596296032703</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>-0.5323947140528623</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>1.097518482996764</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>-0.5399880921782313</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>0.6478256076245061</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>-0.2306826362346843</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,171 +425,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH7"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>id_team_away</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_home</t>
+          <t>dif_mean_last_180_matches_expected_points</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>id_competition</t>
+          <t>dif_mean_last_30_matches_goal_attempts</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>is_cup</t>
+          <t>dif_mean_last_180_matches_goal_attempts</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goal_attempts</t>
+          <t>dif_mean_last_30_matches_goals</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goal_attempts_against</t>
+          <t>dif_mean_last_180_matches_goals</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goal_attempts</t>
+          <t>dif_mean_last_180_matches_goal_ratio</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goal_attempts_against</t>
+          <t>dif_mean_last_30_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goals_against</t>
+          <t>dif_mean_last_180_matches_ball_possession</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_points</t>
+          <t>dif_mean_last_180_matches_yellow_cards</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_points</t>
+          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goal_ratio</t>
+          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goal_ratio_against</t>
+          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_attacks</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_attacks_against</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_attacks</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_dangerous_attacks</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_dangerous_attacks_against</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_dangerous_attacks</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_dangerous_attacks_against</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_dead_balls</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_ball_possession</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_ball_possession</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_total_passes</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_defensive_actions</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_PPDA</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_PPDA_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_clean_sheet_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_clean_sheet</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_clean_sheet_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
         </is>
@@ -598,637 +503,589 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vuXo7iAM</t>
+          <t>Cl5M5C3L</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1162095880515784</v>
+        <v>-0.1993815215187167</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.3597591963168335</v>
+        <v>1.081410632948609</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.067492437629781</v>
+        <v>0.6844715864273663</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2063420238640809</v>
+        <v>1.217379511957522</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.589513646358695</v>
+        <v>1.172181751439272</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09523370319926526</v>
+        <v>-0.3118253281393665</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7215593090350828</v>
+        <v>-2.439268863748098</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2835680927964619</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7783177411340728</v>
+        <v>0.9165026248447742</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5860218286014244</v>
+        <v>1.003183324196641</v>
       </c>
       <c r="L2" t="n">
-        <v>1.26139600936521</v>
+        <v>0.3333418482721841</v>
       </c>
       <c r="M2" t="n">
-        <v>0.576927001028755</v>
+        <v>0.3034527244546491</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4117842667428089</v>
+        <v>1.956245743568843</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.277475856744321</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.5491051809487889</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.25606183616252</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-2.983513808521003</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.843381771920138</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.282640397161049</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-0.2457136801751998</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-0.4401165068626659</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-2.630210980860448</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.8753590784308233</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.8777833103810669</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.928996287460295</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>4.923368943762314</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-1.764395599992055</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-1.871941077829013</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-0.1542778636855293</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-0.8231643556203306</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-0.8095447279388814</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-0.6673509078372444</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-0.1259966357902757</v>
+        <v>2.027661977236333</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WETw9DuA</t>
+          <t>EXLhbUee</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.47247248857905</v>
+        <v>-0.1993815215187167</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.625453300044154</v>
+        <v>-3.614297164813512</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.067492437629781</v>
+        <v>0.2042905746156609</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2063420238640809</v>
+        <v>-0.464412536678676</v>
       </c>
       <c r="F3" t="n">
-        <v>3.770252329971022</v>
+        <v>-1.802547432648264</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3042321654294421</v>
+        <v>-0.07728177080107683</v>
       </c>
       <c r="H3" t="n">
-        <v>2.716135442423736</v>
+        <v>2.729545476610175</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8064966658205548</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.4955410364194141</v>
+        <v>-2.068625586561245</v>
       </c>
       <c r="K3" t="n">
-        <v>1.503484241148247</v>
+        <v>0.7208040714939992</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.01550499746927442</v>
+        <v>-0.8591717639183694</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8131055336952909</v>
+        <v>-0.3492705157574899</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.03005700637640362</v>
+        <v>0.7322451675039051</v>
       </c>
       <c r="O3" t="n">
-        <v>2.533663200211273</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-1.322550743314403</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.297687473363445</v>
-      </c>
-      <c r="R3" t="n">
-        <v>3.795239826949472</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-1.890093625244842</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.394213759368675</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-0.9459707373789445</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.610957403131019</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.9713604403109094</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.123261530420383</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.08326688445175</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-0.3478524028866566</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-0.005128636092465054</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>4.550412035152017</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-1.172103469830892</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-0.6570142075229976</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-0.5761136014536516</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-0.2873295817083004</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.393608512057648</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0.426338139968115</v>
+        <v>0.3670021551199236</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0YqKhheT</t>
+          <t>SIOithtm</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.3312268771595922</v>
+        <v>-0.1993815215187167</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.189007057379561</v>
+        <v>-4.234083282200756</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.067492437629781</v>
+        <v>-0.3769811765248246</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2063420238640809</v>
+        <v>-0.6063767575707483</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7972159621203203</v>
+        <v>-1.926494481985245</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4754318234131739</v>
+        <v>-0.322994068964999</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7481000218976329</v>
+        <v>0.3439945253519748</v>
       </c>
       <c r="I4" t="n">
-        <v>1.758620414633675</v>
+        <v>-0.6186863043631206</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.429704139958638</v>
+        <v>-0.07243797087588752</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7389322306925615</v>
+        <v>0.5623259194670067</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2509653497329598</v>
+        <v>-1.460439563544758</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6192335151358288</v>
+        <v>-0.4636473684404315</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.039345048768842</v>
+        <v>0.09197258465244156</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7881281097775168</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.996590485086558</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-2.590853481961584</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-0.8451057216217996</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.07846612962396611</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-1.913815944463395</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.022386612248799</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.08612102511372671</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-1.485095964898273</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-2.558486454902184</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-1.542684917319834</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.5361735001628013</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.835302791907013</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.1099252608486066</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.09380536749367</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.8389174732767446</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.665528740272937</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.2470368273257786</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-1.110071676277845</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-0.6503332937504971</v>
+        <v>0.1528291792140144</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>lnhZhVPh</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.4966247918580644</v>
+        <v>-0.1993815215187167</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.523615843422416</v>
+        <v>-3.306769701987783</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.067492437629781</v>
+        <v>-1.034070982161895</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2063420238640809</v>
+        <v>-0.7971411793944705</v>
       </c>
       <c r="F5" t="n">
-        <v>1.920138591402377</v>
+        <v>-1.120838661294871</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3234999138442409</v>
+        <v>-0.556420752220726</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1800558710055756</v>
+        <v>1.643857217238465</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.08095676320729783</v>
+        <v>-0.8151253918201364</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.259856302951506</v>
+        <v>-0.8275287601243866</v>
       </c>
       <c r="K5" t="n">
-        <v>0.81538743173813</v>
+        <v>0.5496476673048474</v>
       </c>
       <c r="L5" t="n">
-        <v>1.031841160216381</v>
+        <v>-1.38085647272413</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6752735517309593</v>
+        <v>1.112881669988385</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01694718883124799</v>
+        <v>0.6306906181423748</v>
       </c>
       <c r="O5" t="n">
-        <v>3.137979694399375</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-1.435394863488275</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.02000821151441191</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.661883540892894</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-1.262190944812549</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.2016694042494782</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-0.146197935123673</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-0.5287646625365124</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.356580217684508</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.3534733613886618</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.6117398287683578</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-2.297821212576386</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-2.384296783010802</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.244837652845735</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-1.172103469830892</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-0.4238594551467178</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-1.209165733758878</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-0.04287214093348445</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.021466661000633</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-1.076645049407116</v>
+        <v>-0.1091822277654793</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>h8tCfEQG</t>
+          <t>dzYLoEIP</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.107734980717116</v>
+        <v>-0.1993815215187167</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.8253018551590663</v>
+        <v>-0.9884857514553499</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.067492437629781</v>
+        <v>-0.730798764175555</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2063420238640809</v>
+        <v>0.05131685953080554</v>
       </c>
       <c r="F6" t="n">
-        <v>0.821633559127244</v>
+        <v>0.8003406034283297</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7800323351341922</v>
+        <v>-0.2615659944240186</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3177322353150387</v>
+        <v>-0.8643479812519259</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08682697732182144</v>
+        <v>1.149265482750023</v>
       </c>
       <c r="J6" t="n">
-        <v>1.287861252155468</v>
+        <v>1.176335743147178</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.79017179021881</v>
+        <v>-1.339411904856906</v>
       </c>
       <c r="L6" t="n">
-        <v>1.64504650119526</v>
+        <v>0.8460173392328035</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06017140579854546</v>
+        <v>1.091688130232487</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1036963255887045</v>
+        <v>0.2496179646609617</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6633659948483602</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-0.6532683753866086</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-0.7050196846750928</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-0.1287390125105665</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.843381771920138</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.4485802868342021</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.2363670998090114</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.5510976679295613</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-0.1368153815879699</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.111439941318164</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.8687056027859857</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.6484107031446</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-1.887849635215403</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-0.8950687491003759</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.227571746165349</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.252737480285285</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-1.12118012550671</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.9744288076679534</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.294229633197986</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.285446843900555</v>
+        <v>1.095412551624397</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>SW3Qfiet</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.03351063070234232</v>
+        <v>-0.1993815215187167</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.189007057379561</v>
+        <v>2.649800693359837</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.067492437629781</v>
+        <v>1.998651197701507</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2063420238640809</v>
+        <v>1.238445124077515</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.358249429037614</v>
+        <v>-0.2532093159360059</v>
       </c>
       <c r="G7" t="n">
-        <v>1.750163730375339</v>
+        <v>0.5510396773609537</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4453014327492025</v>
+        <v>-0.4066732617812116</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4144776125035224</v>
+        <v>1.149265482750023</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.005084547440809</v>
+        <v>2.547658453876072</v>
       </c>
       <c r="K7" t="n">
-        <v>1.274118638011541</v>
+        <v>0.4627110810500397</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1141903205229799</v>
+        <v>2.133359861502126</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2741624706108665</v>
+        <v>-0.2722039159264435</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2869552687344193</v>
+        <v>0.9821785942927346</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5814908569261013</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.342905198723614</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-0.08461564840164408</v>
-      </c>
-      <c r="R7" t="n">
-        <v>-0.9306420450977679</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.438593987072448</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.1345267657700064</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.1871823024300138</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-0.3129731031578801</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-0.9402428524646572</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.2140112658452735</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-0.5268487029067253</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-0.1513618700174632</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.030800483744702</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-0.4996523872492206</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.9274093541634696</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.736103927665998</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.679749843678042</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-0.484330665212982</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>-0.6461241657669964</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.1322074508172598</v>
+        <v>0.9090586633536603</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>x8OGzlAO</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.1993815215187167</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2.58829520079469</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.02316358887409439</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.162226407102737</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.544022899450214</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.611990279075891</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.7712087363447461</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.6090579922432289</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.438530980706875</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.337829984046312</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.88627988371712</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2527269083078288</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.3742389929281661</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.4975694900768853</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ttV7xAuC</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.1993815215187167</v>
+      </c>
+      <c r="C9" t="n">
+        <v>7.2627126357458</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7855623257561463</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.72454582686421</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2425788814119167</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.132851297656242</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-2.659798083818181</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.36207449416179</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.544545142611643</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.05234291303768644</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.095976678433162</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.2806803307734941</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.391929107705166</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.9640125753510719</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>EB8yv2aJ</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.1993815215187167</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.154006532124047</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.949834777165414</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.695966813088085</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.172181751439272</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9232279932851452</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-2.240689935623934</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.0197407298721812</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.76351922185632</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.14552551892634</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.093538707268977</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.4910613433927201</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.4983280502828141</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.4064924770714149</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>WUqjkmPH</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.1993815215187167</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-2.416714256694081</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.263254094779947</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1.151635820821256</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8003406034283297</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.107896142373968</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6973086770484191</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.4386171408608559</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-1.02894863762661</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.351547116561431</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.2328186421288635</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.9156401006314676</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.9577032359430458</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.4178504874796971</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8SWavWAa</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.1993815215187167</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.1577441437315419</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-1.236252460819455</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.3717937443260651</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.05665830740644594</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.07022303844333676</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.99794399388647</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.2325497412839484</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0.7401568139266987</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.627858435742611</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.602558475644311</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.09309490637747896</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1683026988010895</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.400338393188684</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>z3jsi9f5</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.1993815215187167</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.4687213031650373</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.8697985307526273</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3563181153536168</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.605996424118704</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6291410864202004</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.087386692952327</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.182005330659525</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.08739876553437868</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.3721521370346153</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.210931015600047</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.1663028353379459</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.5673645106843337</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.3663987919983595</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,589 +503,687 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>0lpzB7u1</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>-0.1993815215187167</v>
       </c>
       <c r="C2" t="n">
-        <v>1.081410632948609</v>
+        <v>-5.685268820066513</v>
       </c>
       <c r="D2" t="n">
         <v>0.6844715864273663</v>
       </c>
       <c r="E2" t="n">
-        <v>1.217379511957522</v>
+        <v>-0.6422459135241251</v>
       </c>
       <c r="F2" t="n">
-        <v>1.172181751439272</v>
+        <v>1.544022899450214</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.3118253281393665</v>
+        <v>-0.9924204722013679</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.439268863748098</v>
+        <v>0.5199304772796999</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9165026248447742</v>
+        <v>-0.4816214476735984</v>
       </c>
       <c r="K2" t="n">
-        <v>1.003183324196641</v>
+        <v>-0.6949340866138023</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3333418482721841</v>
+        <v>-1.470578683294993</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3034527244546491</v>
+        <v>-1.699837649440178</v>
       </c>
       <c r="N2" t="n">
-        <v>1.956245743568843</v>
+        <v>-1.018665941507787</v>
       </c>
       <c r="O2" t="n">
-        <v>2.027661977236333</v>
+        <v>-1.423899109836905</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>GMBD7YY8</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>-0.1993815215187167</v>
       </c>
       <c r="C3" t="n">
-        <v>-3.614297164813512</v>
+        <v>1.069582653609157</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2042905746156609</v>
+        <v>0.1284725201190759</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.464412536678676</v>
+        <v>1.565232183887671</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.802547432648264</v>
+        <v>0.3045524060804072</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.07728177080107683</v>
+        <v>-0.9065607771043154</v>
       </c>
       <c r="H3" t="n">
-        <v>2.729545476610175</v>
+        <v>-1.000105532756697</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.6581677641074828</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.068625586561245</v>
+        <v>-0.9731927809908854</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7208040714939992</v>
+        <v>0.3087608762238176</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.8591717639183694</v>
+        <v>-0.7745041145247595</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3492705157574899</v>
+        <v>-0.5031642514860845</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7322451675039051</v>
+        <v>1.0181358660236</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3670021551199236</v>
+        <v>-0.5083391368716661</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>AJ5eIkmR</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>-0.1993815215187167</v>
       </c>
       <c r="C4" t="n">
-        <v>-4.234083282200756</v>
+        <v>-3.685265040850221</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3769811765248246</v>
+        <v>-0.3011631220282395</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6063767575707483</v>
+        <v>-0.4026200744600283</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.926494481985245</v>
+        <v>-1.430706284637322</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.322994068964999</v>
+        <v>-1.459413447973141</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3439945253519748</v>
+        <v>1.256878036622986</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6186863043631206</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.07243797087588752</v>
+        <v>-1.601685226235334</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5623259194670067</v>
+        <v>-0.5787167751273409</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.460439563544758</v>
+        <v>-0.8330597451758694</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4636473684404315</v>
+        <v>0.1460328655009528</v>
       </c>
       <c r="N4" t="n">
-        <v>0.09197258465244156</v>
+        <v>-0.1163378802864443</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1528291792140144</v>
+        <v>-0.4097323708146962</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>-0.1993815215187167</v>
       </c>
       <c r="C5" t="n">
-        <v>-3.306769701987783</v>
+        <v>-7.636992938160863</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.034070982161895</v>
+        <v>-1.640615418134576</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7971411793944705</v>
+        <v>-2.037456513584827</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.120838661294871</v>
+        <v>-0.687023988615438</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.556420752220726</v>
+        <v>-1.4724669138131</v>
       </c>
       <c r="H5" t="n">
-        <v>1.643857217238465</v>
+        <v>0.06215849168915542</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8151253918201364</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.8275287601243866</v>
+        <v>-1.93993929785655</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5496476673048474</v>
+        <v>-0.1958222399621248</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.38085647272413</v>
+        <v>-1.836272649062574</v>
       </c>
       <c r="M5" t="n">
-        <v>1.112881669988385</v>
+        <v>-0.7143959855170988</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6306906181423748</v>
+        <v>0.3177457696945006</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1091822277654793</v>
+        <v>-0.1559578365529018</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
+          <t>8Kjh0jRr</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>-0.1993815215187167</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.9884857514553499</v>
+        <v>-4.607847429327413</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.730798764175555</v>
+        <v>-1.526888336389698</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05131685953080554</v>
+        <v>-2.293231755034418</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8003406034283297</v>
+        <v>-0.8729445626209091</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2615659944240186</v>
+        <v>-0.7288581328964789</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8643479812519259</v>
+        <v>0.1029129279652561</v>
       </c>
       <c r="I6" t="n">
-        <v>1.149265482750023</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.176335743147178</v>
+        <v>-2.063985709448702</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.339411904856906</v>
+        <v>0.5623259194670064</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8460173392328035</v>
+        <v>-2.297658307147463</v>
       </c>
       <c r="M6" t="n">
-        <v>1.091688130232487</v>
+        <v>0.3566280417182702</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2496179646609617</v>
+        <v>-1.169110552455148</v>
       </c>
       <c r="O6" t="n">
-        <v>1.095412551624397</v>
+        <v>-1.368415215220992</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
+          <t>2g2mKBIE</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>-0.1993815215187167</v>
       </c>
       <c r="C7" t="n">
-        <v>2.649800693359837</v>
+        <v>2.772811678490129</v>
       </c>
       <c r="D7" t="n">
-        <v>1.998651197701507</v>
+        <v>0.002109095958100676</v>
       </c>
       <c r="E7" t="n">
-        <v>1.238445124077515</v>
+        <v>0.5212960673668653</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2532093159360059</v>
+        <v>1.172181751439272</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5510396773609537</v>
+        <v>0.4294998441620133</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4066732617812116</v>
+        <v>-0.3476140086491974</v>
       </c>
       <c r="I7" t="n">
-        <v>1.149265482750023</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.547658453876072</v>
+        <v>-0.4682897897441698</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4627110810500397</v>
+        <v>-1.418650980870402</v>
       </c>
       <c r="L7" t="n">
-        <v>2.133359861502126</v>
+        <v>0.1842576484845563</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2722039159264435</v>
+        <v>0.5985554680006279</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9821785942927346</v>
+        <v>-0.3125332667705741</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9090586633536603</v>
+        <v>-0.8057193838819366</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
+          <t>SznSCTAl</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>-0.1993815215187167</v>
       </c>
       <c r="C8" t="n">
-        <v>2.58829520079469</v>
+        <v>6.694969627452143</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.02316358887409439</v>
+        <v>0.4949264501859036</v>
       </c>
       <c r="E8" t="n">
-        <v>0.162226407102737</v>
+        <v>1.802301341822674</v>
       </c>
       <c r="F8" t="n">
-        <v>1.544022899450214</v>
+        <v>1.729943473455685</v>
       </c>
       <c r="G8" t="n">
-        <v>1.611990279075891</v>
+        <v>0.1745733348169437</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7712087363447461</v>
+        <v>-1.057906108319966</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6090579922432289</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.438530980706875</v>
+        <v>2.418613629212683</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.337829984046312</v>
+        <v>-1.303188327250736</v>
       </c>
       <c r="L8" t="n">
-        <v>1.88627988371712</v>
+        <v>2.352062779093898</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2527269083078288</v>
+        <v>-0.4677240441628552</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3742389929281661</v>
+        <v>-0.8738864612908011</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4975694900768853</v>
+        <v>-0.2347047777493697</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ttV7xAuC</t>
+          <t>Cl5M5C3L</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>-0.1993815215187167</v>
       </c>
       <c r="C9" t="n">
-        <v>7.2627126357458</v>
+        <v>1.081410632948609</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7855623257561463</v>
+        <v>0.1790178897834655</v>
       </c>
       <c r="E9" t="n">
-        <v>1.72454582686421</v>
+        <v>1.145288306035767</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2425788814119167</v>
+        <v>0.4284994554173877</v>
       </c>
       <c r="G9" t="n">
-        <v>1.132851297656242</v>
+        <v>-0.4933173665559001</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.659798083818181</v>
+        <v>-2.604545603033758</v>
       </c>
       <c r="I9" t="n">
-        <v>1.36207449416179</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.544545142611643</v>
+        <v>0.9479080740610769</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.05234291303768644</v>
+        <v>0.9844540880479959</v>
       </c>
       <c r="L9" t="n">
-        <v>2.095976678433162</v>
+        <v>0.3333418482721841</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2806803307734941</v>
+        <v>0.1168260691598848</v>
       </c>
       <c r="N9" t="n">
-        <v>1.391929107705166</v>
+        <v>2.012633140676674</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9640125753510719</v>
+        <v>2.027661977236333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EB8yv2aJ</t>
+          <t>EXLhbUee</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>-0.1993815215187167</v>
       </c>
       <c r="C10" t="n">
-        <v>9.154006532124047</v>
+        <v>-4.536879553290706</v>
       </c>
       <c r="D10" t="n">
-        <v>0.949834777165414</v>
+        <v>-0.2253450675316545</v>
       </c>
       <c r="E10" t="n">
-        <v>1.695966813088085</v>
+        <v>-0.6616730891458972</v>
       </c>
       <c r="F10" t="n">
-        <v>1.172181751439272</v>
+        <v>-2.174388580659206</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9232279932851452</v>
+        <v>-0.4129423209714354</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.240689935623934</v>
+        <v>2.442569520692064</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0197407298721812</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.76351922185632</v>
+        <v>-2.19263684756921</v>
       </c>
       <c r="K10" t="n">
-        <v>1.14552551892634</v>
+        <v>0.7208040714939992</v>
       </c>
       <c r="L10" t="n">
-        <v>1.093538707268977</v>
+        <v>-0.8629514357779279</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4910613433927201</v>
+        <v>-0.3230605194909194</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4983280502828141</v>
+        <v>0.6517850250570331</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4064924770714149</v>
+        <v>0.2574457481713225</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>WUqjkmPH</t>
+          <t>SIOithtm</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>-0.1993815215187167</v>
       </c>
       <c r="C11" t="n">
-        <v>-2.416714256694081</v>
+        <v>-4.234083282200756</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.263254094779947</v>
+        <v>-0.3769811765248246</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.151635820821256</v>
+        <v>-0.6063767575707483</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8003406034283297</v>
+        <v>-1.926494481985245</v>
       </c>
       <c r="G11" t="n">
-        <v>1.107896142373968</v>
+        <v>-0.322994068964999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6973086770484191</v>
+        <v>0.3439945253519748</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4386171408608559</v>
+        <v>-0.6186863043631206</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.02894863762661</v>
+        <v>-0.07243797087588752</v>
       </c>
       <c r="K11" t="n">
-        <v>1.351547116561431</v>
+        <v>0.5623259194670067</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2328186421288635</v>
+        <v>-1.460439563544758</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9156401006314676</v>
+        <v>-0.4636473684404315</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9577032359430458</v>
+        <v>0.09197258465244156</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4178504874796971</v>
+        <v>0.1528291792140144</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8SWavWAa</t>
+          <t>lnhZhVPh</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>-0.1993815215187167</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1577441437315419</v>
+        <v>-3.306769701987783</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.236252460819455</v>
+        <v>-1.034070982161895</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3717937443260651</v>
+        <v>-0.7971411793944705</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05665830740644594</v>
+        <v>-1.120838661294871</v>
       </c>
       <c r="G12" t="n">
-        <v>0.07022303844333676</v>
+        <v>-0.556420752220726</v>
       </c>
       <c r="H12" t="n">
-        <v>1.99794399388647</v>
+        <v>1.643857217238465</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2325497412839484</v>
+        <v>-0.8151253918201364</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7401568139266987</v>
+        <v>-0.8275287601243866</v>
       </c>
       <c r="K12" t="n">
-        <v>1.627858435742611</v>
+        <v>0.5496476673048474</v>
       </c>
       <c r="L12" t="n">
-        <v>0.602558475644311</v>
+        <v>-1.38085647272413</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.09309490637747896</v>
+        <v>1.112881669988385</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1683026988010895</v>
+        <v>0.6306906181423748</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.400338393188684</v>
+        <v>-0.1091822277654793</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>z3jsi9f5</t>
+          <t>dzYLoEIP</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>-0.1993815215187167</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4687213031650373</v>
+        <v>-0.9884857514553499</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.8697985307526273</v>
+        <v>-0.730798764175555</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3563181153536168</v>
+        <v>0.05131685953080554</v>
       </c>
       <c r="F13" t="n">
-        <v>1.605996424118704</v>
+        <v>0.8003406034283297</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6291410864202004</v>
+        <v>-0.2615659944240186</v>
       </c>
       <c r="H13" t="n">
-        <v>2.087386692952327</v>
+        <v>-0.8643479812519259</v>
       </c>
       <c r="I13" t="n">
-        <v>1.182005330659525</v>
+        <v>1.149265482750023</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08739876553437868</v>
+        <v>1.176335743147178</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3721521370346153</v>
+        <v>-1.339411904856906</v>
       </c>
       <c r="L13" t="n">
-        <v>1.210931015600047</v>
+        <v>0.8460173392328035</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1663028353379459</v>
+        <v>1.091688130232487</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5673645106843337</v>
+        <v>0.2496179646609617</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3663987919983595</v>
+        <v>1.095412551624397</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.1993815215187167</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2.649800693359837</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.998651197701507</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.238445124077515</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.2532093159360059</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.5510396773609537</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.4066732617812116</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.149265482750023</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.547658453876072</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.4627110810500397</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.133359861502126</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.2722039159264435</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.9821785942927346</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.9090586633536603</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>x8OGzlAO</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-0.1993815215187167</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2.58829520079469</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.02316358887409439</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.162226407102737</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.544022899450214</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.611990279075891</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.7712087363447461</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.6090579922432289</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.438530980706875</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.337829984046312</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.88627988371712</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2527269083078288</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.3742389929281661</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.4975694900768853</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,765 +425,5868 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:BZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_180_matches_expected_points</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_goal_attempts</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_180_matches_goal_attempts</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_30_matches_goals</t>
+          <t>dif_mean_last_60_matches_expected_points</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_goals</t>
+          <t>dif_mean_last_60_matches_expected_points_against</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_goal_ratio</t>
+          <t>dif_mean_last_360_matches_expected_points</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_30_matches_dangerous_attacks</t>
+          <t>dif_mean_last_360_matches_expected_points_against</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_ball_possession</t>
+          <t>dif_mean_last_60_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_yellow_cards</t>
+          <t>dif_mean_last_60_matches_shots_on_goal_against</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_360_matches_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_goal_attempts</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_goal_attempts</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_goals</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_goals_against</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_goals</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_goals_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_points</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_points_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_points</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_points_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_goal_ratio</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_goal_ratio_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_goal_ratio</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_goal_ratio_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_attacks</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_attacks_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_attacks</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_attacks_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dangerous_attacks_against</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_dangerous_attacks_against</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dead_balls_against</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_dead_balls_against</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_ball_possession</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_ball_possession</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_yellow_cards_against</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_yellow_cards_against</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_red_cards</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_red_cards_against</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_defensive_actions</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_defensive_actions_against</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_defensive_actions</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_defensive_actions_against</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_KGP</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_KGP_against</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_KGP</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_KGP_against</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_clean_sheet_against</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_clean_sheet_against</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_mean_rat_player_start_against</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0lpzB7u1</t>
+          <t>WIDwXGr3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1993815215187167</v>
+        <v>-0.6130169784618973</v>
       </c>
       <c r="C2" t="n">
-        <v>-5.685268820066513</v>
+        <v>-1.547785718004653</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6844715864273663</v>
+        <v>0.2519730554222272</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6422459135241251</v>
+        <v>-0.193078397277103</v>
       </c>
       <c r="F2" t="n">
-        <v>1.544022899450214</v>
+        <v>2.597421956274489</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.9924204722013679</v>
+        <v>-1.231874918018891</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5199304772796999</v>
+        <v>2.89415634268854</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-2.088396573002503</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.4816214476735984</v>
+        <v>1.449853128523822</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.6949340866138023</v>
+        <v>1.353404960080579</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.470578683294993</v>
+        <v>1.522694817798093</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.699837649440178</v>
+        <v>1.185462850180047</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.018665941507787</v>
+        <v>0.3161802189691056</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.423899109836905</v>
+        <v>0.1478958463166837</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.5048680174244224</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.030728573861344</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.17544833733915</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.3403702900486752</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.122752803126459</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.1533314142466691</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.1704045119399647</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.1345389866062172</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.6827196171419604</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-0.4935228448899845</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-0.4795060912956393</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.4472320984824059</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.6996328048206804</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-0.5871774718664917</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-0.6660536911657959</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-1.95749951069505</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-0.04386585203059967</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.1666747279972349</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.7951194906694748</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-0.4457920606377364</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-0.2007112539564736</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.3084546553974687</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-0.8951077267983056</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-0.6931008176013191</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-1.297538635215637</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-0.4124371938524935</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.801501183720331</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-1.801463100857075</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.5971482824903627</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.5971392125246074</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.2923918654544772</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.6025002188157471</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-0.2170235065616638</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-1.073206169552669</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>-1.20757421241802</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.013217841902685</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-0.6340995198291843</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-0.8043982313174884</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>-0.09102278439397789</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>-0.2558122530241582</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0.3244323297452965</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.591792039962583</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>-0.05804047512575159</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1.259270063479941</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>-0.2707828575379491</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>-0.6465171460133313</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.5854457462784461</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>-1.885163898323777</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>-0.5991394379616988</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1.095277226098793</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>2.166001215845864</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0.2936863093154641</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>-0.9242274594846919</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1.206472246124132</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1.088017716219443</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>0.06399656914746225</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>2.076030336463424</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>0.9271550272853821</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1.667239746372771</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>-0.07124703187796592</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>0.8164991284900097</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>-1.383329551263493</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>0.5909288746499061</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GMBD7YY8</t>
+          <t>4CLi9Djd</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1993815215187167</v>
+        <v>-0.1755831547357415</v>
       </c>
       <c r="C3" t="n">
-        <v>1.069582653609157</v>
+        <v>1.814519506046163</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1284725201190759</v>
+        <v>1.049450975946586</v>
       </c>
       <c r="E3" t="n">
-        <v>1.565232183887671</v>
+        <v>-0.193078397277103</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3045524060804072</v>
+        <v>0.8927581732459091</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9065607771043154</v>
+        <v>-1.912594387021969</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.000105532756697</v>
+        <v>0.265218676113322</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6581677641074828</v>
+        <v>0.451697322801301</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9731927809908854</v>
+        <v>0.5142094646568566</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3087608762238176</v>
+        <v>0.104886540194255</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.7745041145247595</v>
+        <v>0.3580355176473215</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5031642514860845</v>
+        <v>0.5799909179787985</v>
       </c>
       <c r="N3" t="n">
-        <v>1.0181358660236</v>
+        <v>1.223626034381941</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5083391368716661</v>
+        <v>1.211994523981119</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.9285645137159854</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.3805276459968847</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-1.030567431779406</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.009470648339543298</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.9727661079065432</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.002945735441979</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-0.217355493249919</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-0.02087385647324174</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.238373724524887</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.09957031308231888</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-1.231803422959269</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-2.79060252292684</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.07788914035595432</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-0.6071817943776909</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.203496718894561</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-0.3244290964969024</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-0.1612410719199348</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.01699889331857178</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.6078811318460915</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.310365611811077</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.1193136357175671</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.2529223696472696</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.158345792122602</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-0.1306715160749591</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.3906690471072081</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>-1.052904622877996</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.5300632562691709</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.5300661454540342</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.3599998344117394</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-0.3600147557813234</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-2.069243687355359</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.007092193823406814</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-1.527773250105875</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.4540182212747259</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-0.7706844178622821</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.346794238266383</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-0.202053046831464</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0.9056541763523229</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-0.1393004972612953</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0.4950045148272478</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>-0.04554309133768435</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-1.05373265236705</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0.3768358998385545</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>-0.7135548140853232</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>-0.2707828575379491</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0.9835409267621519</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>-0.6692806453563351</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1.342238620168932</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>-0.472521821674776</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>-0.1934581301591484</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0.1098657520123151</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>-0.5209134624588349</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>-0.1057008579962242</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>-0.2205164963923844</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>-0.04418064000854764</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>-0.5257188900213324</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>-0.1128538579931708</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>0.1607211463212208</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>-0.0684019892223104</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>-0.03424609214092668</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>-0.02178416011972701</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>-0.522842006524857</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>-0.03915853028770967</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AJ5eIkmR</t>
+          <t>Ug79dz7j</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.1993815215187167</v>
+        <v>-0.9338017825277449</v>
       </c>
       <c r="C4" t="n">
-        <v>-3.685265040850221</v>
+        <v>0.3756951984568496</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3011631220282395</v>
+        <v>0.9355255587288207</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4026200744600283</v>
+        <v>-0.193078397277103</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.430706284637322</v>
+        <v>-0.1300400965712384</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.459413447973141</v>
+        <v>0.1295640199872675</v>
       </c>
       <c r="H4" t="n">
-        <v>1.256878036622986</v>
+        <v>1.378398111566152</v>
       </c>
       <c r="I4" t="n">
+        <v>-1.867033397372013</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-1.824899695010558</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.1829189414371499</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0.4712150595669959</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.3240009466437116</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.000546891868989275</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.02966265990952422</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.06539712155650547</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.06937519075795597</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-2.048728555987971</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.8651316976310026</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.3822985094884938</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.9292000920319289</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-1.070427504667663</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.455548152781618</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.9204585840723711</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.6993036997952791</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.9677926859205859</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.147939657710252</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.4543474297660609</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.4227838889789229</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.4116871334572335</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.9996820501502441</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-1.082649449411731</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.5926139383859851</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.2431192457453176</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.8292265234689363</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.4358364224335446</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.5274218571419582</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.361303407364785</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.9104210207929838</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.328591125768641</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.7421047109270681</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.604450586687248</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.6044111378286789</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-2.612640587250319</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.612643838741588</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.4399940875050921</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-1.034871849913189</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.08018323116841557</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-1.047007090155092</v>
+      </c>
+      <c r="AX4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="n">
-        <v>-1.601685226235334</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-0.5787167751273409</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-0.8330597451758694</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.1460328655009528</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-0.1163378802864443</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-0.4097323708146962</v>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.6476383500640527</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-0.106126831518982</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.1492050528990759</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-0.3603057691985037</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>-0.8479328577516209</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-0.7419717606586362</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-0.4469034850036173</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.6118202829366391</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0.416960911888155</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.68213724366593</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-0.8862247458531354</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>-0.0455444627829325</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>-0.2727934148367125</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>-0.308633155892868</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>-0.6866584121394217</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>-0.6951422899040191</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>-0.1593157541548807</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>-1.111792555841076</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>-0.8615897166366577</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>-0.6600526823078273</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>-0.7357945564590189</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>-0.9015181518998409</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>-0.9365297934381582</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>-0.4482492755068878</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>-0.7095341096777973</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>1.133263073520326</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>-1.006122259764766</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>dGwq9oAD</t>
+          <t>fB59P6ff</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1993815215187167</v>
+        <v>-0.08809638999051034</v>
       </c>
       <c r="C5" t="n">
-        <v>-7.636992938160863</v>
+        <v>-1.547785718004653</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.640615418134576</v>
+        <v>-1.627796328670905</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.037456513584827</v>
+        <v>-0.193078397277103</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.687023988615438</v>
+        <v>2.597421956274489</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.4724669138131</v>
+        <v>-1.231874918018891</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06215849168915542</v>
+        <v>4.629563582413122</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-4.358185554385106</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.93993929785655</v>
+        <v>-0.1095529779211208</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1958222399621248</v>
+        <v>1.197340157594788</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.836272649062574</v>
+        <v>0.5177367738768051</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7143959855170988</v>
+        <v>0.3527578812226481</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3177457696945006</v>
+        <v>-0.275632269343613</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1559578365529018</v>
+        <v>1.211994523981119</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.049819454221823</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.7310342201099161</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.005754816637722</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.040052166825112</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.5999383810347021</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.443622416139113</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.7908205202437788</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.1762866995527007</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.6030050675421331</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.3746092444568376</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.8428559464009913</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-0.8484006153804091</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.3582100425361461</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0.03273099807871632</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.797353907972557</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-1.979568029805835</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.9458246735120551</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-0.6710804276717935</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.2628809787684932</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-1.504298054990446</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.7853480590865541</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0.09629819916847086</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.01508159312812</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.5514235942867967</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.546739740417536</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.5708546018191054</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-0.7218140876827397</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.7217708567889597</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.7177901143645552</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.7177817819273649</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.5875963095557069</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.197908243808087</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-0.1434465751961802</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-0.8631967308361784</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-1.862908904251628</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-0.3210877435521076</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-0.2884623414310081</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.361668151730939</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.4459706230451409</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.3923623930240713</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.857542306206655</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.4634501521821301</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0.4498086297109261</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-0.4337360464820482</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>-1.187774550106088</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-0.6465171460133313</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-0.5109603051272273</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>-0.7646975279930578</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.2110480665633194</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.6958313231344077</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>-0.873330289164734</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>-0.3020891113006994</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>-0.2819986975618585</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>-0.2872334178001691</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>-0.03284106131271645</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0.8819941546517621</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>-1.225773590800219</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>-0.2159822401357954</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-1.709488705771597</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>-1.16836280707291</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0.1595286633059247</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>-0.2605061966873987</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>-0.5672003528888473</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8Kjh0jRr</t>
+          <t>jwaINpP6</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1993815215187167</v>
+        <v>0.2618506689904143</v>
       </c>
       <c r="C6" t="n">
-        <v>-4.607847429327413</v>
+        <v>0.8452062883017833</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.526888336389698</v>
+        <v>-0.3603760621232627</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.293231755034418</v>
+        <v>-0.193078397277103</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8729445626209091</v>
+        <v>-2.857502149416966</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7288581328964789</v>
+        <v>3.533161365002662</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1029129279652561</v>
+        <v>8.915271643554362</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-5.027769442394195</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.063985709448702</v>
+        <v>0.6701500753013505</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5623259194670064</v>
+        <v>1.431437361323474</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.297658307147463</v>
+        <v>1.180254703205829</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3566280417182702</v>
+        <v>0.176382015805172</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.169110552455148</v>
+        <v>0.6318135460692219</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.368415215220992</v>
+        <v>1.409049834659718</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.345808642057142</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.2826930655073507</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.8360612959362946</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.739734043601548</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.843580053465812</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.0213809588410127</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.4500114963638492</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.9116032020035115</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.4381355094677126</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0.1011456920329899</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.8442314303163159</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.1314199843273924</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.6667943523795914</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.342862831387109</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-2.865524761825039</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.279656158575819</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.0718865125102716</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-0.7402315731768302</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-1.577119837645364</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2.970295466591462</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.145199518863976</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.3888098944224508</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.5614116296455941</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-1.052098244107506</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.6148957502879738</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-1.218369929232167</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.3306024176977681</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.3305717935880238</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.713386374045527</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-1.713409569172369</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.4399940875050921</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0.1417598124246783</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-1.739835997520578</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.5266115037721798</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.3215400685270635</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-0.3210877435521076</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-0.2884623414310081</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0.03487464786607332</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-0.3968645839503347</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.03318312217231979</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-1.120426050769305</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>6.270434324854282</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-0.3632655744944128</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0.01090363800330628</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-2.104766242674227</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-1.112248023949184</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.6194469241086026</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-0.6383309146379874</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.1327402370593509</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-1.168872919513523</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.7732912221819292</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.6383831768114635</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1.874229842342994</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.1729604285863885</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0.2883848145003069</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0.1835862561332074</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1.450328854571415</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0.1749539200881468</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>2.453610850075878</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.869503899822435</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0.3363708675903912</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0.8324229294080131</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0.8683019149103564</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2g2mKBIE</t>
+          <t>xY3xTu1n</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.1993815215187167</v>
+        <v>-0.1755831547357415</v>
       </c>
       <c r="C7" t="n">
-        <v>2.772811678490129</v>
+        <v>-1.047983590105207</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002109095958100676</v>
+        <v>1.049450975946586</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5212960673668653</v>
+        <v>-0.193078397277103</v>
       </c>
       <c r="F7" t="n">
-        <v>1.172181751439272</v>
+        <v>0.2108926600344777</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4294998441620133</v>
+        <v>-0.5511554490158118</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3476140086491974</v>
+        <v>-2.66990156942974</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>4.062816519517454</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4682897897441698</v>
+        <v>-0.1095529779211208</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.418650980870402</v>
+        <v>-0.09019446291298334</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1842576484845563</v>
+        <v>-1.565204749593494</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5985554680006279</v>
+        <v>0.2620776808504022</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3125332667705741</v>
+        <v>-1.557892660687836</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8057193838819366</v>
+        <v>-0.2659203061083745</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-1.341331408580339</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.6263542080806678</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.4966742545334401</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-1.146453698101253</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.8768008668671909</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.745908913977526</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.7132685192058019</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-1.186470179569183</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.7774758906761233</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.657205472748367</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.9046164317455212</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-1.324705842453175</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9659978865370715</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-1.24165226445861</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.313470272427523</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.367930235018962</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.2634843539680486</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.9660475189446713</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-0.4731193477970498</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.430650383896612</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-0.7004936077776891</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.05772512223145513</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.6091663626437541</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-0.3580365528622113</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-0.4408205630438257</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-0.784537603996262</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.2659953790293147</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0.2660067777934025</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.2765354700199176</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-0.2765498811406772</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.3661929764797845</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-0.216185815548721</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.7380850753009199</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-0.2529963543216925</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0.6146523483780899</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.6319876746298871</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.3740089171654966</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.6776471886630147</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>-2.33521249326231</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-1.973528291220233</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-2.275831438340352</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.261174391884083</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.2162610273495087</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.1445856052079675</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>-0.2707828575379491</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>-0.6465171460133313</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-1.204007594480146</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.4371893723618338</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>2.137614336838829</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.1532857974199902</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0.2767480333138714</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0.8905590956565738</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>-0.06067770825826625</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.5903426341193927</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.3507294596515902</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>-0.2438728820478834</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0.6290460931499693</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0.4753171938339037</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.2934481446511506</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0.7194656902962521</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0.6436950432009093</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0.5697029002252847</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0.4157160686638761</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SznSCTAl</t>
+          <t>OjcQLOgJ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.1993815215187167</v>
+        <v>-1.137937566933284</v>
       </c>
       <c r="C8" t="n">
-        <v>6.694969627452143</v>
+        <v>0.01220274180270737</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4949264501859036</v>
+        <v>1.490911967665428</v>
       </c>
       <c r="E8" t="n">
-        <v>1.802301341822674</v>
+        <v>-0.193078397277103</v>
       </c>
       <c r="F8" t="n">
-        <v>1.729943473455685</v>
+        <v>6.688615035543079</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1745733348169437</v>
+        <v>-9.400508546055839</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.057906108319966</v>
+        <v>5.115426947142764</v>
       </c>
       <c r="I8" t="n">
+        <v>-5.904605486215623</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.683764044490563</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-1.611826287149441</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.9275134363149382</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.7953589280140587</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5134510484066785</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-1.625601949790708</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.2393798807823731</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-1.280941194977544</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.17544833733915</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-1.933595809474744</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.1778982941338998</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.6027656397444733</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.7214445326995</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-2.041240816506207</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.9605096725652952</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-0.7468073275354932</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0.6720377841115495</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.931111199418598</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.7418896764765541</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.2678745380889304</v>
+      </c>
+      <c r="AD8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="n">
-        <v>2.418613629212683</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-1.303188327250736</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2.352062779093898</v>
-      </c>
-      <c r="M8" t="n">
-        <v>-0.4677240441628552</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-0.8738864612908011</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-0.2347047777493697</v>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.578346125955441</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-1.467859883404796</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.133582432677136</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.9586772385441946</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.803034687597771</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.09669352071229317</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.044907072517564</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0.342479313423367</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.9212749262541434</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0.9212652086549701</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.827331188596538</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-1.827355080310577</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>-0.002812578646752469</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.3047962063195767</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.8690704076485403</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.3354695274483507</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.777839383712858</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-0.02457539122882023</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>-0.202053046831464</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0.3071358336678889</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.07514071335406437</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.5197211462574753</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0.5566047447901808</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-0.2699645358395943</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>-0.2707828575379491</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>-1.112248023949184</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.9084569356649282</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>-0.2411787012363377</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.001646091719741389</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>-1.045310378705022</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1.79850279086091</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.602230246034963</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>-0.1175819669548527</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.599983733491037</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0.4890311475020379</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>-0.6294184633851228</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1.254010023964715</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1.482235480468085</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1.770872642517591</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1.201509106112881</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0.2983945002976939</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0.4589533152129093</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1.454248323739909</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>jeAhPc0B</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.1993815215187167</v>
+        <v>-1.662858155404671</v>
       </c>
       <c r="C9" t="n">
-        <v>1.081410632948609</v>
+        <v>1.572191201610068</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1790178897834655</v>
+        <v>-0.3888574164277042</v>
       </c>
       <c r="E9" t="n">
-        <v>1.145288306035767</v>
+        <v>-0.193078397277103</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4284994554173877</v>
+        <v>-1.152838366388386</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4933173665559001</v>
+        <v>2.171722426996504</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.604545603033758</v>
+        <v>4.580633989870019</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-5.225143516572039</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9479080740610769</v>
+        <v>0.04638763272337356</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9844540880479959</v>
+        <v>0.8852105526232072</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3333418482721841</v>
+        <v>1.581951303929723</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1168260691598848</v>
+        <v>0.3329049456466711</v>
       </c>
       <c r="N9" t="n">
-        <v>2.012633140676674</v>
+        <v>1.08553645377564</v>
       </c>
       <c r="O9" t="n">
-        <v>2.027661977236333</v>
+        <v>0.1478958463166837</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.573342353714164</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.6316993743481049</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.1572872131305852</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.439415920377985</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.8215219596654645</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.8107379054010728</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-2.078603518161361</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.310318789718641</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.06805026569253049</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.2268572952367886</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-1.44804803176261</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0.7922580661956421</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-0.4941287782556156</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0.3927431027870387</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0.1821700556207624</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.3464976156076882</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.695522732794807</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-1.288525582267004</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-0.1971192253349712</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0.5660768327232716</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.693152768495922</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.9813692079946688</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.5852889961446741</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-3.218049384028169</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.01841119636358518</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-1.98331534234165</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.508092431231602</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-1.508063803456374</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.237293183739159</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-1.23731346833056</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.2923918654544772</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.6025002188157471</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.1279794169634325</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.521851172835317</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.8416469668077043</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0.5328822809258842</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>-1.109350640126677</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.3498871438596342</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>2.131717955603921</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2.770045486304225</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.591838703122462</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.2642849091889334</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2.395808401768399</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-0.2604522784823988</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-0.9585266269640533</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.2849446098583733</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-0.4710371926661206</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>-0.8047916263044813</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-2.214320147284549</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>-0.09748063137600475</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.2392955820943836</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>-0.05965363259382422</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>-0.6091532133137959</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0.1405812521376459</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.1018255421023101</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>-0.5239884697230311</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>-0.01246772496552436</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.8945474223896835</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>-0.03156961902544374</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>-0.1386212056838056</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>-0.005685567568068622</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>-0.2118380202722731</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.5730785322742703</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>OMVUWl2K</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1993815215187167</v>
+        <v>-0.1755831547357415</v>
       </c>
       <c r="C10" t="n">
-        <v>-4.536879553290706</v>
+        <v>-0.9116739188599041</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2253450675316545</v>
+        <v>1.049450975946586</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6616730891458972</v>
+        <v>-0.193078397277103</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.174388580659206</v>
+        <v>3.961152982697352</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4129423209714354</v>
+        <v>-3.954752794031207</v>
       </c>
       <c r="H10" t="n">
-        <v>2.442569520692064</v>
+        <v>7.267642506898926</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-4.508115139952967</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.19263684756921</v>
+        <v>1.76173434981281</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7208040714939992</v>
+        <v>-0.2072430647773262</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.8629514357779279</v>
+        <v>1.878695473440848</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3230605194909194</v>
+        <v>0.1093509706795085</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6517850250570331</v>
+        <v>1.065809370831883</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2574457481713225</v>
+        <v>-0.6797364585334322</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.690661290165701</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.2952740672946681</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.345141858040577</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.6902112284368933</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.020832336426317</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.1593006015150202</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.4806125160918717</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.4871123857116184</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.275671907055117</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0.9651457200046757</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-1.169083005946753</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.08179167723786308</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-0.03593304461717602</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.08931838804511032</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.225491429601154</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-0.01546982894590157</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.8198055420804815</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-0.160428387911455</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.3088809991788396</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.5405430704636519</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.417966561259231</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0.07034014603769237</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.444874190111566</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-1.746159935352801</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.3642941221772744</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-1.323705701789912</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2.173152270206054</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-2.173102210897964</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.773302466884302</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-1.773326028300591</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-2.216845909405973</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.6025002188157471</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-1.855168368921557</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-0.3203101253647863</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-1.134759246658731</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.161474018064329</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-0.3460685378307039</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.5066419478960335</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-0.3253234481393124</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-0.3881249209810446</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.5735355957734335</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.2839409876186421</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.07256639837781485</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0.3323545563958617</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>-1.187774550106088</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0.2849446098583733</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-0.01232191212885439</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>-0.9573397527175533</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>-0.05060491166124366</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.259746007345965</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1.31257462142745</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0.2836327759083006</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.4226444336110163</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0.6898613834820226</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1.176491910585693</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0.6896260900522886</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1.2053732246889</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1.07562945971346</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1.337924872839875</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.205966008317683</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0.9261591768514015</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-0.3662943931614823</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1.137920412414799</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>8f71RSPs</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1993815215187167</v>
+        <v>0.7576090025467243</v>
       </c>
       <c r="C11" t="n">
-        <v>-4.234083282200756</v>
+        <v>1.572191201610068</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3769811765248246</v>
+        <v>-0.488542156493249</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6063767575707483</v>
+        <v>-0.193078397277103</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.926494481985245</v>
+        <v>-4.221233175839829</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.322994068964999</v>
+        <v>4.213880834005742</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3439945253519748</v>
+        <v>-0.4626861079115353</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6186863043631206</v>
+        <v>0.2789596108235628</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.07243797087588752</v>
+        <v>-2.448662137588535</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5623259194670067</v>
+        <v>-0.05117826229153585</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.460439563544758</v>
+        <v>-2.201084172187152</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4636473684404315</v>
+        <v>-1.145158888844613</v>
       </c>
       <c r="N11" t="n">
-        <v>0.09197258465244156</v>
+        <v>-0.8279905917688172</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1528291792140144</v>
+        <v>1.13317239970968</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-1.059115780630027</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.5077532085915754</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-1.369954473182261</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.7091525251159798</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-1.267833660452734</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-1.658960657579778</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.760219500515756</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.1345389866062172</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.1027827712161138</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.167757582619503</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.9486517432186963</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-1.062808372086842</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.855952216475594</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.311397037715227</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.797353907972557</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.4127031729400455</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.4266255464554338</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.4797173005456287</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.826881672720272</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-0.205222516466666</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-0.03214001355301317</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.3886321349971841</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.635893122104209</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.07276035894521438</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.434922180121113</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.6832011231165388</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.256215087279691</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.2562268012133797</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.1467275834300079</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0.1467412009866877</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-0.298017022747982</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-1.481427868657444</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-0.5644816850521592</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.9650179941489622</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.3215400685270635</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-1.062368624360326</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.9212677829626086</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.9056541763523231</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.6844068717635536</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.5400704191249238</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-0.1201172522297816</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-2.747514895600019</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-2.430170050115199</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-0.5799392547386715</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.6462088350301897</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.216406365730078</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1.567609850591815</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.23018805015692</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.0007633429688880534</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.2698621209894785</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>-3.594340960694194</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>-1.149891216769178</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.2118168534453613</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>-1.251030816794885</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>-2.727214258689602</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0.8740894178412917</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>-3.361197391698297</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-1.513138940021764</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>-2.680598328881311</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-1.484131513156717</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>-2.397064891687064</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0.1118740540973925</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>-1.489344818251133</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
+          <t>UuMqRJVb</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.1993815215187167</v>
+        <v>0.2035261591602602</v>
       </c>
       <c r="C12" t="n">
-        <v>-3.306769701987783</v>
+        <v>-1.74467746535898</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.034070982161895</v>
+        <v>-0.4315794478843663</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7971411793944705</v>
+        <v>-0.193078397277103</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.120838661294871</v>
+        <v>1.915556443063057</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.556420752220726</v>
+        <v>-0.891515183517351</v>
       </c>
       <c r="H12" t="n">
-        <v>1.643857217238465</v>
+        <v>4.909921030369708</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8151253918201364</v>
+        <v>-4.010549929664274</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8275287601243866</v>
+        <v>-0.343463893887862</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5496476673048474</v>
+        <v>-0.4413402685060122</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.38085647272413</v>
+        <v>0.5749435954447353</v>
       </c>
       <c r="M12" t="n">
-        <v>1.112881669988385</v>
+        <v>-0.9000442252162297</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6306906181423748</v>
+        <v>-0.2164510205123412</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1091822277654793</v>
+        <v>0.2070124395202634</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.9629626659420494</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.6341102265424535</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.702690023651996</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.5342320559218706</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.9687357595938698</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.03369401385004394</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.031652536851406</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-1.73041513034729</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.9881669301486529</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0.9249080608529128</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.891770312447853</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.09298834178895524</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.712620911434662</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.01604237584324937</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.709375065146187</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.7216624404910462</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.769060487706384</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-1.215455024409508</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2.792882101337547</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.08346093653861836</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.953502626702205</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-0.8277668878832485</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-0.6205180120588818</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-0.2264041631432753</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.118278151101638</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-1.214886688743424</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.6376464655150389</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.637645887834292</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.383289298367696</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-2.38331658886125</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-0.3718181337732893</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.0815181969474493</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.2479845034980509</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.1218489589378893</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.1030951712491944</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.09870347930964227</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.6476383500640527</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-0.1346277049801458</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-0.2727079826162983</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.1927735751959315</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.8832685224081391</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0.157086742591008</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.771843819685218</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>-0.6466603324348517</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0.1877129887461204</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-2.509440657756741</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>-0.03703180839791965</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>-0.7592033274124028</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>-0.6572986038144346</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-0.1449904561907999</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1.81457509896034</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1.954758101599981</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1.015164417388985</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.058587328068563</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>2.582721333877288</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0.09690285105127627</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1.921795607378016</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0.8218789373710359</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1.964242586051142</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>1.988829666963744</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>2.507061211186089</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>1.241323536338891</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1.503843323251059</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
+          <t>bLD0NyVN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.1993815215187167</v>
+        <v>-0.6130169784618973</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.9884857514553499</v>
+        <v>0.8452062883017833</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.730798764175555</v>
+        <v>0.2519730554222272</v>
       </c>
       <c r="E13" t="n">
-        <v>0.05131685953080554</v>
+        <v>-0.193078397277103</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8003406034283297</v>
+        <v>-4.221233175839829</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2615659944240186</v>
+        <v>4.213880834005742</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8643479812519259</v>
+        <v>1.06534857560162</v>
       </c>
       <c r="I13" t="n">
-        <v>1.149265482750023</v>
+        <v>-1.063438952505081</v>
       </c>
       <c r="J13" t="n">
-        <v>1.176335743147178</v>
+        <v>-0.5773748098546033</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.339411904856906</v>
+        <v>0.5730809476516261</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8460173392328035</v>
+        <v>-0.8529515807518148</v>
       </c>
       <c r="M13" t="n">
-        <v>1.091688130232487</v>
+        <v>0.8048168928035269</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2496179646609617</v>
+        <v>-1.617073909519109</v>
       </c>
       <c r="O13" t="n">
-        <v>1.095412551624397</v>
+        <v>1.527283021066878</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-1.143239540184284</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.46299082693724</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0.6911803903765515</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.009470648339543065</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.8339379800506068</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.749209700728021</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-1.070427504667663</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.7561903589240528</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.3801804678041052</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.1996642156332425</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.515330534866538</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.7520403825971058</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.548447498283904</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.5278900080689072</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-1.567836830136086</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-0.3464976156076882</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.1999700508147336</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.287423849945448</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-1.784119929491923</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.1315748453728324</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-0.7211847770771389</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.2162797469734592</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.8718173941336379</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.9343541825600626</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-0.7012369084815139</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-0.4301319579655489</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.177972753282696</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-0.177986988573192</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0.2258236132680879</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.2258122732559806</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.8828007536569363</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.3047962063195769</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-0.4957345460209878</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.245917478115357</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-1.134759246658731</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.161474018064329</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-0.05803755583222377</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.1646314663620712</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-3.012595860855799</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-2.494164437533893</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.1508381256170023</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0.515454164200188</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-0.9581807998264982</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.5252605284425924</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0.6462088350301897</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0.2849446098583733</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1.404003370113946</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.184156464638471</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>2.042717936458526</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.97187834559833</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0.4680613382522639</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>-0.6090682003333117</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-0.7196809342173139</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0.5152754591947546</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0.4214200896656881</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>1.029856554761798</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0.1191932363097398</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0.4384745837787851</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>-0.5314667323084734</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>-0.5236918375704931</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0.1947018046349112</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>-1.530910391479715</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0.1745805413874862</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
+          <t>I5fXHFho</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.1993815215187167</v>
+        <v>0.2618506689904143</v>
       </c>
       <c r="C14" t="n">
-        <v>2.649800693359837</v>
+        <v>1.814519506046163</v>
       </c>
       <c r="D14" t="n">
-        <v>1.998651197701507</v>
+        <v>-0.3603760621232627</v>
       </c>
       <c r="E14" t="n">
-        <v>1.238445124077515</v>
+        <v>-0.193078397277103</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2532093159360059</v>
+        <v>-0.8119056097826699</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5510396773609537</v>
+        <v>1.491002957993425</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4066732617812116</v>
+        <v>0.4711723181952515</v>
       </c>
       <c r="I14" t="n">
-        <v>1.149265482750023</v>
+        <v>-2.407577029092517</v>
       </c>
       <c r="J14" t="n">
-        <v>2.547658453876072</v>
+        <v>-0.0315826725988735</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4627110810500397</v>
+        <v>-0.2462592653987741</v>
       </c>
       <c r="L14" t="n">
-        <v>2.133359861502126</v>
+        <v>-0.3148070986333641</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2722039159264435</v>
+        <v>0.2105251698766709</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9821785942927346</v>
+        <v>-0.9858072553188754</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9090586633536603</v>
+        <v>-0.423564554651254</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.7127782779722107</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.03882142461296942</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.07244045277987164</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.009470648339543065</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.4418076306737703</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.4712340746734379</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.403060515053895</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.0985802780129711</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.134790991994152</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.16956016996703</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.07304500930402</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-1.371826532210142</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.6665392646041214</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-1.191868189946558</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-1.743794515788825</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.911407973707101</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.6834881453972343</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.9798607992355055</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-1.945120000928136</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.743390791319004</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-1.160868676621975</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.518026881019508</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-0.7518435278038242</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.8146883737246676</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-0.9614110672515772</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.9773616677461766</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.3540180047759335</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0.3540265670136131</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-0.6694478684210747</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.6694392404496844</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-0.002812578646752469</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>-1.853557884277657</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.437384814622514</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-0.1071151167670002</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.7584298630828017</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0.7658562720370384</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-0.2164545959313878</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.02212709905625383</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.3168847836764194</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.3736585876755701</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-1.119135533873708</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.57051214013532</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-1.074671712832147</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2.273865242013889</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>1.104704681314259</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-0.6465171460133313</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.1824073944380604</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>-0.6971682795863799</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.4341772786965591</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.3095710499862441</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-0.08754821025190562</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>-0.08983838435487664</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-0.00794297355995504</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>-0.1265620014325971</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>-0.09875493792051843</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0.411365771096446</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>-0.06472839306557042</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-0.1190369285333109</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>-0.1722023052316627</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>-0.0711861106250308</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>-0.1484769425421064</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>-0.2941489479037044</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>-0.1071042689503714</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
+          <t>McP0d8Q7</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1993815215187167</v>
+        <v>-0.08809638999051034</v>
       </c>
       <c r="C15" t="n">
-        <v>2.58829520079469</v>
+        <v>-0.1998345245788756</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.02316358887409439</v>
+        <v>-1.627796328670905</v>
       </c>
       <c r="E15" t="n">
-        <v>0.162226407102737</v>
+        <v>-0.193078397277103</v>
       </c>
       <c r="F15" t="n">
-        <v>1.544022899450214</v>
+        <v>2.597421956274488</v>
       </c>
       <c r="G15" t="n">
-        <v>1.611990279075891</v>
+        <v>-5.316191732037364</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7712087363447461</v>
+        <v>0.7994866535140929</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6090579922432289</v>
+        <v>-1.983479651219303</v>
       </c>
       <c r="J15" t="n">
-        <v>1.438530980706875</v>
+        <v>-0.4214341992101092</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.337829984046312</v>
+        <v>0.3389837439229406</v>
       </c>
       <c r="L15" t="n">
-        <v>1.88627988371712</v>
+        <v>0.4201439202237902</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2527269083078288</v>
+        <v>-0.2393079314552869</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3742389929281661</v>
+        <v>1.184171868494426</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4975694900768853</v>
+        <v>0.4237732812667223</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.4502841289618508</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.1462450895472876</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0.0124063075708422</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.6902112284368935</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.2199847663806969</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.067670452292923</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.01530050986401119</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.4453646727651349</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.4938860582867076</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.761669029956107</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-2.053843221170732</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.2758467481506092</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.6727503420501195</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-1.055169149560042</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.401449115253893</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-2.045773587138193</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.8106237909257208</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-0.353427946014394</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.458881509437501</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-1.79298150799573</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-0.03882237025584196</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-0.286006642285388</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.086713692625361</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-1.435028832380773</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.095616606348528</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.7463211339687336</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-0.4284053351940106</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.428371559388258</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-1.259238252469865</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.259233230107315</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-0.002812578646752469</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-1.332575862409359</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.3173258453052292</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-0.2899692797389152</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.1153497260286747</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0.1236807849328232</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-0.2884623414310081</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-1.174909586312614</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.04562305135573294</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.07340506651637355</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.304237091687787</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>-4.920959529637039</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0.7386260576296991</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-1.312853430445029</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>-0.2707828575379491</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>-0.1807862680774791</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-1.09421243853126</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>-1.922975557856788</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.1435460865404678</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>-0.002600351332247126</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-0.1167675014014083</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>-0.358894576973516</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-0.2555381744377039</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>-0.2159459355811046</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>-0.3308063609579721</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0.3570055844532571</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>-0.4449622931647177</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0.009054620960128131</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>-0.4322611614701462</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>-0.7565513811300834</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>-0.775765235133519</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>-0.5937015717763341</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0.06615409652342767</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>0lpzB7u1</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.05771488458487495</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-1.047983590105207</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.314501431322049</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.193078397277103</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-5.584964202262691</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.852441895999583</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.7439541700881322</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.460192620111682</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.5921797699791037</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.275372558837683</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-1.246709513477213</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.8394956257624219</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.7501760437317656</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.960804704559795</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.2491951173990537</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.8600036030024055</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.3517933489736969</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.1843911175336523</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-1.35671480311884</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.08284906677096</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.4500114963638492</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.9116032020035115</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-1.051052124846767</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.215833008197282</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.501691803332643</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-1.086846159560748</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9151572584137988</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.3995270908868673</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.5216606869901956</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-1.560266166700906</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0.2681718482869729</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.1453967233839127</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.5848811216409182</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.08346093653861836</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-0.4314108265470228</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.1188124091936782</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.325487357616164</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-0.6931008176013191</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.1133914710898659</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-0.1160533234518232</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0.7256690912616568</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-0.7256656770545021</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-0.4207439640614934</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0.4207338156702719</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.2923918654544772</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.9002042313119174</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.030168400963028</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.6234025471021185</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.959876798111082</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>-0.8770484041582712</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.3452058189656487</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0.2216332132843984</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0.4795583976641717</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0.4410253910104378</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.770647036136435</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>-0.1467350884944564</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0.5590704766420728</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-0.1688736622168747</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0.6462088350301897</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0.2849446098583733</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>-0.7621619116240782</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.2883575832991953</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>-0.07884549907279725</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>-0.3130423027901837</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>-2.206587660342057</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>-0.9246586627043196</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>-1.376294232707399</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>-0.2242178932418709</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>-2.116236318920825</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>-1.876955900519309</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>-1.251453323293423</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>-1.072844084889729</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>-2.078854131341793</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>-1.502882974922295</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>-1.745672357696996</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>-1.165857036416477</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>-1.44297828873084</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>GMBD7YY8</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.05771488458487495</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.3756951984568496</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.314501431322049</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.193078397277103</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-1.493771122994101</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-1.23187491801889</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.571899467430932</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-3.21220304577571</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.9672263364658392</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.2462592653987741</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.1576246540934551</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.2976052995403432</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.335907301912863</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-1.25119685950137</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.3313251598844033</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.6974001614596482</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-1.879035035286543</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.4278305246457297</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.04504601106246832</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.8708905574526674</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-1.38063550881957</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.1447224666227</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.362276514633422</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.2409266976372108</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.0100861832687151</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.6763780898308062</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.1751764297921763</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.4559652009020236</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-1.281905590950384</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.102668472667244</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0.6069830775681739</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.8914939401970551</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-0.7184527899855643</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.2438406326526654</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-0.2500241500458313</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.3919159450475307</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>3.008841695801327</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.137786057580236</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.956856180459141</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.952776256042559</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0.08995012753607726</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-0.08996719935298149</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-1.477602132748316</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.477598445325701</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-0.2242159117226746</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>-0.5138898280448911</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-0.5819060751291842</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>-0.04030746430317733</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0.3215400685270635</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-0.3210877435521076</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.9644724302623809</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0.8629028661605777</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0.2612836475022781</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0.06777688604698147</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0.8770541961183675</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0.03526167056343001</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>-0.0692309081156023</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0.6272678730560726</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>-0.5000307806799837</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>1.68213724366593</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>-1.241495589327253</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>-0.1382133125766507</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>-0.2906295482721281</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>-0.2804241182218168</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>-0.6469652715825848</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0.0164938525556262</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>-0.4816304526309539</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>-0.4397139995169081</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>-0.627315070951066</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>-0.7246343651559146</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>-0.4881094875828946</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>-0.6115221616792171</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>-0.307756588880434</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>-0.1555798451617917</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>-0.404950196807651</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>0.8990431689812414</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>-0.7227905332715922</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>dGwq9oAD</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-1.137937566933284</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.1998345245788756</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.490911967665428</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.193078397277103</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.233690929851625</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.5511554490158114</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.667572843306799</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-4.219017138445961</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.889256031143592</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.05117826229153585</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.3185658149102028</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.05441901098206892</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-2.208886397831828</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.5420064676738818</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.2630177633848626</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.2193976305133965</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0.01240630757084208</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-1.583754871086526</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.4024181774588639</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.2870412090577342</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.6357165181678253</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.3316995426321596</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.5909861214386049</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.3785093879905773</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.208949816433528</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.1992083660483126</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.7217853516347419</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.6623046504934328</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-1.611826251549271</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.566546907016034</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.3492750062700154</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-0.07993046001704719</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-1.163119653952246</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>2.272643788495358</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-0.6137015866021267</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.7657418233801926</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-0.01164516633233365</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-0.02297228812310289</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.3176807142338006</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-0.6706733653462399</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-1.249949842162452</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.249889592110223</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-0.2648637218601544</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0.2648526205148081</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-0.5932214668492114</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.049056237560002</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-0.5522846119982416</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.9718503030898986</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.19531965763854</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>-1.210624800521969</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>-1.267767680225841</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0.6491463152018512</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>2.084829678630981</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>3.617592701233439</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>-4.852224949460504</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-0.05625901763174035</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>-0.8896264960597947</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.409367519928038</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>1.104704681314259</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0.7506754877942258</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>-0.1272797561564417</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>-0.5439459750332744</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>-2.971362188778002</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>-1.292298624728675</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>-1.569311001279533</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>-0.9025211174367671</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>-0.2597441041411541</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>-1.158296748301813</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>-1.290553152365283</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>-0.7913308196374228</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>-1.463494609727003</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>-1.697999589850041</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>-1.325390332122655</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>-1.237667728846138</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>-0.851502515345254</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0.3824267855866584</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>-1.819799562752324</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>AJ5eIkmR</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.7576090025467243</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.814519506046163</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.488542156493249</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.193078397277103</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.1300400965712384</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.1295640199872675</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.973604137182928</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-2.948120660813021</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.5921797699791037</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.197340157594788</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.2344159341261454</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.089510545134996</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-0.03890727401852558</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.591381698731313</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.2183990788396275</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.536380004029922</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-0.3517933489736969</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.1654498208545659</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.7346765579490433</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.108652711383622</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.3255085140159181</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.1762866995527007</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.5394203336515941</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.4690462224985254</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.8132118179094073</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-2.81017645206341</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8860892127468667</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-0.4256774014067412</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-0.116185923500985</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-0.2361550200537593</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>-1.399513653746791</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.76162466845604</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.1478809277426271</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.9013973867202575</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>-0.9964509795024293</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.9027888217701773</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-0.6563340618075023</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.4556909472184804</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-0.2048424943130504</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1.158806244982968</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>-1.543358594651181</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.543288889510924</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-2.194033489858823</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.194034182248603</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>-0.002812578646752272</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0.9002042313119174</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>-0.7055650539892202</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.32385973932315</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>-0.2245721746676093</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-0.3210877435521076</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>-0.6629026180290323</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.6491463152018512</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0.2611929934759068</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0.7424463178236099</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>-1.137406783423877</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>-0.8264309185912154</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>-0.8367984952506048</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>-0.08671646526312979</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>-0.7292787038220186</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>-0.1807862680774791</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>-0.9052571124678203</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0.7671466405667396</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>-0.6507283942158947</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>-0.03859064637970749</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>-0.6961678649709097</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>-1.62061740718929</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>-0.2709741934308153</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>-1.478003900187891</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>-0.831494340203122</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0.1249431579727408</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>-1.298373083371704</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>-0.6673686128563281</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>-1.111985811466869</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>-1.021412253196115</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>-1.043655013601767</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>-0.09764365617091551</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>-0.7953898547986179</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>8Kjh0jRr</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>-0.6130169784618973</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.01220274180270737</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.2519730554222272</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.193078397277103</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.1300400965712384</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.1295640199872675</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-5.377103455590049</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6.17044829557252</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.889256031143592</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.1829189414371499</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.6420365156758087</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.510327872626262</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.9858072553188754</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.8572949647596405</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-1.114635048054644</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.599331609269422</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-2.388115597390825</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.3403702900486752</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-1.310976696856355</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.5236551106596683</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-1.38063550881957</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.9116032020035115</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.8223688752364477</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.7577662187455315</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-0.5533538638825638</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-1.441522398539419</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9539840192493229</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-1.2591748421367</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-1.941746912148157</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.220367241258102</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-1.796553023466749</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.139179614859853</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>-2.037120041748829</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.4683722072123309</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>-1.429440454104778</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.8262787619475065</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>-0.6324566953084223</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.484816903202883</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>-0.07761646124930524</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1.800237392225858</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>-1.015222840171469</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.015170154189661</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>-3.076169081757357</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>3.07617516697139</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>-0.1504148006973671</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0.1559442000714918</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0.8803170594255287</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>-1.196269067500734</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>-2.955133390640974</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.902754898872546</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>-0.1156437522319199</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>-0.291382509016545</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0.6063910831867287</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0.5432358615709714</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>-0.0618565062189479</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>-0.937423285668889</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>-1.082291949606378</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.358765881597024</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>-0.2707828575379491</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>1.68213724366593</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0.299200058122946</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>1.095929259061446</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>-0.3830176088011811</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0.9500946615386422</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>-2.180157601270191</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>-1.911069675654538</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>-1.339355291029787</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>-1.223651785446806</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>-2.34707291749995</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0.4481846916654893</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>-1.955919533055946</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>-1.670609201737649</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>-2.027381824102029</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>-1.901799019801653</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>-2.146908826657831</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>-1.275516148234406</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>-2.291613717656634</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>2g2mKBIE</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-1.662858155404671</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.3756951984568496</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.3888574164277042</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.193078397277103</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.233690929851626</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-2.593313856025048</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5.809116259791445</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-6.721422806181894</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-1.513018473721569</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-1.29969668217786</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.5028904337237732</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-1.317061453327588</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-1.459257245969051</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.2856258371762345</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.5576822075822021</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-1.292350229146064</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-1.709341514585116</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-1.408834401892417</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.126474753435829</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-1.298123595215551</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.4500114963638492</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-0.4871123857116184</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.5145384754046394</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.9664333504487467</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.827537998336899</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.5935833594641792</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.3352958128287119</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.5944247061089669</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.1257558942715317</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.132093164814959</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>-0.1485332318167943</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.2201303832396152</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>-1.025119592721207</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>2.056131198741395</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.4426610841732618</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.1300952437256394</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>-1.372655056779912</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>-0.4059028763963689</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>-0.5583139357123373</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>-0.2359553744170403</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0.8430325922571492</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>-0.8430253960147832</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>-0.4610322013971533</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0.4610222993029699</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0.2923918654544772</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>-1.779131881153615</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>-1.048518205310605</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>-1.471729893207182</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.231727140518185</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>-1.24768884456238</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>-0.05803755583222377</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0.5636436948183606</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>-0.09226705534416699</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>-0.1794278333157332</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>-3.563275681695259</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>-0.2721499185201052</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>-0.8383421105449602</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>-0.1299908216498068</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>1.563200527598329</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.147868121601783</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>1.8709692136197</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>0.6955388929988664</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>-0.123590509209274</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>1.549776649460291</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>1.223084232994966</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>0.385501680266975</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>-0.7642500833966542</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0.3971443635501917</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1.485361941929458</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>0.5011326865827175</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>0.9707706658296217</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>0.5063427892774189</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>0.2262569723526237</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>0.1687247291331343</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>1.267357888772379</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>-0.3774529832256418</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>0.1765842715179003</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SznSCTAl</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.2035261591602602</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-1.547785718004653</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.4315794478843663</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.193078397277103</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.915556443063057</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-3.954752794031207</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5.585001251089563</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-5.453808602509783</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.9820312965903392</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.2852754660202216</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.775881622178695</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.2948269840619764</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.5123572646687005</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.1478958463166837</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.9229220664288097</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-0.3094393433811286</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.684528899443432</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-2.283436747862962</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.71211749685449</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.1252306582763833</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.9459245223197321</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-0.9533509149499951</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.4042233158150066</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-0.2837268300194592</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.883837402616812</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-0.5151292370279656</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.2650357013005428</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>-0.5573231600841592</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>-0.1821700556207624</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>-1.074758746263619</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.933654687065258</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>-2.200226612634693</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>-0.2431192457453176</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.08346093653861836</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.133558839695375</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>-1.103836267024814</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>-0.2742961978222175</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>-1.243563538244139</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0.2005752507193688</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>-2.179694850711041</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.39072893023611</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>-1.390704084496093</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.989661694405811</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>-2.989692691880236</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>-1.036028133001056</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>-0.2906118186727635</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>-1.617310854569861</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0.3233503127793075</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0.9768747603606711</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>-0.09870347930964227</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>-1.238964582025993</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>-0.291382509016545</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>-0.3841730202584107</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>-0.1546650617213482</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>-1.605163578133513</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0.5598900422396587</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.806625740427696</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0.2830479020640683</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>2.480192220166467</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>-1.112248023949184</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>0.4352324126775785</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>-0.7395802134866798</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>-0.4756797936574723</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>-0.1526671863778226</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>4.271791735145901</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>1.847648068182665</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>-0.1978736789566336</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>2.395346707787056</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>3.593420770160806</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>-0.6139745338096708</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>4.087682756170034</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>2.395695705112367</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>3.663051951449357</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>1.93477948792635</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>3.197662413480505</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>-0.9588544588398877</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>2.402562361816049</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Cl5M5C3L</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.9338017825277449</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-1.74467746535898</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.9355255587288207</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.193078397277103</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.961152982697352</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-1.912594387021969</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.28892101487911</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-2.177172429895981</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.9040609912680919</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.02685413895135955</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.3920818832660227</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.9226639384309325</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.04000105775650328</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-2.019712571147906</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.7206896374590986</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.1698176331318619</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.17544833733915</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.040052166825112</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.03517547749214495</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.4541784525715656</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.7908205202437788</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-0.6425252287910773</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.2674470258141952</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-0.1064276921676032</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.082037800689272</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.5349114096649893</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.619261802286594</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>-0.2412664260589587</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>-0.4461065840998716</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>-1.560266166700906</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-0.8553181407004894</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>-0.3615315958782654</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>-0.3351192865660105</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>-2.514690140508941</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>-0.6201874034019308</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>-0.3759167299619542</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.0389589596272</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.1924261677806094</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.7649658858371895</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1.137311463888542</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.195123095243624</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>-1.195104552895625</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0.5351453483259503</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>-0.5351613404254585</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0.8828007536569363</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0.3047962063195767</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0.3674855787494498</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>-0.661071533794013</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>-0.1881646917879646</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0.2719369610944668</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0.08597793516701646</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>-0.3768851294000356</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0.2817981204110301</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0.73577389835181</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0.7630981352655806</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0.8677204258211082</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>-0.06268433615126072</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0.4715068136199105</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>-1.187774550106088</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>-0.6465171460133313</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>-0.8791342563300172</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>-0.1795292563455588</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>-0.1585252202871176</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>-1.428495651991231</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>-0.04361012845143337</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>0.9683385472456102</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>2.201435754384585</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>-0.1958613860212668</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>-0.09671297396678527</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>0.05432887954270438</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>0.2793231050743081</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>-0.6073918650591004</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>0.8851471503187952</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>0.6816703819950299</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>0.04403614831055737</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>1.977095827796441</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>0.2622024813253664</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>EXLhbUee</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-0.9338017825277449</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.9116739188599041</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.9355255587288207</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.193078397277103</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.8119056097826699</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.491002957993425</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.5781614882121794</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.770039282013928</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.9672263364658392</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.4170161451658357</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.324050712800073</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.2438649556170761</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.5320843476124578</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.7390617783524811</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.03020296836523042</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.3660672599919559</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-1.200260952480834</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.3403702900486752</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.5939058138777354</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.4268287218147572</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.458187509857547</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.533254574321347</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.7239938145202746</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.6882252189934603</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.4704816885263645</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-0.5065804447655708</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.3714546391283565</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>-0.4044956797298181</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>-1.369884433776754</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.477833297550602</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-0.3982128737715195</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.08299794243545569</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>-0.503786028070614</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.5245051008522471</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>-0.3003135391270564</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0.1806291679373767</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>-0.8592916770496857</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>-0.6931008176013186</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0.34206631191979</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0.3025113840458792</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>-1.934570264636154</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.934487952711861</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>-1.78153967610941</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.781537846770485</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0.8089996426316288</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.197908243808087</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>-0.4494663102214158</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>-0.6568789805802562</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>-0.5764933234294886</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>-0.6618938640116711</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>-0.191261252141171</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>-0.07590309831378496</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>-0.824832567020207</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0.04859530466613205</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>-0.1911790917200311</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>-0.01458384528110896</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>-0.2707828575379491</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>0.7506754877942258</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>0.0999978878168996</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>-0.09635855069290779</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>-0.588085907872702</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>-0.604608544341154</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>-0.6469174055211639</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>-1.095362673178881</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>0.2508266372936601</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>-1.429758737499249</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>-0.4610763326171992</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>-0.1917007974254276</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>-0.721232061675677</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>-0.7882280649428245</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>-0.8169920101628726</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>-0.1524993502119059</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>-0.3423538227228154</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>0.6205498908920375</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>-0.7990158562752449</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ24"/>
+  <dimension ref="A1:BZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,731 +818,731 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WIDwXGr3</t>
+          <t>EssDGebM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.6130169784618973</v>
+        <v>0.7576090025467243</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.547785718004653</v>
+        <v>-0.9116739188599041</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2519730554222272</v>
+        <v>-0.488542156493249</v>
       </c>
       <c r="E2" t="n">
         <v>-0.193078397277103</v>
       </c>
       <c r="F2" t="n">
-        <v>2.597421956274489</v>
+        <v>-2.175636636205533</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.231874918018891</v>
+        <v>4.213880834005742</v>
       </c>
       <c r="H2" t="n">
-        <v>2.89415634268854</v>
+        <v>1.130223972857427</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.088396573002503</v>
+        <v>-1.376005212832012</v>
       </c>
       <c r="J2" t="n">
-        <v>1.449853128523822</v>
+        <v>0.4362391593346091</v>
       </c>
       <c r="K2" t="n">
-        <v>1.353404960080579</v>
+        <v>0.5730809476516261</v>
       </c>
       <c r="L2" t="n">
-        <v>1.522694817798093</v>
+        <v>-0.2711606260048987</v>
       </c>
       <c r="M2" t="n">
-        <v>1.185462850180047</v>
+        <v>0.493176927699943</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3161802189691056</v>
+        <v>-0.5912655964437297</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1478958463166837</v>
+        <v>1.330227710388278</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5048680174244224</v>
+        <v>-0.291742949574121</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.030728573861344</v>
+        <v>1.444398902073761</v>
       </c>
       <c r="R2" t="n">
-        <v>1.17544833733915</v>
+        <v>-0.6911803903765517</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3403702900486752</v>
+        <v>0.8651316976310026</v>
       </c>
       <c r="T2" t="n">
-        <v>1.122752803126459</v>
+        <v>-0.2681478740716963</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1533314142466691</v>
+        <v>0.05304906813837012</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1704045119399647</v>
+        <v>-0.6051154984398027</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1345389866062172</v>
+        <v>0.7561903589240526</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6827196171419604</v>
+        <v>-0.0716005690387993</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.4935228448899845</v>
+        <v>-0.05411073845333728</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.4795060912956393</v>
+        <v>0.8156333409218951</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.4472320984824059</v>
+        <v>-0.8215958519493847</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.6996328048206804</v>
+        <v>0.9766245784602097</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.5871774718664917</v>
+        <v>-0.5275668087699054</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.6660536911657959</v>
+        <v>-0.8860007982317203</v>
       </c>
       <c r="AE2" t="n">
-        <v>-1.95749951069505</v>
+        <v>-0.01546982894590157</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.04386585203059967</v>
+        <v>-1.493082468398824</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.1666747279972349</v>
+        <v>1.312592704206847</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.7951194906694748</v>
+        <v>0.1478809277426271</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.4457920606377364</v>
+        <v>0.4202582983781168</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.2007112539564736</v>
+        <v>-0.9980095064527276</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.3084546553974687</v>
+        <v>1.113932046937221</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.8951077267983056</v>
+        <v>-0.8115369440515247</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.6931008176013191</v>
+        <v>0.5753567560538759</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1.297538635215637</v>
+        <v>-0.594765081619347</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.4124371938524935</v>
+        <v>1.217281375060798</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.801501183720331</v>
+        <v>-2.208418433625634</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1.801463100857075</v>
+        <v>2.208327296952515</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.5971482824903627</v>
+        <v>-2.011021306159888</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.5971392125246074</v>
+        <v>2.011020879727853</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.2923918654544772</v>
+        <v>0.5875963095557069</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.6025002188157471</v>
+        <v>1.793316268800428</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0.2170235065616638</v>
+        <v>-0.8256099308883037</v>
       </c>
       <c r="AW2" t="n">
-        <v>-1.073206169552669</v>
+        <v>0.4975741907731983</v>
       </c>
       <c r="AX2" t="n">
-        <v>-1.20757421241802</v>
+        <v>-1.316796661056955</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.013217841902685</v>
+        <v>0.2348729170540559</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.6340995198291843</v>
+        <v>0.04277328786724412</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0.8043982313174884</v>
+        <v>-0.06337552132723674</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.09102278439397789</v>
+        <v>-0.007052270555536726</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0.2558122530241582</v>
+        <v>0.536309968700296</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.3244323297452965</v>
+        <v>-1.113286834575392</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.591792039962583</v>
+        <v>-0.8354508286616851</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.05804047512575159</v>
+        <v>-1.78592192123651</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.259270063479941</v>
+        <v>0.4916672663409129</v>
       </c>
       <c r="BH2" t="n">
-        <v>-0.2707828575379491</v>
+        <v>-1.187774550106088</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0.6465171460133313</v>
+        <v>0.05207917089044719</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.5854457462784461</v>
+        <v>-0.1418477404787931</v>
       </c>
       <c r="BK2" t="n">
-        <v>-1.885163898323777</v>
+        <v>-0.4471094785557116</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0.5991394379616988</v>
+        <v>-0.2250800784950177</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.095277226098793</v>
+        <v>0.6294103125180968</v>
       </c>
       <c r="BN2" t="n">
-        <v>2.166001215845864</v>
+        <v>-0.8707248883225009</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.2936863093154641</v>
+        <v>-1.636361146734042</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.9242274594846919</v>
+        <v>0.4525170992983878</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.206472246124132</v>
+        <v>-1.793866906551585</v>
       </c>
       <c r="BR2" t="n">
-        <v>1.088017716219443</v>
+        <v>-0.2649408634693247</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.06399656914746225</v>
+        <v>0.8527175686213623</v>
       </c>
       <c r="BT2" t="n">
-        <v>2.076030336463424</v>
+        <v>-1.358683339439873</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.9271550272853821</v>
+        <v>-1.105743811434875</v>
       </c>
       <c r="BV2" t="n">
-        <v>1.667239746372771</v>
+        <v>-0.9375715170396854</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0.07124703187796592</v>
+        <v>-0.6732205102238157</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.8164991284900097</v>
+        <v>-0.4445689564350525</v>
       </c>
       <c r="BY2" t="n">
-        <v>-1.383329551263493</v>
+        <v>0.3058445816295443</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.5909288746499061</v>
+        <v>-0.7931411052618916</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4CLi9Djd</t>
+          <t>rcXrBZLq</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1755831547357415</v>
+        <v>-0.9338017825277449</v>
       </c>
       <c r="C3" t="n">
-        <v>1.814519506046163</v>
+        <v>0.3756951984568496</v>
       </c>
       <c r="D3" t="n">
-        <v>1.049450975946586</v>
+        <v>0.9355255587288207</v>
       </c>
       <c r="E3" t="n">
         <v>-0.193078397277103</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8927581732459091</v>
+        <v>1.915556443063057</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.912594387021969</v>
+        <v>-0.891515183517351</v>
       </c>
       <c r="H3" t="n">
-        <v>0.265218676113322</v>
+        <v>5.376613611419393</v>
       </c>
       <c r="I3" t="n">
-        <v>0.451697322801301</v>
+        <v>-3.255341503546603</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5142094646568566</v>
+        <v>-1.513018473721569</v>
       </c>
       <c r="K3" t="n">
-        <v>0.104886540194255</v>
+        <v>-0.3633078672631169</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3580355176473215</v>
+        <v>-0.8024681328266857</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5799909179787985</v>
+        <v>-0.191158995670376</v>
       </c>
       <c r="N3" t="n">
-        <v>1.223626034381941</v>
+        <v>-1.893253070731711</v>
       </c>
       <c r="O3" t="n">
-        <v>1.211994523981119</v>
+        <v>-1.507368763383549</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9285645137159854</v>
+        <v>-0.8832472937570154</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3805276459968847</v>
+        <v>-0.9386136895547483</v>
       </c>
       <c r="R3" t="n">
         <v>-1.030567431779406</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.009470648339543298</v>
+        <v>-0.3593115867277615</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9727661079065432</v>
+        <v>-0.001717612526071513</v>
       </c>
       <c r="U3" t="n">
-        <v>1.002945735441979</v>
+        <v>-0.4117516471572373</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.217355493249919</v>
+        <v>-0.4500114963638492</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.02087385647324174</v>
+        <v>0.4453646727651349</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.238373724524887</v>
+        <v>0.09633276711830488</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09957031308231888</v>
+        <v>-0.08073796424016545</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1.231803422959269</v>
+        <v>2.67962768203218</v>
       </c>
       <c r="AA3" t="n">
-        <v>-2.79060252292684</v>
+        <v>0.6420726629444031</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.07788914035595432</v>
+        <v>2.053684905581136</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.6071817943776909</v>
+        <v>0.5713877431256944</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.203496718894561</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.3244290964969024</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.1612410719199348</v>
+        <v>-0.3410631205501464</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.01699889331857178</v>
+        <v>-0.1095602138536794</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.6078811318460915</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.310365611811077</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1193136357175671</v>
+        <v>-0.4073191721184035</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.2529223696472696</v>
+        <v>-0.4675689874442458</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.158345792122602</v>
+        <v>-0.393683030317619</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.1306715160749591</v>
+        <v>-0.3700031337457507</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.3906690471072081</v>
+        <v>-0.577709393416236</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1.052904622877996</v>
+        <v>0.2835752221161652</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.5300632562691709</v>
+        <v>1.801501183720331</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.5300661454540342</v>
+        <v>-1.801463100857075</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.3599998344117394</v>
+        <v>0.1402407815822054</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.3600147557813234</v>
+        <v>-0.1402543594826434</v>
       </c>
       <c r="AT3" t="n">
-        <v>-2.069243687355359</v>
+        <v>2.654027418264313</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.007092193823406814</v>
+        <v>-1.332575862409359</v>
       </c>
       <c r="AV3" t="n">
-        <v>-1.527773250105875</v>
+        <v>0.01052318748966809</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.4540182212747259</v>
+        <v>-1.713409784720694</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.7706844178622821</v>
+        <v>-0.2245721746676093</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.346794238266383</v>
+        <v>-0.209895611430875</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.202053046831464</v>
+        <v>-0.4900840288299441</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.9056541763523229</v>
+        <v>-0.1631285784413092</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.1393004972612953</v>
+        <v>-2.291368909599301</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.4950045148272478</v>
+        <v>-3.415517199409096</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.04554309133768435</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>-1.05373265236705</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.3768358998385545</v>
+        <v>-0.1222734584534232</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.7135548140853232</v>
+        <v>0.9784844664564079</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.2707828575379491</v>
+        <v>0.1877129887461204</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.9835409267621519</v>
+        <v>0.7506754877942258</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.6692806453563351</v>
+        <v>0.431045719235964</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.342238620168932</v>
+        <v>0.3866427270198055</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.472521821674776</v>
+        <v>2.218739461643981</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.1934581301591484</v>
+        <v>0.3600621169416382</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.1098657520123151</v>
+        <v>2.929517997404923</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0.5209134624588349</v>
+        <v>2.049334942218567</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.1057008579962242</v>
+        <v>0.6548957005146118</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-0.2205164963923844</v>
+        <v>1.647200952602671</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0.04418064000854764</v>
+        <v>2.164147324853847</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.5257188900213324</v>
+        <v>0.571915296304029</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0.1128538579931708</v>
+        <v>2.227079893382953</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.1607211463212208</v>
+        <v>1.45275016281254</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.0684019892223104</v>
+        <v>2.288869703377163</v>
       </c>
       <c r="BW3" t="n">
-        <v>-0.03424609214092668</v>
+        <v>1.737169871166028</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0.02178416011972701</v>
+        <v>1.823894225813812</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.522842006524857</v>
+        <v>0.9102844309881237</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.03915853028770967</v>
+        <v>1.744569889565004</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Ug79dz7j</t>
+          <t>Y96v2dqT</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.9338017825277449</v>
+        <v>-0.08809638999051034</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3756951984568496</v>
+        <v>-0.9116739188599041</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9355255587288207</v>
+        <v>-1.627796328670905</v>
       </c>
       <c r="E4" t="n">
         <v>-0.193078397277103</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1300400965712384</v>
+        <v>4.643018495908784</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1295640199872675</v>
+        <v>-6.337270935541984</v>
       </c>
       <c r="H4" t="n">
-        <v>1.378398111566152</v>
+        <v>8.234413132671749</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.867033397372013</v>
+        <v>-6.354249436715055</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.824899695010558</v>
+        <v>2.073615571101799</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1829189414371499</v>
+        <v>1.119307756351893</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4712150595669959</v>
+        <v>2.269326543056635</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3240009466437116</v>
+        <v>-0.4973929613793059</v>
       </c>
       <c r="N4" t="n">
-        <v>0.000546891868989275</v>
+        <v>1.815438522694659</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02966265990952422</v>
+        <v>0.108484784180964</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.06539712155650547</v>
+        <v>2.305321651786875</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.06937519075795597</v>
+        <v>-0.7959280439755061</v>
       </c>
       <c r="R4" t="n">
-        <v>-2.048728555987971</v>
+        <v>2.023915940846287</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8651316976310026</v>
+        <v>0.3403702900486752</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3822985094884938</v>
+        <v>2.631526419070219</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9292000920319289</v>
+        <v>0.328825519936192</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.070427504667663</v>
+        <v>0.5581645171298485</v>
       </c>
       <c r="W4" t="n">
-        <v>1.455548152781618</v>
+        <v>-0.1762866995527007</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.9204585840723711</v>
+        <v>1.040550874975409</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6993036997952791</v>
+        <v>-0.4313964623542934</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.9677926859205859</v>
+        <v>-2.021172689642035</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.147939657710252</v>
+        <v>0.05558335186839508</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4543474297660609</v>
+        <v>-0.6971930452041913</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.4227838889789229</v>
+        <v>0.06527456241484471</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4116871334572335</v>
+        <v>2.237248122104406</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.9996820501502441</v>
+        <v>-1.11889578448519</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1.082649449411731</v>
+        <v>1.627876599183165</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.5926139383859851</v>
+        <v>-0.2624869864309478</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.2431192457453176</v>
+        <v>0.9988813053340363</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.8292265234689363</v>
+        <v>-0.8307033313114489</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.4358364224335446</v>
+        <v>1.643572302292974</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.5274218571419582</v>
+        <v>-0.4805881753167625</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.361303407364785</v>
+        <v>1.385180773863865</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9104210207929838</v>
+        <v>-0.7409671411354772</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.328591125768641</v>
+        <v>1.375625080517812</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.7421047109270681</v>
+        <v>0.1489629527062998</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.604450586687248</v>
+        <v>1.801501183720331</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.6044111378286789</v>
+        <v>-1.801463100857075</v>
       </c>
       <c r="AR4" t="n">
-        <v>-2.612640587250319</v>
+        <v>0.4130145273293763</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.612643838741588</v>
+        <v>-0.4130297727975732</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.4399940875050921</v>
+        <v>-1.036028133001056</v>
       </c>
       <c r="AU4" t="n">
-        <v>-1.034871849913189</v>
+        <v>1.049056237560002</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.08018323116841557</v>
+        <v>-1.775179788756362</v>
       </c>
       <c r="AW4" t="n">
-        <v>-1.047007090155092</v>
+        <v>0.1031506892036964</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>-1.862908904251628</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.902754898872546</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.6476383500640527</v>
+        <v>0.02837173876732031</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0.106126831518982</v>
+        <v>0.121880156170326</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.1492050528990759</v>
+        <v>-0.2713709709741701</v>
       </c>
       <c r="BC4" t="n">
-        <v>-0.3603057691985037</v>
+        <v>-0.3182166898176655</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.8479328577516209</v>
+        <v>0.7666445939099694</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.7419717606586362</v>
+        <v>-2.89828328524304</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.4469034850036173</v>
+        <v>-0.115449968714235</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.6118202829366391</v>
+        <v>-1.387540138889959</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.416960911888155</v>
+        <v>-0.2707828575379491</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.68213724366593</v>
+        <v>-0.6465171460133313</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-0.8862247458531354</v>
+        <v>-0.6120591509592433</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0.0455444627829325</v>
+        <v>-2.230400789712139</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0.2727934148367125</v>
+        <v>0.07752805547579052</v>
       </c>
       <c r="BM4" t="n">
-        <v>-0.308633155892868</v>
+        <v>1.189290880717879</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0.6866584121394217</v>
+        <v>1.203884272792868</v>
       </c>
       <c r="BO4" t="n">
-        <v>-0.6951422899040191</v>
+        <v>-0.04746693917554533</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.1593157541548807</v>
+        <v>0.2043986556384593</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-1.111792555841076</v>
+        <v>0.4913806151672535</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0.8615897166366577</v>
+        <v>0.8614752534725191</v>
       </c>
       <c r="BS4" t="n">
-        <v>-0.6600526823078273</v>
+        <v>1.049986971144224</v>
       </c>
       <c r="BT4" t="n">
-        <v>-0.7357945564590189</v>
+        <v>0.7876399234148812</v>
       </c>
       <c r="BU4" t="n">
-        <v>-0.9015181518998409</v>
+        <v>1.101888540347094</v>
       </c>
       <c r="BV4" t="n">
-        <v>-0.9365297934381582</v>
+        <v>0.9283042709535084</v>
       </c>
       <c r="BW4" t="n">
-        <v>-0.4482492755068878</v>
+        <v>0.4608492347460389</v>
       </c>
       <c r="BX4" t="n">
-        <v>-0.7095341096777973</v>
+        <v>0.1349054454124502</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.133263073520326</v>
+        <v>-0.9555729761208542</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-1.006122259764766</v>
+        <v>1.2131149394904</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fB59P6ff</t>
+          <t>0b5fTYsS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.08809638999051034</v>
+        <v>0.2035261591602602</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.547785718004653</v>
+        <v>-0.1998345245788756</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.627796328670905</v>
+        <v>-0.4315794478843663</v>
       </c>
       <c r="E5" t="n">
         <v>-0.193078397277103</v>
@@ -1551,639 +1551,639 @@
         <v>2.597421956274489</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.231874918018891</v>
+        <v>-3.274033325028127</v>
       </c>
       <c r="H5" t="n">
-        <v>4.629563582413122</v>
+        <v>5.311082907120597</v>
       </c>
       <c r="I5" t="n">
-        <v>-4.358185554385106</v>
+        <v>-5.478020199844369</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1095529779211208</v>
+        <v>-0.4214341992101092</v>
       </c>
       <c r="K5" t="n">
-        <v>1.197340157594788</v>
+        <v>-2.158053095849708</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5177367738768051</v>
+        <v>0.7081874811524103</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3527578812226481</v>
+        <v>-0.8927697994592522</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.275632269343613</v>
+        <v>-0.8674447576563316</v>
       </c>
       <c r="O5" t="n">
-        <v>1.211994523981119</v>
+        <v>-0.3250368993119542</v>
       </c>
       <c r="P5" t="n">
-        <v>1.049819454221823</v>
+        <v>0.2490569580625178</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.7310342201099161</v>
+        <v>-0.2124696960539612</v>
       </c>
       <c r="R5" t="n">
-        <v>1.005754816637722</v>
+        <v>0.1572872131305852</v>
       </c>
       <c r="S5" t="n">
-        <v>1.040052166825112</v>
+        <v>-2.283436747862962</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5999383810347021</v>
+        <v>1.351564978338518</v>
       </c>
       <c r="U5" t="n">
-        <v>0.443622416139113</v>
+        <v>0.00585737585211199</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7908205202437788</v>
+        <v>0.1704045119399647</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1762866995527007</v>
+        <v>-0.3316995426321594</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6030050675421331</v>
+        <v>0.7651149725641357</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.3746092444568376</v>
+        <v>-0.4744070348790028</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.8428559464009913</v>
+        <v>0.8525941142146516</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.8484006153804091</v>
+        <v>0.1477309630100428</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3582100425361461</v>
+        <v>0.2777471021607614</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.03273099807871632</v>
+        <v>-0.7679563779960898</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.797353907972557</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1.979568029805835</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.9458246735120551</v>
+        <v>1.125718019134562</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.6710804276717935</v>
+        <v>-1.117512087623424</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.2628809787684932</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1.504298054990446</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.7853480590865541</v>
+        <v>0.4439779015235248</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.09629819916847086</v>
+        <v>-0.344604759129319</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.01508159312812</v>
+        <v>-0.250418831323137</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.5514235942867967</v>
+        <v>-1.243563538244139</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.546739740417536</v>
+        <v>0.8102419549385461</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.5708546018191054</v>
+        <v>-0.8870611433552944</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.7218140876827397</v>
+        <v>0.1584121697834477</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.7217708567889597</v>
+        <v>-0.1584270354131455</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.7177901143645552</v>
+        <v>1.884808353819818</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.7177817819273649</v>
+        <v>-1.88483259691323</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.5875963095557069</v>
+        <v>-0.1504148006973671</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.197908243808087</v>
+        <v>0.6025002188157471</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.1434465751961802</v>
+        <v>-0.4508271406861097</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.8631967308361784</v>
+        <v>1.248985834506651</v>
       </c>
       <c r="AX5" t="n">
-        <v>-1.862908904251628</v>
+        <v>0.1030951712491944</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.3210877435521076</v>
+        <v>-0.09870347930964227</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.2884623414310081</v>
+        <v>-0.9797366982273608</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.361668151730939</v>
+        <v>-0.006373774404909899</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.4459706230451409</v>
+        <v>2.335347044172118</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.3923623930240713</v>
+        <v>3.397673587294291</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.857542306206655</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.4634501521821301</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.4498086297109261</v>
+        <v>0.7635034514565208</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.4337360464820482</v>
+        <v>1.219766303650119</v>
       </c>
       <c r="BH5" t="n">
-        <v>-1.187774550106088</v>
+        <v>1.104704681314259</v>
       </c>
       <c r="BI5" t="n">
         <v>-0.6465171460133313</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.5109603051272273</v>
+        <v>0.005076048275092397</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.7646975279930578</v>
+        <v>-0.802873643574546</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.2110480665633194</v>
+        <v>-2.793611040436429</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.6958313231344077</v>
+        <v>-0.9125152363331198</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.873330289164734</v>
+        <v>-0.09957567350960544</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.3020891113006994</v>
+        <v>-0.5205771775137636</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.2819986975618585</v>
+        <v>-0.05853833770136784</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.2872334178001691</v>
+        <v>-0.1411414014034193</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.03284106131271645</v>
+        <v>-0.1707334174784613</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.8819941546517621</v>
+        <v>-0.3480028003671512</v>
       </c>
       <c r="BT5" t="n">
-        <v>-1.225773590800219</v>
+        <v>-0.07392011097954973</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.2159822401357954</v>
+        <v>-0.1709291148374902</v>
       </c>
       <c r="BV5" t="n">
-        <v>-1.709488705771597</v>
+        <v>0.08093652993953095</v>
       </c>
       <c r="BW5" t="n">
-        <v>-1.16836280707291</v>
+        <v>0.002544371612472152</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.1595286633059247</v>
+        <v>-0.04381048717633469</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.2605061966873987</v>
+        <v>-0.2798406147467206</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.5672003528888473</v>
+        <v>-0.3849327024222857</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jwaINpP6</t>
+          <t>IFm4IHT9</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2618506689904143</v>
+        <v>0.05771488458487495</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8452062883017833</v>
+        <v>0.01220274180270737</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3603760621232627</v>
+        <v>-1.314501431322049</v>
       </c>
       <c r="E6" t="n">
         <v>-0.193078397277103</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.857502149416966</v>
+        <v>-5.584964202262692</v>
       </c>
       <c r="G6" t="n">
-        <v>3.533161365002662</v>
+        <v>2.852441895999584</v>
       </c>
       <c r="H6" t="n">
-        <v>8.915271643554362</v>
+        <v>-7.591912769312289</v>
       </c>
       <c r="I6" t="n">
-        <v>-5.027769442394195</v>
+        <v>7.320145198244029</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6701500753013505</v>
+        <v>-1.590988779043816</v>
       </c>
       <c r="K6" t="n">
-        <v>1.431437361323474</v>
+        <v>-0.05117826229153585</v>
       </c>
       <c r="L6" t="n">
-        <v>1.180254703205829</v>
+        <v>-1.823363683048631</v>
       </c>
       <c r="M6" t="n">
-        <v>0.176382015805172</v>
+        <v>1.269396134899122</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6318135460692219</v>
+        <v>-2.4061572272694</v>
       </c>
       <c r="O6" t="n">
-        <v>1.409049834659718</v>
+        <v>2.039626828831235</v>
       </c>
       <c r="P6" t="n">
-        <v>1.345808642057142</v>
+        <v>-1.407921612928166</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2826930655073507</v>
+        <v>1.472955126537275</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8360612959362946</v>
+        <v>-2.388115597390825</v>
       </c>
       <c r="S6" t="n">
-        <v>1.739734043601548</v>
+        <v>-1.233913932698307</v>
       </c>
       <c r="T6" t="n">
-        <v>0.843580053465812</v>
+        <v>-2.839472843727486</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0213809588410127</v>
+        <v>0.9890176318158264</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4500114963638492</v>
+        <v>-1.070427504667663</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9116032020035115</v>
+        <v>0.7561903589240527</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4381355094677126</v>
+        <v>-2.368221385560565</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.1011456920329899</v>
+        <v>2.168647143591152</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.8442314303163159</v>
+        <v>1.491661376986113</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.1314199843273924</v>
+        <v>-1.528752959586087</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6667943523795914</v>
+        <v>1.005909209974455</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.342862831387109</v>
+        <v>-1.174167428914968</v>
       </c>
       <c r="AD6" t="n">
-        <v>-2.865524761825039</v>
+        <v>-3.657334347262367</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.279656158575819</v>
+        <v>1.838285776360103</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0718865125102716</v>
+        <v>-1.148985359327639</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.7402315731768302</v>
+        <v>0.4882658566765367</v>
       </c>
       <c r="AH6" t="n">
-        <v>-1.577119837645364</v>
+        <v>-2.635120307083332</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.970295466591462</v>
+        <v>1.382536475062398</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.145199518863976</v>
+        <v>-1.250785682255625</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.3888098944224508</v>
+        <v>0.5018446439925581</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.5614116296455941</v>
+        <v>0.1077416661630678</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1.052098244107506</v>
+        <v>1.269418447299171</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.6148957502879738</v>
+        <v>0.8688086311424776</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1.218369929232167</v>
+        <v>1.725097292663126</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.3306024176977681</v>
+        <v>-3.127765858090318</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.3305717935880238</v>
+        <v>3.127645095474714</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.713386374045527</v>
+        <v>-2.872095786844278</v>
       </c>
       <c r="AS6" t="n">
-        <v>-1.713409569172369</v>
+        <v>2.87210062448206</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.4399940875050921</v>
+        <v>-0.1504148006973671</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.1417598124246783</v>
+        <v>0.1559442000714918</v>
       </c>
       <c r="AV6" t="n">
-        <v>-1.739835997520578</v>
+        <v>0.7217551097246008</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.5266115037721798</v>
+        <v>-0.1281514364009368</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.3215400685270635</v>
+        <v>-0.4066095890658336</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.3210877435521076</v>
+        <v>-1.062368624360326</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.2884623414310081</v>
+        <v>-0.0004313594325276169</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.03487464786607332</v>
+        <v>0.3356367071290524</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.3968645839503347</v>
+        <v>0.7263388027849087</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.03318312217231979</v>
+        <v>0.8453273623760026</v>
       </c>
       <c r="BD6" t="n">
-        <v>-1.120426050769305</v>
+        <v>-1.682717068837148</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.270434324854282</v>
+        <v>0.6759063134618456</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.3632655744944128</v>
+        <v>-0.2886806912756892</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.01090363800330628</v>
+        <v>-0.1635099986745803</v>
       </c>
       <c r="BH6" t="n">
-        <v>-2.104766242674227</v>
+        <v>1.563200527598329</v>
       </c>
       <c r="BI6" t="n">
-        <v>-1.112248023949184</v>
+        <v>2.147868121601783</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.6194469241086026</v>
+        <v>-0.4496551511607337</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.6383309146379874</v>
+        <v>3.222871160100274</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.1327402370593509</v>
+        <v>0.1227553291779954</v>
       </c>
       <c r="BM6" t="n">
-        <v>-1.168872919513523</v>
+        <v>1.076781615062302</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.7732912221819292</v>
+        <v>-3.99754402857821</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.6383831768114635</v>
+        <v>-2.711569989965643</v>
       </c>
       <c r="BP6" t="n">
-        <v>1.874229842342994</v>
+        <v>-2.076808528611301</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.1729604285863885</v>
+        <v>-2.027379676590062</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.2883848145003069</v>
+        <v>-2.647442698487749</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.1835862561332074</v>
+        <v>-0.379564223517124</v>
       </c>
       <c r="BT6" t="n">
-        <v>1.450328854571415</v>
+        <v>-3.741142035009838</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.1749539200881468</v>
+        <v>-2.707954424123383</v>
       </c>
       <c r="BV6" t="n">
-        <v>2.453610850075878</v>
+        <v>-4.825581633255207</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.869503899822435</v>
+        <v>-3.574585301763964</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.3363708675903912</v>
+        <v>-2.193795491641211</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.8324229294080131</v>
+        <v>-1.655312110348721</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.8683019149103564</v>
+        <v>-3.417708979431416</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>xY3xTu1n</t>
+          <t>WIDwXGr3</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.1755831547357415</v>
+        <v>-0.6130169784618973</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.047983590105207</v>
+        <v>-1.547785718004653</v>
       </c>
       <c r="D7" t="n">
-        <v>1.049450975946586</v>
+        <v>0.2519730554222272</v>
       </c>
       <c r="E7" t="n">
         <v>-0.193078397277103</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2108926600344777</v>
+        <v>2.597421956274489</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5511554490158118</v>
+        <v>-1.231874918018891</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.66990156942974</v>
+        <v>2.89415634268854</v>
       </c>
       <c r="I7" t="n">
-        <v>4.062816519517454</v>
+        <v>-2.088396573002503</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1095529779211208</v>
+        <v>1.449853128523822</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.09019446291298334</v>
+        <v>1.353404960080579</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.565204749593494</v>
+        <v>1.522694817798093</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2620776808504022</v>
+        <v>1.185462850180047</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.557892660687836</v>
+        <v>0.3161802189691056</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2659203061083745</v>
+        <v>0.1478958463166837</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.341331408580339</v>
+        <v>0.5048680174244224</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6263542080806678</v>
+        <v>1.030728573861344</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4966742545334401</v>
+        <v>1.17544833733915</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.146453698101253</v>
+        <v>0.3403702900486752</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8768008668671909</v>
+        <v>1.122752803126459</v>
       </c>
       <c r="U7" t="n">
-        <v>0.745908913977526</v>
+        <v>0.1533314142466691</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7132685192058019</v>
+        <v>0.1704045119399647</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.186470179569183</v>
+        <v>0.1345389866062172</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.7774758906761233</v>
+        <v>0.6827196171419604</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.657205472748367</v>
+        <v>-0.4935228448899845</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.9046164317455212</v>
+        <v>-0.4795060912956393</v>
       </c>
       <c r="AA7" t="n">
-        <v>-1.324705842453175</v>
+        <v>-0.4472320984824059</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9659978865370715</v>
+        <v>0.6996328048206804</v>
       </c>
       <c r="AC7" t="n">
-        <v>-1.24165226445861</v>
+        <v>-0.5871774718664917</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.313470272427523</v>
+        <v>-0.6660536911657959</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.367930235018962</v>
+        <v>-1.95749951069505</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.2634843539680486</v>
+        <v>-0.04386585203059967</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.9660475189446713</v>
+        <v>0.1666747279972349</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.4731193477970498</v>
+        <v>-0.7951194906694748</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.430650383896612</v>
+        <v>-0.4457920606377364</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.7004936077776891</v>
+        <v>-0.2007112539564736</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.05772512223145513</v>
+        <v>0.3084546553974687</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.6091663626437541</v>
+        <v>-0.8951077267983056</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.3580365528622113</v>
+        <v>-0.6931008176013191</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.4408205630438257</v>
+        <v>-1.297538635215637</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.784537603996262</v>
+        <v>-0.4124371938524935</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.2659953790293147</v>
+        <v>1.801501183720331</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.2660067777934025</v>
+        <v>-1.801463100857075</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.2765354700199176</v>
+        <v>-0.5971482824903627</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.2765498811406772</v>
+        <v>0.5971392125246074</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.3661929764797845</v>
+        <v>0.2923918654544772</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.216185815548721</v>
+        <v>0.6025002188157471</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.7380850753009199</v>
+        <v>-0.2170235065616638</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.2529963543216925</v>
+        <v>-1.073206169552669</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.6146523483780899</v>
+        <v>-1.20757421241802</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.6319876746298871</v>
+        <v>1.013217841902685</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.3740089171654966</v>
+        <v>-0.6340995198291843</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.6776471886630147</v>
+        <v>-0.8043982313174884</v>
       </c>
       <c r="BB7" t="n">
-        <v>-2.33521249326231</v>
+        <v>-0.09102278439397789</v>
       </c>
       <c r="BC7" t="n">
-        <v>-1.973528291220233</v>
+        <v>-0.2558122530241582</v>
       </c>
       <c r="BD7" t="n">
-        <v>-2.275831438340352</v>
+        <v>0.3244323297452965</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.261174391884083</v>
+        <v>0.591792039962583</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.2162610273495087</v>
+        <v>-0.05804047512575159</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.1445856052079675</v>
+        <v>1.259270063479941</v>
       </c>
       <c r="BH7" t="n">
         <v>-0.2707828575379491</v>
@@ -2192,4101 +2192,5291 @@
         <v>-0.6465171460133313</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-1.204007594480146</v>
+        <v>0.5854457462784461</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.4371893723618338</v>
+        <v>-1.885163898323777</v>
       </c>
       <c r="BL7" t="n">
-        <v>2.137614336838829</v>
+        <v>-0.5963470295420045</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.1532857974199902</v>
+        <v>1.271544276285036</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.2767480333138714</v>
+        <v>2.267664083113391</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.8905590956565738</v>
+        <v>0.1920510019104789</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.06067770825826625</v>
+        <v>-0.9137340503467528</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.5903426341193927</v>
+        <v>1.155470919073376</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.3507294596515902</v>
+        <v>1.101640545922399</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0.2438728820478834</v>
+        <v>0.07365085862282077</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.6290460931499693</v>
+        <v>1.886223522245064</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.4753171938339037</v>
+        <v>0.9574340053183805</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.2934481446511506</v>
+        <v>1.814234387431176</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.7194656902962521</v>
+        <v>-0.2630779005276015</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.6436950432009093</v>
+        <v>0.7060541746501593</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.5697029002252847</v>
+        <v>-1.464213182924009</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.4157160686638761</v>
+        <v>0.6152479436550911</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OjcQLOgJ</t>
+          <t>4CLi9Djd</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.137937566933284</v>
+        <v>-0.1755831547357415</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01220274180270737</v>
+        <v>1.814519506046163</v>
       </c>
       <c r="D8" t="n">
-        <v>1.490911967665428</v>
+        <v>1.049450975946586</v>
       </c>
       <c r="E8" t="n">
         <v>-0.193078397277103</v>
       </c>
       <c r="F8" t="n">
-        <v>6.688615035543079</v>
+        <v>0.8927581732459091</v>
       </c>
       <c r="G8" t="n">
-        <v>-9.400508546055839</v>
+        <v>-1.912594387021969</v>
       </c>
       <c r="H8" t="n">
-        <v>5.115426947142764</v>
+        <v>0.265218676113322</v>
       </c>
       <c r="I8" t="n">
-        <v>-5.904605486215623</v>
+        <v>0.451697322801301</v>
       </c>
       <c r="J8" t="n">
-        <v>1.683764044490563</v>
+        <v>0.5142094646568566</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.611826287149441</v>
+        <v>0.104886540194255</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9275134363149382</v>
+        <v>0.3580355176473215</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7953589280140587</v>
+        <v>0.5799909179787985</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5134510484066785</v>
+        <v>1.223626034381941</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.625601949790708</v>
+        <v>1.211994523981119</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2393798807823731</v>
+        <v>0.9285645137159854</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.280941194977544</v>
+        <v>0.3805276459968847</v>
       </c>
       <c r="R8" t="n">
-        <v>1.17544833733915</v>
+        <v>-1.030567431779406</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.933595809474744</v>
+        <v>-0.009470648339543298</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1778982941338998</v>
+        <v>-0.9727661079065432</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6027656397444733</v>
+        <v>1.002945735441979</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7214445326995</v>
+        <v>-0.217355493249919</v>
       </c>
       <c r="W8" t="n">
-        <v>-2.041240816506207</v>
+        <v>-0.02087385647324174</v>
       </c>
       <c r="X8" t="n">
-        <v>0.9605096725652952</v>
+        <v>-0.238373724524887</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.7468073275354932</v>
+        <v>0.09957031308231888</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.6720377841115495</v>
+        <v>-1.231803422959269</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.931111199418598</v>
+        <v>-2.79060252292684</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.7418896764765541</v>
+        <v>-0.07788914035595432</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.2678745380889304</v>
+        <v>-0.6071817943776909</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.203496718894561</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>-0.3244290964969024</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.578346125955441</v>
+        <v>-0.1612410719199348</v>
       </c>
       <c r="AG8" t="n">
-        <v>-1.467859883404796</v>
+        <v>0.01699889331857178</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>0.6078811318460915</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.310365611811077</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.133582432677136</v>
+        <v>0.1193136357175671</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0.9586772385441946</v>
+        <v>0.2529223696472696</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.803034687597771</v>
+        <v>1.158345792122602</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.09669352071229317</v>
+        <v>-0.1306715160749591</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.044907072517564</v>
+        <v>0.3906690471072081</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.342479313423367</v>
+        <v>-1.052904622877996</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.9212749262541434</v>
+        <v>0.5300632562691709</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.9212652086549701</v>
+        <v>-0.5300661454540342</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.827331188596538</v>
+        <v>0.3599998344117394</v>
       </c>
       <c r="AS8" t="n">
-        <v>-1.827355080310577</v>
+        <v>-0.3600147557813234</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0.002812578646752469</v>
+        <v>-2.069243687355359</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.3047962063195767</v>
+        <v>0.007092193823406814</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.8690704076485403</v>
+        <v>-1.527773250105875</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.3354695274483507</v>
+        <v>0.4540182212747259</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.777839383712858</v>
+        <v>-0.7706844178622821</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.02457539122882023</v>
+        <v>1.346794238266383</v>
       </c>
       <c r="AZ8" t="n">
         <v>-0.202053046831464</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.3071358336678889</v>
+        <v>0.9056541763523229</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.07514071335406437</v>
+        <v>-0.1393004972612953</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.5197211462574753</v>
+        <v>0.4950045148272478</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>-0.04554309133768435</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>-1.05373265236705</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.5566047447901808</v>
+        <v>0.3768358998385545</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.2699645358395943</v>
+        <v>-0.7135548140853232</v>
       </c>
       <c r="BH8" t="n">
         <v>-0.2707828575379491</v>
       </c>
       <c r="BI8" t="n">
-        <v>-1.112248023949184</v>
+        <v>0.9835409267621519</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.9084569356649282</v>
+        <v>-0.6692806453563351</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0.2411787012363377</v>
+        <v>1.342238620168932</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.001646091719741389</v>
+        <v>-0.4733103558275309</v>
       </c>
       <c r="BM8" t="n">
-        <v>-1.045310378705022</v>
+        <v>-0.1934581301591484</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.79850279086091</v>
+        <v>0.1098657520123151</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.602230246034963</v>
+        <v>-0.5209134624588349</v>
       </c>
       <c r="BP8" t="n">
-        <v>-0.1175819669548527</v>
+        <v>-0.1057008579962242</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.599983733491037</v>
+        <v>-0.2205164963923844</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.4890311475020379</v>
+        <v>-0.04418064000854764</v>
       </c>
       <c r="BS8" t="n">
-        <v>-0.6294184633851228</v>
+        <v>-0.5257188900213324</v>
       </c>
       <c r="BT8" t="n">
-        <v>1.254010023964715</v>
+        <v>-0.1128538579931708</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.482235480468085</v>
+        <v>0.1607211463212208</v>
       </c>
       <c r="BV8" t="n">
-        <v>1.770872642517591</v>
+        <v>-0.0684019892223104</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.201509106112881</v>
+        <v>-0.03424609214092668</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.2983945002976939</v>
+        <v>-0.02178416011972701</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.4589533152129093</v>
+        <v>-0.522842006524857</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.454248323739909</v>
+        <v>-0.03915853028770967</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jeAhPc0B</t>
+          <t>Ug79dz7j</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.662858155404671</v>
+        <v>-0.9338017825277449</v>
       </c>
       <c r="C9" t="n">
-        <v>1.572191201610068</v>
+        <v>0.3756951984568496</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3888574164277042</v>
+        <v>0.9355255587288207</v>
       </c>
       <c r="E9" t="n">
         <v>-0.193078397277103</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.152838366388386</v>
+        <v>-0.1300400965712384</v>
       </c>
       <c r="G9" t="n">
-        <v>2.171722426996504</v>
+        <v>0.1295640199872675</v>
       </c>
       <c r="H9" t="n">
-        <v>4.580633989870019</v>
+        <v>1.378398111566152</v>
       </c>
       <c r="I9" t="n">
-        <v>-5.225143516572039</v>
+        <v>-1.867033397372013</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04638763272337356</v>
+        <v>-1.824899695010558</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8852105526232072</v>
+        <v>0.1829189414371499</v>
       </c>
       <c r="L9" t="n">
-        <v>1.581951303929723</v>
+        <v>-0.4712150595669959</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3329049456466711</v>
+        <v>0.3240009466437116</v>
       </c>
       <c r="N9" t="n">
-        <v>1.08553645377564</v>
+        <v>0.000546891868989275</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1478958463166837</v>
+        <v>0.02966265990952422</v>
       </c>
       <c r="P9" t="n">
-        <v>1.573342353714164</v>
+        <v>-0.06539712155650547</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.6316993743481049</v>
+        <v>-0.06937519075795597</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1572872131305852</v>
+        <v>-2.048728555987971</v>
       </c>
       <c r="S9" t="n">
-        <v>2.439415920377985</v>
+        <v>0.8651316976310026</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8215219596654645</v>
+        <v>-0.3822985094884938</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8107379054010728</v>
+        <v>0.9292000920319289</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.078603518161361</v>
+        <v>-1.070427504667663</v>
       </c>
       <c r="W9" t="n">
-        <v>2.310318789718641</v>
+        <v>1.455548152781618</v>
       </c>
       <c r="X9" t="n">
-        <v>0.06805026569253049</v>
+        <v>-0.9204585840723711</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.2268572952367886</v>
+        <v>0.6993036997952791</v>
       </c>
       <c r="Z9" t="n">
-        <v>-1.44804803176261</v>
+        <v>0.9677926859205859</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.7922580661956421</v>
+        <v>1.147939657710252</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.4941287782556156</v>
+        <v>0.4543474297660609</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.3927431027870387</v>
+        <v>0.4227838889789229</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.1821700556207624</v>
+        <v>0.4116871334572335</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.3464976156076882</v>
+        <v>0.9996820501502441</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.695522732794807</v>
+        <v>-1.082649449411731</v>
       </c>
       <c r="AG9" t="n">
-        <v>-1.288525582267004</v>
+        <v>0.5926139383859851</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.1971192253349712</v>
+        <v>-0.2431192457453176</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.5660768327232716</v>
+        <v>0.8292265234689363</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.693152768495922</v>
+        <v>-0.4358364224335446</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.9813692079946688</v>
+        <v>0.5274218571419582</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.5852889961446741</v>
+        <v>1.361303407364785</v>
       </c>
       <c r="AM9" t="n">
-        <v>-3.218049384028169</v>
+        <v>0.9104210207929838</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.01841119636358518</v>
+        <v>1.328591125768641</v>
       </c>
       <c r="AO9" t="n">
-        <v>-1.98331534234165</v>
+        <v>0.7421047109270681</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.508092431231602</v>
+        <v>-0.604450586687248</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.508063803456374</v>
+        <v>0.6044111378286789</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.237293183739159</v>
+        <v>-2.612640587250319</v>
       </c>
       <c r="AS9" t="n">
-        <v>-1.23731346833056</v>
+        <v>2.612643838741588</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.2923918654544772</v>
+        <v>0.4399940875050921</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.6025002188157471</v>
+        <v>-1.034871849913189</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.1279794169634325</v>
+        <v>0.08018323116841557</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.521851172835317</v>
+        <v>-1.047007090155092</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.8416469668077043</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.5328822809258842</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-1.109350640126677</v>
+        <v>0.6476383500640527</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.3498871438596342</v>
+        <v>-0.106126831518982</v>
       </c>
       <c r="BB9" t="n">
-        <v>2.131717955603921</v>
+        <v>0.1492050528990759</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.770045486304225</v>
+        <v>-0.3603057691985037</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.591838703122462</v>
+        <v>-0.8479328577516209</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.2642849091889334</v>
+        <v>-0.7419717606586362</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.395808401768399</v>
+        <v>-0.4469034850036173</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.2604522784823988</v>
+        <v>0.6118202829366391</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.9585266269640533</v>
+        <v>0.416960911888155</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.2849446098583733</v>
+        <v>1.68213724366593</v>
       </c>
       <c r="BJ9" t="n">
-        <v>-0.4710371926661206</v>
+        <v>-0.8862247458531354</v>
       </c>
       <c r="BK9" t="n">
-        <v>-0.8047916263044813</v>
+        <v>-0.0455444627829325</v>
       </c>
       <c r="BL9" t="n">
-        <v>-2.214320147284549</v>
+        <v>-0.2733875631559007</v>
       </c>
       <c r="BM9" t="n">
-        <v>-0.09748063137600475</v>
+        <v>-0.308633155892868</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.2392955820943836</v>
+        <v>-0.6866584121394217</v>
       </c>
       <c r="BO9" t="n">
-        <v>-0.05965363259382422</v>
+        <v>-0.6951422899040191</v>
       </c>
       <c r="BP9" t="n">
-        <v>-0.6091532133137959</v>
+        <v>-0.1593157541548807</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.1405812521376459</v>
+        <v>-1.111792555841076</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.1018255421023101</v>
+        <v>-0.8615897166366577</v>
       </c>
       <c r="BS9" t="n">
-        <v>-0.5239884697230311</v>
+        <v>-0.6600526823078273</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0.01246772496552436</v>
+        <v>-0.7357945564590189</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.8945474223896835</v>
+        <v>-0.9015181518998409</v>
       </c>
       <c r="BV9" t="n">
-        <v>-0.03156961902544374</v>
+        <v>-0.9365297934381582</v>
       </c>
       <c r="BW9" t="n">
-        <v>-0.1386212056838056</v>
+        <v>-0.4482492755068878</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.005685567568068622</v>
+        <v>-0.7095341096777973</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.2118380202722731</v>
+        <v>1.133263073520326</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.5730785322742703</v>
+        <v>-1.006122259764766</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OMVUWl2K</t>
+          <t>fB59P6ff</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1755831547357415</v>
+        <v>-0.08809638999051034</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.9116739188599041</v>
+        <v>-1.547785718004653</v>
       </c>
       <c r="D10" t="n">
-        <v>1.049450975946586</v>
+        <v>-1.627796328670905</v>
       </c>
       <c r="E10" t="n">
         <v>-0.193078397277103</v>
       </c>
       <c r="F10" t="n">
-        <v>3.961152982697352</v>
+        <v>2.597421956274489</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.954752794031207</v>
+        <v>-1.231874918018891</v>
       </c>
       <c r="H10" t="n">
-        <v>7.267642506898926</v>
+        <v>4.629563582413122</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.508115139952967</v>
+        <v>-4.358185554385106</v>
       </c>
       <c r="J10" t="n">
-        <v>1.76173434981281</v>
+        <v>-0.1095529779211208</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2072430647773262</v>
+        <v>1.197340157594788</v>
       </c>
       <c r="L10" t="n">
-        <v>1.878695473440848</v>
+        <v>0.5177367738768051</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1093509706795085</v>
+        <v>0.3527578812226481</v>
       </c>
       <c r="N10" t="n">
-        <v>1.065809370831883</v>
+        <v>-0.275632269343613</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6797364585334322</v>
+        <v>1.211994523981119</v>
       </c>
       <c r="P10" t="n">
-        <v>1.690661290165701</v>
+        <v>1.049819454221823</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2952740672946681</v>
+        <v>-0.7310342201099161</v>
       </c>
       <c r="R10" t="n">
-        <v>1.345141858040577</v>
+        <v>1.005754816637722</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6902112284368933</v>
+        <v>1.040052166825112</v>
       </c>
       <c r="T10" t="n">
-        <v>2.020832336426317</v>
+        <v>0.5999383810347021</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1593006015150202</v>
+        <v>0.443622416139113</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4806125160918717</v>
+        <v>0.7908205202437788</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.4871123857116184</v>
+        <v>-0.1762866995527007</v>
       </c>
       <c r="X10" t="n">
-        <v>1.275671907055117</v>
+        <v>0.6030050675421331</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.9651457200046757</v>
+        <v>-0.3746092444568376</v>
       </c>
       <c r="Z10" t="n">
-        <v>-1.169083005946753</v>
+        <v>0.8428559464009913</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.08179167723786308</v>
+        <v>-0.8484006153804091</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.03593304461717602</v>
+        <v>0.3582100425361461</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.08931838804511032</v>
+        <v>-0.03273099807871632</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.225491429601154</v>
+        <v>1.797353907972557</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.01546982894590157</v>
+        <v>-1.979568029805835</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.8198055420804815</v>
+        <v>0.9458246735120551</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.160428387911455</v>
+        <v>-0.6710804276717935</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.3088809991788396</v>
+        <v>0.2628809787684932</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.5405430704636519</v>
+        <v>-1.504298054990446</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.417966561259231</v>
+        <v>0.7853480590865541</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.07034014603769237</v>
+        <v>-0.09629819916847086</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.444874190111566</v>
+        <v>1.01508159312812</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1.746159935352801</v>
+        <v>0.5514235942867967</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.3642941221772744</v>
+        <v>1.546739740417536</v>
       </c>
       <c r="AO10" t="n">
-        <v>-1.323705701789912</v>
+        <v>0.5708546018191054</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.173152270206054</v>
+        <v>-0.7218140876827397</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-2.173102210897964</v>
+        <v>0.7217708567889597</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.773302466884302</v>
+        <v>-0.7177901143645552</v>
       </c>
       <c r="AS10" t="n">
-        <v>-1.773326028300591</v>
+        <v>0.7177817819273649</v>
       </c>
       <c r="AT10" t="n">
-        <v>-2.216845909405973</v>
+        <v>0.5875963095557069</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.6025002188157471</v>
+        <v>1.197908243808087</v>
       </c>
       <c r="AV10" t="n">
-        <v>-1.855168368921557</v>
+        <v>-0.1434465751961802</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.3203101253647863</v>
+        <v>-0.8631967308361784</v>
       </c>
       <c r="AX10" t="n">
-        <v>-1.134759246658731</v>
+        <v>-1.862908904251628</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.161474018064329</v>
+        <v>-0.3210877435521076</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0.3460685378307039</v>
+        <v>-0.2884623414310081</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.5066419478960335</v>
+        <v>1.361668151730939</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0.3253234481393124</v>
+        <v>0.4459706230451409</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0.3881249209810446</v>
+        <v>0.3923623930240713</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.5735355957734335</v>
+        <v>4.857542306206655</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.2839409876186421</v>
+        <v>0.4634501521821301</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.07256639837781485</v>
+        <v>0.4498086297109261</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.3323545563958617</v>
+        <v>-0.4337360464820482</v>
       </c>
       <c r="BH10" t="n">
         <v>-1.187774550106088</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.2849446098583733</v>
+        <v>-0.6465171460133313</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-0.01232191212885439</v>
+        <v>-0.5109603051272273</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0.9573397527175533</v>
+        <v>-0.7646975279930578</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0.05060491166124366</v>
+        <v>0.2110480665633194</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.259746007345965</v>
+        <v>0.5324901685362253</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.31257462142745</v>
+        <v>-0.8688318088292567</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.2836327759083006</v>
+        <v>-0.225579271019948</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.4226444336110163</v>
+        <v>-0.3297401399526929</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.6898613834820226</v>
+        <v>-0.2708289184240715</v>
       </c>
       <c r="BR10" t="n">
-        <v>1.176491910585693</v>
+        <v>-0.0388771062383434</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.6896260900522886</v>
+        <v>1.02837038658204</v>
       </c>
       <c r="BT10" t="n">
-        <v>1.2053732246889</v>
+        <v>-1.172060565370307</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.07562945971346</v>
+        <v>-0.2161157814612571</v>
       </c>
       <c r="BV10" t="n">
-        <v>1.337924872839875</v>
+        <v>-1.666926855766329</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.205966008317683</v>
+        <v>-1.158528544815606</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.9261591768514015</v>
+        <v>0.197509003536231</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.3662943931614823</v>
+        <v>-0.159159811498862</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.137920412414799</v>
+        <v>-0.5770697060017476</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>8f71RSPs</t>
+          <t>jwaINpP6</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7576090025467243</v>
+        <v>0.2618506689904143</v>
       </c>
       <c r="C11" t="n">
-        <v>1.572191201610068</v>
+        <v>0.8452062883017833</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.488542156493249</v>
+        <v>-0.3603760621232627</v>
       </c>
       <c r="E11" t="n">
         <v>-0.193078397277103</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.221233175839829</v>
+        <v>-2.857502149416966</v>
       </c>
       <c r="G11" t="n">
-        <v>4.213880834005742</v>
+        <v>3.533161365002662</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4626861079115353</v>
+        <v>8.915271643554362</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2789596108235628</v>
+        <v>-5.027769442394195</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.448662137588535</v>
+        <v>0.6701500753013505</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.05117826229153585</v>
+        <v>1.431437361323474</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.201084172187152</v>
+        <v>1.180254703205829</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.145158888844613</v>
+        <v>0.176382015805172</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8279905917688172</v>
+        <v>0.6318135460692219</v>
       </c>
       <c r="O11" t="n">
-        <v>1.13317239970968</v>
+        <v>1.409049834659718</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.059115780630027</v>
+        <v>1.345808642057142</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.5077532085915754</v>
+        <v>-0.2826930655073507</v>
       </c>
       <c r="R11" t="n">
-        <v>-1.369954473182261</v>
+        <v>0.8360612959362946</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7091525251159798</v>
+        <v>1.739734043601548</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.267833660452734</v>
+        <v>0.843580053465812</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.658960657579778</v>
+        <v>0.0213809588410127</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.760219500515756</v>
+        <v>-0.4500114963638492</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1345389866062172</v>
+        <v>0.9116032020035115</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1027827712161138</v>
+        <v>0.4381355094677126</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.167757582619503</v>
+        <v>-0.1011456920329899</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.9486517432186963</v>
+        <v>0.8442314303163159</v>
       </c>
       <c r="AA11" t="n">
-        <v>-1.062808372086842</v>
+        <v>-0.1314199843273924</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.855952216475594</v>
+        <v>0.6667943523795914</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.311397037715227</v>
+        <v>0.342862831387109</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.797353907972557</v>
+        <v>-2.865524761825039</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.4127031729400455</v>
+        <v>2.279656158575819</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.4266255464554338</v>
+        <v>0.0718865125102716</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.4797173005456287</v>
+        <v>-0.7402315731768302</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.826881672720272</v>
+        <v>-1.577119837645364</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.205222516466666</v>
+        <v>2.970295466591462</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0.03214001355301317</v>
+        <v>1.145199518863976</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.3886321349971841</v>
+        <v>-0.3888098944224508</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.635893122104209</v>
+        <v>0.5614116296455941</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.07276035894521438</v>
+        <v>-1.052098244107506</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.434922180121113</v>
+        <v>0.6148957502879738</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.6832011231165388</v>
+        <v>-1.218369929232167</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.256215087279691</v>
+        <v>-0.3306024176977681</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.2562268012133797</v>
+        <v>0.3305717935880238</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.1467275834300079</v>
+        <v>1.713386374045527</v>
       </c>
       <c r="AS11" t="n">
-        <v>-0.1467412009866877</v>
+        <v>-1.713409569172369</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0.298017022747982</v>
+        <v>0.4399940875050921</v>
       </c>
       <c r="AU11" t="n">
-        <v>-1.481427868657444</v>
+        <v>-0.1417598124246783</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.5644816850521592</v>
+        <v>-1.739835997520578</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.9650179941489622</v>
+        <v>0.5266115037721798</v>
       </c>
       <c r="AX11" t="n">
         <v>0.3215400685270635</v>
       </c>
       <c r="AY11" t="n">
-        <v>-1.062368624360326</v>
+        <v>-0.3210877435521076</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.9212677829626086</v>
+        <v>-0.2884623414310081</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.9056541763523231</v>
+        <v>-0.03487464786607332</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.6844068717635536</v>
+        <v>-0.3968645839503347</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.5400704191249238</v>
+        <v>0.03318312217231979</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.1201172522297816</v>
+        <v>-1.120426050769305</v>
       </c>
       <c r="BE11" t="n">
-        <v>-2.747514895600019</v>
+        <v>6.270434324854282</v>
       </c>
       <c r="BF11" t="n">
-        <v>-2.430170050115199</v>
+        <v>-0.3632655744944128</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.5799392547386715</v>
+        <v>0.01090363800330628</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.6462088350301897</v>
+        <v>-2.104766242674227</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.216406365730078</v>
+        <v>-1.112248023949184</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1.567609850591815</v>
+        <v>0.6194469241086026</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.23018805015692</v>
+        <v>-0.6383309146379874</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.0007633429688880534</v>
+        <v>0.1327402370593509</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.2698621209894785</v>
+        <v>-1.183742387325845</v>
       </c>
       <c r="BN11" t="n">
-        <v>-3.594340960694194</v>
+        <v>0.72000096009207</v>
       </c>
       <c r="BO11" t="n">
-        <v>-1.149891216769178</v>
+        <v>0.6618237776190061</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.2118168534453613</v>
+        <v>1.871351650122302</v>
       </c>
       <c r="BQ11" t="n">
-        <v>-1.251030816794885</v>
+        <v>0.1636189391396162</v>
       </c>
       <c r="BR11" t="n">
-        <v>-2.727214258689602</v>
+        <v>0.2764671205441435</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.8740894178412917</v>
+        <v>0.2958222678452578</v>
       </c>
       <c r="BT11" t="n">
-        <v>-3.361197391698297</v>
+        <v>1.468284575723401</v>
       </c>
       <c r="BU11" t="n">
-        <v>-1.513138940021764</v>
+        <v>0.1612962845297374</v>
       </c>
       <c r="BV11" t="n">
-        <v>-2.680598328881311</v>
+        <v>2.442003072801712</v>
       </c>
       <c r="BW11" t="n">
-        <v>-1.484131513156717</v>
+        <v>1.924595561039917</v>
       </c>
       <c r="BX11" t="n">
-        <v>-2.397064891687064</v>
+        <v>0.3570812238362571</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.1118740540973925</v>
+        <v>0.9099356477237649</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-1.489344818251133</v>
+        <v>0.8614099404725118</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>UuMqRJVb</t>
+          <t>xY3xTu1n</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2035261591602602</v>
+        <v>-0.1755831547357415</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.74467746535898</v>
+        <v>-1.047983590105207</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4315794478843663</v>
+        <v>1.049450975946586</v>
       </c>
       <c r="E12" t="n">
         <v>-0.193078397277103</v>
       </c>
       <c r="F12" t="n">
-        <v>1.915556443063057</v>
+        <v>0.2108926600344777</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.891515183517351</v>
+        <v>-0.5511554490158118</v>
       </c>
       <c r="H12" t="n">
-        <v>4.909921030369708</v>
+        <v>-2.66990156942974</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.010549929664274</v>
+        <v>4.062816519517454</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.343463893887862</v>
+        <v>-0.1095529779211208</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4413402685060122</v>
+        <v>-0.09019446291298334</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5749435954447353</v>
+        <v>-1.565204749593494</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9000442252162297</v>
+        <v>0.2620776808504022</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2164510205123412</v>
+        <v>-1.557892660687836</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2070124395202634</v>
+        <v>-0.2659203061083745</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9629626659420494</v>
+        <v>-1.341331408580339</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.6341102265424535</v>
+        <v>0.6263542080806678</v>
       </c>
       <c r="R12" t="n">
-        <v>2.702690023651996</v>
+        <v>0.4966742545334401</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5342320559218706</v>
+        <v>-1.146453698101253</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9687357595938698</v>
+        <v>-0.8768008668671909</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.03369401385004394</v>
+        <v>0.745908913977526</v>
       </c>
       <c r="V12" t="n">
-        <v>2.031652536851406</v>
+        <v>0.7132685192058019</v>
       </c>
       <c r="W12" t="n">
-        <v>-1.73041513034729</v>
+        <v>-1.186470179569183</v>
       </c>
       <c r="X12" t="n">
-        <v>0.9881669301486529</v>
+        <v>-0.7774758906761233</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.9249080608529128</v>
+        <v>0.657205472748367</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.891770312447853</v>
+        <v>0.9046164317455212</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.09298834178895524</v>
+        <v>-1.324705842453175</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.712620911434662</v>
+        <v>0.9659978865370715</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.01604237584324937</v>
+        <v>-1.24165226445861</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.709375065146187</v>
+        <v>1.313470272427523</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.7216624404910462</v>
+        <v>2.367930235018962</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.769060487706384</v>
+        <v>-0.2634843539680486</v>
       </c>
       <c r="AG12" t="n">
-        <v>-1.215455024409508</v>
+        <v>0.9660475189446713</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.792882101337547</v>
+        <v>-0.4731193477970498</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.08346093653861836</v>
+        <v>1.430650383896612</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.953502626702205</v>
+        <v>-0.7004936077776891</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0.8277668878832485</v>
+        <v>0.05772512223145513</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.6205180120588818</v>
+        <v>0.6091663626437541</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0.2264041631432753</v>
+        <v>-0.3580365528622113</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.118278151101638</v>
+        <v>-0.4408205630438257</v>
       </c>
       <c r="AO12" t="n">
-        <v>-1.214886688743424</v>
+        <v>-0.784537603996262</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.6376464655150389</v>
+        <v>0.2659953790293147</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.637645887834292</v>
+        <v>-0.2660067777934025</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.383289298367696</v>
+        <v>0.2765354700199176</v>
       </c>
       <c r="AS12" t="n">
-        <v>-2.38331658886125</v>
+        <v>-0.2765498811406772</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0.3718181337732893</v>
+        <v>0.3661929764797845</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.0815181969474493</v>
+        <v>-0.216185815548721</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.2479845034980509</v>
+        <v>0.7380850753009199</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.1218489589378893</v>
+        <v>-0.2529963543216925</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.1030951712491944</v>
+        <v>-0.6146523483780899</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0.09870347930964227</v>
+        <v>0.6319876746298871</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.6476383500640527</v>
+        <v>0.3740089171654966</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0.1346277049801458</v>
+        <v>0.6776471886630147</v>
       </c>
       <c r="BB12" t="n">
-        <v>-0.2727079826162983</v>
+        <v>-2.33521249326231</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.1927735751959315</v>
+        <v>-1.973528291220233</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.8832685224081391</v>
+        <v>-2.275831438340352</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.157086742591008</v>
+        <v>1.261174391884083</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.771843819685218</v>
+        <v>0.2162610273495087</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.6466603324348517</v>
+        <v>0.1445856052079675</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.1877129887461204</v>
+        <v>-0.2707828575379491</v>
       </c>
       <c r="BI12" t="n">
-        <v>-2.509440657756741</v>
+        <v>-0.6465171460133313</v>
       </c>
       <c r="BJ12" t="n">
-        <v>-0.03703180839791965</v>
+        <v>-1.204007594480146</v>
       </c>
       <c r="BK12" t="n">
-        <v>-0.7592033274124028</v>
+        <v>0.4371893723618338</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0.6572986038144346</v>
+        <v>2.137614336838829</v>
       </c>
       <c r="BM12" t="n">
-        <v>-0.1449904561907999</v>
+        <v>0.1916073655395703</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.81457509896034</v>
+        <v>0.2928598425319493</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.954758101599981</v>
+        <v>0.8845701894782559</v>
       </c>
       <c r="BP12" t="n">
-        <v>1.015164417388985</v>
+        <v>-0.05964121641688617</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.058587328068563</v>
+        <v>0.5963871334234327</v>
       </c>
       <c r="BR12" t="n">
-        <v>2.582721333877288</v>
+        <v>0.3584742915782847</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.09690285105127627</v>
+        <v>-0.2500851718916215</v>
       </c>
       <c r="BT12" t="n">
-        <v>1.921795607378016</v>
+        <v>0.6203264975224827</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.8218789373710359</v>
+        <v>0.4926123129960354</v>
       </c>
       <c r="BV12" t="n">
-        <v>1.964242586051142</v>
+        <v>0.3023772040928152</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.988829666963744</v>
+        <v>0.7252279355783846</v>
       </c>
       <c r="BX12" t="n">
-        <v>2.507061211186089</v>
+        <v>0.6735369221129571</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.241323536338891</v>
+        <v>0.5672464811897908</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.503843323251059</v>
+        <v>0.4566778843992584</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bLD0NyVN</t>
+          <t>OjcQLOgJ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.6130169784618973</v>
+        <v>-1.137937566933284</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8452062883017833</v>
+        <v>0.01220274180270737</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2519730554222272</v>
+        <v>1.490911967665428</v>
       </c>
       <c r="E13" t="n">
         <v>-0.193078397277103</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.221233175839829</v>
+        <v>6.688615035543079</v>
       </c>
       <c r="G13" t="n">
-        <v>4.213880834005742</v>
+        <v>-9.400508546055839</v>
       </c>
       <c r="H13" t="n">
-        <v>1.06534857560162</v>
+        <v>5.115426947142764</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.063438952505081</v>
+        <v>-5.904605486215623</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5773748098546033</v>
+        <v>1.683764044490563</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5730809476516261</v>
+        <v>-1.611826287149441</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.8529515807518148</v>
+        <v>0.9275134363149382</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8048168928035269</v>
+        <v>-0.7953589280140587</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.617073909519109</v>
+        <v>0.5134510484066785</v>
       </c>
       <c r="O13" t="n">
-        <v>1.527283021066878</v>
+        <v>-1.625601949790708</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.143239540184284</v>
+        <v>0.2393798807823731</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.46299082693724</v>
+        <v>-1.280941194977544</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.6911803903765515</v>
+        <v>1.17544833733915</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.009470648339543065</v>
+        <v>-1.933595809474744</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8339379800506068</v>
+        <v>0.1778982941338998</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.749209700728021</v>
+        <v>-0.6027656397444733</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.070427504667663</v>
+        <v>1.7214445326995</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7561903589240528</v>
+        <v>-2.041240816506207</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3801804678041052</v>
+        <v>0.9605096725652952</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1996642156332425</v>
+        <v>-0.7468073275354932</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.515330534866538</v>
+        <v>-0.6720377841115495</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.7520403825971058</v>
+        <v>0.931111199418598</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.548447498283904</v>
+        <v>-0.7418896764765541</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.5278900080689072</v>
+        <v>0.2678745380889304</v>
       </c>
       <c r="AD13" t="n">
-        <v>-1.567836830136086</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.3464976156076882</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.1999700508147336</v>
+        <v>1.578346125955441</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.287423849945448</v>
+        <v>-1.467859883404796</v>
       </c>
       <c r="AH13" t="n">
-        <v>-1.784119929491923</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.1315748453728324</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.7211847770771389</v>
+        <v>0.133582432677136</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.2162797469734592</v>
+        <v>-0.9586772385441946</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.8718173941336379</v>
+        <v>1.803034687597771</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.9343541825600626</v>
+        <v>0.09669352071229317</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.7012369084815139</v>
+        <v>1.044907072517564</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.4301319579655489</v>
+        <v>-0.342479313423367</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.177972753282696</v>
+        <v>0.9212749262541434</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0.177986988573192</v>
+        <v>-0.9212652086549701</v>
       </c>
       <c r="AR13" t="n">
-        <v>-0.2258236132680879</v>
+        <v>1.827331188596538</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.2258122732559806</v>
+        <v>-1.827355080310577</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.8828007536569363</v>
+        <v>-0.002812578646752469</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.3047962063195769</v>
+        <v>0.3047962063195767</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.4957345460209878</v>
+        <v>0.8690704076485403</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.245917478115357</v>
+        <v>0.3354695274483507</v>
       </c>
       <c r="AX13" t="n">
-        <v>-1.134759246658731</v>
+        <v>1.777839383712858</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.161474018064329</v>
+        <v>-0.02457539122882023</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-0.05803755583222377</v>
+        <v>-0.202053046831464</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.1646314663620712</v>
+        <v>0.3071358336678889</v>
       </c>
       <c r="BB13" t="n">
-        <v>-3.012595860855799</v>
+        <v>0.07514071335406437</v>
       </c>
       <c r="BC13" t="n">
-        <v>-2.494164437533893</v>
+        <v>0.5197211462574753</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1508381256170023</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.515454164200188</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>-0.9581807998264982</v>
+        <v>0.5566047447901808</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.5252605284425924</v>
+        <v>-0.2699645358395943</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.6462088350301897</v>
+        <v>-0.2707828575379491</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.2849446098583733</v>
+        <v>-1.112248023949184</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.404003370113946</v>
+        <v>0.9084569356649282</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.184156464638471</v>
+        <v>-0.2411787012363377</v>
       </c>
       <c r="BL13" t="n">
-        <v>2.042717936458526</v>
+        <v>0.001646091719741389</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.97187834559833</v>
+        <v>-1.052562665153359</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.4680613382522639</v>
+        <v>1.80463513040749</v>
       </c>
       <c r="BO13" t="n">
-        <v>-0.6090682003333117</v>
+        <v>1.631878489111758</v>
       </c>
       <c r="BP13" t="n">
-        <v>-0.7196809342173139</v>
+        <v>-0.08643581542379859</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.5152754591947546</v>
+        <v>1.577750926658694</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.4214200896656881</v>
+        <v>0.5051003175697697</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.029856554761798</v>
+        <v>-0.671709038169659</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.1191932363097398</v>
+        <v>1.25004133012329</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.4384745837787851</v>
+        <v>1.506409495406472</v>
       </c>
       <c r="BV13" t="n">
-        <v>-0.5314667323084734</v>
+        <v>1.814066967566644</v>
       </c>
       <c r="BW13" t="n">
-        <v>-0.5236918375704931</v>
+        <v>1.19322228396272</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.1947018046349112</v>
+        <v>0.3028832585933547</v>
       </c>
       <c r="BY13" t="n">
-        <v>-1.530910391479715</v>
+        <v>0.5524029014146137</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.1745805413874862</v>
+        <v>1.468289435840891</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>I5fXHFho</t>
+          <t>jeAhPc0B</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2618506689904143</v>
+        <v>-1.662858155404671</v>
       </c>
       <c r="C14" t="n">
-        <v>1.814519506046163</v>
+        <v>1.572191201610068</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3603760621232627</v>
+        <v>-0.3888574164277042</v>
       </c>
       <c r="E14" t="n">
         <v>-0.193078397277103</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8119056097826699</v>
+        <v>-1.152838366388386</v>
       </c>
       <c r="G14" t="n">
-        <v>1.491002957993425</v>
+        <v>2.171722426996504</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4711723181952515</v>
+        <v>4.580633989870019</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.407577029092517</v>
+        <v>-5.225143516572039</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0315826725988735</v>
+        <v>0.04638763272337356</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2462592653987741</v>
+        <v>0.8852105526232072</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.3148070986333641</v>
+        <v>1.581951303929723</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2105251698766709</v>
+        <v>0.3329049456466711</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9858072553188754</v>
+        <v>1.08553645377564</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.423564554651254</v>
+        <v>0.1478958463166837</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7127782779722107</v>
+        <v>1.573342353714164</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.03882142461296942</v>
+        <v>-0.6316993743481049</v>
       </c>
       <c r="R14" t="n">
-        <v>0.07244045277987164</v>
+        <v>0.1572872131305852</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.009470648339543065</v>
+        <v>2.439415920377985</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4418076306737703</v>
+        <v>0.8215219596654645</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4712340746734379</v>
+        <v>0.8107379054010728</v>
       </c>
       <c r="V14" t="n">
-        <v>0.403060515053895</v>
+        <v>-2.078603518161361</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.0985802780129711</v>
+        <v>2.310318789718641</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.134790991994152</v>
+        <v>0.06805026569253049</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.16956016996703</v>
+        <v>-0.2268572952367886</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.07304500930402</v>
+        <v>-1.44804803176261</v>
       </c>
       <c r="AA14" t="n">
-        <v>-1.371826532210142</v>
+        <v>-0.7922580661956421</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.6665392646041214</v>
+        <v>-0.4941287782556156</v>
       </c>
       <c r="AC14" t="n">
-        <v>-1.191868189946558</v>
+        <v>-0.3927431027870387</v>
       </c>
       <c r="AD14" t="n">
-        <v>-1.743794515788825</v>
+        <v>-0.1821700556207624</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.911407973707101</v>
+        <v>-0.3464976156076882</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.6834881453972343</v>
+        <v>1.695522732794807</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.9798607992355055</v>
+        <v>-1.288525582267004</v>
       </c>
       <c r="AH14" t="n">
-        <v>-1.945120000928136</v>
+        <v>-0.1971192253349712</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.743390791319004</v>
+        <v>-0.5660768327232716</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-1.160868676621975</v>
+        <v>1.693152768495922</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.518026881019508</v>
+        <v>-0.9813692079946688</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.7518435278038242</v>
+        <v>0.5852889961446741</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.8146883737246676</v>
+        <v>-3.218049384028169</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.9614110672515772</v>
+        <v>0.01841119636358518</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.9773616677461766</v>
+        <v>-1.98331534234165</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.3540180047759335</v>
+        <v>1.508092431231602</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0.3540265670136131</v>
+        <v>-1.508063803456374</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0.6694478684210747</v>
+        <v>1.237293183739159</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.6694392404496844</v>
+        <v>-1.23731346833056</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0.002812578646752469</v>
+        <v>0.2923918654544772</v>
       </c>
       <c r="AU14" t="n">
-        <v>-1.853557884277657</v>
+        <v>0.6025002188157471</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.437384814622514</v>
+        <v>0.1279794169634325</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0.1071151167670002</v>
+        <v>1.521851172835317</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.7584298630828017</v>
+        <v>0.8416469668077043</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.7658562720370384</v>
+        <v>-0.5328822809258842</v>
       </c>
       <c r="AZ14" t="n">
-        <v>-0.2164545959313878</v>
+        <v>-1.109350640126677</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.02212709905625383</v>
+        <v>0.3498871438596342</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.3168847836764194</v>
+        <v>2.131717955603921</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.3736585876755701</v>
+        <v>2.770045486304225</v>
       </c>
       <c r="BD14" t="n">
-        <v>-1.119135533873708</v>
+        <v>1.591838703122462</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.57051214013532</v>
+        <v>0.2642849091889334</v>
       </c>
       <c r="BF14" t="n">
-        <v>-1.074671712832147</v>
+        <v>2.395808401768399</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.273865242013889</v>
+        <v>-0.2604522784823988</v>
       </c>
       <c r="BH14" t="n">
-        <v>1.104704681314259</v>
+        <v>-0.9585266269640533</v>
       </c>
       <c r="BI14" t="n">
-        <v>-0.6465171460133313</v>
+        <v>0.2849446098583733</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.1824073944380604</v>
+        <v>-0.4710371926661206</v>
       </c>
       <c r="BK14" t="n">
-        <v>-0.6971682795863799</v>
+        <v>-0.8047916263044813</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.4341772786965591</v>
+        <v>-2.214320147284549</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.3095710499862441</v>
+        <v>-0.1349685159730622</v>
       </c>
       <c r="BN14" t="n">
-        <v>-0.08754821025190562</v>
+        <v>0.251269223141596</v>
       </c>
       <c r="BO14" t="n">
-        <v>-0.08983838435487664</v>
+        <v>-0.08681255271733931</v>
       </c>
       <c r="BP14" t="n">
-        <v>-0.00794297355995504</v>
+        <v>-0.6027543752517207</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-0.1265620014325971</v>
+        <v>0.1225211185662725</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0.09875493792051843</v>
+        <v>0.1126901100037866</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.411365771096446</v>
+        <v>-0.4767453678119234</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0.06472839306557042</v>
+        <v>-0.02826001914936708</v>
       </c>
       <c r="BU14" t="n">
-        <v>-0.1190369285333109</v>
+        <v>0.9559096614385567</v>
       </c>
       <c r="BV14" t="n">
-        <v>-0.1722023052316627</v>
+        <v>-0.03156961902544374</v>
       </c>
       <c r="BW14" t="n">
-        <v>-0.0711861106250308</v>
+        <v>-0.1559675418042673</v>
       </c>
       <c r="BX14" t="n">
-        <v>-0.1484769425421064</v>
+        <v>-0.04459348843532066</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.2941489479037044</v>
+        <v>-0.1727742474890413</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0.1071042689503714</v>
+        <v>0.6117201642436786</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>McP0d8Q7</t>
+          <t>OMVUWl2K</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.08809638999051034</v>
+        <v>-0.1755831547357415</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.1998345245788756</v>
+        <v>-0.9116739188599041</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.627796328670905</v>
+        <v>1.049450975946586</v>
       </c>
       <c r="E15" t="n">
         <v>-0.193078397277103</v>
       </c>
       <c r="F15" t="n">
-        <v>2.597421956274488</v>
+        <v>3.961152982697352</v>
       </c>
       <c r="G15" t="n">
-        <v>-5.316191732037364</v>
+        <v>-3.954752794031207</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7994866535140929</v>
+        <v>7.267642506898926</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.983479651219303</v>
+        <v>-4.508115139952967</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4214341992101092</v>
+        <v>1.76173434981281</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3389837439229406</v>
+        <v>-0.2072430647773262</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4201439202237902</v>
+        <v>1.878695473440848</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2393079314552869</v>
+        <v>0.1093509706795085</v>
       </c>
       <c r="N15" t="n">
-        <v>1.184171868494426</v>
+        <v>1.065809370831883</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4237732812667223</v>
+        <v>-0.6797364585334322</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4502841289618508</v>
+        <v>1.690661290165701</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1462450895472876</v>
+        <v>-0.2952740672946681</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.0124063075708422</v>
+        <v>1.345141858040577</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6902112284368935</v>
+        <v>0.6902112284368933</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2199847663806969</v>
+        <v>2.020832336426317</v>
       </c>
       <c r="U15" t="n">
-        <v>1.067670452292923</v>
+        <v>0.1593006015150202</v>
       </c>
       <c r="V15" t="n">
-        <v>0.01530050986401119</v>
+        <v>0.4806125160918717</v>
       </c>
       <c r="W15" t="n">
-        <v>0.4453646727651349</v>
+        <v>-0.4871123857116184</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.4938860582867076</v>
+        <v>1.275671907055117</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.761669029956107</v>
+        <v>-0.9651457200046757</v>
       </c>
       <c r="Z15" t="n">
-        <v>-2.053843221170732</v>
+        <v>-1.169083005946753</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.2758467481506092</v>
+        <v>0.08179167723786308</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.6727503420501195</v>
+        <v>-0.03593304461717602</v>
       </c>
       <c r="AC15" t="n">
-        <v>-1.055169149560042</v>
+        <v>0.08931838804511032</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.401449115253893</v>
+        <v>1.225491429601154</v>
       </c>
       <c r="AE15" t="n">
-        <v>-2.045773587138193</v>
+        <v>-0.01546982894590157</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.8106237909257208</v>
+        <v>0.8198055420804815</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.353427946014394</v>
+        <v>-0.160428387911455</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.458881509437501</v>
+        <v>0.3088809991788396</v>
       </c>
       <c r="AI15" t="n">
-        <v>-1.79298150799573</v>
+        <v>0.5405430704636519</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0.03882237025584196</v>
+        <v>1.417966561259231</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0.286006642285388</v>
+        <v>-0.07034014603769237</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.086713692625361</v>
+        <v>1.444874190111566</v>
       </c>
       <c r="AM15" t="n">
-        <v>-1.435028832380773</v>
+        <v>-1.746159935352801</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.095616606348528</v>
+        <v>0.3642941221772744</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.7463211339687336</v>
+        <v>-1.323705701789912</v>
       </c>
       <c r="AP15" t="n">
-        <v>-0.4284053351940106</v>
+        <v>2.173152270206054</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.428371559388258</v>
+        <v>-2.173102210897964</v>
       </c>
       <c r="AR15" t="n">
-        <v>-1.259238252469865</v>
+        <v>1.773302466884302</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.259233230107315</v>
+        <v>-1.773326028300591</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0.002812578646752469</v>
+        <v>-2.216845909405973</v>
       </c>
       <c r="AU15" t="n">
-        <v>-1.332575862409359</v>
+        <v>0.6025002188157471</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.3173258453052292</v>
+        <v>-1.855168368921557</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0.2899692797389152</v>
+        <v>-0.3203101253647863</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.1153497260286747</v>
+        <v>-1.134759246658731</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.1236807849328232</v>
+        <v>1.161474018064329</v>
       </c>
       <c r="AZ15" t="n">
-        <v>-0.2884623414310081</v>
+        <v>-0.3460685378307039</v>
       </c>
       <c r="BA15" t="n">
-        <v>-1.174909586312614</v>
+        <v>0.5066419478960335</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.04562305135573294</v>
+        <v>-0.3253234481393124</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.07340506651637355</v>
+        <v>-0.3881249209810446</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.304237091687787</v>
+        <v>0.5735355957734335</v>
       </c>
       <c r="BE15" t="n">
-        <v>-4.920959529637039</v>
+        <v>0.2839409876186421</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.7386260576296991</v>
+        <v>0.07256639837781485</v>
       </c>
       <c r="BG15" t="n">
-        <v>-1.312853430445029</v>
+        <v>0.3323545563958617</v>
       </c>
       <c r="BH15" t="n">
-        <v>-0.2707828575379491</v>
+        <v>-1.187774550106088</v>
       </c>
       <c r="BI15" t="n">
-        <v>-0.1807862680774791</v>
+        <v>0.2849446098583733</v>
       </c>
       <c r="BJ15" t="n">
-        <v>-1.09421243853126</v>
+        <v>-0.01232191212885439</v>
       </c>
       <c r="BK15" t="n">
-        <v>-1.922975557856788</v>
+        <v>-0.9573397527175533</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.1435460865404678</v>
+        <v>-0.05060491166124366</v>
       </c>
       <c r="BM15" t="n">
-        <v>-0.002600351332247126</v>
+        <v>1.259746007345965</v>
       </c>
       <c r="BN15" t="n">
-        <v>-0.1167675014014083</v>
+        <v>1.31257462142745</v>
       </c>
       <c r="BO15" t="n">
-        <v>-0.358894576973516</v>
+        <v>0.2836327759083006</v>
       </c>
       <c r="BP15" t="n">
-        <v>-0.2555381744377039</v>
+        <v>0.4226444336110163</v>
       </c>
       <c r="BQ15" t="n">
-        <v>-0.2159459355811046</v>
+        <v>0.6898613834820226</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0.3308063609579721</v>
+        <v>1.176491910585693</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.3570055844532571</v>
+        <v>0.6896260900522886</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0.4449622931647177</v>
+        <v>1.2053732246889</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.009054620960128131</v>
+        <v>1.07562945971346</v>
       </c>
       <c r="BV15" t="n">
-        <v>-0.4322611614701462</v>
+        <v>1.337924872839875</v>
       </c>
       <c r="BW15" t="n">
-        <v>-0.7565513811300834</v>
+        <v>1.205966008317683</v>
       </c>
       <c r="BX15" t="n">
-        <v>-0.775765235133519</v>
+        <v>0.9261591768514015</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.5937015717763341</v>
+        <v>-0.3662943931614823</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.06615409652342767</v>
+        <v>1.137920412414799</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>0lpzB7u1</t>
+          <t>8f71RSPs</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05771488458487495</v>
+        <v>0.7576090025467243</v>
       </c>
       <c r="C16" t="n">
-        <v>-1.047983590105207</v>
+        <v>1.572191201610068</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.314501431322049</v>
+        <v>-0.488542156493249</v>
       </c>
       <c r="E16" t="n">
         <v>-0.193078397277103</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.584964202262691</v>
+        <v>-4.221233175839829</v>
       </c>
       <c r="G16" t="n">
-        <v>2.852441895999583</v>
+        <v>4.213880834005742</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7439541700881322</v>
+        <v>-0.4626861079115353</v>
       </c>
       <c r="I16" t="n">
-        <v>0.460192620111682</v>
+        <v>0.2789596108235628</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5921797699791037</v>
+        <v>-2.448662137588535</v>
       </c>
       <c r="K16" t="n">
-        <v>1.275372558837683</v>
+        <v>-0.05117826229153585</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.246709513477213</v>
+        <v>-2.201084172187152</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8394956257624219</v>
+        <v>-1.145158888844613</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7501760437317656</v>
+        <v>-0.8279905917688172</v>
       </c>
       <c r="O16" t="n">
-        <v>1.960804704559795</v>
+        <v>1.13317239970968</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2491951173990537</v>
+        <v>-1.059115780630027</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.8600036030024055</v>
+        <v>-0.5077532085915754</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.3517933489736969</v>
+        <v>-1.369954473182261</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1843911175336523</v>
+        <v>-0.7091525251159798</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.35671480311884</v>
+        <v>-1.267833660452734</v>
       </c>
       <c r="U16" t="n">
-        <v>1.08284906677096</v>
+        <v>-1.658960657579778</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.4500114963638492</v>
+        <v>-0.760219500515756</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9116032020035115</v>
+        <v>0.1345389866062172</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.051052124846767</v>
+        <v>-0.1027827712161138</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.215833008197282</v>
+        <v>-0.167757582619503</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.501691803332643</v>
+        <v>0.9486517432186963</v>
       </c>
       <c r="AA16" t="n">
-        <v>-1.086846159560748</v>
+        <v>-1.062808372086842</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9151572584137988</v>
+        <v>1.855952216475594</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.3995270908868673</v>
+        <v>0.311397037715227</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.5216606869901956</v>
+        <v>1.797353907972557</v>
       </c>
       <c r="AE16" t="n">
-        <v>-1.560266166700906</v>
+        <v>-0.4127031729400455</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.2681718482869729</v>
+        <v>0.4266255464554338</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.1453967233839127</v>
+        <v>0.4797173005456287</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.5848811216409182</v>
+        <v>1.826881672720272</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.08346093653861836</v>
+        <v>-0.205222516466666</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.4314108265470228</v>
+        <v>-0.03214001355301317</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.1188124091936782</v>
+        <v>0.3886321349971841</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.325487357616164</v>
+        <v>1.635893122104209</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0.6931008176013191</v>
+        <v>0.07276035894521438</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.1133914710898659</v>
+        <v>1.434922180121113</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.1160533234518232</v>
+        <v>0.6832011231165388</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.7256690912616568</v>
+        <v>0.256215087279691</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-0.7256656770545021</v>
+        <v>-0.2562268012133797</v>
       </c>
       <c r="AR16" t="n">
-        <v>-0.4207439640614934</v>
+        <v>0.1467275834300079</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.4207338156702719</v>
+        <v>-0.1467412009866877</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.2923918654544772</v>
+        <v>-0.298017022747982</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.9002042313119174</v>
+        <v>-1.481427868657444</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.030168400963028</v>
+        <v>-0.5644816850521592</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.6234025471021185</v>
+        <v>0.9650179941489622</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.959876798111082</v>
+        <v>0.3215400685270635</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.8770484041582712</v>
+        <v>-1.062368624360326</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.3452058189656487</v>
+        <v>0.9212677829626086</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.2216332132843984</v>
+        <v>0.9056541763523231</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.4795583976641717</v>
+        <v>0.6844068717635536</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.4410253910104378</v>
+        <v>0.5400704191249238</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.770647036136435</v>
+        <v>-0.1201172522297816</v>
       </c>
       <c r="BE16" t="n">
-        <v>-0.1467350884944564</v>
+        <v>-2.747514895600019</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.5590704766420728</v>
+        <v>-2.430170050115199</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.1688736622168747</v>
+        <v>-0.5799392547386715</v>
       </c>
       <c r="BH16" t="n">
         <v>0.6462088350301897</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.2849446098583733</v>
+        <v>1.216406365730078</v>
       </c>
       <c r="BJ16" t="n">
-        <v>-0.7621619116240782</v>
+        <v>1.567609850591815</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.2883575832991953</v>
+        <v>1.23018805015692</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0.07884549907279725</v>
+        <v>0.0007633429688880534</v>
       </c>
       <c r="BM16" t="n">
-        <v>-0.3130423027901837</v>
+        <v>0.09359507080323486</v>
       </c>
       <c r="BN16" t="n">
-        <v>-2.206587660342057</v>
+        <v>-3.696003827961722</v>
       </c>
       <c r="BO16" t="n">
-        <v>-0.9246586627043196</v>
+        <v>-1.048255909364193</v>
       </c>
       <c r="BP16" t="n">
-        <v>-1.376294232707399</v>
+        <v>0.2013234443074223</v>
       </c>
       <c r="BQ16" t="n">
-        <v>-0.2242178932418709</v>
+        <v>-1.20002948974413</v>
       </c>
       <c r="BR16" t="n">
-        <v>-2.116236318920825</v>
+        <v>-2.740837088392558</v>
       </c>
       <c r="BS16" t="n">
-        <v>-1.876955900519309</v>
+        <v>0.8644351283659332</v>
       </c>
       <c r="BT16" t="n">
-        <v>-1.251453323293423</v>
+        <v>-3.171390577479937</v>
       </c>
       <c r="BU16" t="n">
-        <v>-1.072844084889729</v>
+        <v>-1.543417918054763</v>
       </c>
       <c r="BV16" t="n">
-        <v>-2.078854131341793</v>
+        <v>-2.827592969939716</v>
       </c>
       <c r="BW16" t="n">
-        <v>-1.502882974922295</v>
+        <v>-1.292300644507081</v>
       </c>
       <c r="BX16" t="n">
-        <v>-1.745672357696996</v>
+        <v>-2.286619937847213</v>
       </c>
       <c r="BY16" t="n">
-        <v>-1.165857036416477</v>
+        <v>0.1927576857579081</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-1.44297828873084</v>
+        <v>-1.513663887256318</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>GMBD7YY8</t>
+          <t>UuMqRJVb</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.05771488458487495</v>
+        <v>0.2035261591602602</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3756951984568496</v>
+        <v>-1.74467746535898</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.314501431322049</v>
+        <v>-0.4315794478843663</v>
       </c>
       <c r="E17" t="n">
         <v>-0.193078397277103</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.493771122994101</v>
+        <v>1.915556443063057</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.23187491801889</v>
+        <v>-0.891515183517351</v>
       </c>
       <c r="H17" t="n">
-        <v>2.571899467430932</v>
+        <v>4.909921030369708</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.21220304577571</v>
+        <v>-4.010549929664274</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9672263364658392</v>
+        <v>-0.343463893887862</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2462592653987741</v>
+        <v>-0.4413402685060122</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1576246540934551</v>
+        <v>0.5749435954447353</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2976052995403432</v>
+        <v>-0.9000442252162297</v>
       </c>
       <c r="N17" t="n">
-        <v>0.335907301912863</v>
+        <v>-0.2164510205123412</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.25119685950137</v>
+        <v>0.2070124395202634</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3313251598844033</v>
+        <v>0.9629626659420494</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.6974001614596482</v>
+        <v>-0.6341102265424535</v>
       </c>
       <c r="R17" t="n">
-        <v>-1.879035035286543</v>
+        <v>2.702690023651996</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4278305246457297</v>
+        <v>-0.5342320559218706</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.04504601106246832</v>
+        <v>0.9687357595938698</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8708905574526674</v>
+        <v>-0.03369401385004394</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.38063550881957</v>
+        <v>2.031652536851406</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1447224666227</v>
+        <v>-1.73041513034729</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.362276514633422</v>
+        <v>0.9881669301486529</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.2409266976372108</v>
+        <v>-0.9249080608529128</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.0100861832687151</v>
+        <v>1.891770312447853</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.6763780898308062</v>
+        <v>0.09298834178895524</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.1751764297921763</v>
+        <v>1.712620911434662</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.4559652009020236</v>
+        <v>-0.01604237584324937</v>
       </c>
       <c r="AD17" t="n">
-        <v>-1.281905590950384</v>
+        <v>1.709375065146187</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.102668472667244</v>
+        <v>-0.7216624404910462</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.6069830775681739</v>
+        <v>1.769060487706384</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.8914939401970551</v>
+        <v>-1.215455024409508</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.7184527899855643</v>
+        <v>2.792882101337547</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.2438406326526654</v>
+        <v>0.08346093653861836</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0.2500241500458313</v>
+        <v>1.953502626702205</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.3919159450475307</v>
+        <v>-0.8277668878832485</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.008841695801327</v>
+        <v>-0.6205180120588818</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.137786057580236</v>
+        <v>-0.2264041631432753</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.956856180459141</v>
+        <v>1.118278151101638</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.952776256042559</v>
+        <v>-1.214886688743424</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.08995012753607726</v>
+        <v>0.6376464655150389</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0.08996719935298149</v>
+        <v>-0.637645887834292</v>
       </c>
       <c r="AR17" t="n">
-        <v>-1.477602132748316</v>
+        <v>2.383289298367696</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.477598445325701</v>
+        <v>-2.38331658886125</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0.2242159117226746</v>
+        <v>-0.3718181337732893</v>
       </c>
       <c r="AU17" t="n">
-        <v>-0.5138898280448911</v>
+        <v>0.0815181969474493</v>
       </c>
       <c r="AV17" t="n">
-        <v>-0.5819060751291842</v>
+        <v>0.2479845034980509</v>
       </c>
       <c r="AW17" t="n">
-        <v>-0.04030746430317733</v>
+        <v>0.1218489589378893</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.3215400685270635</v>
+        <v>0.1030951712491944</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0.3210877435521076</v>
+        <v>-0.09870347930964227</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.9644724302623809</v>
+        <v>0.6476383500640527</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.8629028661605777</v>
+        <v>-0.1346277049801458</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.2612836475022781</v>
+        <v>-0.2727079826162983</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.06777688604698147</v>
+        <v>0.1927735751959315</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.8770541961183675</v>
+        <v>0.8832685224081391</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.03526167056343001</v>
+        <v>0.157086742591008</v>
       </c>
       <c r="BF17" t="n">
-        <v>-0.0692309081156023</v>
+        <v>1.771843819685218</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.6272678730560726</v>
+        <v>-0.6466603324348517</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.5000307806799837</v>
+        <v>0.1877129887461204</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.68213724366593</v>
+        <v>-2.509440657756741</v>
       </c>
       <c r="BJ17" t="n">
-        <v>-1.241495589327253</v>
+        <v>-0.03703180839791965</v>
       </c>
       <c r="BK17" t="n">
-        <v>-0.1382133125766507</v>
+        <v>-0.7592033274124028</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0.2906295482721281</v>
+        <v>-0.6572986038144346</v>
       </c>
       <c r="BM17" t="n">
-        <v>-0.2804241182218168</v>
+        <v>-0.1449904561907999</v>
       </c>
       <c r="BN17" t="n">
-        <v>-0.6469652715825848</v>
+        <v>1.81457509896034</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.0164938525556262</v>
+        <v>1.954758101599981</v>
       </c>
       <c r="BP17" t="n">
-        <v>-0.4816304526309539</v>
+        <v>1.015164417388985</v>
       </c>
       <c r="BQ17" t="n">
-        <v>-0.4397139995169081</v>
+        <v>1.058587328068563</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0.627315070951066</v>
+        <v>2.582721333877288</v>
       </c>
       <c r="BS17" t="n">
-        <v>-0.7246343651559146</v>
+        <v>0.09690285105127627</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0.4881094875828946</v>
+        <v>1.921795607378016</v>
       </c>
       <c r="BU17" t="n">
-        <v>-0.6115221616792171</v>
+        <v>0.8218789373710359</v>
       </c>
       <c r="BV17" t="n">
-        <v>-0.307756588880434</v>
+        <v>1.964242586051142</v>
       </c>
       <c r="BW17" t="n">
-        <v>-0.1555798451617917</v>
+        <v>1.988829666963744</v>
       </c>
       <c r="BX17" t="n">
-        <v>-0.404950196807651</v>
+        <v>2.507061211186089</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.8990431689812414</v>
+        <v>1.241323536338891</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0.7227905332715922</v>
+        <v>1.503843323251059</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>dGwq9oAD</t>
+          <t>bLD0NyVN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-1.137937566933284</v>
+        <v>-0.6130169784618973</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1998345245788756</v>
+        <v>0.8452062883017833</v>
       </c>
       <c r="D18" t="n">
-        <v>1.490911967665428</v>
+        <v>0.2519730554222272</v>
       </c>
       <c r="E18" t="n">
         <v>-0.193078397277103</v>
       </c>
       <c r="F18" t="n">
-        <v>1.233690929851625</v>
+        <v>-4.221233175839829</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5511554490158114</v>
+        <v>4.213880834005742</v>
       </c>
       <c r="H18" t="n">
-        <v>3.667572843306799</v>
+        <v>1.06534857560162</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.219017138445961</v>
+        <v>-1.063438952505081</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.889256031143592</v>
+        <v>-0.5773748098546033</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.05117826229153585</v>
+        <v>0.5730809476516261</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.3185658149102028</v>
+        <v>-0.8529515807518148</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.05441901098206892</v>
+        <v>0.8048168928035269</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.208886397831828</v>
+        <v>-1.617073909519109</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5420064676738818</v>
+        <v>1.527283021066878</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2630177633848626</v>
+        <v>-1.143239540184284</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2193976305133965</v>
+        <v>1.46299082693724</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.01240630757084208</v>
+        <v>-0.6911803903765515</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.583754871086526</v>
+        <v>-0.009470648339543065</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4024181774588639</v>
+        <v>-0.8339379800506068</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2870412090577342</v>
+        <v>-0.749209700728021</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6357165181678253</v>
+        <v>-1.070427504667663</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3316995426321596</v>
+        <v>0.7561903589240528</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5909861214386049</v>
+        <v>-0.3801804678041052</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.3785093879905773</v>
+        <v>0.1996642156332425</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.208949816433528</v>
+        <v>1.515330534866538</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0.1992083660483126</v>
+        <v>-0.7520403825971058</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.7217853516347419</v>
+        <v>1.548447498283904</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.6623046504934328</v>
+        <v>-0.5278900080689072</v>
       </c>
       <c r="AD18" t="n">
-        <v>-1.611826251549271</v>
+        <v>-1.567836830136086</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.566546907016034</v>
+        <v>-0.3464976156076882</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.3492750062700154</v>
+        <v>-0.1999700508147336</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.07993046001704719</v>
+        <v>0.287423849945448</v>
       </c>
       <c r="AH18" t="n">
-        <v>-1.163119653952246</v>
+        <v>-1.784119929491923</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.272643788495358</v>
+        <v>0.1315748453728324</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-0.6137015866021267</v>
+        <v>-0.7211847770771389</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.7657418233801926</v>
+        <v>0.2162797469734592</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0.01164516633233365</v>
+        <v>0.8718173941336379</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0.02297228812310289</v>
+        <v>0.9343541825600626</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.3176807142338006</v>
+        <v>-0.7012369084815139</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.6706733653462399</v>
+        <v>-0.4301319579655489</v>
       </c>
       <c r="AP18" t="n">
-        <v>-1.249949842162452</v>
+        <v>0.177972753282696</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.249889592110223</v>
+        <v>-0.177986988573192</v>
       </c>
       <c r="AR18" t="n">
-        <v>-0.2648637218601544</v>
+        <v>-0.2258236132680879</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.2648526205148081</v>
+        <v>0.2258122732559806</v>
       </c>
       <c r="AT18" t="n">
-        <v>-0.5932214668492114</v>
+        <v>0.8828007536569363</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.049056237560002</v>
+        <v>0.3047962063195769</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0.5522846119982416</v>
+        <v>-0.4957345460209878</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.9718503030898986</v>
+        <v>0.245917478115357</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.19531965763854</v>
+        <v>-1.134759246658731</v>
       </c>
       <c r="AY18" t="n">
-        <v>-1.210624800521969</v>
+        <v>1.161474018064329</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-1.267767680225841</v>
+        <v>-0.05803755583222377</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.6491463152018512</v>
+        <v>0.1646314663620712</v>
       </c>
       <c r="BB18" t="n">
-        <v>2.084829678630981</v>
+        <v>-3.012595860855799</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.617592701233439</v>
+        <v>-2.494164437533893</v>
       </c>
       <c r="BD18" t="n">
-        <v>-4.852224949460504</v>
+        <v>0.1508381256170023</v>
       </c>
       <c r="BE18" t="n">
-        <v>-0.05625901763174035</v>
+        <v>0.515454164200188</v>
       </c>
       <c r="BF18" t="n">
-        <v>-0.8896264960597947</v>
+        <v>-0.9581807998264982</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.409367519928038</v>
+        <v>0.5252605284425924</v>
       </c>
       <c r="BH18" t="n">
-        <v>1.104704681314259</v>
+        <v>0.6462088350301897</v>
       </c>
       <c r="BI18" t="n">
-        <v>0.7506754877942258</v>
+        <v>0.2849446098583733</v>
       </c>
       <c r="BJ18" t="n">
-        <v>-0.1272797561564417</v>
+        <v>1.404003370113946</v>
       </c>
       <c r="BK18" t="n">
-        <v>-0.5439459750332744</v>
+        <v>1.184156464638471</v>
       </c>
       <c r="BL18" t="n">
-        <v>-2.971362188778002</v>
+        <v>2.042717936458526</v>
       </c>
       <c r="BM18" t="n">
-        <v>-1.292298624728675</v>
+        <v>1.973738929569219</v>
       </c>
       <c r="BN18" t="n">
-        <v>-1.569311001279533</v>
+        <v>0.451545781129696</v>
       </c>
       <c r="BO18" t="n">
-        <v>-0.9025211174367671</v>
+        <v>-0.6149024639842241</v>
       </c>
       <c r="BP18" t="n">
-        <v>-0.2597441041411541</v>
+        <v>-0.7356052179621529</v>
       </c>
       <c r="BQ18" t="n">
-        <v>-1.158296748301813</v>
+        <v>0.5121362314519678</v>
       </c>
       <c r="BR18" t="n">
-        <v>-1.290553152365283</v>
+        <v>0.4085131666046634</v>
       </c>
       <c r="BS18" t="n">
-        <v>-0.7913308196374228</v>
+        <v>0.9694402303530438</v>
       </c>
       <c r="BT18" t="n">
-        <v>-1.463494609727003</v>
+        <v>0.1185819388017502</v>
       </c>
       <c r="BU18" t="n">
-        <v>-1.697999589850041</v>
+        <v>0.4307250137356852</v>
       </c>
       <c r="BV18" t="n">
-        <v>-1.325390332122655</v>
+        <v>-0.5308528594718587</v>
       </c>
       <c r="BW18" t="n">
-        <v>-1.237667728846138</v>
+        <v>-0.5319323032323316</v>
       </c>
       <c r="BX18" t="n">
-        <v>-0.851502515345254</v>
+        <v>0.1863357304435326</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.3824267855866584</v>
+        <v>-1.512158709756398</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-1.819799562752324</v>
+        <v>0.1508422326660881</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>AJ5eIkmR</t>
+          <t>I5fXHFho</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7576090025467243</v>
+        <v>0.2618506689904143</v>
       </c>
       <c r="C19" t="n">
         <v>1.814519506046163</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.488542156493249</v>
+        <v>-0.3603760621232627</v>
       </c>
       <c r="E19" t="n">
         <v>-0.193078397277103</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1300400965712384</v>
+        <v>-0.8119056097826699</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1295640199872675</v>
+        <v>1.491002957993425</v>
       </c>
       <c r="H19" t="n">
-        <v>1.973604137182928</v>
+        <v>0.4711723181952515</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.948120660813021</v>
+        <v>-2.407577029092517</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5921797699791037</v>
+        <v>-0.0315826725988735</v>
       </c>
       <c r="K19" t="n">
-        <v>1.197340157594788</v>
+        <v>-0.2462592653987741</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.2344159341261454</v>
+        <v>-0.3148070986333641</v>
       </c>
       <c r="M19" t="n">
-        <v>1.089510545134996</v>
+        <v>0.2105251698766709</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.03890727401852558</v>
+        <v>-0.9858072553188754</v>
       </c>
       <c r="O19" t="n">
-        <v>2.591381698731313</v>
+        <v>-0.423564554651254</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2183990788396275</v>
+        <v>-0.7127782779722107</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.536380004029922</v>
+        <v>0.03882142461296942</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.3517933489736969</v>
+        <v>0.07244045277987164</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1654498208545659</v>
+        <v>-0.009470648339543065</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7346765579490433</v>
+        <v>0.4418076306737703</v>
       </c>
       <c r="U19" t="n">
-        <v>1.108652711383622</v>
+        <v>-0.4712340746734379</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3255085140159181</v>
+        <v>0.403060515053895</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.1762866995527007</v>
+        <v>-0.0985802780129711</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5394203336515941</v>
+        <v>-0.134790991994152</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.4690462224985254</v>
+        <v>-0.16956016996703</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.8132118179094073</v>
+        <v>1.07304500930402</v>
       </c>
       <c r="AA19" t="n">
-        <v>-2.81017645206341</v>
+        <v>-1.371826532210142</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8860892127468667</v>
+        <v>0.6665392646041214</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.4256774014067412</v>
+        <v>-1.191868189946558</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.116185923500985</v>
+        <v>-1.743794515788825</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.2361550200537593</v>
+        <v>0.911407973707101</v>
       </c>
       <c r="AF19" t="n">
-        <v>-1.399513653746791</v>
+        <v>-0.6834881453972343</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.76162466845604</v>
+        <v>0.9798607992355055</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.1478809277426271</v>
+        <v>-1.945120000928136</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.9013973867202575</v>
+        <v>1.743390791319004</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-0.9964509795024293</v>
+        <v>-1.160868676621975</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.9027888217701773</v>
+        <v>0.518026881019508</v>
       </c>
       <c r="AL19" t="n">
-        <v>-0.6563340618075023</v>
+        <v>-0.7518435278038242</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.4556909472184804</v>
+        <v>0.8146883737246676</v>
       </c>
       <c r="AN19" t="n">
-        <v>-0.2048424943130504</v>
+        <v>-0.9614110672515772</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.158806244982968</v>
+        <v>0.9773616677461766</v>
       </c>
       <c r="AP19" t="n">
-        <v>-1.543358594651181</v>
+        <v>0.3540180047759335</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.543288889510924</v>
+        <v>-0.3540265670136131</v>
       </c>
       <c r="AR19" t="n">
-        <v>-2.194033489858823</v>
+        <v>-0.6694478684210747</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.194034182248603</v>
+        <v>0.6694392404496844</v>
       </c>
       <c r="AT19" t="n">
-        <v>-0.002812578646752272</v>
+        <v>-0.002812578646752469</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.9002042313119174</v>
+        <v>-1.853557884277657</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0.7055650539892202</v>
+        <v>1.437384814622514</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.32385973932315</v>
+        <v>-0.1071151167670002</v>
       </c>
       <c r="AX19" t="n">
-        <v>-0.2245721746676093</v>
+        <v>0.7584298630828017</v>
       </c>
       <c r="AY19" t="n">
-        <v>-0.3210877435521076</v>
+        <v>-0.7658562720370384</v>
       </c>
       <c r="AZ19" t="n">
-        <v>-0.6629026180290323</v>
+        <v>-0.2164545959313878</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.6491463152018512</v>
+        <v>0.02212709905625383</v>
       </c>
       <c r="BB19" t="n">
-        <v>0.2611929934759068</v>
+        <v>0.3168847836764194</v>
       </c>
       <c r="BC19" t="n">
-        <v>0.7424463178236099</v>
+        <v>0.3736585876755701</v>
       </c>
       <c r="BD19" t="n">
-        <v>-1.137406783423877</v>
+        <v>-1.119135533873708</v>
       </c>
       <c r="BE19" t="n">
-        <v>-0.8264309185912154</v>
+        <v>1.57051214013532</v>
       </c>
       <c r="BF19" t="n">
-        <v>-0.8367984952506048</v>
+        <v>-1.074671712832147</v>
       </c>
       <c r="BG19" t="n">
-        <v>-0.08671646526312979</v>
+        <v>2.273865242013889</v>
       </c>
       <c r="BH19" t="n">
-        <v>-0.7292787038220186</v>
+        <v>1.104704681314259</v>
       </c>
       <c r="BI19" t="n">
-        <v>-0.1807862680774791</v>
+        <v>-0.6465171460133313</v>
       </c>
       <c r="BJ19" t="n">
-        <v>-0.9052571124678203</v>
+        <v>0.1824073944380604</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.7671466405667396</v>
+        <v>-0.6971682795863799</v>
       </c>
       <c r="BL19" t="n">
-        <v>-0.6507283942158947</v>
+        <v>0.4341772786965591</v>
       </c>
       <c r="BM19" t="n">
-        <v>-0.03859064637970749</v>
+        <v>0.3095710499862441</v>
       </c>
       <c r="BN19" t="n">
-        <v>-0.6961678649709097</v>
+        <v>-0.08754821025190562</v>
       </c>
       <c r="BO19" t="n">
-        <v>-1.62061740718929</v>
+        <v>-0.08983838435487664</v>
       </c>
       <c r="BP19" t="n">
-        <v>-0.2709741934308153</v>
+        <v>-0.00794297355995504</v>
       </c>
       <c r="BQ19" t="n">
-        <v>-1.478003900187891</v>
+        <v>-0.1265620014325971</v>
       </c>
       <c r="BR19" t="n">
-        <v>-0.831494340203122</v>
+        <v>-0.09875493792051843</v>
       </c>
       <c r="BS19" t="n">
-        <v>0.1249431579727408</v>
+        <v>0.411365771096446</v>
       </c>
       <c r="BT19" t="n">
-        <v>-1.298373083371704</v>
+        <v>-0.06472839306557042</v>
       </c>
       <c r="BU19" t="n">
-        <v>-0.6673686128563281</v>
+        <v>-0.1190369285333109</v>
       </c>
       <c r="BV19" t="n">
-        <v>-1.111985811466869</v>
+        <v>-0.1722023052316627</v>
       </c>
       <c r="BW19" t="n">
-        <v>-1.021412253196115</v>
+        <v>-0.0711861106250308</v>
       </c>
       <c r="BX19" t="n">
-        <v>-1.043655013601767</v>
+        <v>-0.1484769425421064</v>
       </c>
       <c r="BY19" t="n">
-        <v>-0.09764365617091551</v>
+        <v>-0.2941489479037044</v>
       </c>
       <c r="BZ19" t="n">
-        <v>-0.7953898547986179</v>
+        <v>-0.1071042689503714</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>8Kjh0jRr</t>
+          <t>McP0d8Q7</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.6130169784618973</v>
+        <v>-0.7588282530372826</v>
       </c>
       <c r="C20" t="n">
-        <v>0.01220274180270737</v>
+        <v>-0.1998345245788756</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2519730554222272</v>
+        <v>-1.627796328670905</v>
       </c>
       <c r="E20" t="n">
         <v>-0.193078397277103</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1300400965712384</v>
+        <v>2.597421956274488</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1295640199872675</v>
+        <v>-5.316191732037364</v>
       </c>
       <c r="H20" t="n">
-        <v>-5.377103455590049</v>
+        <v>0.7994866535140929</v>
       </c>
       <c r="I20" t="n">
-        <v>6.17044829557252</v>
+        <v>-1.983479651219303</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.889256031143592</v>
+        <v>-0.4214341992101092</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1829189414371499</v>
+        <v>0.3389837439229406</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6420365156758087</v>
+        <v>0.4201439202237902</v>
       </c>
       <c r="M20" t="n">
-        <v>1.510327872626262</v>
+        <v>-0.2393079314552869</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9858072553188754</v>
+        <v>1.184171868494426</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8572949647596405</v>
+        <v>0.4237732812667223</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.114635048054644</v>
+        <v>0.4502841289618508</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.599331609269422</v>
+        <v>0.1462450895472876</v>
       </c>
       <c r="R20" t="n">
-        <v>-2.388115597390825</v>
+        <v>-0.0124063075708422</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3403702900486752</v>
+        <v>0.6902112284368935</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.310976696856355</v>
+        <v>0.2199847663806969</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5236551106596683</v>
+        <v>1.067670452292923</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.38063550881957</v>
+        <v>0.01530050986401119</v>
       </c>
       <c r="W20" t="n">
-        <v>0.9116032020035115</v>
+        <v>0.4453646727651349</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8223688752364477</v>
+        <v>-0.4938860582867076</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.7577662187455315</v>
+        <v>0.761669029956107</v>
       </c>
       <c r="Z20" t="n">
-        <v>-0.5533538638825638</v>
+        <v>-2.053843221170732</v>
       </c>
       <c r="AA20" t="n">
-        <v>-1.441522398539419</v>
+        <v>-0.2758467481506092</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9539840192493229</v>
+        <v>-0.6727503420501195</v>
       </c>
       <c r="AC20" t="n">
-        <v>-1.2591748421367</v>
+        <v>-1.055169149560042</v>
       </c>
       <c r="AD20" t="n">
-        <v>-1.941746912148157</v>
+        <v>1.401449115253893</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.220367241258102</v>
+        <v>-2.045773587138193</v>
       </c>
       <c r="AF20" t="n">
-        <v>-1.796553023466749</v>
+        <v>0.8106237909257208</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.139179614859853</v>
+        <v>-0.353427946014394</v>
       </c>
       <c r="AH20" t="n">
-        <v>-2.037120041748829</v>
+        <v>1.458881509437501</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.4683722072123309</v>
+        <v>-1.79298150799573</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-1.429440454104778</v>
+        <v>-0.03882237025584196</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.8262787619475065</v>
+        <v>-0.286006642285388</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.6324566953084223</v>
+        <v>1.086713692625361</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.484816903202883</v>
+        <v>-1.435028832380773</v>
       </c>
       <c r="AN20" t="n">
-        <v>-0.07761646124930524</v>
+        <v>1.095616606348528</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.800237392225858</v>
+        <v>0.7463211339687336</v>
       </c>
       <c r="AP20" t="n">
-        <v>-1.015222840171469</v>
+        <v>-0.4284053351940106</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.015170154189661</v>
+        <v>0.428371559388258</v>
       </c>
       <c r="AR20" t="n">
-        <v>-3.076169081757357</v>
+        <v>-1.259238252469865</v>
       </c>
       <c r="AS20" t="n">
-        <v>3.07617516697139</v>
+        <v>1.259233230107315</v>
       </c>
       <c r="AT20" t="n">
-        <v>-0.1504148006973671</v>
+        <v>-0.002812578646752469</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.1559442000714918</v>
+        <v>-1.332575862409359</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.8803170594255287</v>
+        <v>0.3173258453052292</v>
       </c>
       <c r="AW20" t="n">
-        <v>-1.196269067500734</v>
+        <v>-0.2899692797389152</v>
       </c>
       <c r="AX20" t="n">
-        <v>-2.955133390640974</v>
+        <v>-0.1153497260286747</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.902754898872546</v>
+        <v>0.1236807849328232</v>
       </c>
       <c r="AZ20" t="n">
-        <v>-0.1156437522319199</v>
+        <v>-0.2884623414310081</v>
       </c>
       <c r="BA20" t="n">
-        <v>-0.291382509016545</v>
+        <v>-1.174909586312614</v>
       </c>
       <c r="BB20" t="n">
-        <v>0.6063910831867287</v>
+        <v>0.04562305135573294</v>
       </c>
       <c r="BC20" t="n">
-        <v>0.5432358615709714</v>
+        <v>0.07340506651637355</v>
       </c>
       <c r="BD20" t="n">
-        <v>-0.0618565062189479</v>
+        <v>4.304237091687787</v>
       </c>
       <c r="BE20" t="n">
-        <v>-0.937423285668889</v>
+        <v>-4.920959529637039</v>
       </c>
       <c r="BF20" t="n">
-        <v>-1.082291949606378</v>
+        <v>0.7386260576296991</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.358765881597024</v>
+        <v>-1.312853430445029</v>
       </c>
       <c r="BH20" t="n">
         <v>-0.2707828575379491</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.68213724366593</v>
+        <v>-0.1807862680774791</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.299200058122946</v>
+        <v>-1.09421243853126</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.095929259061446</v>
+        <v>-1.922975557856788</v>
       </c>
       <c r="BL20" t="n">
-        <v>-0.3830176088011811</v>
+        <v>0.1435460865404678</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.9500946615386422</v>
+        <v>-0.0409219194518272</v>
       </c>
       <c r="BN20" t="n">
-        <v>-2.180157601270191</v>
+        <v>-0.1328793106194862</v>
       </c>
       <c r="BO20" t="n">
-        <v>-1.911069675654538</v>
+        <v>-0.3529056707951981</v>
       </c>
       <c r="BP20" t="n">
-        <v>-1.339355291029787</v>
+        <v>-0.256574666279084</v>
       </c>
       <c r="BQ20" t="n">
-        <v>-1.223651785446806</v>
+        <v>-0.2219904348851447</v>
       </c>
       <c r="BR20" t="n">
-        <v>-2.34707291749995</v>
+        <v>-0.3385511928846666</v>
       </c>
       <c r="BS20" t="n">
-        <v>0.4481846916654893</v>
+        <v>0.3632178742969953</v>
       </c>
       <c r="BT20" t="n">
-        <v>-1.955919533055946</v>
+        <v>-0.4362426975372312</v>
       </c>
       <c r="BU20" t="n">
-        <v>-1.670609201737649</v>
+        <v>-0.008240498202003508</v>
       </c>
       <c r="BV20" t="n">
-        <v>-2.027381824102029</v>
+        <v>-0.4411902209118108</v>
       </c>
       <c r="BW20" t="n">
-        <v>-1.901799019801653</v>
+        <v>-0.7623136264122159</v>
       </c>
       <c r="BX20" t="n">
-        <v>-2.146908826657831</v>
+        <v>-0.8056071140455668</v>
       </c>
       <c r="BY20" t="n">
-        <v>-1.275516148234406</v>
+        <v>-0.5912451527408402</v>
       </c>
       <c r="BZ20" t="n">
-        <v>-2.291613717656634</v>
+        <v>0.02519228078804529</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2g2mKBIE</t>
+          <t>0lpzB7u1</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1.662858155404671</v>
+        <v>0.3784996886507226</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3756951984568496</v>
+        <v>-1.047983590105207</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3888574164277042</v>
+        <v>-1.314501431322049</v>
       </c>
       <c r="E21" t="n">
         <v>-0.193078397277103</v>
       </c>
       <c r="F21" t="n">
-        <v>1.233690929851626</v>
+        <v>-5.584964202262691</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.593313856025048</v>
+        <v>2.852441895999583</v>
       </c>
       <c r="H21" t="n">
-        <v>5.809116259791445</v>
+        <v>-0.7439541700881322</v>
       </c>
       <c r="I21" t="n">
-        <v>-6.721422806181894</v>
+        <v>0.460192620111682</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.513018473721569</v>
+        <v>0.5921797699791037</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.29969668217786</v>
+        <v>1.275372558837683</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5028904337237732</v>
+        <v>-1.246709513477213</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.317061453327588</v>
+        <v>0.8394956257624219</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.459257245969051</v>
+        <v>0.7501760437317656</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2856258371762345</v>
+        <v>1.960804704559795</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5576822075822021</v>
+        <v>-0.2491951173990537</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.292350229146064</v>
+        <v>0.8600036030024055</v>
       </c>
       <c r="R21" t="n">
-        <v>-1.709341514585116</v>
+        <v>-0.3517933489736969</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.408834401892417</v>
+        <v>-0.1843911175336523</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.126474753435829</v>
+        <v>-1.35671480311884</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.298123595215551</v>
+        <v>1.08284906677096</v>
       </c>
       <c r="V21" t="n">
         <v>-0.4500114963638492</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.4871123857116184</v>
+        <v>0.9116032020035115</v>
       </c>
       <c r="X21" t="n">
-        <v>0.5145384754046394</v>
+        <v>-1.051052124846767</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.9664333504487467</v>
+        <v>1.215833008197282</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.827537998336899</v>
+        <v>1.501691803332643</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.5935833594641792</v>
+        <v>-1.086846159560748</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.3352958128287119</v>
+        <v>0.9151572584137988</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.5944247061089669</v>
+        <v>-0.3995270908868673</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.1257558942715317</v>
+        <v>0.5216606869901956</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.132093164814959</v>
+        <v>-1.560266166700906</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.1485332318167943</v>
+        <v>-0.2681718482869729</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.2201303832396152</v>
+        <v>0.1453967233839127</v>
       </c>
       <c r="AH21" t="n">
-        <v>-1.025119592721207</v>
+        <v>0.5848811216409182</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.056131198741395</v>
+        <v>0.08346093653861836</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.4426610841732618</v>
+        <v>-0.4314108265470228</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.1300952437256394</v>
+        <v>0.1188124091936782</v>
       </c>
       <c r="AL21" t="n">
-        <v>-1.372655056779912</v>
+        <v>1.325487357616164</v>
       </c>
       <c r="AM21" t="n">
-        <v>-0.4059028763963689</v>
+        <v>-0.6931008176013191</v>
       </c>
       <c r="AN21" t="n">
-        <v>-0.5583139357123373</v>
+        <v>0.1133914710898659</v>
       </c>
       <c r="AO21" t="n">
-        <v>-0.2359553744170403</v>
+        <v>-0.1160533234518232</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.8430325922571492</v>
+        <v>0.7256690912616568</v>
       </c>
       <c r="AQ21" t="n">
-        <v>-0.8430253960147832</v>
+        <v>-0.7256656770545021</v>
       </c>
       <c r="AR21" t="n">
-        <v>-0.4610322013971533</v>
+        <v>-0.4207439640614934</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.4610222993029699</v>
+        <v>0.4207338156702719</v>
       </c>
       <c r="AT21" t="n">
         <v>0.2923918654544772</v>
       </c>
       <c r="AU21" t="n">
-        <v>-1.779131881153615</v>
+        <v>0.9002042313119174</v>
       </c>
       <c r="AV21" t="n">
-        <v>-1.048518205310605</v>
+        <v>2.030168400963028</v>
       </c>
       <c r="AW21" t="n">
-        <v>-1.471729893207182</v>
+        <v>0.6234025471021185</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.231727140518185</v>
+        <v>1.959876798111082</v>
       </c>
       <c r="AY21" t="n">
-        <v>-1.24768884456238</v>
+        <v>-0.8770484041582712</v>
       </c>
       <c r="AZ21" t="n">
-        <v>-0.05803755583222377</v>
+        <v>0.3452058189656487</v>
       </c>
       <c r="BA21" t="n">
-        <v>0.5636436948183606</v>
+        <v>0.2216332132843984</v>
       </c>
       <c r="BB21" t="n">
-        <v>-0.09226705534416699</v>
+        <v>0.4795583976641717</v>
       </c>
       <c r="BC21" t="n">
-        <v>-0.1794278333157332</v>
+        <v>0.4410253910104378</v>
       </c>
       <c r="BD21" t="n">
-        <v>-3.563275681695259</v>
+        <v>1.770647036136435</v>
       </c>
       <c r="BE21" t="n">
-        <v>-0.2721499185201052</v>
+        <v>-0.1467350884944564</v>
       </c>
       <c r="BF21" t="n">
-        <v>-0.8383421105449602</v>
+        <v>0.5590704766420728</v>
       </c>
       <c r="BG21" t="n">
-        <v>-0.1299908216498068</v>
+        <v>-0.1688736622168747</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.563200527598329</v>
+        <v>0.6462088350301897</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.147868121601783</v>
+        <v>0.2849446098583733</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1.8709692136197</v>
+        <v>-0.7621619116240782</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.6955388929988664</v>
+        <v>0.2883575832991953</v>
       </c>
       <c r="BL21" t="n">
-        <v>-0.123590509209274</v>
+        <v>-0.07884549907279725</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.549776649460291</v>
+        <v>-0.298172834977861</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.223084232994966</v>
+        <v>-2.153297398252198</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.385501680266975</v>
+        <v>-0.9480992635118624</v>
       </c>
       <c r="BP21" t="n">
-        <v>-0.7642500833966542</v>
+        <v>-1.373416040486706</v>
       </c>
       <c r="BQ21" t="n">
-        <v>0.3971443635501917</v>
+        <v>-0.2148764037950985</v>
       </c>
       <c r="BR21" t="n">
-        <v>1.485361941929458</v>
+        <v>-2.104318624964662</v>
       </c>
       <c r="BS21" t="n">
-        <v>0.5011326865827175</v>
+        <v>-1.989191912231359</v>
       </c>
       <c r="BT21" t="n">
-        <v>0.9707706658296217</v>
+        <v>-1.269409044445409</v>
       </c>
       <c r="BU21" t="n">
-        <v>0.5063427892774189</v>
+        <v>-1.05918644933132</v>
       </c>
       <c r="BV21" t="n">
-        <v>0.2262569723526237</v>
+        <v>-2.067246354067628</v>
       </c>
       <c r="BW21" t="n">
-        <v>0.1687247291331343</v>
+        <v>-1.557974636139778</v>
       </c>
       <c r="BX21" t="n">
-        <v>1.267357888772379</v>
+        <v>-1.766382713942862</v>
       </c>
       <c r="BY21" t="n">
-        <v>-0.3774529832256418</v>
+        <v>-1.243369754732229</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0.1765842715179003</v>
+        <v>-1.436086314292996</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>SznSCTAl</t>
+          <t>GMBD7YY8</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2035261591602602</v>
+        <v>-1.692020410319748</v>
       </c>
       <c r="C22" t="n">
-        <v>-1.547785718004653</v>
+        <v>0.3756951984568496</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4315794478843663</v>
+        <v>-1.314501431322049</v>
       </c>
       <c r="E22" t="n">
         <v>-0.193078397277103</v>
       </c>
       <c r="F22" t="n">
-        <v>1.915556443063057</v>
+        <v>-1.493771122994101</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.954752794031207</v>
+        <v>-1.23187491801889</v>
       </c>
       <c r="H22" t="n">
-        <v>5.585001251089563</v>
+        <v>2.571899467430932</v>
       </c>
       <c r="I22" t="n">
-        <v>-5.453808602509783</v>
+        <v>-3.21220304577571</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9820312965903392</v>
+        <v>-0.9672263364658392</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2852754660202216</v>
+        <v>-0.2462592653987741</v>
       </c>
       <c r="L22" t="n">
-        <v>1.775881622178695</v>
+        <v>0.1576246540934551</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2948269840619764</v>
+        <v>-0.2976052995403432</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5123572646687005</v>
+        <v>0.335907301912863</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1478958463166837</v>
+        <v>-1.25119685950137</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9229220664288097</v>
+        <v>0.3313251598844033</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.3094393433811286</v>
+        <v>-0.6974001614596482</v>
       </c>
       <c r="R22" t="n">
-        <v>1.684528899443432</v>
+        <v>-1.879035035286543</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.283436747862962</v>
+        <v>0.4278305246457297</v>
       </c>
       <c r="T22" t="n">
-        <v>1.71211749685449</v>
+        <v>-0.04504601106246832</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1252306582763833</v>
+        <v>0.8708905574526674</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9459245223197321</v>
+        <v>-1.38063550881957</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.9533509149499951</v>
+        <v>1.1447224666227</v>
       </c>
       <c r="X22" t="n">
-        <v>0.4042233158150066</v>
+        <v>-0.362276514633422</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.2837268300194592</v>
+        <v>0.2409266976372108</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.883837402616812</v>
+        <v>0.0100861832687151</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.5151292370279656</v>
+        <v>0.6763780898308062</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.2650357013005428</v>
+        <v>0.1751764297921763</v>
       </c>
       <c r="AC22" t="n">
-        <v>-0.5573231600841592</v>
+        <v>0.4559652009020236</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.1821700556207624</v>
+        <v>-1.281905590950384</v>
       </c>
       <c r="AE22" t="n">
-        <v>-1.074758746263619</v>
+        <v>1.102668472667244</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.933654687065258</v>
+        <v>-0.6069830775681739</v>
       </c>
       <c r="AG22" t="n">
-        <v>-2.200226612634693</v>
+        <v>0.8914939401970551</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.2431192457453176</v>
+        <v>-0.7184527899855643</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.08346093653861836</v>
+        <v>0.2438406326526654</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.133558839695375</v>
+        <v>-0.2500241500458313</v>
       </c>
       <c r="AK22" t="n">
-        <v>-1.103836267024814</v>
+        <v>0.3919159450475307</v>
       </c>
       <c r="AL22" t="n">
-        <v>-0.2742961978222175</v>
+        <v>3.008841695801327</v>
       </c>
       <c r="AM22" t="n">
-        <v>-1.243563538244139</v>
+        <v>1.137786057580236</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.2005752507193688</v>
+        <v>1.956856180459141</v>
       </c>
       <c r="AO22" t="n">
-        <v>-2.179694850711041</v>
+        <v>0.952776256042559</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.39072893023611</v>
+        <v>0.08995012753607726</v>
       </c>
       <c r="AQ22" t="n">
-        <v>-1.390704084496093</v>
+        <v>-0.08996719935298149</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.989661694405811</v>
+        <v>-1.477602132748316</v>
       </c>
       <c r="AS22" t="n">
-        <v>-2.989692691880236</v>
+        <v>1.477598445325701</v>
       </c>
       <c r="AT22" t="n">
-        <v>-1.036028133001056</v>
+        <v>-0.2242159117226746</v>
       </c>
       <c r="AU22" t="n">
-        <v>-0.2906118186727635</v>
+        <v>-0.5138898280448911</v>
       </c>
       <c r="AV22" t="n">
-        <v>-1.617310854569861</v>
+        <v>-0.5819060751291842</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.3233503127793075</v>
+        <v>-0.04030746430317733</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.9768747603606711</v>
+        <v>0.3215400685270635</v>
       </c>
       <c r="AY22" t="n">
-        <v>-0.09870347930964227</v>
+        <v>-0.3210877435521076</v>
       </c>
       <c r="AZ22" t="n">
-        <v>-1.238964582025993</v>
+        <v>0.9644724302623809</v>
       </c>
       <c r="BA22" t="n">
-        <v>-0.291382509016545</v>
+        <v>0.8629028661605777</v>
       </c>
       <c r="BB22" t="n">
-        <v>-0.3841730202584107</v>
+        <v>0.2612836475022781</v>
       </c>
       <c r="BC22" t="n">
-        <v>-0.1546650617213482</v>
+        <v>0.06777688604698147</v>
       </c>
       <c r="BD22" t="n">
-        <v>-1.605163578133513</v>
+        <v>0.8770541961183675</v>
       </c>
       <c r="BE22" t="n">
-        <v>0.5598900422396587</v>
+        <v>0.03526167056343001</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.806625740427696</v>
+        <v>-0.0692309081156023</v>
       </c>
       <c r="BG22" t="n">
-        <v>0.2830479020640683</v>
+        <v>0.6272678730560726</v>
       </c>
       <c r="BH22" t="n">
-        <v>2.480192220166467</v>
+        <v>-0.5000307806799837</v>
       </c>
       <c r="BI22" t="n">
-        <v>-1.112248023949184</v>
+        <v>1.68213724366593</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.4352324126775785</v>
+        <v>-1.241495589327253</v>
       </c>
       <c r="BK22" t="n">
-        <v>-0.7395802134866798</v>
+        <v>-0.1382133125766507</v>
       </c>
       <c r="BL22" t="n">
-        <v>-0.4756797936574723</v>
+        <v>-0.2906295482721281</v>
       </c>
       <c r="BM22" t="n">
-        <v>-0.1526671863778226</v>
+        <v>-0.2822847021927058</v>
       </c>
       <c r="BN22" t="n">
-        <v>4.271791735145901</v>
+        <v>-0.6304497144600169</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.847648068182665</v>
+        <v>0.0223281162065386</v>
       </c>
       <c r="BP22" t="n">
-        <v>-0.1978736789566336</v>
+        <v>-0.4657061688861148</v>
       </c>
       <c r="BQ22" t="n">
-        <v>2.395346707787056</v>
+        <v>-0.4365747717741214</v>
       </c>
       <c r="BR22" t="n">
-        <v>3.593420770160806</v>
+        <v>-0.6144081478900413</v>
       </c>
       <c r="BS22" t="n">
-        <v>-0.6139745338096708</v>
+        <v>-0.66421804074716</v>
       </c>
       <c r="BT22" t="n">
-        <v>4.087682756170034</v>
+        <v>-0.487498190074905</v>
       </c>
       <c r="BU22" t="n">
-        <v>2.395695705112367</v>
+        <v>-0.6037725916361172</v>
       </c>
       <c r="BV22" t="n">
-        <v>3.663051951449357</v>
+        <v>-0.3083704617170486</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.93477948792635</v>
+        <v>-0.1473393794999532</v>
       </c>
       <c r="BX22" t="n">
-        <v>3.197662413480505</v>
+        <v>-0.3965841226162725</v>
       </c>
       <c r="BY22" t="n">
-        <v>-0.9588544588398877</v>
+        <v>0.8802914872579246</v>
       </c>
       <c r="BZ22" t="n">
-        <v>2.402562361816049</v>
+        <v>-0.699052224550194</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.9338017825277449</v>
+        <v>2.040748218810115</v>
       </c>
       <c r="C23" t="n">
-        <v>-1.74467746535898</v>
+        <v>-0.1998345245788756</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9355255587288207</v>
+        <v>1.490911967665428</v>
       </c>
       <c r="E23" t="n">
         <v>-0.193078397277103</v>
       </c>
       <c r="F23" t="n">
-        <v>3.961152982697352</v>
+        <v>1.233690929851625</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.912594387021969</v>
+        <v>-0.5511554490158114</v>
       </c>
       <c r="H23" t="n">
-        <v>3.28892101487911</v>
+        <v>3.667572843306799</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.177172429895981</v>
+        <v>-4.219017138445961</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9040609912680919</v>
+        <v>-0.889256031143592</v>
       </c>
       <c r="K23" t="n">
-        <v>0.02685413895135955</v>
+        <v>-0.05117826229153585</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.3920818832660227</v>
+        <v>-0.3185658149102028</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9226639384309325</v>
+        <v>-0.05441901098206892</v>
       </c>
       <c r="N23" t="n">
-        <v>0.04000105775650328</v>
+        <v>-2.208886397831828</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.019712571147906</v>
+        <v>0.5420064676738818</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.7206896374590986</v>
+        <v>-0.2630177633848626</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1698176331318619</v>
+        <v>0.2193976305133965</v>
       </c>
       <c r="R23" t="n">
-        <v>1.17544833733915</v>
+        <v>-0.01240630757084208</v>
       </c>
       <c r="S23" t="n">
-        <v>1.040052166825112</v>
+        <v>-1.583754871086526</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.03517547749214495</v>
+        <v>0.4024181774588639</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4541784525715656</v>
+        <v>0.2870412090577342</v>
       </c>
       <c r="V23" t="n">
-        <v>0.7908205202437788</v>
+        <v>0.6357165181678253</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6425252287910773</v>
+        <v>-0.3316995426321596</v>
       </c>
       <c r="X23" t="n">
-        <v>0.2674470258141952</v>
+        <v>0.5909861214386049</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.1064276921676032</v>
+        <v>-0.3785093879905773</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.082037800689272</v>
+        <v>3.208949816433528</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.5349114096649893</v>
+        <v>-0.1992083660483126</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.619261802286594</v>
+        <v>0.7217853516347419</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.2412664260589587</v>
+        <v>-0.6623046504934328</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.4461065840998716</v>
+        <v>-1.611826251549271</v>
       </c>
       <c r="AE23" t="n">
-        <v>-1.560266166700906</v>
+        <v>2.566546907016034</v>
       </c>
       <c r="AF23" t="n">
-        <v>-0.8553181407004894</v>
+        <v>-0.3492750062700154</v>
       </c>
       <c r="AG23" t="n">
-        <v>-0.3615315958782654</v>
+        <v>-0.07993046001704719</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.3351192865660105</v>
+        <v>-1.163119653952246</v>
       </c>
       <c r="AI23" t="n">
-        <v>-2.514690140508941</v>
+        <v>2.272643788495358</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-0.6201874034019308</v>
+        <v>-0.6137015866021267</v>
       </c>
       <c r="AK23" t="n">
-        <v>-0.3759167299619542</v>
+        <v>0.7657418233801926</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.0389589596272</v>
+        <v>-0.01164516633233365</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.1924261677806094</v>
+        <v>-0.02297228812310289</v>
       </c>
       <c r="AN23" t="n">
-        <v>0.7649658858371895</v>
+        <v>0.3176807142338006</v>
       </c>
       <c r="AO23" t="n">
-        <v>1.137311463888542</v>
+        <v>-0.6706733653462399</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.195123095243624</v>
+        <v>-1.249949842162452</v>
       </c>
       <c r="AQ23" t="n">
-        <v>-1.195104552895625</v>
+        <v>1.249889592110223</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.5351453483259503</v>
+        <v>-0.2648637218601544</v>
       </c>
       <c r="AS23" t="n">
-        <v>-0.5351613404254585</v>
+        <v>0.2648526205148081</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.8828007536569363</v>
+        <v>-0.5932214668492114</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.3047962063195767</v>
+        <v>1.049056237560002</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.3674855787494498</v>
+        <v>-0.5522846119982416</v>
       </c>
       <c r="AW23" t="n">
-        <v>-0.661071533794013</v>
+        <v>0.9718503030898986</v>
       </c>
       <c r="AX23" t="n">
-        <v>-0.1881646917879646</v>
+        <v>1.19531965763854</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.2719369610944668</v>
+        <v>-1.210624800521969</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.08597793516701646</v>
+        <v>-1.267767680225841</v>
       </c>
       <c r="BA23" t="n">
-        <v>-0.3768851294000356</v>
+        <v>0.6491463152018512</v>
       </c>
       <c r="BB23" t="n">
-        <v>0.2817981204110301</v>
+        <v>2.084829678630981</v>
       </c>
       <c r="BC23" t="n">
-        <v>0.73577389835181</v>
+        <v>3.617592701233439</v>
       </c>
       <c r="BD23" t="n">
-        <v>0.7630981352655806</v>
+        <v>-4.852224949460504</v>
       </c>
       <c r="BE23" t="n">
-        <v>0.8677204258211082</v>
+        <v>-0.05625901763174035</v>
       </c>
       <c r="BF23" t="n">
-        <v>-0.06268433615126072</v>
+        <v>-0.8896264960597947</v>
       </c>
       <c r="BG23" t="n">
-        <v>0.4715068136199105</v>
+        <v>1.409367519928038</v>
       </c>
       <c r="BH23" t="n">
-        <v>-1.187774550106088</v>
+        <v>1.104704681314259</v>
       </c>
       <c r="BI23" t="n">
-        <v>-0.6465171460133313</v>
+        <v>0.7506754877942258</v>
       </c>
       <c r="BJ23" t="n">
-        <v>-0.8791342563300172</v>
+        <v>-0.1272797561564417</v>
       </c>
       <c r="BK23" t="n">
-        <v>-0.1795292563455588</v>
+        <v>-0.5439459750332744</v>
       </c>
       <c r="BL23" t="n">
-        <v>-0.1585252202871176</v>
+        <v>-2.971362188778002</v>
       </c>
       <c r="BM23" t="n">
-        <v>-1.428495651991231</v>
+        <v>-1.292298624728675</v>
       </c>
       <c r="BN23" t="n">
-        <v>-0.04361012845143337</v>
+        <v>-1.569311001279533</v>
       </c>
       <c r="BO23" t="n">
-        <v>0.9683385472456102</v>
+        <v>-0.9025211174367671</v>
       </c>
       <c r="BP23" t="n">
-        <v>2.201435754384585</v>
+        <v>-0.2597441041411541</v>
       </c>
       <c r="BQ23" t="n">
-        <v>-0.1958613860212668</v>
+        <v>-1.158296748301813</v>
       </c>
       <c r="BR23" t="n">
-        <v>-0.09671297396678527</v>
+        <v>-1.290553152365283</v>
       </c>
       <c r="BS23" t="n">
-        <v>0.05432887954270438</v>
+        <v>-0.7913308196374228</v>
       </c>
       <c r="BT23" t="n">
-        <v>0.2793231050743081</v>
+        <v>-1.463494609727003</v>
       </c>
       <c r="BU23" t="n">
-        <v>-0.6073918650591004</v>
+        <v>-1.697999589850041</v>
       </c>
       <c r="BV23" t="n">
-        <v>0.8851471503187952</v>
+        <v>-1.325390332122655</v>
       </c>
       <c r="BW23" t="n">
-        <v>0.6816703819950299</v>
+        <v>-1.237667728846138</v>
       </c>
       <c r="BX23" t="n">
-        <v>0.04403614831055737</v>
+        <v>-0.851502515345254</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.977095827796441</v>
+        <v>0.3824267855866584</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0.2622024813253664</v>
+        <v>-1.819799562752324</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>AJ5eIkmR</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.9338017825277449</v>
+        <v>-0.5838547235468203</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.9116739188599041</v>
+        <v>1.814519506046163</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9355255587288207</v>
+        <v>-0.488542156493249</v>
       </c>
       <c r="E24" t="n">
         <v>-0.193078397277103</v>
       </c>
       <c r="F24" t="n">
+        <v>-0.1300400965712384</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.1295640199872675</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.973604137182928</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-2.948120660813021</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.5921797699791037</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.197340157594788</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.2344159341261454</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.089510545134996</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.03890727401852558</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.591381698731313</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.2183990788396275</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.536380004029922</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-0.3517933489736969</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.1654498208545659</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.7346765579490433</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.108652711383622</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.3255085140159181</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-0.1762866995527007</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.5394203336515941</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.4690462224985254</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.8132118179094073</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-2.81017645206341</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.8860892127468667</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>-0.4256774014067412</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>-0.116185923500985</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>-0.2361550200537593</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-1.399513653746791</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.76162466845604</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.1478809277426271</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.9013973867202575</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>-0.9964509795024293</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0.9027888217701773</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>-0.6563340618075023</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0.4556909472184804</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>-0.2048424943130504</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1.158806244982968</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>-1.543358594651181</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.543288889510924</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>-2.194033489858823</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.194034182248603</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>-0.002812578646752272</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0.9002042313119174</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>-0.7055650539892202</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0.32385973932315</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>-0.2245721746676093</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>-0.3210877435521076</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>-0.6629026180290323</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0.6491463152018512</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0.2611929934759068</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0.7424463178236099</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>-1.137406783423877</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>-0.8264309185912154</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>-0.8367984952506048</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>-0.08671646526312979</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>-0.7292787038220186</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>-0.1807862680774791</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>-0.9052571124678203</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>0.7671466405667396</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>-0.6507283942158947</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>0.1247505082184748</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>-0.7006663453063869</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>-1.697127247470041</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>-0.223232751039981</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>-1.494408399563989</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>-0.825458295277495</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>-0.02143307395753694</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>-1.352086108801616</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>-0.6672350715308664</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>-1.154547661472137</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>-1.031246515453419</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>-1.081635353832074</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>-0.1989900413594523</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>-0.7855205016857175</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>8Kjh0jRr</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-1.750344920149903</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.01220274180270737</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.2519730554222272</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.193078397277103</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.1300400965712384</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.1295640199872675</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-5.377103455590049</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6.17044829557252</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.889256031143592</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.1829189414371499</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.6420365156758087</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.510327872626262</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.9858072553188754</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.8572949647596405</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.114635048054644</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.599331609269422</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-2.388115597390825</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.3403702900486752</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-1.310976696856355</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.5236551106596683</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1.38063550881957</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.9116032020035115</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.8223688752364477</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.7577662187455315</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-0.5533538638825638</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-1.441522398539419</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.9539840192493229</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>-1.2591748421367</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>-1.941746912148157</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.220367241258102</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>-1.796553023466749</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.139179614859853</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>-2.037120041748829</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0.4683722072123309</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>-1.429440454104778</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0.8262787619475065</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>-0.6324566953084223</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.484816903202883</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>-0.07761646124930524</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1.800237392225858</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>-1.015222840171469</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.015170154189661</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>-3.076169081757357</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>3.07617516697139</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>-0.1504148006973671</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0.1559442000714918</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0.8803170594255287</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>-1.196269067500734</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>-2.955133390640974</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.902754898872546</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>-0.1156437522319199</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>-0.291382509016545</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0.6063910831867287</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0.5432358615709714</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>-0.0618565062189479</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>-0.937423285668889</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>-1.082291949606378</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.358765881597024</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>-0.2707828575379491</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>1.68213724366593</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>0.299200058122946</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>1.095929259061446</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>-0.3830176088011811</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>0.9808370581812944</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>-2.186079423090327</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>-1.882746132409181</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>-1.318899567747015</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>-1.199891949156967</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>-2.355648148970509</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>0.5172154978586955</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>-1.943419508823373</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>-1.725294374513525</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>-2.027381824102029</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>-1.884452683681191</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>-2.107761169015057</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>-1.302982318222942</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>-2.322884765852235</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>2g2mKBIE</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.632476649999036</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.3756951984568496</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.3888574164277042</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.193078397277103</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.233690929851626</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-2.593313856025048</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5.809116259791445</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-6.721422806181894</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1.513018473721569</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-1.29969668217786</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.5028904337237732</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.317061453327588</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.459257245969051</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.2856258371762345</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.5576822075822021</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-1.292350229146064</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-1.709341514585116</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-1.408834401892417</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.126474753435829</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-1.298123595215551</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.4500114963638492</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-0.4871123857116184</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.5145384754046394</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>-0.9664333504487467</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.827537998336899</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.5935833594641792</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.3352958128287119</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.5944247061089669</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.1257558942715317</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.132093164814959</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>-0.1485332318167943</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.2201303832396152</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>-1.025119592721207</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>2.056131198741395</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0.4426610841732618</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0.1300952437256394</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>-1.372655056779912</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>-0.4059028763963689</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>-0.5583139357123373</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>-0.2359553744170403</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0.8430325922571492</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>-0.8430253960147832</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>-0.4610322013971533</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0.4610222993029699</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0.2923918654544772</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>-1.779131881153615</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>-1.048518205310605</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>-1.471729893207182</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.231727140518185</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>-1.24768884456238</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>-0.05803755583222377</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0.5636436948183606</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>-0.09226705534416699</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>-0.1794278333157332</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>-3.563275681695259</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>-0.2721499185201052</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>-0.8383421105449602</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>-0.1299908216498068</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>1.563200527598329</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>2.147868121601783</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>1.8709692136197</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>0.6955388929988664</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>-0.123590509209274</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>1.549776649460291</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>1.223084232994966</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>0.385501680266975</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>-0.7642500833966542</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0.3971443635501917</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>1.485361941929458</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>0.5011326865827175</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>0.9707706658296217</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>0.5063427892774189</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>0.2262569723526237</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>0.1687247291331343</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>1.267357888772379</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>-0.3774529832256418</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>0.1765842715179003</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>SznSCTAl</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-1.137937566933284</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-1.547785718004653</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.4315794478843663</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.193078397277103</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.915556443063057</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-3.954752794031207</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5.585001251089563</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-5.453808602509783</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.9820312965903392</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.2852754660202216</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.775881622178695</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.2948269840619764</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.5123572646687005</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.1478958463166837</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.9229220664288097</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-0.3094393433811286</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.684528899443432</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-2.283436747862962</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.71211749685449</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.1252306582763833</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.9459245223197321</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-0.9533509149499951</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.4042233158150066</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>-0.2837268300194592</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.883837402616812</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-0.5151292370279656</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.2650357013005428</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>-0.5573231600841592</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>-0.1821700556207624</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>-1.074758746263619</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.933654687065258</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>-2.200226612634693</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>-0.2431192457453176</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0.08346093653861836</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.133558839695375</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>-1.103836267024814</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>-0.2742961978222175</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>-1.243563538244139</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0.2005752507193688</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>-2.179694850711041</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.39072893023611</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>-1.390704084496093</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>2.989661694405811</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>-2.989692691880236</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>-1.036028133001056</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>-0.2906118186727635</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>-1.617310854569861</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0.3233503127793075</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0.9768747603606711</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>-0.09870347930964227</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>-1.238964582025993</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>-0.291382509016545</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>-0.3841730202584107</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>-0.1546650617213482</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>-1.605163578133513</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0.5598900422396587</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>1.806625740427696</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0.2830479020640683</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>2.480192220166467</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>-1.112248023949184</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0.4352324126775785</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>-0.7395802134866798</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>-0.4756797936574723</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>0.02359986380842114</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>4.373454602413428</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>1.74601276077768</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>-0.1873802698186946</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>2.3443453807363</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>3.607043599863762</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>-0.6043202443343123</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>3.897875941951674</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>2.425974683145365</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>3.810046592507762</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>1.742948619276714</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>3.087217459640655</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>-1.039738090500403</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>2.426881430821234</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Cl5M5C3L</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>-0.6421792333769744</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-1.74467746535898</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.9355255587288207</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.193078397277103</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.961152982697352</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-1.912594387021969</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.28892101487911</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-2.177172429895981</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.9040609912680919</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.02685413895135955</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-0.3920818832660227</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.9226639384309325</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.04000105775650328</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-2.019712571147906</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-0.7206896374590986</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-0.1698176331318619</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.17544833733915</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.040052166825112</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-0.03517547749214495</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.4541784525715656</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.7908205202437788</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-0.6425252287910773</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.2674470258141952</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>-0.1064276921676032</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.082037800689272</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.5349114096649893</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.619261802286594</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>-0.2412664260589587</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>-0.4461065840998716</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>-1.560266166700906</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>-0.8553181407004894</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>-0.3615315958782654</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>-0.3351192865660105</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>-2.514690140508941</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>-0.6201874034019308</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>-0.3759167299619542</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.0389589596272</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0.1924261677806094</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0.7649658858371895</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1.137311463888542</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.195123095243624</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>-1.195104552895625</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0.5351453483259503</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>-0.5351613404254585</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0.8828007536569363</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0.3047962063195767</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0.3674855787494498</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>-0.661071533794013</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>-0.1881646917879646</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0.2719369610944668</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0.08597793516701646</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>-0.3768851294000356</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0.2817981204110301</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0.73577389835181</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0.7630981352655806</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0.8677204258211082</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>-0.06268433615126072</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0.4715068136199105</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>-1.187774550106088</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>-0.6465171460133313</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>-0.8791342563300172</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>-0.1795292563455588</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>-0.1585252202871176</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>-1.421750164036826</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>-0.0496619476785095</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>0.9671739241237678</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>2.174581193039738</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>-0.2015610887397322</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>-0.0990023103977028</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>-0.06194502856160956</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>0.282615375025578</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>-0.6140689313320972</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>0.8851471503187952</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>0.6816703819950299</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>0.04379641153503495</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>1.965498225001746</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>0.2548318975515582</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>EXLhbUee</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>-0.7005037432071285</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.9116739188599041</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.9355255587288207</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.193078397277103</v>
+      </c>
+      <c r="F29" t="n">
         <v>-0.8119056097826699</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G29" t="n">
         <v>1.491002957993425</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H29" t="n">
         <v>-0.5781614882121794</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I29" t="n">
         <v>0.770039282013928</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J29" t="n">
         <v>-0.9672263364658392</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K29" t="n">
         <v>0.4170161451658357</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L29" t="n">
         <v>-0.324050712800073</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M29" t="n">
         <v>0.2438649556170761</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N29" t="n">
         <v>-0.5320843476124578</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O29" t="n">
         <v>0.7390617783524811</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P29" t="n">
         <v>0.03020296836523042</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q29" t="n">
         <v>0.3660672599919559</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R29" t="n">
         <v>-1.200260952480834</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S29" t="n">
         <v>0.3403702900486752</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T29" t="n">
         <v>-0.5939058138777354</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U29" t="n">
         <v>0.4268287218147572</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V29" t="n">
         <v>-1.458187509857547</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W29" t="n">
         <v>1.533254574321347</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X29" t="n">
         <v>-0.7239938145202746</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="Y29" t="n">
         <v>0.6882252189934603</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="Z29" t="n">
         <v>0.4704816885263645</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AA29" t="n">
         <v>-0.5065804447655708</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AB29" t="n">
         <v>0.3714546391283565</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AC29" t="n">
         <v>-0.4044956797298181</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AD29" t="n">
         <v>-1.369884433776754</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AE29" t="n">
         <v>1.477833297550602</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AF29" t="n">
         <v>-0.3982128737715195</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AG29" t="n">
         <v>0.08299794243545569</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AH29" t="n">
         <v>-0.503786028070614</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AI29" t="n">
         <v>0.5245051008522471</v>
       </c>
-      <c r="AJ24" t="n">
+      <c r="AJ29" t="n">
         <v>-0.3003135391270564</v>
       </c>
-      <c r="AK24" t="n">
+      <c r="AK29" t="n">
         <v>0.1806291679373767</v>
       </c>
-      <c r="AL24" t="n">
+      <c r="AL29" t="n">
         <v>-0.8592916770496857</v>
       </c>
-      <c r="AM24" t="n">
+      <c r="AM29" t="n">
         <v>-0.6931008176013186</v>
       </c>
-      <c r="AN24" t="n">
+      <c r="AN29" t="n">
         <v>0.34206631191979</v>
       </c>
-      <c r="AO24" t="n">
+      <c r="AO29" t="n">
         <v>0.3025113840458792</v>
       </c>
-      <c r="AP24" t="n">
+      <c r="AP29" t="n">
         <v>-1.934570264636154</v>
       </c>
-      <c r="AQ24" t="n">
+      <c r="AQ29" t="n">
         <v>1.934487952711861</v>
       </c>
-      <c r="AR24" t="n">
+      <c r="AR29" t="n">
         <v>-1.78153967610941</v>
       </c>
-      <c r="AS24" t="n">
+      <c r="AS29" t="n">
         <v>1.781537846770485</v>
       </c>
-      <c r="AT24" t="n">
+      <c r="AT29" t="n">
         <v>0.8089996426316288</v>
       </c>
-      <c r="AU24" t="n">
+      <c r="AU29" t="n">
         <v>1.197908243808087</v>
       </c>
-      <c r="AV24" t="n">
+      <c r="AV29" t="n">
         <v>-0.4494663102214158</v>
       </c>
-      <c r="AW24" t="n">
+      <c r="AW29" t="n">
         <v>-0.6568789805802562</v>
       </c>
-      <c r="AX24" t="n">
+      <c r="AX29" t="n">
         <v>0</v>
       </c>
-      <c r="AY24" t="n">
+      <c r="AY29" t="n">
         <v>0</v>
       </c>
-      <c r="AZ24" t="n">
+      <c r="AZ29" t="n">
         <v>-0.5764933234294886</v>
       </c>
-      <c r="BA24" t="n">
+      <c r="BA29" t="n">
         <v>-0.6618938640116711</v>
       </c>
-      <c r="BB24" t="n">
+      <c r="BB29" t="n">
         <v>-0.191261252141171</v>
       </c>
-      <c r="BC24" t="n">
+      <c r="BC29" t="n">
         <v>-0.07590309831378496</v>
       </c>
-      <c r="BD24" t="n">
+      <c r="BD29" t="n">
         <v>-0.824832567020207</v>
       </c>
-      <c r="BE24" t="n">
+      <c r="BE29" t="n">
         <v>0.04859530466613205</v>
       </c>
-      <c r="BF24" t="n">
+      <c r="BF29" t="n">
         <v>-0.1911790917200311</v>
       </c>
-      <c r="BG24" t="n">
+      <c r="BG29" t="n">
         <v>-0.01458384528110896</v>
       </c>
-      <c r="BH24" t="n">
+      <c r="BH29" t="n">
         <v>-0.2707828575379491</v>
       </c>
-      <c r="BI24" t="n">
+      <c r="BI29" t="n">
         <v>0.7506754877942258</v>
       </c>
-      <c r="BJ24" t="n">
+      <c r="BJ29" t="n">
         <v>0.0999978878168996</v>
       </c>
-      <c r="BK24" t="n">
+      <c r="BK29" t="n">
         <v>-0.09635855069290779</v>
       </c>
-      <c r="BL24" t="n">
+      <c r="BL29" t="n">
         <v>-0.588085907872702</v>
       </c>
-      <c r="BM24" t="n">
-        <v>-0.604608544341154</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>-0.6469174055211639</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>-1.095362673178881</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>0.2508266372936601</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>-1.429758737499249</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>-0.4610763326171992</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>-0.1917007974254276</v>
-      </c>
-      <c r="BT24" t="n">
-        <v>-0.721232061675677</v>
-      </c>
-      <c r="BU24" t="n">
-        <v>-0.7882280649428245</v>
-      </c>
-      <c r="BV24" t="n">
-        <v>-0.8169920101628726</v>
-      </c>
-      <c r="BW24" t="n">
-        <v>-0.1524993502119059</v>
-      </c>
-      <c r="BX24" t="n">
-        <v>-0.3423538227228154</v>
-      </c>
-      <c r="BY24" t="n">
-        <v>0.6205498908920375</v>
-      </c>
-      <c r="BZ24" t="n">
-        <v>-0.7990158562752449</v>
+      <c r="BM29" t="n">
+        <v>-0.5973562578928173</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>-0.6530497450677435</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>-1.125010916255676</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>0.2196804857626059</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>-1.407525930666907</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>-0.4771455026849311</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>-0.1494102226408914</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>-0.7172633678342518</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>-0.8124020798812112</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>-0.8601863352119253</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>-0.1442125280617442</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>-0.3468425810184763</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>0.5271003046903331</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>-0.8130569683762269</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X7"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,457 +548,2281 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>McP0d8Q7</t>
+          <t>rXmhxCKr</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.09344548130567</v>
+        <v>-1.156103520828798</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7769839346139357</v>
+        <v>-0.4330658455852732</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09907313004817027</v>
+        <v>-0.319783526030758</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6874645885407199</v>
+        <v>-0.4640890296111926</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1863099543387716</v>
+        <v>-0.5973922943603484</v>
       </c>
       <c r="G2" t="n">
-        <v>0.204611474754654</v>
+        <v>-0.4276482227885157</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8095633690997432</v>
+        <v>0.6512585972488756</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.05484797548009437</v>
+        <v>-0.968447061743685</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7605748573532818</v>
+        <v>0.8001482968525961</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4574114602977682</v>
+        <v>-0.5594144125380394</v>
       </c>
       <c r="L2" t="n">
-        <v>1.184877180038532</v>
+        <v>0.845936522568033</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1398656611771235</v>
+        <v>0.9060923080472563</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5102201151018146</v>
+        <v>-1.204169365081432</v>
       </c>
       <c r="O2" t="n">
-        <v>0.09824373898959518</v>
+        <v>-0.6724591299516247</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3456787564003013</v>
+        <v>0.2153775405127027</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.576813794501196</v>
+        <v>-0.9630422642975776</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.02707566775242537</v>
+        <v>1.578273047620724</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3594307274479482</v>
+        <v>1.133210269597756</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1308250221801643</v>
+        <v>1.419843781362283</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3856880672217437</v>
+        <v>1.000237214618635</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.7687711421844848</v>
+        <v>1.437020705494865</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.286613239316792</v>
+        <v>1.296741883565155</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.01531891160414867</v>
+        <v>1.643279853888353</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0lpzB7u1</t>
+          <t>vJXfdXBE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.384227496866481</v>
+        <v>-2.869017704491104</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2042661988400386</v>
+        <v>-1.152634282839657</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6608571758791495</v>
+        <v>-0.05774997815199738</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2190359981060441</v>
+        <v>1.111652700989899</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5570663199549941</v>
+        <v>0.01115953334076306</v>
       </c>
       <c r="G3" t="n">
-        <v>1.329226596342081</v>
+        <v>-0.2650244518837948</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.588993780155831</v>
+        <v>0.06760969093001958</v>
       </c>
       <c r="I3" t="n">
-        <v>0.306575838865942</v>
+        <v>-0.7693293121734154</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9291418080515739</v>
+        <v>-0.04170863427739507</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7516283790994358</v>
+        <v>-0.2348176188015512</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.214943073132272</v>
+        <v>0.7265251686074415</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8773044740319064</v>
+        <v>-0.4469358906741888</v>
       </c>
       <c r="N3" t="n">
-        <v>1.021978168887859</v>
+        <v>-1.242551219115385</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1093064595964061</v>
+        <v>-0.5120496811528539</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1908162712414</v>
+        <v>0.1860806932574611</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6864766538090865</v>
+        <v>-0.07702619862737627</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.390787780996351</v>
+        <v>-0.05889407371990548</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.002445675122287</v>
+        <v>0.0456495272430097</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.668309905386592</v>
+        <v>0.0638247283895011</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.167209510261132</v>
+        <v>-0.001390958478978787</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.627559641426089</v>
+        <v>-0.3467171976341616</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.283923825182029</v>
+        <v>0.361036391356012</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.116750906841944</v>
+        <v>0.6003121070971865</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GMBD7YY8</t>
+          <t>jqCRLjz2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.2368824066880337</v>
+        <v>3.317439234656253</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.7062081503389782</v>
+        <v>-0.8442478097306354</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2634787967344952</v>
+        <v>0.1804623381014211</v>
       </c>
       <c r="E4" t="n">
-        <v>0.93469078904791</v>
+        <v>-1.730147414313804</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8684279823280689</v>
+        <v>1.48779264467434</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6585391916398706</v>
+        <v>1.971052398056117</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00364816694987074</v>
+        <v>-1.531428408573696</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6711940556115009</v>
+        <v>-0.9199225681509303</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1562768798225844</v>
+        <v>-0.5807539193646432</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0807818224433068</v>
+        <v>0.6863728555337695</v>
       </c>
       <c r="L4" t="n">
-        <v>1.317950033757642</v>
+        <v>-0.8419677488448331</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6757896359244572</v>
+        <v>0.2151842916788588</v>
       </c>
       <c r="N4" t="n">
-        <v>1.175505585023672</v>
+        <v>-0.3597685763344598</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2678721216273743</v>
+        <v>1.564976112776054</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.35493347236825</v>
+        <v>0.946626848003534</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.3101883211721663</v>
+        <v>2.209294957297534</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.6827145523487441</v>
+        <v>-1.087959513076989</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03597275744205735</v>
+        <v>-1.030844156466758</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5080428958484638</v>
+        <v>-0.2591238723680938</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4018285529915866</v>
+        <v>-0.2761112960569187</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1618926530373511</v>
+        <v>-0.6098548657938907</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.4762891618749431</v>
+        <v>-0.1320633944185146</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6400609193415283</v>
+        <v>-0.6192912157930485</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>AJ5eIkmR</t>
+          <t>v5hMsYdL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.127123117520842</v>
+        <v>-2.47688258977772</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3390813966377615</v>
+        <v>-0.2480339617198597</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3807772404054328</v>
+        <v>-0.635428472773418</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2515657613306743</v>
+        <v>1.293819375047829</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7999756629449333</v>
+        <v>-1.474422869576655</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9679702817303741</v>
+        <v>-1.117245030835796</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.011139838424811</v>
+        <v>1.386797827390156</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0962016236973527</v>
+        <v>-0.7522521211828302</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.011314228581668</v>
+        <v>0.9437971463730852</v>
       </c>
       <c r="K5" t="n">
-        <v>1.115477358980726</v>
+        <v>-1.282893833403445</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5134259858833995</v>
+        <v>0.02593211038132837</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.662844645789313</v>
+        <v>4.907601236180892</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2446230142326</v>
+        <v>3.171361994789242</v>
       </c>
       <c r="O5" t="n">
-        <v>0.006054400599496171</v>
+        <v>-0.9490271451219184</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5317834908693124</v>
+        <v>0.07178392649901146</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.754228146559357</v>
+        <v>-1.300724463217956</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.7361022979220453</v>
+        <v>3.07192858296218</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.684227240710651</v>
+        <v>2.760165338220277</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5587275037486925</v>
+        <v>3.093863535042556</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.125529602698059</v>
+        <v>3.176433203927112</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.014580568462529</v>
+        <v>3.56604001836358</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.63296691519468</v>
+        <v>2.171693318576598</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7049705098276294</v>
+        <v>2.551146776880555</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dGwq9oAD</t>
+          <t>WvkEqfS8</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.415837620145053</v>
+        <v>-0.3018350506979807</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3070616898763791</v>
+        <v>0.1220298060109661</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3617022087175642</v>
+        <v>-0.02233156797221274</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.374922399900841</v>
+        <v>-1.384030733603738</v>
       </c>
       <c r="F6" t="n">
-        <v>1.049277357066187</v>
+        <v>0.8881901085570693</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6305123688869263</v>
+        <v>-0.2398819609873417</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.03396765581809</v>
+        <v>0.4967410208968323</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4599438340596094</v>
+        <v>1.265352901922788</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0305358257699307</v>
+        <v>-0.2599177705812608</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0508021825385047</v>
+        <v>0.7023571630738442</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1484446993144453</v>
+        <v>-0.08796076629176482</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.84794381275455</v>
+        <v>-0.9075412349197871</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.76710322424608</v>
+        <v>-1.050641948945619</v>
       </c>
       <c r="O6" t="n">
-        <v>1.038574990568594</v>
+        <v>0.6440046222589744</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8920565871827705</v>
+        <v>-0.9057151477878775</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.220977199901298</v>
+        <v>-0.3685581586527666</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.767340287299124</v>
+        <v>-1.372278641103444</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.989882846477812</v>
+        <v>-1.285010004075423</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.260489778585338</v>
+        <v>-1.399756239404839</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.279352526504356</v>
+        <v>-1.887004114461414</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.288929096437388</v>
+        <v>-1.904912956328324</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.250836048204975</v>
+        <v>-1.704987792870693</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.752510818725282</v>
+        <v>-1.072026067100061</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>8Kjh0jRr</t>
+          <t>b7pTwPem</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.467948242032435</v>
+        <v>0.8602524714799752</v>
       </c>
       <c r="C7" t="n">
+        <v>0.1220298060109661</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3591215752914858</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.5642807003430536</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8971394001409091</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.498726004619612</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-1.051716978722582</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.1000259522733482</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.2982198389051199</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.3818470788939942</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.1234361712913432</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.936329068935137</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.5997777745143724</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.1995278240104218</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.7661582689112455</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.8756076163413363</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.3537447954987015</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-1.378228560972186</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.291559025350601</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.8279535319942871</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-0.8273826635283226</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-1.229798176626913</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.7266634147515231</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>CCu9YTJ7</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.272300424526791</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.23487067566873</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.797651869545193</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.484222404335598</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01115953334076306</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.685443859620431</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.855471393783489</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.4742273762174767</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.171203421154676</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.2208601873722282</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.2088490678010621</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.5620872267355884</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.098741876955765</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.2761691620824834</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.5727990770266507</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.9122473784555175</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.2720728949391935</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.9493988324153215</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.43177200084108</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.4120674880042935</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.6900800069277783</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.07194643561648201</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.07565050938743433</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Gpn0zjke</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4.743290972074599</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.3892980827054515</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1507363647596922</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-1.547980740255874</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.6018127778741937</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8652862777790487</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-2.13737968838563</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.174001586788619</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-1.066514268224876</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.074280690063008</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-1.059612875196528</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.04390621445929027</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-1.587987905420965</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.8016483909060418</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.4124120435281897</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.727045897851834</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-2.17757416806067</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-1.44878729520661</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-3.098286947612894</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-2.744431161012629</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-1.115676065894234</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-2.01624771331278</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-2.141232903739449</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>pOryx3Qa</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.56361202707415</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.869553153628756</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.723428477470158</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.400330693690917</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.416198312003621</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.811798504757042</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.2173378038835489</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.164044711537914</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.1804973053803185</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.6736842815071122</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-1.11109222549524</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-2.404508603717982</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.3213867223005065</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.7408034275685772</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-2.177198318665365</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.7976081868729412</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-2.04670542595148</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-1.679911154856869</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-2.551325432667743</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-1.903252527310636</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-1.663837127502203</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-1.949245998042277</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-2.39954736387953</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rJ8JNC5k</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-1.531699244886314</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.481579854155947</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.009554452304913</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.03686932404811415</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.4631529206027503</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.9698952855265477</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.185253162583143</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-1.003585488138439</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5692093554881532</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-1.057399746415421</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.04491567337673735</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-1.137843907042586</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.2446230142326</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.3729679673920863</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.1645963386036169</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-1.567043191270747</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.6258331461062911</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.081380112445437</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.3255005367115183</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.5687032021132246</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.5032656025063593</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.160411320087456</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.32327411452432</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.2368824066880337</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.245384395254575</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.06449055255699342</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.5287193440045245</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.5615951280249886</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.6904643479038858</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1248384229122576</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4864951499548678</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0.3039651491536985</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.09670021531311354</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-1.136268010231701</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-3.152992288117079</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.513295992470273</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.1351194743456337</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.4924342891739354</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.08818581963293194</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-1.18251064332924</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.6783230484000187</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-1.36363481762086</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.7827947677507541</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.8181271073219734</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-1.457201293335776</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-1.474991830477828</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.1268523997676665</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1220298060109661</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.04777389878482367</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.293819375047829</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-1.000110415633142</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.0683529023182947</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.4558648869075125</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.6020034721983989</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.1018654121742789</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.126157284864177</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.7767149692781991</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.13026971650534</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.2446230142326</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.4880804531714288</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.08813779705160098</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.4940533092360573</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.7905815455338985</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.417935642710884</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.9278263647185635</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.624469285204036</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.755508631603126</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.420699932306694</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.7827941080409105</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.263794387694904</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5332117701563287</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.1209092590380669</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.928614048458913</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.5839141947065136</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.409043778017743</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-1.339543836633251</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.3015560636666918</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.7003915563056371</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.7175175372355649</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.543134520363334</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.7923898988583876</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.7533051906501855</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.3158105775902259</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.007278498627133844</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.9155782659204431</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.8388833654505479</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-1.732794102245689</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.7179515188235565</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-1.14900532962366</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.6628803617811313</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-1.974026907676995</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-1.224051732248702</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-3.824809981237467</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.001324783232642655</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.3103994044813813</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.488312280656253</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.159919193915997</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.478359445467027</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.918132873355683</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.02701104028425066</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.185422042933764</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.8812427901232567</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.5543820040338766</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.230332672753351</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.789615249566924</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-1.310409351611102</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.1919400627085094</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-1.26948391107073</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.183149759085257</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.1692138227541478</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.9671050408641424</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.7299825136059708</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.4764156810665075</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.6901211829740276</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.149159203780463</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-0.6292810973481231</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-1.317107068497802</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.581909882027043</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.2637056881474697</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-2.163518321532324</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.581279192044929</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.06865283802768943</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-1.084045999705373</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.6125808152078172</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.7410917224651782</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.04207329953377887</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.028817834645902</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.9068326067859986</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.4401419972085778</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.11967261210341</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.3626509467427989</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.736042506812294</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.99174215016493</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.303014797854847</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.802084627515881</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.613867304032899</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.728533785633705</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.505802756297031</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4.612915012721301</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.8442478097306354</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.04150515362026015</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-2.331297438704971</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.165618147656105</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.20725876816354</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-2.102285010096522</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.005389326910911891</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-1.325938361241936</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.384574000351264</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-1.151505576240405</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-3.872688138500826</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-3.123262066779097</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.67217006684113</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.3666531582914314</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.046077333962359</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-3.328913352616192</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-2.752623279977202</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-3.16115783740116</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-3.131281948136591</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-3.501527236200983</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-2.245018723228211</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-2.771296895876299</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.9946632534707415</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.07181311994327649</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.3694786325198951</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.009973534995353315</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6120405396842964</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.01729354767631629</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.1423509638743813</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.3408412608782173</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.1433217684777495</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.3328230428819091</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.9269539497003046</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-1.982287038159517</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-1.152993559702828</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.2198094784562431</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.6216271557853867</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.4559157957607147</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0.351013012473876</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.4847310220110802</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.08318435583011885</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.05853448318501198</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0.005719750769177289</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.1247180201690684</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.1290212463800246</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>WIDwXGr3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.9554563313980714</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.9238346360944225</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.224493350963296</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.03469615504607274</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.09681703850037288</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.1371438360531624</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.054422772623748</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.6812816421363108</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.006619563695944733</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.06590158563022694</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.4956238392129355</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-1.972691093487733</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-3.890899147458163</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-0.3046236697751338</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-0.290871980057873</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-1.425369444429247</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.4823698466066022</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.1867442337101378</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.546991289404277</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.515502565131387</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.1507592690386605</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.235269606992909</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.8533119529328037</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>4CLi9Djd</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.3909931520747812</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4685974615049143</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.05973508078744253</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.6939705411856462</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2118793588640278</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.1819189218993972</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-1.565008208663275</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.2606587586493647</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.3265440574975532</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.1111025707667478</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-1.855300420088992</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.52982871171317</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.456972514605996</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.2437787064376687</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.7499752485226359</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.016892415222059</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.0342557206745631</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.5121521829327498</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.07359635006623642</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.1037893232376352</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.08278039463107656</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-0.2337859075602083</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.1099044332773201</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Ug79dz7j</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.127123117520842</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6741884435775956</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.7352462851653053</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7330062570552024</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5634586710863088</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.6311684651762769</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4530620328103885</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.405906607501802</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.05522701133287456</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.4707824477535646</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.3352159930846394</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.3783153510991746</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.1903713314855377</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.212558518593316</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-1.274074173943783</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.5246974739133727</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-0.9688788410794381</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.6721858185330667</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.5618184698015783</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.6241433808622612</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.5034811269612445</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-1.233164404178599</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.9401417079250346</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>fB59P6ff</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>-0.8052180417750656</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.001324783232642655</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.4984427632208223</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.1452973500098154</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.1588770067521947</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-1.528293731084171</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.056832806123</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.5753619836258096</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.2401495273293545</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.1818716599084994</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.3096272151100196</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.827302996538453</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.06243181803902633</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.7804448430763197</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.4654811896991131</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-0.1263233331082748</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-0.6168230006074101</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.1472798864839505</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.7505813017455087</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.8616746989129824</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-1.00308070327876</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-0.313004274901525</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-0.2169398855995996</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>jwaINpP6</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.890221284588082</v>
+      </c>
+      <c r="C23" t="n">
         <v>1.232221109203444</v>
       </c>
-      <c r="D7" t="n">
-        <v>1.133782378443662</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-1.680702174212366</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.816359492823889</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.591031347730783</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-1.660741924446605</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-0.1829613686087916</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-0.5685873800147115</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.7901884612064202</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.5137193126967361</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-1.823953951075092</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-3.340759239638165</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3.144179479398432</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-0.1947783210606806</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.608402858624961</v>
-      </c>
-      <c r="R7" t="n">
-        <v>-2.248372450048929</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-1.919499467699386</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-1.727792422994082</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-1.647687140544067</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-1.964192321356801</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-1.278675829266306</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-1.832666420496852</v>
+      <c r="D23" t="n">
+        <v>1.198043210792657</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.8110776887943149</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9597844412277882</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.5939103227516332</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.479699379583061</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.628277953809213</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.9137026641186247</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.5469565398573213</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.6514787479762113</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-0.9075412349197871</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.06243181803902633</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.3295147911404601</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-1.541261420911587</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-1.718487541342697</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.7942009782516329</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.6672383645158287</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.5355630547963918</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.258085490566953</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.946452963561504</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.1791309798464161</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.1297842948278085</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>xY3xTu1n</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2.339572472373175</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.5153022384143453</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.4277009238485948</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.348898589321136</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.2228005180653363</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.2305103828582278</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.316886288450647</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.160089671687814</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.6420935552538817</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.3195577154904037</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1.082589337893776</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.5894261338784075</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.396078635251199</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.4928141072992139</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.6361841530396544</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.4559157957607147</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.4467128351577051</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.7501345375652999</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.2066108220508867</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.4852757831245655</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.7400142543814009</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.5258415986883888</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.4398054020863006</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>OjcQLOgJ</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-2.51022494703616</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.8971140622636103</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.4150684525321257</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.3881907668741216</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.8300738755401844</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.10368915277278</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.6447170777509057</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.6704549521881781</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.931952473143522</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.7151378210470153</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.348258416056939</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.9060923080472563</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.3853564790237622</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.02713376122093926</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.2768094933753569</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.6166299679453183</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.472901631991463</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.697031568395095</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.402108087754383</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.008122923842681</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.165042718609775</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.653647961102794</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.612488372720007</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>jeAhPc0B</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-3.214961134544078</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9091495659463736</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.214028619028039</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.845524159337559</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.6337745335307651</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.18941961721519</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.9835677877457388</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.3070321820658739</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.2090572601017516</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.5241171066093383</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.1249837519662235</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.1672045683199426</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.5613959204804191</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-2.505183177146773</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.1420439960012453</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-1.995617378424504</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.5586882001226481</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.04978764103056061</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.1701613682465258</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.01576676421722032</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.158732678332029</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.1745505987857645</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.9212975883378433</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>OMVUWl2K</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-2.287597406335401</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.4125067473780051</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.391765073768205</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.220952705424657</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-1.14329908097458</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.5702039708130501</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.346840170532992</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.4623227710018628</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.7002088664781577</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.6948690599394978</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.05948178321708623</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.913666498584503</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.250197497974364</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.8199620713757809</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.1277660163398848</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-0.08749470208857094</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.185837365099907</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.4121794856957269</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.065896944252381</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.060806932603029</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.202884525251611</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.8937305891764498</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.119163692873611</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>8f71RSPs</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2.241060962291423</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.1041202742689831</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.9570014720086536</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.03686932404811415</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.1096017407630012</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.1774348105693042</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-1.809661037887343</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0.6321221233939017</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-0.5993416878159277</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.1762921796621455</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-0.4875432665025865</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.395485486308204</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.173433789906457</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.8320708725747744</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-0.007278498627133844</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.018768194303791</v>
+      </c>
+      <c r="R28" t="n">
+        <v>-1.400182073579656</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-1.050809825472</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-2.721772655971681</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-2.566902403998609</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-1.371689878734751</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-1.211830027506792</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-1.570852716824148</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>UuMqRJVb</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>-2.964893455105784</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-2.115974884551649</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-1.362503801267315</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.002166391821442072</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-1.367031370570576</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.9667199339626539</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.110017445296129</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-0.8621190961595612</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.242875145419553</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-1.351873535839274</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.365745403546984</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.8293247506729902</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.851513211172965</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-0.373765673567707</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.2622524961210894</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-2.148838201811081</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.423654539364537</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.873730501043798</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.424072595027225</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.576663743844958</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.975744926810466</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.055570061120176</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.9336087502088567</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>bLD0NyVN</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1.354457371555654</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.5273377420971087</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.589213017127174</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-1.010589051784982</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.611804256621835</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.858270203996192</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.7564763987142136</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-0.3637923218339656</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-0.412788084450309</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.3911904834045325</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-0.7334273549407448</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.3303356277402584</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-0.3597685763344598</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-0.2078248644655309</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.825532265660783</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.13008741866165</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.01476133071741058</v>
+      </c>
+      <c r="S30" t="n">
+        <v>-0.771715783466826</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.2736052609618865</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.03056469583421289</v>
+      </c>
+      <c r="V30" t="n">
+        <v>-0.5863726482389493</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.4256795440613199</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.1990825829447876</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>I5fXHFho</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.6724546094512158</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.2079374663770508</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.1533927567089872</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.6608940971202059</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.1109343732673382</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.694031844110122</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.08793310602170562</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-0.9579511681452519</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.1546457924534461</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-0.07840210625475755</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-1.162618482091849</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-0.7396122031635791</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-1.082626827307247</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-0.1276201400661452</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.2622524961210893</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>-0.6166299679453183</v>
+      </c>
+      <c r="R31" t="n">
+        <v>-0.1441947435150219</v>
+      </c>
+      <c r="S31" t="n">
+        <v>-0.1346255730827663</v>
+      </c>
+      <c r="T31" t="n">
+        <v>-0.09054090456379804</v>
+      </c>
+      <c r="U31" t="n">
+        <v>-0.06700527036229037</v>
+      </c>
+      <c r="V31" t="n">
+        <v>-0.07473921074907156</v>
+      </c>
+      <c r="W31" t="n">
+        <v>-0.135180219109036</v>
+      </c>
+      <c r="X31" t="n">
+        <v>-0.1554348911101582</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,808 +425,1074 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X10"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_expected_points_against</t>
+          <t>dif_mean_last_360_matches_goal_attempts</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_shots_on_goal_against</t>
+          <t>dif_mean_last_360_matches_goals</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_shots_on_goal_against</t>
+          <t>dif_mean_last_360_matches_dead_balls</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goal_attempts</t>
+          <t>dif_mean_last_60_matches_ball_possession</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goal_attempts_against</t>
+          <t>dif_mean_last_360_matches_ball_possession</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_goal_attempts_against</t>
+          <t>dif_mean_last_360_matches_PPDA</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_goals</t>
+          <t>dif_mean_wage_player_start</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_goals_against</t>
+          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_points</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_240_matches_points_against</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_goal_ratio_against</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_attacks</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_dangerous_attacks</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_dead_balls_against</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_240_matches_clean_sheet</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_240_matches_clean_sheet_against</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
+          <t>dif_sum_wage_player_miss</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>fB59P6ff</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.8052180417750656</v>
+        <v>0.7244015632940887</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.001324783232642655</v>
+        <v>1.143048970266537</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.4984427632208223</v>
+        <v>0.06024815242756035</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1452973500098154</v>
+        <v>1.546668271949273</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1588770067521947</v>
+        <v>0.184482108717704</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.528293731084171</v>
+        <v>0.1671860002346544</v>
       </c>
       <c r="H2" t="n">
-        <v>1.056832806123</v>
+        <v>0.2981542376718941</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5753619836258096</v>
+        <v>1.133271046012877</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2401495273293545</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-0.1818716599084994</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-0.3096272151100196</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.827302996538453</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.06243181803902633</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.7804448430763197</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-0.4654811896991131</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-0.1263233331082748</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-0.5830553268729352</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-0.1416167200363636</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-0.6948210742528871</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-0.9528325800773081</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-1.083684591072691</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-0.3484343316739564</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-0.2011523662804816</v>
+        <v>-0.08251771438814438</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jwaINpP6</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.890221284588082</v>
+        <v>-0.4894030598859481</v>
       </c>
       <c r="C3" t="n">
-        <v>1.232221109203444</v>
+        <v>-0.8598761252300247</v>
       </c>
       <c r="D3" t="n">
-        <v>1.198043210792657</v>
+        <v>-0.2199845703579752</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8110776887943149</v>
+        <v>-0.009731775465660139</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9597844412277882</v>
+        <v>0.1538492204777766</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5939103227516332</v>
+        <v>1.213666351775356</v>
       </c>
       <c r="H3" t="n">
-        <v>1.479699379583061</v>
+        <v>-0.7055222220427489</v>
       </c>
       <c r="I3" t="n">
-        <v>0.628277953809213</v>
+        <v>-0.183947456229278</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9137026641186247</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-0.5469565398573213</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.6514787479762113</v>
-      </c>
-      <c r="M3" t="n">
-        <v>-0.9075412349197871</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.06243181803902633</v>
-      </c>
-      <c r="O3" t="n">
-        <v>-0.3295147911404601</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-1.541261420911587</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-1.718487541342697</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.7820697657818546</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.7043645863425831</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.5697415508193858</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.320099030772462</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2.022574869321733</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.1780796055273166</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.1348114754267236</v>
+        <v>0.09717546371878232</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OjcQLOgJ</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-2.51022494703616</v>
+        <v>0.9507600650063842</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.8971140622636103</v>
+        <v>1.473309654077134</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4150684525321257</v>
+        <v>3.063527461420913</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3881907668741216</v>
+        <v>0.5066774568563452</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8300738755401844</v>
+        <v>1.801879817834924</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.10368915277278</v>
+        <v>-1.353972389121269</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6447170777509057</v>
+        <v>0.7264648872886714</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6704549521881781</v>
+        <v>-0.4887548526340084</v>
       </c>
       <c r="J4" t="n">
-        <v>0.931952473143522</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-0.7151378210470153</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.348258416056939</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.9060923080472563</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-0.3853564790237622</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-0.02713376122093926</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-0.2768094933753569</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-0.6166299679453183</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.487671136604061</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.764168891516006</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.432430305382848</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.003724681607908</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.284693510117699</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.658418665973765</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.668820724208948</v>
+        <v>0.160884237098969</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xY3xTu1n</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.339572472373175</v>
+        <v>0.03481450799154166</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.5153022384143453</v>
+        <v>0.214638988213204</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4277009238485948</v>
+        <v>0.6164485001884773</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.348898589321136</v>
+        <v>0.1839216866550923</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2228005180653363</v>
+        <v>-0.65129803091919</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2305103828582278</v>
+        <v>0.7913821122822668</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.316886288450647</v>
+        <v>-0.1933595836191932</v>
       </c>
       <c r="I5" t="n">
-        <v>0.160089671687814</v>
+        <v>-2.309457133330815</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6420935552538817</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.3195577154904037</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-1.082589337893776</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.5894261338784075</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-1.396078635251199</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.4928141072992139</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.6361841530396544</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.4559157957607147</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.4313844399977219</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.7297396825944241</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.2047131173342875</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.4999811398888604</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.7692676642877823</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.5225492021740837</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.4230108950484496</v>
+        <v>-0.4587645113841273</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jeAhPc0B</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-3.214961134544078</v>
+        <v>1.403538025852277</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9091495659463736</v>
+        <v>2.009109941007726</v>
       </c>
       <c r="D6" t="n">
-        <v>0.214028619028039</v>
+        <v>2.261124786058056</v>
       </c>
       <c r="E6" t="n">
-        <v>1.845524159337559</v>
+        <v>1.13425812113656</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6337745335307651</v>
+        <v>2.556909509178139</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.18941961721519</v>
+        <v>-2.403006362129322</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9835677877457388</v>
+        <v>1.098441331511944</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3070321820658739</v>
+        <v>0.4475621803697424</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2090572601017516</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-0.5241171066093383</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.1249837519662235</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.1672045683199426</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.5613959204804191</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-2.505183177146773</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-0.1420439960012453</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-1.995617378424504</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.6027350764737912</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-0.1539744552221385</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.1779139301076554</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-0.03663046368847153</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-0.177839502131654</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.1417112211110653</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.9647423589457395</v>
+        <v>0.7110525417053819</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OMVUWl2K</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-2.287597406335401</v>
+        <v>1.043278355050231</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.4125067473780051</v>
+        <v>1.167951681885293</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.391765073768205</v>
+        <v>0.2884169025824911</v>
       </c>
       <c r="E7" t="n">
-        <v>1.220952705424657</v>
+        <v>1.941147546639693</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.14329908097458</v>
+        <v>-0.1567301322355074</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5702039708130501</v>
+        <v>-0.7662989895760891</v>
       </c>
       <c r="H7" t="n">
-        <v>1.346840170532992</v>
+        <v>1.673314311753033</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4623227710018628</v>
+        <v>-0.3098896583951497</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7002088664781577</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-0.6948690599394978</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.05948178321708623</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.913666498584503</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.250197497974364</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-0.8199620713757809</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.1277660163398848</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-0.08749470208857094</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.211234009091517</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.5658216879871295</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.085222265239577</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.088682962636346</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.349733948519564</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.9681556934722051</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.133072225863941</v>
+        <v>2.053275866714116</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>UuMqRJVb</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2.964893455105784</v>
+        <v>-0.6862420454673717</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.115974884551649</v>
+        <v>-0.9166750599804708</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.362503801267315</v>
+        <v>-0.5749076116576725</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.002166391821442072</v>
+        <v>-0.3181428447690801</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.367031370570576</v>
+        <v>-2.669158276698791</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9667199339626539</v>
+        <v>2.213888956238534</v>
       </c>
       <c r="H8" t="n">
-        <v>2.110017445296129</v>
+        <v>-3.297358428183978</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8621190961595612</v>
+        <v>-0.4945754933793109</v>
       </c>
       <c r="J8" t="n">
-        <v>1.242875145419553</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-1.351873535839274</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.365745403546984</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.8293247506729902</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.851513211172965</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-0.373765673567707</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.2622524961210894</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-2.148838201811081</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.384194195550873</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.871285781195637</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.410996104579718</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.678987513448348</v>
-      </c>
-      <c r="V8" t="n">
-        <v>2.009912310062539</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.115930024082402</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.9610123150692632</v>
+        <v>-2.463228482668724</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bLD0NyVN</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.354457371555654</v>
+        <v>-0.916629898273287</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5273377420971087</v>
+        <v>-0.0838553662392703</v>
       </c>
       <c r="D9" t="n">
-        <v>0.589213017127174</v>
+        <v>-1.025963346014396</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.010589051784982</v>
+        <v>0.02254380155446489</v>
       </c>
       <c r="F9" t="n">
-        <v>1.611804256621835</v>
+        <v>0.3124606011415131</v>
       </c>
       <c r="G9" t="n">
-        <v>1.858270203996192</v>
+        <v>-0.2503330669844383</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7564763987142136</v>
+        <v>-0.4579501500269184</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3637923218339656</v>
+        <v>-0.01204700132456174</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.412788084450309</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.3911904834045325</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-0.7334273549407448</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.3303356277402584</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-0.3597685763344598</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-0.2078248644655309</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.825532265660783</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.13008741866165</v>
-      </c>
-      <c r="R9" t="n">
-        <v>-0.01072263992222603</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-0.6927920196922263</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.2606858598090415</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.06082128749857044</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-0.5639112219314752</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.4468220888122145</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.1983145414644018</v>
+        <v>-0.3162772569312297</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>I5fXHFho</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6724546094512158</v>
+        <v>0.7436719738989661</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2079374663770508</v>
+        <v>-1.676829563540793</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1533927567089872</v>
+        <v>1.413123875358429</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6608940971202059</v>
+        <v>0.3632304478780106</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1109343732673382</v>
+        <v>-0.01648646519093176</v>
       </c>
       <c r="G10" t="n">
-        <v>0.694031844110122</v>
+        <v>0.2532082112853711</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.08793310602170562</v>
+        <v>-0.2917206027026393</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9579511681452519</v>
+        <v>-0.8063309592333924</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1546457924534461</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-0.07840210625475755</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-1.162618482091849</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-0.7396122031635791</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-1.082626827307247</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-0.1276201400661452</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.2622524961210893</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-0.6166299679453183</v>
-      </c>
-      <c r="R10" t="n">
-        <v>-0.1763802638616704</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-0.1542900076636948</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-0.09723461507248488</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-0.06624027815703398</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-0.07473921074907156</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.1323244763894951</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-0.1696052564233461</v>
+        <v>-0.1361019583771015</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>bR8Aj2ug</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-1.719857317828599</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.4845092520966391</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.184370575208983</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-2.075368704753682</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1.290985618183766</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.540317301534273</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.07493564310501995</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.391041631117365</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.9456110267038293</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>rXmhxCKr</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.7271644896976972</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.673401264983563</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.8977156415262545</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.443212078063866</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.809974104049433</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-2.168956972597296</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7592988377164152</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.2444929069724435</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.3046250047145904</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vJXfdXBE</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.607280013349561</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.5622009077811534</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.729567515240394</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.403221262970938</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.76674426809108</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.4277487796001959</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.1651058276983375</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.6068647704066507</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.5832342359816121</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>jqCRLjz2</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-2.147480576091239</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.4943873277054123</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.432594279341331</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-1.931921695775347</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-2.223141621026731</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.770127751556292</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.07493564310501995</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.044815243560422</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.2951616690795226</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>v5hMsYdL</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.260117977049398</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.60425473572215</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.606209682920088</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.725977033172191</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.404187792299748</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-2.295649894212056</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.816475041415737</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.7965163601673231</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.8275879412289234</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>WvkEqfS8</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-0.254094828905587</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.6195096187498739</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.453545637005236</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-1.609165925574093</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-2.16490799239299</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.086948362984063</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.8317363708598975</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.746553278005523</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.4250436298198685</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>b7pTwPem</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-1.523299129658847</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.3682979421274553</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.726960854519182</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-1.089170518027629</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-1.418458752633223</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.499588174527934</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.08752998445374012</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.03777059260324</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.1859545003534425</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>CCu9YTJ7</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.051238738816018</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.3275576063127965</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.109398170222253</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.8560691284378357</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.183525654047102</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-1.130802194212001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.228093111483372</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-1.110508203860396</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.08884166741715784</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Gpn0zjke</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-1.737774866954277</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-1.257387965251052</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.4840303641995346</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1.049722590558587</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1.098151551592021</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.476886771521465</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-3.177086569773049</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.4281398996344978</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-2.118167991171712</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>pOryx3Qa</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>-1.017863788650911</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.7951198517947328</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.9922915211974069</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-1.089170518027629</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-1.463437563539667</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.86021507291797</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-2.355456190370651</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.07723232241860165</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-2.32547978346832</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>rJ8JNC5k</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.6411533894810172</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.751228527355716</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.395372819954395</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9997765502193712</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.955209640531346</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-3.117620620375417</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.9239041755648214</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.237286436867444</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.033384497834327</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.5882974061076385</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.5348694131773575</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.2549739245294577</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.582530024193856</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1884157059234731</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.034756684388465</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.07493564310501995</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.8088067074998476</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-0.0121281290967381</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.5514817454663198</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.6097620125641359</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.8916678623901503</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.188050749503436</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.4019226209254984</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.2295153528673306</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.05981098255044132</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-2.30734930397805</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-0.44603653157801</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-1.149437432976787</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.4219481065744082</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-2.220440153781494</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-2.218815713732016</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-2.067268148894312</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.379469413502525</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.271907003357366</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9492591888772481</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.8094051129344702</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.1645485848585611</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.4820454794406021</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-1.047708315711023</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.066663679495736</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.3737641242612207</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.851620652215302</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.989549536986365</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.3825414442366686</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.094656032669169</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.893116571848199</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.714704550314874</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.58105751668969</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.959078422761985</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.6323970762555843</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.5653036216660285</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.8762652815559208</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.923969197631249</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.3823966325474235</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.1315703220000323</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.9465635011857086</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.098630388204854</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.5871059866034579</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.646851503256909</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.6390009189950288</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.1585387393798952</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.3232462661442763</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-0.2956149520511691</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>-1.542642951351743</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-2.331709390937245</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-1.080669668803476</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-1.788474686797012</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-2.648609328795737</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3.810624097760946</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-2.58754077969119</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0.5356112619963488</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-1.446918579968144</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>WIDwXGr3</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>-0.3126768771444154</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7824208131208455</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.872628164680038</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.829433227057599</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.5825459321381977</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.51674244171968</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.9397376912592316</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.6028986198603495</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.100441478035586</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Ug79dz7j</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>-0.03408337120864064</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.5569484732276432</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.2434893916785302</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-1.035377889660754</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-2.614138841853277</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.296344863501701</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.8001606318735267</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-0.9291273496720124</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-1.250213437509967</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>4CLi9Djd</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.2995715969305567</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-1.061117704789151</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.824756431813952</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.5425392091009289</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.4278734358246692</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.5076495116451016</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.03179870656025553</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-0.6861628675454476</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.08043899676593325</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -478,341 +478,341 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rXmhxCKr</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7271644896976972</v>
+        <v>0.8307191715169997</v>
       </c>
       <c r="C2" t="n">
-        <v>1.673401264983563</v>
+        <v>0.979275211262692</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.8977156415262545</v>
+        <v>0.06577698292219972</v>
       </c>
       <c r="E2" t="n">
-        <v>2.443212078063866</v>
+        <v>1.591495462255002</v>
       </c>
       <c r="F2" t="n">
-        <v>1.809974104049433</v>
+        <v>0.3197268293132805</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.168956972597296</v>
+        <v>-0.03061498471867119</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7149665180735241</v>
+        <v>0.2346742064613014</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2807906952549372</v>
+        <v>1.199367629098181</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3738437260627933</v>
+        <v>0.01390637505213822</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jqCRLjz2</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-2.240455719066772</v>
+        <v>-0.5716633302002555</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.6919488398808783</v>
+        <v>-1.15872711110815</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.474496994669139</v>
+        <v>-0.2545792525958746</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.425020789138373</v>
+        <v>-0.210557588035329</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.388926353261543</v>
+        <v>0.08729650203921602</v>
       </c>
       <c r="G3" t="n">
-        <v>2.85378049858832</v>
+        <v>1.229232208539515</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.08993819205826524</v>
+        <v>-0.6613869570229295</v>
       </c>
       <c r="I3" t="n">
-        <v>1.055989350828942</v>
+        <v>-0.1984844207807871</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2721851860528953</v>
+        <v>0.09128670682796504</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>vJXfdXBE</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.607280013349561</v>
+        <v>0.08567003921641408</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5622009077811534</v>
+        <v>0.1114679762993493</v>
       </c>
       <c r="D4" t="n">
-        <v>2.729567515240394</v>
+        <v>0.6646366228154574</v>
       </c>
       <c r="E4" t="n">
-        <v>1.403221262970938</v>
+        <v>0.05840555379904885</v>
       </c>
       <c r="F4" t="n">
-        <v>1.76674426809108</v>
+        <v>-0.6414995495462085</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4277487796001959</v>
+        <v>0.7301399139305237</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1507727548289306</v>
+        <v>-0.1993553902613317</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.71717294735103</v>
+        <v>-2.227589904804938</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.696463666724344</v>
+        <v>-0.4567809301156415</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v5hMsYdL</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.260117977049398</v>
+        <v>0.9970503441951012</v>
       </c>
       <c r="C5" t="n">
-        <v>1.60425473572215</v>
+        <v>1.500910159454589</v>
       </c>
       <c r="D5" t="n">
-        <v>1.606209682920088</v>
+        <v>3.297689694135134</v>
       </c>
       <c r="E5" t="n">
-        <v>1.725977033172191</v>
+        <v>0.2825415053276972</v>
       </c>
       <c r="F5" t="n">
-        <v>1.404187792299748</v>
+        <v>1.777940191090438</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.295649894212056</v>
+        <v>-1.313287417013717</v>
       </c>
       <c r="H5" t="n">
-        <v>2.772133774786036</v>
+        <v>0.7121616377086308</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9872497427524766</v>
+        <v>-0.3604378416931301</v>
       </c>
       <c r="J5" t="n">
-        <v>1.544156674469424</v>
+        <v>0.2142274208643254</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WvkEqfS8</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.254094828905587</v>
+        <v>1.443453159833185</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.6195096187498739</v>
+        <v>2.066196123366097</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.453545637005236</v>
+        <v>2.302339704290836</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.609165925574093</v>
+        <v>1.11274106978981</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.16490799239299</v>
+        <v>2.490252987479982</v>
       </c>
       <c r="G6" t="n">
-        <v>2.086948362984063</v>
+        <v>-2.378976133671757</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8113312762755275</v>
+        <v>1.143830610621299</v>
       </c>
       <c r="I6" t="n">
-        <v>1.575440992452404</v>
+        <v>0.6746441761797837</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3823966325474235</v>
+        <v>0.5656932268741558</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>b7pTwPem</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.469386026618</v>
+        <v>1.124365192025146</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2958587209964512</v>
+        <v>1.14956392209407</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.766768434080599</v>
+        <v>0.3112729291249311</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.393995412106591</v>
+        <v>1.887354918272818</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.498704135630914</v>
+        <v>-0.02442319288641064</v>
       </c>
       <c r="G7" t="n">
-        <v>1.524561775521861</v>
+        <v>-0.8574447342015226</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1100674442277952</v>
+        <v>1.619431083690609</v>
       </c>
       <c r="I7" t="n">
-        <v>1.012811808321355</v>
+        <v>-0.2718573635610662</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4854201724151204</v>
+        <v>1.995421413049947</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>CCu9YTJ7</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.051238738816018</v>
+        <v>-0.73530451086739</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.3275576063127965</v>
+        <v>-1.092661139506242</v>
       </c>
       <c r="D8" t="n">
-        <v>3.109398170222253</v>
+        <v>-0.6278728785811271</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8560691284378357</v>
+        <v>-0.6911050681127501</v>
       </c>
       <c r="F8" t="n">
-        <v>1.183525654047102</v>
+        <v>-2.667211965581354</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.130802194212001</v>
+        <v>2.189754523826362</v>
       </c>
       <c r="H8" t="n">
-        <v>1.217645019108739</v>
+        <v>-3.198510626744099</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.139691562540348</v>
+        <v>-0.4571979540494456</v>
       </c>
       <c r="J8" t="n">
-        <v>1.278026187614244</v>
+        <v>-2.484166284947185</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Gpn0zjke</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.737774866954277</v>
+        <v>-0.7570341929208904</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.257387965251052</v>
+        <v>-0.04511781483231576</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4840303641995346</v>
+        <v>-0.8857056460977045</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.049722590558587</v>
+        <v>0.551504647162075</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.098151551592021</v>
+        <v>0.4330362821572416</v>
       </c>
       <c r="G9" t="n">
-        <v>1.476886771521465</v>
+        <v>-0.3804224275621028</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.076828126746147</v>
+        <v>-0.4502213203239559</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3770510054756258</v>
+        <v>-0.1964437846296028</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.96760866294567</v>
+        <v>-0.2869367840015437</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>pOryx3Qa</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.017863788650911</v>
+        <v>0.8017034389776552</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.7951198517947328</v>
+        <v>-1.541463342235382</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9922915211974069</v>
+        <v>1.622637451997469</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.089170518027629</v>
+        <v>0.65012446583468</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.463437563539667</v>
+        <v>0.07778328451121676</v>
       </c>
       <c r="G10" t="n">
-        <v>1.86021507291797</v>
+        <v>0.1761458807027751</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.277522343389953</v>
+        <v>-0.3055481708172888</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2834210021220275</v>
+        <v>-0.9223773008138825</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.384160729327692</v>
+        <v>-0.15604108258636</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rJ8JNC5k</t>
+          <t>bR8Aj2ug</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6411533894810172</v>
+        <v>-1.689504454757488</v>
       </c>
       <c r="C11" t="n">
-        <v>1.751228527355716</v>
+        <v>-0.488429123369962</v>
       </c>
       <c r="D11" t="n">
-        <v>2.395372819954395</v>
+        <v>-1.252138240414731</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9997765502193712</v>
+        <v>-2.319228620016851</v>
       </c>
       <c r="F11" t="n">
-        <v>2.955209640531346</v>
+        <v>-1.457785358983283</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.117620620375417</v>
+        <v>2.558358943687598</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9123329049756677</v>
+        <v>-0.1227694362986405</v>
       </c>
       <c r="I11" t="n">
-        <v>1.346129860590425</v>
+        <v>1.353626096354161</v>
       </c>
       <c r="J11" t="n">
-        <v>1.376378758843332</v>
+        <v>1.387949649576166</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,51 +425,136 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_goal_attempts</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_360_matches_goal_attempts</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_goals</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_360_matches_goals</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_PPS</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_attacks</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_360_matches_dead_balls</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_ball_possession</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_360_matches_ball_possession</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_PPDA</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_defensive_actions</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_PPDA</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_KGP</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_KGP</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_wage_player_start</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_wage_player_miss</t>
         </is>
@@ -478,341 +563,936 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>KtcJltA5</t>
+          <t>z7KrCz8T</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8307191715169997</v>
+        <v>-1.776881095052083</v>
       </c>
       <c r="C2" t="n">
-        <v>0.979275211262692</v>
+        <v>-0.8053694613890752</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06577698292219972</v>
+        <v>-0.2300118779692441</v>
       </c>
       <c r="E2" t="n">
-        <v>1.591495462255002</v>
+        <v>-0.161318409364178</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3197268293132805</v>
+        <v>-0.4424112891749428</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.03061498471867119</v>
+        <v>-0.07741727678444282</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2346742064613014</v>
+        <v>-1.100800096943473</v>
       </c>
       <c r="I2" t="n">
-        <v>1.199367629098181</v>
+        <v>0.1569535857584796</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01390637505213822</v>
+        <v>1.135270100885861</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.452884552239374</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.7460667691633106</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.6999945300040911</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.4557886495881314</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.9028817891172712</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-0.2638482970709466</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.81809894640142</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.4304144417414237</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.7109417918068333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.002245572261617</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.7030980002990518</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-0.200720842362693</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.5243321894043136</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.2169146655857098</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.04158832620130015</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>voUq51fn</t>
+          <t>WENRFI84</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.5716633302002555</v>
+        <v>-1.264595827795513</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.15872711110815</v>
+        <v>-0.3843624887496304</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2545792525958746</v>
+        <v>-0.2300118779692441</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.210557588035329</v>
+        <v>-2.24468669410217</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08729650203921602</v>
+        <v>-0.8888856065361981</v>
       </c>
       <c r="G3" t="n">
-        <v>1.229232208539515</v>
+        <v>-1.718822838952302</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6613869570229295</v>
+        <v>-1.812837089305473</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1984844207807871</v>
+        <v>-2.668382323110348</v>
       </c>
       <c r="J3" t="n">
-        <v>0.09128670682796504</v>
+        <v>2.114875084795983</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1400105899465695</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-1.367857824769063</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-2.18507772377289</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.292852967397463</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.849405728559096</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.475574910662843</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.03815992170841363</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.413473871016158</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-1.191572247871462</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-2.851657276329841</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.4554141546408524</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.7027948575565591</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.505908426043975</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-1.956344331283374</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-0.7422182298521379</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pbap3uPb</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08567003921641408</v>
+        <v>0.1299585108473732</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1114679762993493</v>
+        <v>-1.22637643402852</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6646366228154574</v>
+        <v>-0.2300118779692441</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05840555379904885</v>
+        <v>0.8178569716598204</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6414995495462085</v>
+        <v>1.131410679523483</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7301399139305237</v>
+        <v>0.8118897266575432</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1993553902613317</v>
+        <v>-1.456818593124473</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.227589904804938</v>
+        <v>0.9361438486154314</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4567809301156415</v>
+        <v>-0.8025749135593216</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5286903814148344</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.003968146001830948</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.321788644119548</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.9266373283558803</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.3097498858031976</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.3269147782679621</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-3.165776239544406</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-1.861055871078087</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.5570202611659728</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.224046099602259</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.152591806435771</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.216674788991167</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0.7808706256132558</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.6265570915387236</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0.8232339635299092</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hU52hOAt</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9970503441951012</v>
+        <v>-1.093834072043323</v>
       </c>
       <c r="C5" t="n">
-        <v>1.500910159454589</v>
+        <v>0.3975076032950526</v>
       </c>
       <c r="D5" t="n">
-        <v>3.297689694135134</v>
+        <v>-0.2300118779692441</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2825415053276972</v>
+        <v>-1.241321158659748</v>
       </c>
       <c r="F5" t="n">
-        <v>1.777940191090438</v>
+        <v>-0.9000474644702298</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.313287417013717</v>
+        <v>-0.6019854631465361</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7121616377086308</v>
+        <v>-0.9227908488529724</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3604378416931301</v>
+        <v>-1.184711569755008</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2142274208643254</v>
+        <v>0.6093662735826858</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.3695918033118211</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.2897430186686367</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1008790294312055</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.2988390899988816</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.02071781336141021</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.9310630645125362</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.912387012473338</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.2669053595869906</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.1873879826158935</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.6738975167737536</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-1.07252111897793</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.2059689429579172</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.7208017025693589</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.2440076646864897</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.646622918909656</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tjxpzseC</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.443453159833185</v>
+        <v>-0.04080324490481693</v>
       </c>
       <c r="C6" t="n">
-        <v>2.066196123366097</v>
+        <v>-1.627335455589896</v>
       </c>
       <c r="D6" t="n">
-        <v>2.302339704290836</v>
+        <v>-0.2300118779692441</v>
       </c>
       <c r="E6" t="n">
-        <v>1.11274106978981</v>
+        <v>0.2618340019841816</v>
       </c>
       <c r="F6" t="n">
-        <v>2.490252987479982</v>
+        <v>-0.1745266987581896</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.378976133671757</v>
+        <v>0.06073482986231767</v>
       </c>
       <c r="H6" t="n">
-        <v>1.143830610621299</v>
+        <v>-0.2107538564909714</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6746441761797837</v>
+        <v>0.07529647856573848</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5656932268741558</v>
+        <v>0.3055576045856886</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.1191092710322731</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.553018680394385</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.5917932944875433</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.7696877687666307</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.742267761011462</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.3228178454854256</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.6169030433612407</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.872106994304364</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.6504140215138647</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.2108953101781931</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.4137705818488736</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-2.271061739123587</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-1.841494987871243</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.03334658267274833</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.02465030299187772</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>S60RnKvI</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.124365192025146</v>
+        <v>1.92295694624537</v>
       </c>
       <c r="C7" t="n">
-        <v>1.14956392209407</v>
+        <v>1.7808162276818</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3112729291249311</v>
+        <v>-0.2300118779692441</v>
       </c>
       <c r="E7" t="n">
-        <v>1.887354918272818</v>
+        <v>0.935686312335521</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.02442319288641064</v>
+        <v>0.863526089106729</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8574447342015226</v>
+        <v>0.9795840026860961</v>
       </c>
       <c r="H7" t="n">
-        <v>1.619431083690609</v>
+        <v>2.459384864866533</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2718573635610662</v>
+        <v>1.453595253933538</v>
       </c>
       <c r="J7" t="n">
-        <v>1.995421413049947</v>
+        <v>-0.1226307582722807</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.340599279148542</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.967072157348861</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.707723757069542</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-1.532239105209031</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.8849788230434195</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.7289362379052312</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.014782413174472</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.2917277217087765</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.309425246005917</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.7025366404947445</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-1.277465730529191</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.3707946976925515</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0.6332786395358928</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.05338106510150279</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.1894627074422322</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>E3zhYKPO</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.73530451086739</v>
+        <v>-0.9799929015418625</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.092661139506242</v>
+        <v>1.861008031994075</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6278728785811271</v>
+        <v>-0.2300118779692441</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6911050681127501</v>
+        <v>1.466495901311696</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.667211965581354</v>
+        <v>0.3210597935128038</v>
       </c>
       <c r="G8" t="n">
-        <v>2.189754523826362</v>
+        <v>1.429645141438542</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.198510626744099</v>
+        <v>1.889755270976932</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4571979540494456</v>
+        <v>2.014347591265437</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.484166284947185</v>
+        <v>-0.2198223480186003</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.39191816300388</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.155760444983635</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.054508665962057</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.384729839853422</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.7998078271258657</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-1.561997461091057</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.06595846263656546</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.1488533897303016</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.454598712844526</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.9069199051049119</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.3689647754474505</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.135112467246711</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.4336587022775</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.6826450743545768</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.03910437632873631</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.1882399645103388</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.5424598327525214</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hO2h1JgB</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.7570341929208904</v>
+        <v>1.609893727366354</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.04511781483231576</v>
+        <v>-0.2039309290470113</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8857056460977045</v>
+        <v>-0.2300118779692441</v>
       </c>
       <c r="E9" t="n">
-        <v>0.551504647162075</v>
+        <v>0.8163399079571632</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4330362821572416</v>
+        <v>1.399295269940236</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3804224275621028</v>
+        <v>1.107942210536064</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4502213203239559</v>
+        <v>0.1452646396900291</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1964437846296028</v>
+        <v>1.10506683400001</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2869367840015437</v>
+        <v>-0.3701521608694661</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2177465482402228</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.229045395284886</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.005303132976622693</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.554435566712879</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.7605865190532015</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.5673368937807809</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-2.430249671294382</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-1.035321471098163</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.3141226778071637</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.611712085823433</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.1571465503296423</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.2806431956086616</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.3909400034703291</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0.8156757662530875</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.798203704757977</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OYgzob9U</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8017034389776552</v>
+        <v>-0.6953899752882123</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.541463342235382</v>
+        <v>-1.025896923247832</v>
       </c>
       <c r="D10" t="n">
-        <v>1.622637451997469</v>
+        <v>-0.2300118779692441</v>
       </c>
       <c r="E10" t="n">
-        <v>0.65012446583468</v>
+        <v>-1.236742970867002</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07778328451121676</v>
+        <v>-0.3531164257026921</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1761458807027751</v>
+        <v>-0.7669677023660015</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3055481708172888</v>
+        <v>-1.48055315953654</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9223773008138825</v>
+        <v>-1.119175451119535</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.15604108258636</v>
+        <v>0.5823630346079788</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.03636264555503269</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.6319885987332227</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-2.517098630258368</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.8324675926023305</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.01308943434115489</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.3496809124021291</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.7442955552117209</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-1.212515437755222</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.166124122863723</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-3.21635119741773</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.181869608085955</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.4692709043542795</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0.3933408555179438</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.186097132610912</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-2.54771172324247</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bR8Aj2ug</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1.689504454757488</v>
+        <v>-1.179214949919418</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.488429123369962</v>
+        <v>-1.166232580794313</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.252138240414731</v>
+        <v>-0.2300118779692441</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.319228620016851</v>
+        <v>-0.04868032479684677</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.457785358983283</v>
+        <v>-0.185688556692221</v>
       </c>
       <c r="G11" t="n">
-        <v>2.558358943687598</v>
+        <v>-0.7888754616971068</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1227694362986405</v>
+        <v>-0.1514174404608045</v>
       </c>
       <c r="I11" t="n">
-        <v>1.353626096354161</v>
+        <v>-0.08003348533867445</v>
       </c>
       <c r="J11" t="n">
-        <v>1.387949649576166</v>
+        <v>-0.3446868881286716</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.5114157240162444</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.8683765757458675</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.4294817660192194</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.9789538482189636</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.6477231195788828</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.190033327622873</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.3851045310189663</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-1.028476871888851</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.066927745623604</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.4622882615142978</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.3112982760732408</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.2038921149918085</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.4600860740846163</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.9357873578145635</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.8405944778894316</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>OYgzob9U</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.524512849490259</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-1.647383406667965</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.2300118779692441</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.2484802668397567</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2273001868669403</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7826362068074778</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-1.990846337395974</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-1.564378233864494</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0.3995979319105071</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.413553043349554</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.290705436070967</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.431339462380373</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.09183734694852883</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.9567573867151153</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-1.404548083107204</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.06895135184458659</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.1383797188328188</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.229642238621464</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.643577461096754</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.3231980518992875</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.3173111814281677</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.6459017235038766</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.9427004650605759</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0.6696264673853628</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.3065561286723307</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.25612382778551</v>
       </c>
     </row>
   </sheetData>
